--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -3753,7 +3753,7 @@
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="23"/>
+      <c r="U52" s="6"/>
       <c r="V52" s="6"/>
       <c r="W52" s="14" t="s">
         <v>6</v>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="210">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -429,78 +429,132 @@
     <t xml:space="preserve">Del</t>
   </si>
   <si>
+    <t xml:space="preserve">C+→</t>
+  </si>
+  <si>
     <t xml:space="preserve">PgUp</t>
   </si>
   <si>
+    <t xml:space="preserve">S+F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PgDn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">””←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">()←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[]←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{}←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;&gt;←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space修飾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Space or F13) &amp; 無変換 修飾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+↑</t>
+  </si>
+  <si>
     <t xml:space="preserve">S+→</t>
   </si>
   <si>
-    <t xml:space="preserve">C+a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PgDn</t>
-  </si>
-  <si>
     <t xml:space="preserve">S+Home</t>
   </si>
   <si>
     <t xml:space="preserve">S+←</t>
   </si>
   <si>
-    <t xml:space="preserve">C+z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mouse</t>
+    <t xml:space="preserve">S+↓</t>
   </si>
   <si>
     <t xml:space="preserve">S+End</t>
   </si>
   <si>
-    <t xml:space="preserve">Space修飾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Space or F13) &amp; 無変換 修飾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+↑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+↓</t>
-  </si>
-  <si>
     <t xml:space="preserve">頻度マップ</t>
   </si>
   <si>
@@ -546,12 +600,39 @@
     <t xml:space="preserve">Space &amp; F13 修飾</t>
   </si>
   <si>
+    <t xml:space="preserve">SC+→</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC+←</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (F14 or 変換 or 無変換) 修飾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">＼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shiftt</t>
+  </si>
+  <si>
     <t xml:space="preserve">/ 修飾   C+k,C+{}</t>
   </si>
   <si>
-    <t xml:space="preserve">C+→</t>
-  </si>
-  <si>
     <t xml:space="preserve">C+q</t>
   </si>
   <si>
@@ -564,73 +645,13 @@
     <t xml:space="preserve">C+p</t>
   </si>
   <si>
-    <t xml:space="preserve">C+Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+←</t>
-  </si>
-  <si>
     <t xml:space="preserve">C+k</t>
   </si>
   <si>
-    <t xml:space="preserve">C+End</t>
-  </si>
-  <si>
     <t xml:space="preserve">C+b</t>
   </si>
   <si>
     <t xml:space="preserve">C+n</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (F14 or 変換 or 無変換) 修飾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layer1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">＼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shiftt</t>
   </si>
 </sst>
 </file>
@@ -729,6 +750,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB2B2B2"/>
+        <bgColor rgb="FFCCCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBBE33D"/>
         <bgColor rgb="FF81D41A"/>
       </patternFill>
@@ -737,12 +764,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF729FCF"/>
         <bgColor rgb="FF808080"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2B2B2"/>
-        <bgColor rgb="FFCCCCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -864,7 +885,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -941,7 +962,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -949,19 +978,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2128,18 +2153,42 @@
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
       <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
-      <c r="AB18" s="6"/>
-      <c r="AC18" s="6"/>
+      <c r="R18" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="S18" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="T18" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="V18" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="W18" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="X18" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y18" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z18" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA18" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB18" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC18" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="AD18" s="6"/>
       <c r="AE18" s="6"/>
     </row>
@@ -2174,56 +2223,78 @@
       <c r="J19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>41</v>
+      <c r="K19" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="L19" s="14" t="s">
         <v>21</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA19" s="6"/>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="6"/>
+      <c r="R19" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="T19" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="W19" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="X19" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="Z19" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA19" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB19" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC19" s="19" t="s">
+        <v>147</v>
+      </c>
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>40</v>
@@ -2238,32 +2309,50 @@
         <v>21</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
       <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="9"/>
-      <c r="V20" s="6"/>
+      <c r="R20" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="S20" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="T20" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="U20" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="V20" s="14" t="s">
+        <v>71</v>
+      </c>
       <c r="W20" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="X20" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y20" s="7"/>
+        <v>72</v>
+      </c>
+      <c r="X20" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y20" s="14" t="s">
+        <v>157</v>
+      </c>
       <c r="Z20" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA20" s="6"/>
-      <c r="AB20" s="6"/>
-      <c r="AC20" s="6"/>
+        <v>158</v>
+      </c>
+      <c r="AA20" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC20" s="16" t="s">
+        <v>159</v>
+      </c>
       <c r="AD20" s="6"/>
       <c r="AE20" s="6"/>
     </row>
@@ -2272,31 +2361,31 @@
         <v>43</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>8</v>
+        <v>165</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
@@ -2305,21 +2394,37 @@
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="7"/>
+      <c r="Q21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14" t="s">
+        <v>76</v>
+      </c>
       <c r="W21" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="6"/>
-      <c r="AA21" s="6"/>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="6"/>
+        <v>113</v>
+      </c>
+      <c r="X21" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z21" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA21" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB21" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC21" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="AD21" s="6"/>
       <c r="AE21" s="6"/>
     </row>
@@ -2327,9 +2432,7 @@
       <c r="A22" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="B22" s="7"/>
       <c r="C22" s="7" t="s">
         <v>57</v>
       </c>
@@ -2337,37 +2440,41 @@
         <v>58</v>
       </c>
       <c r="E22" s="7"/>
-      <c r="F22" s="7" t="s">
-        <v>60</v>
-      </c>
+      <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
       <c r="J22" s="11"/>
-      <c r="K22" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="K22" s="6"/>
       <c r="L22" s="11"/>
       <c r="M22" s="6"/>
       <c r="N22" s="11"/>
       <c r="O22" s="11"/>
-      <c r="Q22" s="7"/>
+      <c r="Q22" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="19" t="s">
+      <c r="S22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="T22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U22" s="20" t="s">
         <v>59</v>
       </c>
       <c r="V22" s="7"/>
       <c r="W22" s="7"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="7"/>
+      <c r="X22" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y22" s="21" t="s">
+        <v>114</v>
+      </c>
       <c r="Z22" s="11"/>
-      <c r="AA22" s="6"/>
+      <c r="AA22" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="AB22" s="11"/>
       <c r="AC22" s="6"/>
       <c r="AD22" s="11"/>
@@ -2393,11 +2500,11 @@
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
       <c r="W23" s="7"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="7"/>
+      <c r="X23" s="21"/>
+      <c r="Y23" s="21"/>
       <c r="Z23" s="11"/>
       <c r="AA23" s="6"/>
       <c r="AB23" s="6"/>
@@ -2407,7 +2514,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
-      <c r="B24" s="20"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
@@ -2424,7 +2531,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="4"/>
@@ -2444,7 +2551,7 @@
         <v>7</v>
       </c>
       <c r="Q25" s="18" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="R25" s="18"/>
       <c r="S25" s="4"/>
@@ -2546,14 +2653,14 @@
       <c r="J27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>41</v>
+      <c r="K27" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="L27" s="14" t="s">
         <v>21</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
@@ -2566,10 +2673,10 @@
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
       <c r="Y27" s="14" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="Z27" s="14" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="AA27" s="6"/>
       <c r="AB27" s="6"/>
@@ -2580,22 +2687,22 @@
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="14" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>40</v>
@@ -2610,14 +2717,14 @@
         <v>21</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="M28" s="14" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="Q28" s="19" t="s">
+      <c r="Q28" s="20" t="s">
         <v>90</v>
       </c>
       <c r="R28" s="7"/>
@@ -2626,16 +2733,16 @@
       <c r="U28" s="9"/>
       <c r="V28" s="6"/>
       <c r="W28" s="14" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="X28" s="17" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="Y28" s="14" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="Z28" s="14" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="AA28" s="6"/>
       <c r="AB28" s="6"/>
@@ -2648,31 +2755,31 @@
         <v>43</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>8</v>
+        <v>165</v>
       </c>
       <c r="I29" s="14" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
@@ -2688,7 +2795,7 @@
       <c r="U29" s="6"/>
       <c r="V29" s="7"/>
       <c r="W29" s="14" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="X29" s="6"/>
       <c r="Y29" s="7"/>
@@ -2703,9 +2810,7 @@
       <c r="A30" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="B30" s="7"/>
       <c r="C30" s="7" t="s">
         <v>57</v>
       </c>
@@ -2713,20 +2818,14 @@
         <v>58</v>
       </c>
       <c r="E30" s="7"/>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G30" s="19"/>
-      <c r="H30" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="G30" s="20"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
       <c r="J30" s="11"/>
-      <c r="K30" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="K30" s="6"/>
       <c r="L30" s="11"/>
       <c r="M30" s="6"/>
       <c r="N30" s="11"/>
@@ -2735,13 +2834,13 @@
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
-      <c r="U30" s="19" t="s">
+      <c r="U30" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="V30" s="19" t="s">
+      <c r="V30" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="W30" s="19"/>
+      <c r="W30" s="20"/>
       <c r="X30" s="6"/>
       <c r="Y30" s="7"/>
       <c r="Z30" s="11"/>
@@ -2758,8 +2857,8 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="6"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="11"/>
       <c r="K31" s="6"/>
@@ -2773,7 +2872,7 @@
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
-      <c r="W31" s="19"/>
+      <c r="W31" s="20"/>
       <c r="X31" s="6"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="11"/>
@@ -2785,7 +2884,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
-      <c r="B32" s="20"/>
+      <c r="B32" s="22"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
@@ -2817,7 +2916,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -2836,137 +2935,89 @@
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
-      <c r="B34" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="M34" s="21" t="s">
-        <v>171</v>
-      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
       <c r="Q34" s="6" t="s">
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB34" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC34" s="21" t="s">
-        <v>171</v>
+        <v>187</v>
+      </c>
+      <c r="AB34" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AC34" s="19" t="s">
+        <v>189</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
-      <c r="B35" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>135</v>
-      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="R35" s="22" t="s">
+      <c r="R35" s="23" t="s">
         <v>130</v>
       </c>
       <c r="S35" s="7" t="s">
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>133</v>
@@ -2974,166 +3025,126 @@
       <c r="V35" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="W35" s="22" t="s">
+      <c r="W35" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="X35" s="22" t="s">
+      <c r="X35" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="Y35" s="22" t="s">
+      <c r="Y35" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="Z35" s="22" t="s">
+      <c r="Z35" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="AA35" s="22" t="s">
+      <c r="AA35" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="AB35" s="22" t="s">
+      <c r="AB35" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="AC35" s="22" t="s">
-        <v>135</v>
+      <c r="AC35" s="23" t="s">
+        <v>136</v>
       </c>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
-      <c r="B36" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>144</v>
-      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
       <c r="Q36" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="R36" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="S36" s="22" t="s">
-        <v>138</v>
+      <c r="R36" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="S36" s="23" t="s">
+        <v>149</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="V36" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="W36" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="X36" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="V36" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="W36" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="X36" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="Y36" s="22" t="s">
+      <c r="Y36" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="Z36" s="22" t="s">
+      <c r="Z36" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="AA36" s="22" t="s">
+      <c r="AA36" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="AB36" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC36" s="22" t="s">
-        <v>144</v>
+      <c r="AB36" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="AC36" s="23" t="s">
+        <v>155</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>151</v>
-      </c>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
-      <c r="M37" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="M37" s="6"/>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="Q37" s="7" t="s">
         <v>43</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="S37" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="T37" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="U37" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="V37" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="W37" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="X37" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="S37" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="T37" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="U37" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="V37" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="W37" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="X37" s="23" t="s">
         <v>41</v>
       </c>
       <c r="Y37" s="7"/>
@@ -3147,31 +3158,17 @@
       <c r="AE37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
-      <c r="H38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="I38" s="7" t="s">
-        <v>2</v>
-      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
       <c r="J38" s="11"/>
-      <c r="K38" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="K38" s="6"/>
       <c r="L38" s="11"/>
       <c r="M38" s="6"/>
       <c r="N38" s="11"/>
@@ -3220,7 +3217,7 @@
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
-      <c r="H39" s="6"/>
+      <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="11"/>
       <c r="K39" s="6"/>
@@ -3251,7 +3248,7 @@
       <c r="AE39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="20"/>
+      <c r="B40" s="22"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
       <c r="E40" s="12"/>
@@ -3268,7 +3265,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -3285,7 +3282,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -3319,14 +3316,14 @@
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
       <c r="Q42" s="7"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
       <c r="U42" s="6"/>
       <c r="V42" s="6"/>
       <c r="W42" s="6"/>
       <c r="X42" s="6"/>
-      <c r="Y42" s="6"/>
+      <c r="Y42" s="7"/>
       <c r="Z42" s="6"/>
       <c r="AA42" s="6"/>
       <c r="AB42" s="6"/>
@@ -3341,11 +3338,11 @@
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
       <c r="I43" s="7"/>
-      <c r="J43" s="14" t="s">
-        <v>175</v>
+      <c r="J43" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
@@ -3353,31 +3350,35 @@
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
-      <c r="R43" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y43" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB43" s="6"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="X43" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y43" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z43" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA43" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="AB43" s="14" t="s">
+        <v>21</v>
+      </c>
       <c r="AC43" s="6"/>
       <c r="AD43" s="6"/>
       <c r="AE43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="20" t="s">
         <v>90</v>
       </c>
       <c r="B44" s="7"/>
@@ -3385,15 +3386,15 @@
       <c r="D44" s="7"/>
       <c r="E44" s="9"/>
       <c r="F44" s="6"/>
-      <c r="G44" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="H44" s="17" t="s">
-        <v>181</v>
+      <c r="G44" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="I44" s="7"/>
-      <c r="J44" s="14" t="s">
-        <v>175</v>
+      <c r="J44" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
@@ -3401,22 +3402,30 @@
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
       <c r="Q44" s="7"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="T44" s="6"/>
-      <c r="U44" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="V44" s="6"/>
-      <c r="W44" s="6"/>
-      <c r="X44" s="23"/>
-      <c r="Y44" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z44" s="6"/>
-      <c r="AA44" s="6"/>
+      <c r="R44" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
+      <c r="U44" s="9"/>
+      <c r="V44" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="W44" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X44" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y44" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z44" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA44" s="14" t="s">
+        <v>21</v>
+      </c>
       <c r="AB44" s="6"/>
       <c r="AC44" s="6"/>
       <c r="AD44" s="6"/>
@@ -3429,38 +3438,42 @@
       <c r="D45" s="7"/>
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
-      <c r="G45" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="H45" s="6"/>
+      <c r="G45" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="H45" s="7"/>
       <c r="I45" s="7"/>
-      <c r="J45" s="6"/>
+      <c r="J45" s="7"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
       <c r="O45" s="6"/>
       <c r="Q45" s="7"/>
-      <c r="R45" s="7"/>
-      <c r="S45" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="T45" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="U45" s="7"/>
-      <c r="V45" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="W45" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="X45" s="7"/>
-      <c r="Y45" s="7"/>
+      <c r="R45" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="S45" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="T45" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="U45" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="V45" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="W45" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="X45" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y45" s="6"/>
       <c r="Z45" s="6"/>
-      <c r="AA45" s="24" t="s">
-        <v>52</v>
-      </c>
+      <c r="AA45" s="6"/>
       <c r="AB45" s="6"/>
       <c r="AC45" s="6"/>
       <c r="AD45" s="6"/>
@@ -3472,10 +3485,10 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="19" t="s">
+      <c r="F46" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G46" s="19"/>
+      <c r="G46" s="20"/>
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
       <c r="J46" s="11"/>
@@ -3488,13 +3501,21 @@
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
-      <c r="U46" s="7"/>
+      <c r="U46" s="20" t="s">
+        <v>59</v>
+      </c>
       <c r="V46" s="7"/>
       <c r="W46" s="7"/>
-      <c r="X46" s="6"/>
-      <c r="Y46" s="7"/>
+      <c r="X46" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y46" s="20" t="s">
+        <v>114</v>
+      </c>
       <c r="Z46" s="11"/>
-      <c r="AA46" s="6"/>
+      <c r="AA46" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="AB46" s="11"/>
       <c r="AC46" s="6"/>
       <c r="AD46" s="11"/>
@@ -3507,7 +3528,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="19"/>
+      <c r="G47" s="20"/>
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
       <c r="J47" s="11"/>
@@ -3523,8 +3544,8 @@
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
-      <c r="X47" s="6"/>
-      <c r="Y47" s="7"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
       <c r="Z47" s="11"/>
       <c r="AA47" s="6"/>
       <c r="AB47" s="6"/>
@@ -3533,8 +3554,8 @@
       <c r="AE47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -3551,7 +3572,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="4"/>
@@ -3568,7 +3589,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3617,7 +3638,9 @@
       <c r="T50" s="7"/>
       <c r="U50" s="6"/>
       <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
+      <c r="W50" s="14" t="s">
+        <v>130</v>
+      </c>
       <c r="X50" s="14" t="n">
         <v>7</v>
       </c>
@@ -3633,47 +3656,47 @@
       <c r="AB50" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="AC50" s="6"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
+      <c r="AC50" s="7"/>
+      <c r="AD50" s="7"/>
+      <c r="AE50" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="7" t="s">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>132</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="L51" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="M51" s="21" t="s">
-        <v>198</v>
+        <v>145</v>
+      </c>
+      <c r="L51" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="M51" s="19" t="s">
+        <v>147</v>
       </c>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
@@ -3704,8 +3727,8 @@
       <c r="AC51" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="7"/>
+      <c r="AE51" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
@@ -3753,12 +3776,12 @@
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="6"/>
+      <c r="U52" s="25"/>
       <c r="V52" s="6"/>
       <c r="W52" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="X52" s="14" t="n">
+      <c r="X52" s="17" t="n">
         <v>1</v>
       </c>
       <c r="Y52" s="14" t="n">
@@ -3776,8 +3799,8 @@
       <c r="AC52" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AD52" s="6"/>
-      <c r="AE52" s="6"/>
+      <c r="AD52" s="7"/>
+      <c r="AE52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
@@ -3841,9 +3864,9 @@
         <v>52</v>
       </c>
       <c r="AB53" s="7"/>
-      <c r="AC53" s="6"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
+      <c r="AC53" s="7"/>
+      <c r="AD53" s="7"/>
+      <c r="AE53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
@@ -3856,15 +3879,15 @@
       <c r="D54" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="20" t="s">
         <v>59</v>
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="24" t="s">
+      <c r="H54" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I54" s="24" t="s">
+      <c r="I54" s="21" t="s">
         <v>114</v>
       </c>
       <c r="J54" s="11"/>
@@ -3898,11 +3921,11 @@
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
       <c r="J55" s="11"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
@@ -4264,7 +4287,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4281,7 +4304,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="5"/>
       <c r="Q1" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
@@ -4431,7 +4454,7 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O3" s="6"/>
       <c r="Q3" s="6" t="s">
@@ -4491,7 +4514,7 @@
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="24" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -4500,7 +4523,7 @@
       <c r="G4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="24" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -4534,7 +4557,7 @@
       <c r="T4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="U4" s="23" t="s">
+      <c r="U4" s="24" t="s">
         <v>29</v>
       </c>
       <c r="V4" s="6" t="s">
@@ -4543,7 +4566,7 @@
       <c r="W4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="X4" s="23" t="s">
+      <c r="X4" s="24" t="s">
         <v>32</v>
       </c>
       <c r="Y4" s="6" t="s">
@@ -4599,7 +4622,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -4948,7 +4971,7 @@
         <v>37</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O11" s="6"/>
       <c r="Q11" s="7"/>
@@ -5006,7 +5029,7 @@
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="24" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="6" t="s">
@@ -5015,7 +5038,7 @@
       <c r="G12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="24" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="6" t="s">
@@ -5047,7 +5070,7 @@
       <c r="T12" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U12" s="23" t="s">
+      <c r="U12" s="24" t="s">
         <v>94</v>
       </c>
       <c r="V12" s="6" t="s">
@@ -5056,7 +5079,7 @@
       <c r="W12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X12" s="23" t="s">
+      <c r="X12" s="24" t="s">
         <v>97</v>
       </c>
       <c r="Y12" s="7" t="s">
@@ -5112,7 +5135,7 @@
         <v>52</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>43</v>
@@ -5305,40 +5328,40 @@
         <v>116</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="L18" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="M18" s="21" t="s">
-        <v>171</v>
+        <v>187</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>189</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>6</v>
@@ -5373,7 +5396,7 @@
         <v>131</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>133</v>
@@ -5397,7 +5420,7 @@
         <v>41</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
@@ -5413,7 +5436,7 @@
       <c r="X19" s="6"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="6" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
@@ -5422,28 +5445,28 @@
       <c r="AE19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>140</v>
+        <v>150</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="H20" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="H20" s="24" t="s">
         <v>40</v>
       </c>
       <c r="I20" s="7" t="s">
@@ -5456,7 +5479,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>21</v>
@@ -5470,17 +5493,17 @@
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
-      <c r="U20" s="23"/>
+      <c r="U20" s="24"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="X20" s="23" t="s">
-        <v>146</v>
+        <v>173</v>
+      </c>
+      <c r="X20" s="24" t="s">
+        <v>174</v>
       </c>
       <c r="Y20" s="7"/>
       <c r="Z20" s="6" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
@@ -5493,35 +5516,35 @@
         <v>43</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>41</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>43</v>
@@ -5535,7 +5558,7 @@
       <c r="U21" s="6"/>
       <c r="V21" s="7"/>
       <c r="W21" s="6" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="7"/>
@@ -5640,7 +5663,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
-      <c r="B24" s="20"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
@@ -5657,7 +5680,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="4"/>
@@ -5695,40 +5718,40 @@
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="L26" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="M26" s="21" t="s">
-        <v>171</v>
+        <v>187</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>189</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>6</v>
@@ -5761,7 +5784,7 @@
         <v>131</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>133</v>
@@ -5785,11 +5808,11 @@
         <v>41</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O27" s="6"/>
       <c r="Q27" s="7"/>
@@ -5811,24 +5834,24 @@
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>140</v>
+        <v>150</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="H28" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="H28" s="24" t="s">
         <v>40</v>
       </c>
       <c r="I28" s="7" t="s">
@@ -5841,7 +5864,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>21</v>
@@ -5850,14 +5873,14 @@
         <v>37</v>
       </c>
       <c r="O28" s="6"/>
-      <c r="Q28" s="19"/>
+      <c r="Q28" s="20"/>
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
-      <c r="U28" s="23"/>
+      <c r="U28" s="24"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
-      <c r="X28" s="23"/>
+      <c r="X28" s="24"/>
       <c r="Y28" s="7"/>
       <c r="Z28" s="6"/>
       <c r="AA28" s="6"/>
@@ -5871,35 +5894,35 @@
         <v>43</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>41</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>43</v>
@@ -6016,7 +6039,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
-      <c r="B32" s="20"/>
+      <c r="B32" s="22"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
@@ -6048,7 +6071,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -6068,40 +6091,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="M34" s="21" t="s">
-        <v>171</v>
+        <v>187</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>189</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -6113,40 +6136,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB34" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC34" s="21" t="s">
-        <v>171</v>
+        <v>187</v>
+      </c>
+      <c r="AB34" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AC34" s="19" t="s">
+        <v>189</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -6160,7 +6183,7 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>133</v>
@@ -6184,24 +6207,24 @@
         <v>41</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="R35" s="22" t="s">
+      <c r="R35" s="23" t="s">
         <v>130</v>
       </c>
       <c r="S35" s="7" t="s">
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>133</v>
@@ -6209,26 +6232,26 @@
       <c r="V35" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="W35" s="22" t="s">
+      <c r="W35" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="X35" s="22" t="s">
+      <c r="X35" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="Y35" s="22" t="s">
+      <c r="Y35" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="Z35" s="22" t="s">
+      <c r="Z35" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="AA35" s="22" t="s">
+      <c r="AA35" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="AB35" s="22" t="s">
+      <c r="AB35" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="AC35" s="22" t="s">
-        <v>135</v>
+      <c r="AC35" s="23" t="s">
+        <v>136</v>
       </c>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
@@ -6236,24 +6259,24 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>140</v>
+        <v>150</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="H36" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" s="24" t="s">
         <v>40</v>
       </c>
       <c r="I36" s="7" t="s">
@@ -6266,7 +6289,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>21</v>
@@ -6278,41 +6301,41 @@
       <c r="Q36" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="R36" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="S36" s="22" t="s">
-        <v>138</v>
+      <c r="R36" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="S36" s="23" t="s">
+        <v>149</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="V36" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="W36" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="X36" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="V36" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="W36" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="X36" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="Y36" s="22" t="s">
+      <c r="Y36" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="Z36" s="22" t="s">
+      <c r="Z36" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="AA36" s="22" t="s">
+      <c r="AA36" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="AB36" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC36" s="22" t="s">
-        <v>144</v>
+      <c r="AB36" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="AC36" s="23" t="s">
+        <v>155</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
@@ -6322,22 +6345,22 @@
         <v>43</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>41</v>
@@ -6346,7 +6369,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -6357,24 +6380,24 @@
         <v>43</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="S37" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="T37" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="U37" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="V37" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="W37" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="X37" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="S37" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="T37" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="U37" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="V37" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="W37" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="X37" s="23" t="s">
         <v>41</v>
       </c>
       <c r="Y37" s="7"/>
@@ -6508,7 +6531,7 @@
       <c r="AE39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="20"/>
+      <c r="B40" s="22"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
       <c r="E40" s="12"/>
@@ -6525,7 +6548,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -6542,7 +6565,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -6606,22 +6629,22 @@
       <c r="H43" s="6"/>
       <c r="I43" s="7"/>
       <c r="J43" s="6" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -6629,14 +6652,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -6644,27 +6667,27 @@
       <c r="AE43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="20" t="s">
         <v>90</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="23"/>
+      <c r="E44" s="24"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H44" s="23" t="s">
-        <v>181</v>
+        <v>193</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>165</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>21</v>
@@ -6676,17 +6699,17 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="T44" s="6"/>
-      <c r="U44" s="23" t="s">
-        <v>140</v>
+      <c r="U44" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
-      <c r="X44" s="23"/>
+      <c r="X44" s="24"/>
       <c r="Y44" s="6" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -6703,14 +6726,14 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -6720,22 +6743,22 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="6"/>
-      <c r="AA45" s="24" t="s">
+      <c r="AA45" s="21" t="s">
         <v>52</v>
       </c>
       <c r="AB45" s="6"/>
@@ -6836,8 +6859,8 @@
       <c r="AE47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -6869,7 +6892,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6924,8 +6947,8 @@
       <c r="I51" s="7"/>
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
       <c r="Q51" s="7"/>
@@ -6959,27 +6982,27 @@
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="23"/>
+      <c r="E52" s="24"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="23"/>
+      <c r="H52" s="24"/>
       <c r="I52" s="7"/>
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="23"/>
+      <c r="U52" s="24"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="X52" s="23" t="n">
+      <c r="X52" s="24" t="n">
         <v>1</v>
       </c>
       <c r="Y52" s="7" t="n">
@@ -7437,7 +7460,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7600,7 +7623,7 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O3" s="6"/>
       <c r="Q3" s="7"/>
@@ -7658,7 +7681,7 @@
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="24" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -7667,7 +7690,7 @@
       <c r="G4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="24" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -7699,7 +7722,7 @@
       <c r="T4" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U4" s="23" t="s">
+      <c r="U4" s="24" t="s">
         <v>94</v>
       </c>
       <c r="V4" s="6" t="s">
@@ -7708,7 +7731,7 @@
       <c r="W4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X4" s="23" t="s">
+      <c r="X4" s="24" t="s">
         <v>97</v>
       </c>
       <c r="Y4" s="7" t="s">
@@ -7764,7 +7787,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -7920,7 +7943,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -8141,7 +8164,7 @@
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="24" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="6" t="s">
@@ -8150,7 +8173,7 @@
       <c r="G12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="23" t="s">
+      <c r="H12" s="24" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="6" t="s">
@@ -8180,7 +8203,7 @@
       <c r="T12" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U12" s="23" t="s">
+      <c r="U12" s="24" t="s">
         <v>94</v>
       </c>
       <c r="V12" s="6" t="s">
@@ -8189,7 +8212,7 @@
       <c r="W12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X12" s="23" t="s">
+      <c r="X12" s="24" t="s">
         <v>97</v>
       </c>
       <c r="Y12" s="7" t="s">
@@ -8469,7 +8492,7 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>6</v>
@@ -8514,7 +8537,7 @@
         <v>4</v>
       </c>
       <c r="AD18" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AE18" s="6" t="s">
         <v>6</v>
@@ -8620,7 +8643,7 @@
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="24" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="6" t="s">
@@ -8629,7 +8652,7 @@
       <c r="G20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="23" t="s">
+      <c r="H20" s="24" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="6" t="s">
@@ -8660,7 +8683,7 @@
       <c r="T20" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U20" s="23" t="s">
+      <c r="U20" s="24" t="s">
         <v>94</v>
       </c>
       <c r="V20" s="6" t="s">
@@ -8669,7 +8692,7 @@
       <c r="W20" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X20" s="23" t="s">
+      <c r="X20" s="24" t="s">
         <v>97</v>
       </c>
       <c r="Y20" s="7" t="s">
@@ -8860,7 +8883,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
-      <c r="B24" s="20"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
@@ -9067,10 +9090,10 @@
       <c r="AA27" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AB27" s="25" t="s">
+      <c r="AB27" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="AC27" s="21" t="s">
+      <c r="AC27" s="19" t="s">
         <v>89</v>
       </c>
       <c r="AD27" s="6"/>
@@ -9089,7 +9112,7 @@
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="24" t="s">
         <v>29</v>
       </c>
       <c r="F28" s="6" t="s">
@@ -9098,7 +9121,7 @@
       <c r="G28" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="H28" s="24" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="6" t="s">
@@ -9128,7 +9151,7 @@
       <c r="T28" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U28" s="23" t="s">
+      <c r="U28" s="24" t="s">
         <v>94</v>
       </c>
       <c r="V28" s="6" t="s">
@@ -9137,7 +9160,7 @@
       <c r="W28" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X28" s="23" t="s">
+      <c r="X28" s="24" t="s">
         <v>97</v>
       </c>
       <c r="Y28" s="7" t="s">
@@ -9149,10 +9172,10 @@
       <c r="AA28" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="AB28" s="21" t="s">
+      <c r="AB28" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="AC28" s="21" t="s">
+      <c r="AC28" s="19" t="s">
         <v>102</v>
       </c>
       <c r="AD28" s="6"/>
@@ -9330,7 +9353,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
-      <c r="B32" s="20"/>
+      <c r="B32" s="22"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
@@ -9362,7 +9385,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -9382,40 +9405,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="M34" s="21" t="s">
-        <v>171</v>
+        <v>187</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>189</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -9427,40 +9450,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB34" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="AC34" s="21" t="s">
-        <v>171</v>
+        <v>187</v>
+      </c>
+      <c r="AB34" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AC34" s="19" t="s">
+        <v>189</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -9474,7 +9497,7 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>133</v>
@@ -9498,24 +9521,24 @@
         <v>41</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="R35" s="22" t="s">
+      <c r="R35" s="23" t="s">
         <v>130</v>
       </c>
       <c r="S35" s="7" t="s">
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>133</v>
@@ -9523,26 +9546,26 @@
       <c r="V35" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="W35" s="22" t="s">
+      <c r="W35" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="X35" s="22" t="s">
+      <c r="X35" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="Y35" s="22" t="s">
+      <c r="Y35" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="Z35" s="22" t="s">
+      <c r="Z35" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="AA35" s="22" t="s">
+      <c r="AA35" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="AB35" s="22" t="s">
+      <c r="AB35" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="AC35" s="22" t="s">
-        <v>135</v>
+      <c r="AC35" s="23" t="s">
+        <v>136</v>
       </c>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
@@ -9550,24 +9573,24 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>140</v>
+        <v>150</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="H36" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" s="24" t="s">
         <v>40</v>
       </c>
       <c r="I36" s="7" t="s">
@@ -9580,7 +9603,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>21</v>
@@ -9592,41 +9615,41 @@
       <c r="Q36" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="R36" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="S36" s="22" t="s">
-        <v>138</v>
+      <c r="R36" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="S36" s="23" t="s">
+        <v>149</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="V36" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="W36" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="X36" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="V36" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="W36" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="X36" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="Y36" s="22" t="s">
+      <c r="Y36" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="Z36" s="22" t="s">
+      <c r="Z36" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="AA36" s="22" t="s">
+      <c r="AA36" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="AB36" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="AC36" s="22" t="s">
-        <v>144</v>
+      <c r="AB36" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="AC36" s="23" t="s">
+        <v>155</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
@@ -9636,22 +9659,22 @@
         <v>43</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>41</v>
@@ -9660,7 +9683,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -9671,24 +9694,24 @@
         <v>43</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="S37" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="T37" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="U37" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="V37" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="W37" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="X37" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="S37" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="T37" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="U37" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="V37" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="W37" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="X37" s="23" t="s">
         <v>41</v>
       </c>
       <c r="Y37" s="7"/>
@@ -9822,7 +9845,7 @@
       <c r="AE39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="20"/>
+      <c r="B40" s="22"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
       <c r="E40" s="12"/>
@@ -9839,7 +9862,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -9856,7 +9879,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -9920,22 +9943,22 @@
       <c r="H43" s="6"/>
       <c r="I43" s="7"/>
       <c r="J43" s="6" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -9943,14 +9966,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -9958,27 +9981,27 @@
       <c r="AE43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="20" t="s">
         <v>90</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="23"/>
+      <c r="E44" s="24"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H44" s="23" t="s">
-        <v>181</v>
+        <v>193</v>
+      </c>
+      <c r="H44" s="24" t="s">
+        <v>165</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>21</v>
@@ -9990,17 +10013,17 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="T44" s="6"/>
-      <c r="U44" s="23" t="s">
-        <v>140</v>
+      <c r="U44" s="24" t="s">
+        <v>151</v>
       </c>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
-      <c r="X44" s="23"/>
+      <c r="X44" s="24"/>
       <c r="Y44" s="6" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -10017,14 +10040,14 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -10034,22 +10057,22 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="6"/>
-      <c r="AA45" s="24" t="s">
+      <c r="AA45" s="21" t="s">
         <v>52</v>
       </c>
       <c r="AB45" s="6"/>
@@ -10150,8 +10173,8 @@
       <c r="AE47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
       <c r="C48" s="12"/>
       <c r="D48" s="12"/>
       <c r="E48" s="12"/>
@@ -10183,7 +10206,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10238,8 +10261,8 @@
       <c r="I51" s="7"/>
       <c r="J51" s="6"/>
       <c r="K51" s="6"/>
-      <c r="L51" s="21"/>
-      <c r="M51" s="21"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
       <c r="Q51" s="7"/>
@@ -10273,27 +10296,27 @@
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="23"/>
+      <c r="E52" s="24"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="23"/>
+      <c r="H52" s="24"/>
       <c r="I52" s="7"/>
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
-      <c r="L52" s="21"/>
-      <c r="M52" s="21"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="Q52" s="7"/>
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="23"/>
+      <c r="U52" s="24"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="X52" s="23" t="n">
+      <c r="X52" s="24" t="n">
         <v>1</v>
       </c>
       <c r="Y52" s="7" t="n">

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="211">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -435,6 +435,9 @@
     <t xml:space="preserve">PgUp</t>
   </si>
   <si>
+    <t xml:space="preserve">PgDn</t>
+  </si>
+  <si>
     <t xml:space="preserve">S+F1</t>
   </si>
   <si>
@@ -489,7 +492,7 @@
     <t xml:space="preserve">C+g</t>
   </si>
   <si>
-    <t xml:space="preserve">PgDn</t>
+    <t xml:space="preserve">C+]</t>
   </si>
   <si>
     <t xml:space="preserve">””←</t>
@@ -2223,53 +2226,53 @@
       <c r="J19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="14" t="s">
         <v>135</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>132</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="X19" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Y19" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Z19" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AA19" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AB19" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AC19" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
@@ -2279,22 +2282,22 @@
         <v>90</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>40</v>
@@ -2309,10 +2312,10 @@
         <v>21</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
@@ -2321,7 +2324,7 @@
         <v>67</v>
       </c>
       <c r="S20" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T20" s="14" t="s">
         <v>69</v>
@@ -2339,10 +2342,10 @@
         <v>73</v>
       </c>
       <c r="Y20" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z20" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA20" s="14" t="s">
         <v>100</v>
@@ -2351,7 +2354,7 @@
         <v>101</v>
       </c>
       <c r="AC20" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD20" s="6"/>
       <c r="AE20" s="6"/>
@@ -2361,31 +2364,31 @@
         <v>43</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C21" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>160</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H21" s="7" t="s">
         <v>165</v>
       </c>
+      <c r="H21" s="14" t="s">
+        <v>166</v>
+      </c>
       <c r="I21" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
@@ -2411,10 +2414,10 @@
         <v>3</v>
       </c>
       <c r="Y21" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Z21" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA21" s="14" t="s">
         <v>112</v>
@@ -2531,7 +2534,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="4"/>
@@ -2551,7 +2554,7 @@
         <v>7</v>
       </c>
       <c r="Q25" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R25" s="18"/>
       <c r="S25" s="4"/>
@@ -2653,14 +2656,14 @@
       <c r="J27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="14" t="s">
         <v>135</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
@@ -2673,10 +2676,10 @@
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
       <c r="Y27" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z27" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA27" s="6"/>
       <c r="AB27" s="6"/>
@@ -2687,22 +2690,22 @@
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>40</v>
@@ -2717,10 +2720,10 @@
         <v>21</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M28" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
@@ -2733,16 +2736,16 @@
       <c r="U28" s="9"/>
       <c r="V28" s="6"/>
       <c r="W28" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="X28" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y28" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z28" s="14" t="s">
         <v>173</v>
-      </c>
-      <c r="X28" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y28" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z28" s="14" t="s">
-        <v>172</v>
       </c>
       <c r="AA28" s="6"/>
       <c r="AB28" s="6"/>
@@ -2755,31 +2758,31 @@
         <v>43</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C29" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D29" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="F29" s="14" t="s">
-        <v>160</v>
-      </c>
       <c r="G29" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H29" s="7" t="s">
         <v>165</v>
       </c>
+      <c r="H29" s="14" t="s">
+        <v>166</v>
+      </c>
       <c r="I29" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
@@ -2795,7 +2798,7 @@
       <c r="U29" s="6"/>
       <c r="V29" s="7"/>
       <c r="W29" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X29" s="6"/>
       <c r="Y29" s="7"/>
@@ -2916,7 +2919,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -2953,40 +2956,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -3017,7 +3020,7 @@
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>133</v>
@@ -3069,22 +3072,22 @@
         <v>90</v>
       </c>
       <c r="R36" s="23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S36" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V36" s="23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="W36" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="X36" s="23" t="s">
         <v>40</v>
@@ -3099,10 +3102,10 @@
         <v>21</v>
       </c>
       <c r="AB36" s="23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AC36" s="23" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
@@ -3127,22 +3130,22 @@
         <v>43</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="S37" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="T37" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="U37" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="V37" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="T37" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="U37" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="V37" s="23" t="s">
-        <v>160</v>
-      </c>
       <c r="W37" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="X37" s="23" t="s">
         <v>41</v>
@@ -3265,7 +3268,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -3362,17 +3365,15 @@
         <v>6</v>
       </c>
       <c r="Y43" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z43" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA43" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB43" s="14" t="s">
-        <v>21</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
       <c r="AD43" s="6"/>
       <c r="AE43" s="6"/>
@@ -3387,10 +3388,10 @@
       <c r="E44" s="9"/>
       <c r="F44" s="6"/>
       <c r="G44" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7" t="s">
@@ -3403,25 +3404,25 @@
       <c r="O44" s="6"/>
       <c r="Q44" s="7"/>
       <c r="R44" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="S44" s="7"/>
       <c r="T44" s="7"/>
       <c r="U44" s="9"/>
       <c r="V44" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="W44" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="X44" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y44" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z44" s="14" t="s">
         <v>173</v>
-      </c>
-      <c r="X44" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y44" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z44" s="14" t="s">
-        <v>172</v>
       </c>
       <c r="AA44" s="14" t="s">
         <v>21</v>
@@ -3439,7 +3440,7 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
@@ -3451,25 +3452,25 @@
       <c r="O45" s="6"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="S45" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="T45" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="U45" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="V45" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="T45" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="U45" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="V45" s="14" t="s">
-        <v>160</v>
-      </c>
       <c r="W45" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X45" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Y45" s="6"/>
       <c r="Z45" s="6"/>
@@ -3572,7 +3573,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="4"/>
@@ -3589,7 +3590,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3663,40 +3664,40 @@
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>132</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M51" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
@@ -4287,7 +4288,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4304,7 +4305,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="5"/>
       <c r="Q1" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
@@ -4454,7 +4455,7 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O3" s="6"/>
       <c r="Q3" s="6" t="s">
@@ -4622,7 +4623,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -4971,7 +4972,7 @@
         <v>37</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O11" s="6"/>
       <c r="Q11" s="7"/>
@@ -5135,7 +5136,7 @@
         <v>52</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>43</v>
@@ -5328,40 +5329,40 @@
         <v>116</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M18" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>6</v>
@@ -5396,7 +5397,7 @@
         <v>131</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>133</v>
@@ -5436,7 +5437,7 @@
       <c r="X19" s="6"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
@@ -5449,22 +5450,22 @@
         <v>90</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H20" s="24" t="s">
         <v>40</v>
@@ -5479,7 +5480,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>21</v>
@@ -5496,14 +5497,14 @@
       <c r="U20" s="24"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="X20" s="24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y20" s="7"/>
       <c r="Z20" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
@@ -5516,35 +5517,35 @@
         <v>43</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="G21" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>41</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>43</v>
@@ -5558,7 +5559,7 @@
       <c r="U21" s="6"/>
       <c r="V21" s="7"/>
       <c r="W21" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="7"/>
@@ -5680,7 +5681,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="4"/>
@@ -5718,40 +5719,40 @@
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M26" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>6</v>
@@ -5784,7 +5785,7 @@
         <v>131</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>133</v>
@@ -5812,7 +5813,7 @@
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O27" s="6"/>
       <c r="Q27" s="7"/>
@@ -5834,22 +5835,22 @@
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H28" s="24" t="s">
         <v>40</v>
@@ -5864,7 +5865,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>21</v>
@@ -5894,35 +5895,35 @@
         <v>43</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="G29" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>41</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>43</v>
@@ -6071,7 +6072,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -6091,40 +6092,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -6136,40 +6137,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -6183,7 +6184,7 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>133</v>
@@ -6211,7 +6212,7 @@
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
@@ -6224,7 +6225,7 @@
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>133</v>
@@ -6259,22 +6260,22 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H36" s="24" t="s">
         <v>40</v>
@@ -6289,7 +6290,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>21</v>
@@ -6302,22 +6303,22 @@
         <v>90</v>
       </c>
       <c r="R36" s="23" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="S36" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V36" s="23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="W36" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="X36" s="23" t="s">
         <v>40</v>
@@ -6332,10 +6333,10 @@
         <v>21</v>
       </c>
       <c r="AB36" s="23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AC36" s="23" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
@@ -6345,22 +6346,22 @@
         <v>43</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="G37" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>41</v>
@@ -6369,7 +6370,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -6380,22 +6381,22 @@
         <v>43</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="S37" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="T37" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="U37" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="V37" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="T37" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="U37" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="V37" s="23" t="s">
-        <v>160</v>
-      </c>
       <c r="W37" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="X37" s="23" t="s">
         <v>41</v>
@@ -6548,7 +6549,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -6565,7 +6566,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -6636,15 +6637,15 @@
         <v>136</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -6652,14 +6653,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -6676,10 +6677,10 @@
       <c r="E44" s="24"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6" t="s">
@@ -6687,7 +6688,7 @@
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>21</v>
@@ -6699,17 +6700,17 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
       <c r="X44" s="24"/>
       <c r="Y44" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -6726,14 +6727,14 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -6743,17 +6744,17 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -6892,7 +6893,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7460,7 +7461,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7623,7 +7624,7 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O3" s="6"/>
       <c r="Q3" s="7"/>
@@ -7787,7 +7788,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -7943,7 +7944,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -8492,7 +8493,7 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>6</v>
@@ -8537,7 +8538,7 @@
         <v>4</v>
       </c>
       <c r="AD18" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AE18" s="6" t="s">
         <v>6</v>
@@ -9385,7 +9386,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -9405,40 +9406,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -9450,40 +9451,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -9497,7 +9498,7 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>133</v>
@@ -9525,7 +9526,7 @@
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
@@ -9538,7 +9539,7 @@
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>133</v>
@@ -9573,22 +9574,22 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H36" s="24" t="s">
         <v>40</v>
@@ -9603,7 +9604,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>21</v>
@@ -9616,22 +9617,22 @@
         <v>90</v>
       </c>
       <c r="R36" s="23" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="S36" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V36" s="23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="W36" s="23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="X36" s="23" t="s">
         <v>40</v>
@@ -9646,10 +9647,10 @@
         <v>21</v>
       </c>
       <c r="AB36" s="23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AC36" s="23" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
@@ -9659,22 +9660,22 @@
         <v>43</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="G37" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>41</v>
@@ -9683,7 +9684,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -9694,22 +9695,22 @@
         <v>43</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="S37" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="T37" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="U37" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="V37" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="T37" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="U37" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="V37" s="23" t="s">
-        <v>160</v>
-      </c>
       <c r="W37" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="X37" s="23" t="s">
         <v>41</v>
@@ -9862,7 +9863,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -9879,7 +9880,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -9950,15 +9951,15 @@
         <v>136</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -9966,14 +9967,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -9990,10 +9991,10 @@
       <c r="E44" s="24"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6" t="s">
@@ -10001,7 +10002,7 @@
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>21</v>
@@ -10013,17 +10014,17 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
       <c r="X44" s="24"/>
       <c r="Y44" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -10040,14 +10041,14 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -10057,17 +10058,17 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -10206,7 +10207,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="212">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -553,6 +553,9 @@
   </si>
   <si>
     <t xml:space="preserve">S+↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+”-”</t>
   </si>
   <si>
     <t xml:space="preserve">S+End</t>
@@ -888,7 +891,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -987,6 +990,14 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2226,7 +2237,7 @@
       <c r="J19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K19" s="14" t="s">
+      <c r="K19" s="7" t="s">
         <v>135</v>
       </c>
       <c r="L19" s="14" t="s">
@@ -2381,7 +2392,7 @@
       <c r="G21" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="7" t="s">
         <v>166</v>
       </c>
       <c r="I21" s="14" t="s">
@@ -2656,7 +2667,7 @@
       <c r="J27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K27" s="14" t="s">
+      <c r="K27" s="7" t="s">
         <v>135</v>
       </c>
       <c r="L27" s="14" t="s">
@@ -2735,7 +2746,7 @@
       <c r="T28" s="7"/>
       <c r="U28" s="9"/>
       <c r="V28" s="6"/>
-      <c r="W28" s="14" t="s">
+      <c r="W28" s="16" t="s">
         <v>174</v>
       </c>
       <c r="X28" s="17" t="s">
@@ -2775,7 +2786,7 @@
       <c r="G29" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="H29" s="7" t="s">
         <v>166</v>
       </c>
       <c r="I29" s="14" t="s">
@@ -2785,7 +2796,9 @@
         <v>168</v>
       </c>
       <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
+      <c r="L29" s="14" t="s">
+        <v>177</v>
+      </c>
       <c r="M29" s="6" t="s">
         <v>43</v>
       </c>
@@ -2797,8 +2810,8 @@
       <c r="T29" s="7"/>
       <c r="U29" s="6"/>
       <c r="V29" s="7"/>
-      <c r="W29" s="14" t="s">
-        <v>177</v>
+      <c r="W29" s="16" t="s">
+        <v>178</v>
       </c>
       <c r="X29" s="6"/>
       <c r="Y29" s="7"/>
@@ -2919,7 +2932,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -2956,40 +2969,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -3020,7 +3033,7 @@
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>133</v>
@@ -3268,7 +3281,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -3364,14 +3377,14 @@
       <c r="X43" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Y43" s="14" t="s">
+      <c r="Y43" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="Z43" s="14" t="s">
+      <c r="Z43" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="AA43" s="14" t="s">
-        <v>193</v>
+      <c r="AA43" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -3387,8 +3400,8 @@
       <c r="D44" s="7"/>
       <c r="E44" s="9"/>
       <c r="F44" s="6"/>
-      <c r="G44" s="7" t="s">
-        <v>194</v>
+      <c r="G44" s="25" t="s">
+        <v>195</v>
       </c>
       <c r="H44" s="9" t="s">
         <v>166</v>
@@ -3406,22 +3419,28 @@
       <c r="R44" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="S44" s="7"/>
-      <c r="T44" s="7"/>
-      <c r="U44" s="9"/>
+      <c r="S44" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="T44" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="U44" s="17" t="s">
+        <v>164</v>
+      </c>
       <c r="V44" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="W44" s="14" t="s">
+      <c r="W44" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="X44" s="17" t="s">
+      <c r="X44" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="Y44" s="14" t="s">
+      <c r="Y44" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="Z44" s="14" t="s">
+      <c r="Z44" s="7" t="s">
         <v>173</v>
       </c>
       <c r="AA44" s="14" t="s">
@@ -3439,8 +3458,8 @@
       <c r="D45" s="7"/>
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
-      <c r="G45" s="7" t="s">
-        <v>195</v>
+      <c r="G45" s="25" t="s">
+        <v>196</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
@@ -3466,11 +3485,11 @@
       <c r="V45" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="W45" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="X45" s="17" t="s">
-        <v>196</v>
+      <c r="W45" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="X45" s="26" t="s">
+        <v>197</v>
       </c>
       <c r="Y45" s="6"/>
       <c r="Z45" s="6"/>
@@ -3573,7 +3592,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="4"/>
@@ -3590,8 +3609,9 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>198</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="W49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
@@ -3723,7 +3743,7 @@
         <v>6</v>
       </c>
       <c r="AB51" s="14" t="s">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AC51" s="14" t="s">
         <v>74</v>
@@ -3777,7 +3797,7 @@
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="25"/>
+      <c r="U52" s="27"/>
       <c r="V52" s="6"/>
       <c r="W52" s="14" t="s">
         <v>6</v>
@@ -3792,7 +3812,7 @@
         <v>3</v>
       </c>
       <c r="AA52" s="14" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AB52" s="14" t="s">
         <v>101</v>
@@ -4288,7 +4308,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4305,7 +4325,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="5"/>
       <c r="Q1" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
@@ -4455,7 +4475,7 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O3" s="6"/>
       <c r="Q3" s="6" t="s">
@@ -4623,7 +4643,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -4972,7 +4992,7 @@
         <v>37</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O11" s="6"/>
       <c r="Q11" s="7"/>
@@ -5136,7 +5156,7 @@
         <v>52</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>43</v>
@@ -5329,40 +5349,40 @@
         <v>116</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M18" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>6</v>
@@ -5397,7 +5417,7 @@
         <v>131</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>133</v>
@@ -5545,7 +5565,7 @@
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>43</v>
@@ -5559,7 +5579,7 @@
       <c r="U21" s="6"/>
       <c r="V21" s="7"/>
       <c r="W21" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="7"/>
@@ -5719,40 +5739,40 @@
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M26" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>6</v>
@@ -5785,7 +5805,7 @@
         <v>131</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>133</v>
@@ -5813,7 +5833,7 @@
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O27" s="6"/>
       <c r="Q27" s="7"/>
@@ -5923,7 +5943,7 @@
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>43</v>
@@ -6072,7 +6092,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -6092,40 +6112,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -6137,40 +6157,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -6184,7 +6204,7 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>133</v>
@@ -6212,7 +6232,7 @@
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
@@ -6225,7 +6245,7 @@
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>133</v>
@@ -6303,7 +6323,7 @@
         <v>90</v>
       </c>
       <c r="R36" s="23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S36" s="23" t="s">
         <v>150</v>
@@ -6370,7 +6390,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -6549,7 +6569,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -6566,7 +6586,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -6640,12 +6660,12 @@
         <v>137</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -6653,14 +6673,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -6677,7 +6697,7 @@
       <c r="E44" s="24"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H44" s="24" t="s">
         <v>166</v>
@@ -6710,7 +6730,7 @@
       <c r="W44" s="6"/>
       <c r="X44" s="24"/>
       <c r="Y44" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -6727,14 +6747,14 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -6751,10 +6771,10 @@
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -6893,7 +6913,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7461,7 +7481,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7624,7 +7644,7 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O3" s="6"/>
       <c r="Q3" s="7"/>
@@ -7788,7 +7808,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -7944,7 +7964,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -8493,7 +8513,7 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>6</v>
@@ -8538,7 +8558,7 @@
         <v>4</v>
       </c>
       <c r="AD18" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AE18" s="6" t="s">
         <v>6</v>
@@ -9091,7 +9111,7 @@
       <c r="AA27" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AB27" s="26" t="s">
+      <c r="AB27" s="28" t="s">
         <v>88</v>
       </c>
       <c r="AC27" s="19" t="s">
@@ -9386,7 +9406,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -9406,40 +9426,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -9451,40 +9471,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -9498,7 +9518,7 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>133</v>
@@ -9526,7 +9546,7 @@
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
@@ -9539,7 +9559,7 @@
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>133</v>
@@ -9617,7 +9637,7 @@
         <v>90</v>
       </c>
       <c r="R36" s="23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="S36" s="23" t="s">
         <v>150</v>
@@ -9684,7 +9704,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -9863,7 +9883,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -9880,7 +9900,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -9954,12 +9974,12 @@
         <v>137</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -9967,14 +9987,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -9991,7 +10011,7 @@
       <c r="E44" s="24"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H44" s="24" t="s">
         <v>166</v>
@@ -10024,7 +10044,7 @@
       <c r="W44" s="6"/>
       <c r="X44" s="24"/>
       <c r="Y44" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -10041,14 +10061,14 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -10065,10 +10085,10 @@
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -10207,7 +10227,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="long_press_shift(JP)" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="long_press_shift(US)" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="long_press_shift(US)_2" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="long_press_shift(JP)_2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="long_press_shift(US)" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="long_press_shift(US)_2" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="226">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -423,217 +424,259 @@
     <t xml:space="preserve">S+F3</t>
   </si>
   <si>
+    <t xml:space="preserve">C+h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Del</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+→</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PgUp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PgDn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+F12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">””←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">()←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[]←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{}←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+”-”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;&gt;←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space修飾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find-Next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find-Prev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+↑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+→</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC+→</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SelAll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC+←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space &amp; F13 修飾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+End</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (F14 or 変換 or 無変換) 修飾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">標準(改変なし)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">標準（ahk）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">＼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shiftt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+F12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+e</t>
+  </si>
+  <si>
     <t xml:space="preserve">C+r</t>
   </si>
   <si>
-    <t xml:space="preserve">Del</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+→</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PgUp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PgDn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+F12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">””←</t>
-  </si>
-  <si>
-    <t xml:space="preserve">()←</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[]←</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{}←</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+←</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;&gt;←</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Space修飾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Space or F13) &amp; 無変換 修飾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+↑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+→</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+←</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+”-”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+End</t>
-  </si>
-  <si>
     <t xml:space="preserve">頻度マップ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+F12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Space &amp; F13 修飾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC+→</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC+←</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> (F14 or 変換 or 無変換) 修飾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layer1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">＼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shiftt</t>
   </si>
   <si>
     <t xml:space="preserve">/ 修飾   C+k,C+{}</t>
@@ -762,14 +805,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBBE33D"/>
-        <bgColor rgb="FF81D41A"/>
+        <fgColor rgb="FF729FCF"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF729FCF"/>
-        <bgColor rgb="FF808080"/>
+        <fgColor rgb="FFBBE33D"/>
+        <bgColor rgb="FF81D41A"/>
       </patternFill>
     </fill>
   </fills>
@@ -891,7 +934,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -984,11 +1027,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1001,6 +1040,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2222,11 +2269,11 @@
       <c r="E19" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>8</v>
+      <c r="F19" s="14" t="s">
+        <v>134</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H19" s="14" t="s">
         <v>6</v>
@@ -2238,52 +2285,52 @@
         <v>42</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T19" s="7" t="s">
         <v>132</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="X19" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Y19" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Z19" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA19" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AB19" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AC19" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
@@ -2293,16 +2340,16 @@
         <v>90</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="17" t="s">
         <v>152</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>153</v>
@@ -2402,7 +2449,9 @@
         <v>168</v>
       </c>
       <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
+      <c r="L21" s="14" t="s">
+        <v>169</v>
+      </c>
       <c r="M21" s="6" t="s">
         <v>43</v>
       </c>
@@ -2425,7 +2474,7 @@
         <v>3</v>
       </c>
       <c r="Y21" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Z21" s="16" t="s">
         <v>160</v>
@@ -2459,7 +2508,9 @@
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="11"/>
-      <c r="K22" s="6"/>
+      <c r="K22" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="L22" s="11"/>
       <c r="M22" s="6"/>
       <c r="N22" s="11"/>
@@ -2505,7 +2556,7 @@
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="11"/>
-      <c r="K23" s="6"/>
+      <c r="K23" s="7"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
@@ -2545,7 +2596,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="4"/>
@@ -2564,9 +2615,7 @@
       <c r="P25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="Q25" s="18" t="s">
-        <v>171</v>
-      </c>
+      <c r="Q25" s="18"/>
       <c r="R25" s="18"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
@@ -2652,11 +2701,11 @@
       <c r="E27" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>8</v>
+      <c r="F27" s="14" t="s">
+        <v>134</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H27" s="14" t="s">
         <v>6</v>
@@ -2668,13 +2717,13 @@
         <v>42</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
@@ -2686,12 +2735,8 @@
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
       <c r="X27" s="6"/>
-      <c r="Y27" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z27" s="14" t="s">
-        <v>173</v>
-      </c>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
       <c r="AA27" s="6"/>
       <c r="AB27" s="6"/>
       <c r="AC27" s="6"/>
@@ -2701,16 +2746,16 @@
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" s="17" t="s">
         <v>152</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>153</v>
@@ -2738,26 +2783,16 @@
       </c>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="Q28" s="20" t="s">
-        <v>90</v>
-      </c>
+      <c r="Q28" s="20"/>
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
       <c r="U28" s="9"/>
       <c r="V28" s="6"/>
-      <c r="W28" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="X28" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="Y28" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z28" s="14" t="s">
-        <v>173</v>
-      </c>
+      <c r="W28" s="16"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
       <c r="AA28" s="6"/>
       <c r="AB28" s="6"/>
       <c r="AC28" s="6"/>
@@ -2797,7 +2832,7 @@
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="14" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>43</v>
@@ -2810,9 +2845,7 @@
       <c r="T29" s="7"/>
       <c r="U29" s="6"/>
       <c r="V29" s="7"/>
-      <c r="W29" s="16" t="s">
-        <v>178</v>
-      </c>
+      <c r="W29" s="16"/>
       <c r="X29" s="6"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="6"/>
@@ -2841,7 +2874,9 @@
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="11"/>
-      <c r="K30" s="6"/>
+      <c r="K30" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="L30" s="11"/>
       <c r="M30" s="6"/>
       <c r="N30" s="11"/>
@@ -2850,12 +2885,8 @@
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
-      <c r="U30" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="V30" s="20" t="s">
-        <v>60</v>
-      </c>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
       <c r="W30" s="20"/>
       <c r="X30" s="6"/>
       <c r="Y30" s="7"/>
@@ -2877,7 +2908,7 @@
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="11"/>
-      <c r="K31" s="6"/>
+      <c r="K31" s="7"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
@@ -2931,9 +2962,7 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
-      <c r="Q33" s="3" t="s">
-        <v>179</v>
-      </c>
+      <c r="Q33" s="3"/>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
@@ -2951,240 +2980,296 @@
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="19"/>
+      <c r="B34" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
-      <c r="Q34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="R34" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="S34" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="T34" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="U34" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="V34" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="W34" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="X34" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y34" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z34" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="AA34" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="AB34" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="AC34" s="19" t="s">
-        <v>191</v>
-      </c>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
+      <c r="B35" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>138</v>
+      </c>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
-      <c r="Q35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="R35" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="S35" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="T35" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="U35" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="V35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="W35" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="X35" s="23" t="s">
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="X35" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Y35" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z35" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA35" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="AB35" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC35" s="23" t="s">
-        <v>136</v>
-      </c>
+      <c r="Y35" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z35" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA35" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB35" s="6"/>
+      <c r="AC35" s="6"/>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="24"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
+      <c r="B36" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>156</v>
+      </c>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="Q36" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="R36" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="S36" s="23" t="s">
+      <c r="Q36" s="7"/>
+      <c r="R36" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="T36" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="U36" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="V36" s="23" t="s">
+      <c r="S36" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="T36" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="U36" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="V36" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="W36" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="X36" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y36" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z36" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA36" s="23" t="s">
+      <c r="W36" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="X36" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y36" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z36" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA36" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="AB36" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="AC36" s="23" t="s">
-        <v>137</v>
-      </c>
+      <c r="AB36" s="6"/>
+      <c r="AC36" s="6"/>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
+      <c r="A37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>168</v>
+      </c>
       <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
+      <c r="L37" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="Q37" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="R37" s="7" t="s">
+      <c r="R37" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="S37" s="23" t="s">
+      <c r="S37" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="T37" s="23" t="s">
+      <c r="T37" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="23" t="s">
+      <c r="U37" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="V37" s="23" t="s">
+      <c r="V37" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="W37" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="X37" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y37" s="7"/>
-      <c r="Z37" s="7"/>
+      <c r="W37" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="X37" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y37" s="6"/>
+      <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
-      <c r="AC37" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="AC37" s="6"/>
       <c r="AD37" s="6"/>
       <c r="AE37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7"/>
+      <c r="A38" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="C38" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
+      <c r="F38" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="20"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="11"/>
-      <c r="K38" s="6"/>
+      <c r="K38" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="L38" s="11"/>
       <c r="M38" s="6"/>
       <c r="N38" s="11"/>
@@ -3192,26 +3277,22 @@
       <c r="Q38" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="R38" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="R38" s="7"/>
       <c r="S38" s="7" t="s">
         <v>57</v>
       </c>
       <c r="T38" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="U38" s="7" t="s">
+      <c r="U38" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="V38" s="7" t="s">
-        <v>60</v>
-      </c>
+      <c r="V38" s="7"/>
       <c r="W38" s="7"/>
-      <c r="X38" s="7" t="s">
+      <c r="X38" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="Y38" s="7" t="s">
+      <c r="Y38" s="20" t="s">
         <v>114</v>
       </c>
       <c r="Z38" s="11"/>
@@ -3219,9 +3300,7 @@
         <v>55</v>
       </c>
       <c r="AB38" s="11"/>
-      <c r="AC38" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="AC38" s="6"/>
       <c r="AD38" s="11"/>
       <c r="AE38" s="11"/>
     </row>
@@ -3232,11 +3311,11 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="G39" s="20"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="11"/>
-      <c r="K39" s="6"/>
+      <c r="K39" s="7"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
@@ -3248,19 +3327,13 @@
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
-      <c r="X39" s="7"/>
-      <c r="Y39" s="7"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
       <c r="Z39" s="11"/>
       <c r="AA39" s="6"/>
-      <c r="AB39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="AC39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD39" s="6" t="s">
-        <v>42</v>
-      </c>
+      <c r="AB39" s="6"/>
+      <c r="AC39" s="6"/>
+      <c r="AD39" s="6"/>
       <c r="AE39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3281,7 +3354,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -3358,7 +3431,7 @@
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
@@ -3372,19 +3445,19 @@
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
       <c r="W43" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X43" s="14" t="s">
         <v>6</v>
       </c>
       <c r="Y43" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Z43" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AA43" s="7" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -3400,15 +3473,15 @@
       <c r="D44" s="7"/>
       <c r="E44" s="9"/>
       <c r="F44" s="6"/>
-      <c r="G44" s="25" t="s">
-        <v>195</v>
+      <c r="G44" s="24" t="s">
+        <v>193</v>
       </c>
       <c r="H44" s="9" t="s">
         <v>166</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
@@ -3417,7 +3490,7 @@
       <c r="O44" s="6"/>
       <c r="Q44" s="7"/>
       <c r="R44" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="S44" s="14" t="s">
         <v>162</v>
@@ -3432,16 +3505,16 @@
         <v>153</v>
       </c>
       <c r="W44" s="19" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="Y44" s="7" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="Z44" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AA44" s="14" t="s">
         <v>21</v>
@@ -3452,14 +3525,16 @@
       <c r="AE44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7"/>
+      <c r="A45" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
-      <c r="G45" s="25" t="s">
-        <v>196</v>
+      <c r="G45" s="24" t="s">
+        <v>194</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
@@ -3469,7 +3544,9 @@
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
       <c r="O45" s="6"/>
-      <c r="Q45" s="7"/>
+      <c r="Q45" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="R45" s="14" t="s">
         <v>161</v>
       </c>
@@ -3485,11 +3562,11 @@
       <c r="V45" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="W45" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="X45" s="26" t="s">
-        <v>197</v>
+      <c r="W45" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="X45" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="Y45" s="6"/>
       <c r="Z45" s="6"/>
@@ -3500,10 +3577,16 @@
       <c r="AE45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7"/>
+      <c r="A46" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
+      <c r="C46" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="E46" s="7"/>
       <c r="F46" s="20" t="s">
         <v>60</v>
@@ -3512,15 +3595,23 @@
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
       <c r="J46" s="11"/>
-      <c r="K46" s="6"/>
+      <c r="K46" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="L46" s="11"/>
       <c r="M46" s="6"/>
       <c r="N46" s="11"/>
       <c r="O46" s="11"/>
-      <c r="Q46" s="7"/>
+      <c r="Q46" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
+      <c r="S46" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="T46" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="U46" s="20" t="s">
         <v>59</v>
       </c>
@@ -3534,7 +3625,7 @@
       </c>
       <c r="Z46" s="11"/>
       <c r="AA46" s="6" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="AB46" s="11"/>
       <c r="AC46" s="6"/>
@@ -3552,7 +3643,7 @@
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
       <c r="J47" s="11"/>
-      <c r="K47" s="6"/>
+      <c r="K47" s="7"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
@@ -3592,7 +3683,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="4"/>
@@ -3609,7 +3700,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="W49" s="1"/>
     </row>
@@ -3679,45 +3770,47 @@
       </c>
       <c r="AC50" s="7"/>
       <c r="AD50" s="7"/>
-      <c r="AE50" s="7"/>
+      <c r="AE50" s="7" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
       <c r="B51" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>132</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L51" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M51" s="19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
@@ -3728,7 +3821,7 @@
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X51" s="14" t="n">
         <v>4</v>
@@ -3748,7 +3841,9 @@
       <c r="AC51" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="AD51" s="7"/>
+      <c r="AD51" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="AE51" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3797,7 +3892,7 @@
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="27"/>
+      <c r="U52" s="26"/>
       <c r="V52" s="6"/>
       <c r="W52" s="14" t="s">
         <v>6</v>
@@ -3933,7 +4028,9 @@
       <c r="Z54" s="11"/>
       <c r="AA54" s="6"/>
       <c r="AB54" s="11"/>
-      <c r="AC54" s="6"/>
+      <c r="AC54" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="AD54" s="11"/>
       <c r="AE54" s="11"/>
     </row>
@@ -3964,9 +4061,15 @@
       <c r="Y55" s="7"/>
       <c r="Z55" s="11"/>
       <c r="AA55" s="6"/>
-      <c r="AB55" s="6"/>
-      <c r="AC55" s="6"/>
-      <c r="AD55" s="6"/>
+      <c r="AB55" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC55" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD55" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="AE55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4308,7 +4411,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4325,7 +4428,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="5"/>
       <c r="Q1" s="3" t="s">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
@@ -4344,7 +4447,7 @@
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>1</v>
@@ -4380,59 +4483,31 @@
         <v>3</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="V2" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="W2" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="X2" s="6" t="n">
+      <c r="Q2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="Y2" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z2" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE2" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -4469,57 +4544,35 @@
         <v>18</v>
       </c>
       <c r="L3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="N3" s="6" t="s">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="O3" s="6"/>
-      <c r="Q3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AD3" s="6" t="s">
-        <v>21</v>
-      </c>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
       <c r="AE3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4535,7 +4588,7 @@
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="9" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -4544,7 +4597,7 @@
       <c r="G4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="9" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -4557,54 +4610,36 @@
         <v>35</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="6" t="s">
         <v>37</v>
       </c>
+      <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="Q4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="R4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="U4" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>30</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="6"/>
       <c r="W4" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="X4" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y4" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="Z4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC4" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
       <c r="AD4" s="6"/>
       <c r="AE4" s="6"/>
     </row>
@@ -4643,52 +4678,30 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>203</v>
+        <v>5</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="Q5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="V5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="W5" s="7" t="s">
-        <v>49</v>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC5" s="6" t="s">
-        <v>43</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="6"/>
       <c r="AD5" s="6"/>
       <c r="AE5" s="6"/>
     </row>
@@ -4706,7 +4719,7 @@
         <v>58</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>60</v>
@@ -4715,12 +4728,10 @@
       <c r="H6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="J6" s="11"/>
       <c r="K6" s="6" t="s">
         <v>55</v>
       </c>
@@ -4730,38 +4741,22 @@
       </c>
       <c r="N6" s="11"/>
       <c r="O6" s="11"/>
-      <c r="Q6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="S6" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="T6" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="U6" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
       <c r="V6" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="W6" s="7"/>
-      <c r="X6" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y6" s="10" t="s">
-        <v>62</v>
-      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
       <c r="Z6" s="11"/>
-      <c r="AA6" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="AA6" s="6"/>
       <c r="AB6" s="11"/>
       <c r="AC6" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="AD6" s="11"/>
       <c r="AE6" s="11"/>
@@ -4776,7 +4771,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
+      <c r="J7" s="11"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6" t="s">
         <v>40</v>
@@ -4799,14 +4794,14 @@
       <c r="Y7" s="7"/>
       <c r="Z7" s="11"/>
       <c r="AA7" s="6"/>
-      <c r="AB7" s="6" t="s">
-        <v>40</v>
+      <c r="AB7" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="AD7" s="6" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="AE7" s="6"/>
     </row>
@@ -4829,7 +4824,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>198</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -4865,7 +4860,7 @@
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>1</v>
@@ -4901,55 +4896,53 @@
         <v>3</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="Q10" s="7"/>
-      <c r="R10" s="7" t="s">
+      <c r="R10" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="T10" s="7" t="s">
+      <c r="S10" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="T10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="U10" s="6" t="s">
+      <c r="U10" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="V10" s="6" t="s">
+      <c r="V10" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="W10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="X10" s="7" t="s">
+      <c r="W10" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="Y10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z10" s="7" t="s">
+      <c r="X10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y10" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="AA10" s="6" t="s">
+      <c r="Z10" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="AB10" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AC10" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD10" s="6"/>
-      <c r="AE10" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AD10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
@@ -4971,70 +4964,68 @@
         <v>13</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="L11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="M11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="N11" s="6" t="s">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="O11" s="6"/>
       <c r="Q11" s="7"/>
-      <c r="R11" s="7" t="s">
+      <c r="R11" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="S11" s="7" t="s">
+      <c r="S11" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="T11" s="7" t="s">
+      <c r="T11" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="U11" s="6" t="s">
+      <c r="U11" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="V11" s="6" t="s">
+      <c r="V11" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="W11" s="6" t="s">
+      <c r="W11" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="X11" s="6" t="s">
+      <c r="X11" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="Y11" s="7" t="s">
+      <c r="Y11" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="Z11" s="6" t="s">
+      <c r="Z11" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AA11" s="6" t="s">
+      <c r="AA11" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AB11" s="6" t="s">
+      <c r="AB11" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC11" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="AC11" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="AD11" s="6" t="s">
-        <v>78</v>
-      </c>
+      <c r="AD11" s="6"/>
       <c r="AE11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5050,75 +5041,73 @@
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="9" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="J12" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="L12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="M12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="Q12" s="7"/>
-      <c r="R12" s="7" t="s">
+      <c r="R12" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="S12" s="7" t="s">
+      <c r="S12" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="T12" s="7" t="s">
+      <c r="T12" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="U12" s="24" t="s">
+      <c r="U12" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="V12" s="6" t="s">
+      <c r="V12" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="W12" s="6" t="s">
+      <c r="W12" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="X12" s="24" t="s">
+      <c r="X12" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="Y12" s="7" t="s">
+      <c r="Y12" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="Z12" s="6" t="s">
+      <c r="Z12" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="AA12" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB12" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC12" s="6"/>
-      <c r="AD12" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="AA12" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB12" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC12" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD12" s="6"/>
       <c r="AE12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5140,23 +5129,23 @@
       <c r="F13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="K13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="L13" s="6" t="s">
         <v>7</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>43</v>
@@ -5164,40 +5153,40 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="Q13" s="7"/>
-      <c r="R13" s="7" t="s">
+      <c r="R13" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="S13" s="7" t="s">
+      <c r="S13" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="T13" s="7" t="s">
+      <c r="T13" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="U13" s="7" t="s">
+      <c r="U13" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="V13" s="7" t="s">
+      <c r="V13" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="W13" s="7" t="s">
+      <c r="W13" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="X13" s="7" t="s">
+      <c r="X13" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="Y13" s="7" t="s">
+      <c r="Y13" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="Z13" s="7" t="s">
+      <c r="Z13" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="AA13" s="7" t="s">
+      <c r="AA13" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="AB13" s="6"/>
-      <c r="AC13" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="AB13" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC13" s="6"/>
       <c r="AD13" s="6"/>
       <c r="AE13" s="6"/>
     </row>
@@ -5215,21 +5204,19 @@
         <v>58</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>58</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="J14" s="11"/>
       <c r="K14" s="6" t="s">
         <v>55</v>
       </c>
@@ -5237,7 +5224,9 @@
       <c r="M14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="11" t="s">
+        <v>37</v>
+      </c>
       <c r="O14" s="11"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -5248,7 +5237,7 @@
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
       <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
+      <c r="Z14" s="11"/>
       <c r="AA14" s="6"/>
       <c r="AB14" s="11"/>
       <c r="AC14" s="6"/>
@@ -5265,7 +5254,7 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
+      <c r="J15" s="11"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6" t="s">
         <v>40</v>
@@ -5286,7 +5275,7 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
+      <c r="Z15" s="11"/>
       <c r="AA15" s="6"/>
       <c r="AB15" s="6"/>
       <c r="AC15" s="6"/>
@@ -5349,40 +5338,3312 @@
         <v>116</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="S18" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="T18" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="V18" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="W18" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="X18" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y18" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z18" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA18" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB18" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="T19" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="W19" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="X19" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z19" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA19" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB19" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC19" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="AD19" s="6"/>
+      <c r="AE19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="S20" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="T20" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="U20" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="V20" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="W20" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="X20" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y20" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z20" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA20" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC20" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="Q21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="W21" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="X21" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z21" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA21" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB21" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="11"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="Q22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="T22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U22" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="V22" s="7"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y22" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z22" s="11"/>
+      <c r="AA22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB22" s="11"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="11"/>
+      <c r="AE22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="21"/>
+      <c r="Y23" s="21"/>
+      <c r="Z23" s="11"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q25" s="18"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7"/>
+      <c r="B27" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="6"/>
+      <c r="W27" s="6"/>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="6"/>
+      <c r="AD27" s="6"/>
+      <c r="AE27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7"/>
+      <c r="B28" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I29" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="J29" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="K29" s="6"/>
+      <c r="L29" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="6"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="16"/>
+      <c r="X29" s="6"/>
+      <c r="Y29" s="7"/>
+      <c r="Z29" s="6"/>
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="6"/>
+      <c r="AD29" s="6"/>
+      <c r="AE29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="20"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L30" s="11"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="7"/>
+      <c r="Z30" s="11"/>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="11"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="11"/>
+      <c r="AE30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="11"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="5"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="4"/>
+      <c r="AC33" s="4"/>
+      <c r="AD33" s="4"/>
+      <c r="AE33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="7"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7"/>
+      <c r="B35" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="X35" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y35" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z35" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA35" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB35" s="6"/>
+      <c r="AC35" s="6"/>
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7"/>
+      <c r="B36" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>180</v>
       </c>
+      <c r="D36" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="S36" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="T36" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="U36" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="V36" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="W36" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="X36" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y36" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z36" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA36" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB36" s="6"/>
+      <c r="AC36" s="6"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="Q37" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R37" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="S37" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="T37" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="U37" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="V37" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="W37" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="X37" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y37" s="6"/>
+      <c r="Z37" s="6"/>
+      <c r="AA37" s="6"/>
+      <c r="AB37" s="6"/>
+      <c r="AC37" s="6"/>
+      <c r="AD37" s="6"/>
+      <c r="AE37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G38" s="20"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L38" s="11"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="Q38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="T38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U38" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="V38" s="7"/>
+      <c r="W38" s="7"/>
+      <c r="X38" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y38" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z38" s="11"/>
+      <c r="AA38" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB38" s="11"/>
+      <c r="AC38" s="6"/>
+      <c r="AD38" s="11"/>
+      <c r="AE38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="11"/>
+      <c r="AA39" s="6"/>
+      <c r="AB39" s="6"/>
+      <c r="AC39" s="6"/>
+      <c r="AD39" s="6"/>
+      <c r="AE39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="22"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="13"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="5"/>
+      <c r="Q41" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="R41" s="18"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="4"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="7"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="X43" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y43" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z43" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA43" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB43" s="6"/>
+      <c r="AC43" s="6"/>
+      <c r="AD43" s="6"/>
+      <c r="AE43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="S44" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="T44" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="U44" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="V44" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="W44" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="X44" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y44" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z44" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA44" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB44" s="6"/>
+      <c r="AC44" s="6"/>
+      <c r="AD44" s="6"/>
+      <c r="AE44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="Q45" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R45" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="S45" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="T45" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="U45" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="V45" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="W45" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="X45" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y45" s="6"/>
+      <c r="Z45" s="6"/>
+      <c r="AA45" s="6"/>
+      <c r="AB45" s="6"/>
+      <c r="AC45" s="6"/>
+      <c r="AD45" s="6"/>
+      <c r="AE45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G46" s="20"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L46" s="11"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="Q46" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="T46" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U46" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y46" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z46" s="11"/>
+      <c r="AA46" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB46" s="11"/>
+      <c r="AC46" s="6"/>
+      <c r="AD46" s="11"/>
+      <c r="AE46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="11"/>
+      <c r="AA47" s="6"/>
+      <c r="AB47" s="6"/>
+      <c r="AC47" s="6"/>
+      <c r="AD47" s="6"/>
+      <c r="AE47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="13"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B49" s="18"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="5"/>
+      <c r="Q49" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="W49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="7"/>
+      <c r="T50" s="7"/>
+      <c r="U50" s="6"/>
+      <c r="V50" s="6"/>
+      <c r="W50" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="X50" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y50" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z50" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA50" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC50" s="7"/>
+      <c r="AD50" s="7"/>
+      <c r="AE50" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="L51" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="M51" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="U51" s="6"/>
+      <c r="V51" s="6"/>
+      <c r="W51" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="X51" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y51" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z51" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA51" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB51" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD51" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7"/>
+      <c r="B52" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D52" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F52" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="Q52" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="R52" s="7"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
+      <c r="U52" s="26"/>
+      <c r="V52" s="6"/>
+      <c r="W52" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="X52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z52" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB52" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD52" s="7"/>
+      <c r="AE52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="J53" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="L53" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7"/>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z53" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA53" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB53" s="7"/>
+      <c r="AC53" s="7"/>
+      <c r="AD53" s="7"/>
+      <c r="AE53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I54" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="J54" s="11"/>
+      <c r="K54" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L54" s="11"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="7"/>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="11"/>
+      <c r="AA54" s="6"/>
+      <c r="AB54" s="11"/>
+      <c r="AC54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD54" s="11"/>
+      <c r="AE54" s="11"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7"/>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="11"/>
+      <c r="AA55" s="6"/>
+      <c r="AB55" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC55" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD55" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="182">
+    <mergeCell ref="N3:O4"/>
+    <mergeCell ref="AD3:AE4"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="AD11:AE12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="AC13:AE13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="Q14:Q15"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="V14:W15"/>
+    <mergeCell ref="X14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="AA14:AA15"/>
+    <mergeCell ref="AD14:AE14"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="AD15:AE15"/>
+    <mergeCell ref="N19:O20"/>
+    <mergeCell ref="AD19:AE20"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="AC21:AE21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="Q22:Q23"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="V22:W23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="AA22:AA23"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="N27:O28"/>
+    <mergeCell ref="AD27:AE28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="Q30:Q31"/>
+    <mergeCell ref="R30:R31"/>
+    <mergeCell ref="S30:S31"/>
+    <mergeCell ref="T30:T31"/>
+    <mergeCell ref="U30:U31"/>
+    <mergeCell ref="V30:W31"/>
+    <mergeCell ref="X30:X31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="AA30:AA31"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="N35:O36"/>
+    <mergeCell ref="AD35:AE36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="AC37:AE37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="Q38:Q39"/>
+    <mergeCell ref="R38:R39"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="U38:U39"/>
+    <mergeCell ref="V38:W39"/>
+    <mergeCell ref="X38:X39"/>
+    <mergeCell ref="Y38:Y39"/>
+    <mergeCell ref="AA38:AA39"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="AD39:AE39"/>
+    <mergeCell ref="N43:O44"/>
+    <mergeCell ref="AD43:AE44"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="AC45:AE45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="Q46:Q47"/>
+    <mergeCell ref="R46:R47"/>
+    <mergeCell ref="S46:S47"/>
+    <mergeCell ref="T46:T47"/>
+    <mergeCell ref="U46:U47"/>
+    <mergeCell ref="V46:W47"/>
+    <mergeCell ref="X46:X47"/>
+    <mergeCell ref="Y46:Y47"/>
+    <mergeCell ref="AA46:AA47"/>
+    <mergeCell ref="AD46:AE46"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="AD47:AE47"/>
+    <mergeCell ref="N51:O52"/>
+    <mergeCell ref="AD51:AE52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="AC53:AE53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="Q54:Q55"/>
+    <mergeCell ref="R54:R55"/>
+    <mergeCell ref="S54:S55"/>
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="U54:U55"/>
+    <mergeCell ref="V54:W55"/>
+    <mergeCell ref="X54:X55"/>
+    <mergeCell ref="Y54:Y55"/>
+    <mergeCell ref="AA54:AA55"/>
+    <mergeCell ref="AD54:AE54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="AD55:AE55"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AE62"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="1" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="4.09"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="17" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="21" style="2" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="30" style="2" width="3.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="5"/>
+      <c r="Q1" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="X2" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y2" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE2" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="Q3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="Q4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="U4" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="W4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="X4" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="Q5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="W5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="X5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="11"/>
+      <c r="M6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="Q6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="T6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="V6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y6" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5"/>
+      <c r="Q9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="S10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T10" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="U10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="V10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="W10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="X10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AB10" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="O11" s="6"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="W11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="X11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB11" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" s="6"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="S12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="T12" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="U12" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="W12" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="X12" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB12" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T13" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="U13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="V13" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="W13" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="X13" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="11"/>
+      <c r="M14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="11"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="11"/>
+      <c r="AE14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O15" s="6"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="5"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>203</v>
+      </c>
       <c r="C18" s="7" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="M18" s="19" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>6</v>
@@ -5417,16 +8678,16 @@
         <v>131</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>6</v>
@@ -5441,7 +8702,7 @@
         <v>41</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
@@ -5457,7 +8718,7 @@
       <c r="X19" s="6"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
@@ -5470,16 +8731,16 @@
         <v>90</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="24" t="s">
         <v>152</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>153</v>
@@ -5487,7 +8748,7 @@
       <c r="G20" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H20" s="24" t="s">
+      <c r="H20" s="27" t="s">
         <v>40</v>
       </c>
       <c r="I20" s="7" t="s">
@@ -5500,7 +8761,7 @@
         <v>21</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>21</v>
@@ -5514,17 +8775,17 @@
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
-      <c r="U20" s="24"/>
+      <c r="U20" s="27"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="X20" s="24" t="s">
-        <v>175</v>
+        <v>183</v>
+      </c>
+      <c r="X20" s="27" t="s">
+        <v>184</v>
       </c>
       <c r="Y20" s="7"/>
       <c r="Z20" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
@@ -5565,7 +8826,7 @@
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>43</v>
@@ -5579,7 +8840,7 @@
       <c r="U21" s="6"/>
       <c r="V21" s="7"/>
       <c r="W21" s="6" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="7"/>
@@ -5701,7 +8962,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B25" s="18"/>
       <c r="C25" s="4"/>
@@ -5739,40 +9000,40 @@
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="M26" s="19" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>6</v>
@@ -5805,16 +9066,16 @@
         <v>131</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>6</v>
@@ -5829,11 +9090,11 @@
         <v>41</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O27" s="6"/>
       <c r="Q27" s="7"/>
@@ -5855,16 +9116,16 @@
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E28" s="24" t="s">
         <v>152</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>153</v>
@@ -5872,7 +9133,7 @@
       <c r="G28" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="27" t="s">
         <v>40</v>
       </c>
       <c r="I28" s="7" t="s">
@@ -5885,7 +9146,7 @@
         <v>21</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>21</v>
@@ -5898,10 +9159,10 @@
       <c r="R28" s="7"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
-      <c r="U28" s="24"/>
+      <c r="U28" s="27"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
-      <c r="X28" s="24"/>
+      <c r="X28" s="27"/>
       <c r="Y28" s="7"/>
       <c r="Z28" s="6"/>
       <c r="AA28" s="6"/>
@@ -5943,7 +9204,7 @@
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>43</v>
@@ -6092,7 +9353,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -6112,40 +9373,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -6157,40 +9418,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -6204,16 +9465,16 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>6</v>
@@ -6228,51 +9489,51 @@
         <v>41</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="R35" s="23" t="s">
+      <c r="R35" s="28" t="s">
         <v>130</v>
       </c>
       <c r="S35" s="7" t="s">
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="V35" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="W35" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="X35" s="23" t="s">
+      <c r="W35" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="X35" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="Y35" s="23" t="s">
+      <c r="Y35" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="Z35" s="23" t="s">
+      <c r="Z35" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="AA35" s="23" t="s">
+      <c r="AA35" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="AB35" s="23" t="s">
+      <c r="AB35" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="AC35" s="23" t="s">
-        <v>136</v>
+      <c r="AC35" s="28" t="s">
+        <v>137</v>
       </c>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
@@ -6280,16 +9541,16 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" s="24" t="s">
         <v>152</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>153</v>
@@ -6297,7 +9558,7 @@
       <c r="G36" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H36" s="24" t="s">
+      <c r="H36" s="27" t="s">
         <v>40</v>
       </c>
       <c r="I36" s="7" t="s">
@@ -6310,7 +9571,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>21</v>
@@ -6322,41 +9583,41 @@
       <c r="Q36" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="R36" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="S36" s="23" t="s">
-        <v>150</v>
+      <c r="R36" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="S36" s="28" t="s">
+        <v>151</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="V36" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="V36" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="W36" s="23" t="s">
+      <c r="W36" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="X36" s="23" t="s">
+      <c r="X36" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="Y36" s="23" t="s">
+      <c r="Y36" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="Z36" s="23" t="s">
+      <c r="Z36" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="AA36" s="23" t="s">
+      <c r="AA36" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="AB36" s="23" t="s">
+      <c r="AB36" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="AC36" s="23" t="s">
-        <v>137</v>
+      <c r="AC36" s="28" t="s">
+        <v>138</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
@@ -6390,7 +9651,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -6403,22 +9664,22 @@
       <c r="R37" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="S37" s="23" t="s">
+      <c r="S37" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="T37" s="23" t="s">
+      <c r="T37" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="23" t="s">
+      <c r="U37" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="V37" s="23" t="s">
+      <c r="V37" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="W37" s="23" t="s">
+      <c r="W37" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="X37" s="23" t="s">
+      <c r="X37" s="28" t="s">
         <v>41</v>
       </c>
       <c r="Y37" s="7"/>
@@ -6569,7 +9830,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -6586,7 +9847,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -6650,22 +9911,22 @@
       <c r="H43" s="6"/>
       <c r="I43" s="7"/>
       <c r="J43" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -6673,14 +9934,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -6694,17 +9955,17 @@
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="24"/>
+      <c r="E44" s="27"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="H44" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="H44" s="27" t="s">
         <v>166</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6" t="s">
@@ -6720,17 +9981,17 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T44" s="6"/>
-      <c r="U44" s="24" t="s">
-        <v>152</v>
+      <c r="U44" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
-      <c r="X44" s="24"/>
+      <c r="X44" s="27"/>
       <c r="Y44" s="6" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -6747,14 +10008,14 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -6771,10 +10032,10 @@
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -6913,7 +10174,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6979,7 +10240,7 @@
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X51" s="6" t="n">
         <v>4</v>
@@ -7003,10 +10264,10 @@
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="24"/>
+      <c r="E52" s="27"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="24"/>
+      <c r="H52" s="27"/>
       <c r="I52" s="7"/>
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
@@ -7018,12 +10279,12 @@
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="24"/>
+      <c r="U52" s="27"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="X52" s="24" t="n">
+      <c r="X52" s="27" t="n">
         <v>1</v>
       </c>
       <c r="Y52" s="7" t="n">
@@ -7463,7 +10724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -7481,7 +10742,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7644,7 +10905,7 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O3" s="6"/>
       <c r="Q3" s="7"/>
@@ -7702,7 +10963,7 @@
       <c r="D4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="27" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -7711,7 +10972,7 @@
       <c r="G4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="27" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -7743,7 +11004,7 @@
       <c r="T4" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U4" s="24" t="s">
+      <c r="U4" s="27" t="s">
         <v>94</v>
       </c>
       <c r="V4" s="6" t="s">
@@ -7752,7 +11013,7 @@
       <c r="W4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X4" s="24" t="s">
+      <c r="X4" s="27" t="s">
         <v>97</v>
       </c>
       <c r="Y4" s="7" t="s">
@@ -7792,8 +11053,8 @@
       <c r="F5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>49</v>
+      <c r="G5" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>50</v>
@@ -7808,7 +11069,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -7964,7 +11225,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -8000,7 +11261,7 @@
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>1</v>
@@ -8036,10 +11297,10 @@
         <v>3</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>6</v>
@@ -8106,28 +11367,28 @@
         <v>13</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="L11" s="6" t="s">
         <v>18</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>19</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>20</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="O11" s="6"/>
       <c r="Q11" s="7"/>
@@ -8185,34 +11446,36 @@
       <c r="D12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="27" t="s">
         <v>29</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="I12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="J12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="L12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="M12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7" t="s">
@@ -8224,7 +11487,7 @@
       <c r="T12" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U12" s="24" t="s">
+      <c r="U12" s="27" t="s">
         <v>94</v>
       </c>
       <c r="V12" s="6" t="s">
@@ -8233,7 +11496,7 @@
       <c r="W12" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X12" s="24" t="s">
+      <c r="X12" s="27" t="s">
         <v>97</v>
       </c>
       <c r="Y12" s="7" t="s">
@@ -8274,22 +11537,22 @@
         <v>48</v>
       </c>
       <c r="G13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="I13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="K13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K13" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="L13" s="6" t="s">
-        <v>5</v>
+        <v>202</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>43</v>
@@ -8348,7 +11611,7 @@
         <v>58</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>60</v>
@@ -8357,10 +11620,12 @@
       <c r="H14" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J14" s="11"/>
+      <c r="J14" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="K14" s="6" t="s">
         <v>55</v>
       </c>
@@ -8396,7 +11661,7 @@
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="11"/>
+      <c r="J15" s="7"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6" t="s">
         <v>40</v>
@@ -8474,7 +11739,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B18" s="6" t="n">
         <v>1</v>
@@ -8513,7 +11778,7 @@
         <v>4</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>202</v>
+        <v>5</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>6</v>
@@ -8558,7 +11823,7 @@
         <v>4</v>
       </c>
       <c r="AD18" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AE18" s="6" t="s">
         <v>6</v>
@@ -8599,10 +11864,10 @@
         <v>18</v>
       </c>
       <c r="L19" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M19" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>21</v>
@@ -8664,7 +11929,7 @@
       <c r="D20" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="27" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="6" t="s">
@@ -8673,7 +11938,7 @@
       <c r="G20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="24" t="s">
+      <c r="H20" s="27" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="6" t="s">
@@ -8686,10 +11951,10 @@
         <v>35</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
@@ -8704,7 +11969,7 @@
       <c r="T20" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U20" s="24" t="s">
+      <c r="U20" s="27" t="s">
         <v>94</v>
       </c>
       <c r="V20" s="6" t="s">
@@ -8713,7 +11978,7 @@
       <c r="W20" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X20" s="24" t="s">
+      <c r="X20" s="27" t="s">
         <v>97</v>
       </c>
       <c r="Y20" s="7" t="s">
@@ -8768,7 +12033,9 @@
       <c r="K21" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L21" s="6"/>
+      <c r="L21" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="M21" s="6" t="s">
         <v>43</v>
       </c>
@@ -9111,7 +12378,7 @@
       <c r="AA27" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="AB27" s="28" t="s">
+      <c r="AB27" s="29" t="s">
         <v>88</v>
       </c>
       <c r="AC27" s="19" t="s">
@@ -9133,7 +12400,7 @@
       <c r="D28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="27" t="s">
         <v>29</v>
       </c>
       <c r="F28" s="6" t="s">
@@ -9142,7 +12409,7 @@
       <c r="G28" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="24" t="s">
+      <c r="H28" s="27" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="6" t="s">
@@ -9172,7 +12439,7 @@
       <c r="T28" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="U28" s="24" t="s">
+      <c r="U28" s="27" t="s">
         <v>94</v>
       </c>
       <c r="V28" s="6" t="s">
@@ -9181,7 +12448,7 @@
       <c r="W28" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X28" s="24" t="s">
+      <c r="X28" s="27" t="s">
         <v>97</v>
       </c>
       <c r="Y28" s="7" t="s">
@@ -9406,7 +12673,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>179</v>
+        <v>217</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -9426,40 +12693,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -9471,40 +12738,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -9518,16 +12785,16 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>6</v>
@@ -9542,51 +12809,51 @@
         <v>41</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="R35" s="23" t="s">
+      <c r="R35" s="28" t="s">
         <v>130</v>
       </c>
       <c r="S35" s="7" t="s">
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="V35" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="W35" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="X35" s="23" t="s">
+      <c r="W35" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="X35" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="Y35" s="23" t="s">
+      <c r="Y35" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="Z35" s="23" t="s">
+      <c r="Z35" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="AA35" s="23" t="s">
+      <c r="AA35" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="AB35" s="23" t="s">
+      <c r="AB35" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="AC35" s="23" t="s">
-        <v>136</v>
+      <c r="AC35" s="28" t="s">
+        <v>137</v>
       </c>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
@@ -9594,16 +12861,16 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" s="24" t="s">
         <v>152</v>
+      </c>
+      <c r="E36" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>153</v>
@@ -9611,7 +12878,7 @@
       <c r="G36" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H36" s="24" t="s">
+      <c r="H36" s="27" t="s">
         <v>40</v>
       </c>
       <c r="I36" s="7" t="s">
@@ -9624,7 +12891,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>21</v>
@@ -9636,41 +12903,41 @@
       <c r="Q36" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="R36" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="S36" s="23" t="s">
-        <v>150</v>
+      <c r="R36" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="S36" s="28" t="s">
+        <v>151</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="V36" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="V36" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="W36" s="23" t="s">
+      <c r="W36" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="X36" s="23" t="s">
+      <c r="X36" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="Y36" s="23" t="s">
+      <c r="Y36" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="Z36" s="23" t="s">
+      <c r="Z36" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="AA36" s="23" t="s">
+      <c r="AA36" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="AB36" s="23" t="s">
+      <c r="AB36" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="AC36" s="23" t="s">
-        <v>137</v>
+      <c r="AC36" s="28" t="s">
+        <v>138</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
@@ -9704,7 +12971,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -9717,22 +12984,22 @@
       <c r="R37" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="S37" s="23" t="s">
+      <c r="S37" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="T37" s="23" t="s">
+      <c r="T37" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="U37" s="23" t="s">
+      <c r="U37" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="V37" s="23" t="s">
+      <c r="V37" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="W37" s="23" t="s">
+      <c r="W37" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="X37" s="23" t="s">
+      <c r="X37" s="28" t="s">
         <v>41</v>
       </c>
       <c r="Y37" s="7"/>
@@ -9883,7 +13150,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="4"/>
@@ -9900,7 +13167,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -9964,22 +13231,22 @@
       <c r="H43" s="6"/>
       <c r="I43" s="7"/>
       <c r="J43" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -9987,14 +13254,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -10008,17 +13275,17 @@
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
-      <c r="E44" s="24"/>
+      <c r="E44" s="27"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="H44" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="H44" s="27" t="s">
         <v>166</v>
       </c>
       <c r="I44" s="7"/>
       <c r="J44" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6" t="s">
@@ -10034,17 +13301,17 @@
       <c r="Q44" s="7"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="T44" s="6"/>
-      <c r="U44" s="24" t="s">
-        <v>152</v>
+      <c r="U44" s="27" t="s">
+        <v>134</v>
       </c>
       <c r="V44" s="6"/>
       <c r="W44" s="6"/>
-      <c r="X44" s="24"/>
+      <c r="X44" s="27"/>
       <c r="Y44" s="6" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -10061,14 +13328,14 @@
       <c r="E45" s="6"/>
       <c r="F45" s="7"/>
       <c r="G45" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -10085,10 +13352,10 @@
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -10227,7 +13494,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10293,7 +13560,7 @@
       <c r="U51" s="6"/>
       <c r="V51" s="6"/>
       <c r="W51" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="X51" s="6" t="n">
         <v>4</v>
@@ -10317,10 +13584,10 @@
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
-      <c r="E52" s="24"/>
+      <c r="E52" s="27"/>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
-      <c r="H52" s="24"/>
+      <c r="H52" s="27"/>
       <c r="I52" s="7"/>
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
@@ -10332,12 +13599,12 @@
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="24"/>
+      <c r="U52" s="27"/>
       <c r="V52" s="6"/>
       <c r="W52" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="X52" s="24" t="n">
+      <c r="X52" s="27" t="n">
         <v>1</v>
       </c>
       <c r="Y52" s="7" t="n">
@@ -10614,20 +13881,20 @@
     <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="N7:O7"/>
     <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="N10:O10"/>
     <mergeCell ref="AD10:AE10"/>
-    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="N11:O11"/>
     <mergeCell ref="AD11:AE11"/>
+    <mergeCell ref="M12:O12"/>
     <mergeCell ref="AC12:AE12"/>
-    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="AB13:AE13"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="E14:I15"/>
+    <mergeCell ref="J14:J15"/>
     <mergeCell ref="K14:K15"/>
     <mergeCell ref="N14:O14"/>
     <mergeCell ref="Q14:Q15"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="long_press_shift(JP)" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="long_press_shift(JP)_2" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="long_press_shift(US)" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="long_press_shift(US)_2" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="md770-jp" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="229">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -559,48 +560,48 @@
     <t xml:space="preserve">S+→</t>
   </si>
   <si>
+    <t xml:space="preserve">SelAll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+←</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+↓</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+End</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC+←</t>
+  </si>
+  <si>
     <t xml:space="preserve">SC+→</t>
   </si>
   <si>
-    <t xml:space="preserve">SelAll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+←</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+↓</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Undo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S+End</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC+←</t>
-  </si>
-  <si>
     <t xml:space="preserve">Space &amp; F13 修飾</t>
   </si>
   <si>
@@ -701,6 +702,16 @@
   </si>
   <si>
     <t xml:space="preserve">C+n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定変更</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
   </si>
 </sst>
 </file>
@@ -816,7 +827,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -908,6 +919,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -934,7 +952,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1035,12 +1053,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1053,6 +1071,14 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2672,18 +2698,42 @@
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
       <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="6"/>
-      <c r="AB26" s="6"/>
-      <c r="AC26" s="6"/>
+      <c r="R26" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="S26" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="T26" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="V26" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="W26" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="X26" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y26" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z26" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA26" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB26" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC26" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="AD26" s="6"/>
       <c r="AE26" s="6"/>
     </row>
@@ -2728,18 +2778,40 @@
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
       <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="6"/>
-      <c r="Y27" s="14"/>
-      <c r="Z27" s="14"/>
-      <c r="AA27" s="6"/>
-      <c r="AB27" s="6"/>
-      <c r="AC27" s="6"/>
+      <c r="R27" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="S27" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="T27" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="U27" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="V27" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="W27" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="X27" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA27" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB27" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC27" s="14"/>
       <c r="AD27" s="6"/>
       <c r="AE27" s="6"/>
     </row>
@@ -2783,19 +2855,43 @@
       </c>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="17"/>
-      <c r="Y28" s="14"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="6"/>
-      <c r="AB28" s="6"/>
-      <c r="AC28" s="6"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="S28" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="T28" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="U28" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="V28" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="W28" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA28" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB28" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC28" s="14" t="s">
+        <v>156</v>
+      </c>
       <c r="AD28" s="6"/>
       <c r="AE28" s="6"/>
     </row>
@@ -2839,19 +2935,43 @@
       </c>
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="7"/>
-      <c r="Z29" s="6"/>
-      <c r="AA29" s="6"/>
-      <c r="AB29" s="6"/>
-      <c r="AC29" s="6"/>
+      <c r="Q29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="R29" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="S29" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="T29" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="U29" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="V29" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="W29" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="X29" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y29" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z29" s="7"/>
+      <c r="AA29" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB29" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="AC29" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="AD29" s="6"/>
       <c r="AE29" s="6"/>
     </row>
@@ -2881,17 +3001,27 @@
       <c r="M30" s="6"/>
       <c r="N30" s="11"/>
       <c r="O30" s="11"/>
-      <c r="Q30" s="7"/>
+      <c r="Q30" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="20"/>
-      <c r="V30" s="20"/>
+      <c r="S30" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="T30" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U30" s="7"/>
+      <c r="V30" s="20" t="s">
+        <v>60</v>
+      </c>
       <c r="W30" s="20"/>
-      <c r="X30" s="6"/>
+      <c r="X30" s="7"/>
       <c r="Y30" s="7"/>
       <c r="Z30" s="11"/>
-      <c r="AA30" s="6"/>
+      <c r="AA30" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="AB30" s="11"/>
       <c r="AC30" s="6"/>
       <c r="AD30" s="11"/>
@@ -2920,10 +3050,10 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="20"/>
-      <c r="X31" s="6"/>
+      <c r="X31" s="7"/>
       <c r="Y31" s="7"/>
       <c r="Z31" s="11"/>
-      <c r="AA31" s="6"/>
+      <c r="AA31" s="7"/>
       <c r="AB31" s="6"/>
       <c r="AC31" s="6"/>
       <c r="AD31" s="6"/>
@@ -3092,9 +3222,7 @@
       <c r="Z35" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="AA35" s="7" t="s">
-        <v>178</v>
-      </c>
+      <c r="AA35" s="7"/>
       <c r="AB35" s="6"/>
       <c r="AC35" s="6"/>
       <c r="AD35" s="6"/>
@@ -3103,10 +3231,10 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>179</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>180</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>152</v>
@@ -3115,7 +3243,7 @@
         <v>8</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>154</v>
@@ -3133,14 +3261,16 @@
         <v>21</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M36" s="14" t="s">
         <v>156</v>
       </c>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="Q36" s="7"/>
+      <c r="Q36" s="20" t="s">
+        <v>90</v>
+      </c>
       <c r="R36" s="14" t="s">
         <v>150</v>
       </c>
@@ -3157,13 +3287,13 @@
         <v>153</v>
       </c>
       <c r="W36" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="X36" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="X36" s="9" t="s">
+      <c r="Y36" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="Y36" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="Z36" s="7" t="s">
         <v>177</v>
@@ -3181,19 +3311,19 @@
         <v>43</v>
       </c>
       <c r="B37" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="D37" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="E37" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="14" t="s">
-        <v>189</v>
-      </c>
       <c r="F37" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>165</v>
@@ -3235,13 +3365,15 @@
         <v>161</v>
       </c>
       <c r="W37" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="X37" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="X37" s="25" t="s">
+      <c r="Y37" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="Y37" s="6"/>
-      <c r="Z37" s="6"/>
+      <c r="Z37" s="7"/>
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
       <c r="AC37" s="6"/>
@@ -3287,8 +3419,10 @@
       <c r="U38" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="V38" s="7"/>
-      <c r="W38" s="7"/>
+      <c r="V38" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="W38" s="20"/>
       <c r="X38" s="20" t="s">
         <v>61</v>
       </c>
@@ -3326,7 +3460,7 @@
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
-      <c r="W39" s="7"/>
+      <c r="W39" s="20"/>
       <c r="X39" s="20"/>
       <c r="Y39" s="20"/>
       <c r="Z39" s="11"/>
@@ -3457,7 +3591,7 @@
         <v>177</v>
       </c>
       <c r="AA43" s="7" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -3488,7 +3622,9 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
-      <c r="Q44" s="7"/>
+      <c r="Q44" s="20" t="s">
+        <v>90</v>
+      </c>
       <c r="R44" s="14" t="s">
         <v>150</v>
       </c>
@@ -3505,13 +3641,13 @@
         <v>153</v>
       </c>
       <c r="W44" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="X44" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="X44" s="9" t="s">
+      <c r="Y44" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="Y44" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="Z44" s="7" t="s">
         <v>177</v>
@@ -3563,10 +3699,10 @@
         <v>161</v>
       </c>
       <c r="W45" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="X45" s="7" t="s">
         <v>190</v>
-      </c>
-      <c r="X45" s="7" t="s">
-        <v>191</v>
       </c>
       <c r="Y45" s="6"/>
       <c r="Z45" s="6"/>
@@ -3615,8 +3751,10 @@
       <c r="U46" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="V46" s="7"/>
-      <c r="W46" s="7"/>
+      <c r="V46" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="W46" s="20"/>
       <c r="X46" s="20" t="s">
         <v>61</v>
       </c>
@@ -3654,7 +3792,7 @@
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
-      <c r="W47" s="7"/>
+      <c r="W47" s="20"/>
       <c r="X47" s="20"/>
       <c r="Y47" s="20"/>
       <c r="Z47" s="11"/>
@@ -3706,42 +3844,18 @@
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
-      <c r="B50" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>128</v>
-      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
       <c r="Q50" s="7"/>
@@ -3776,42 +3890,18 @@
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
-      <c r="B51" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="L51" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="M51" s="19" t="s">
-        <v>149</v>
-      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
       <c r="Q51" s="7"/>
@@ -3848,42 +3938,18 @@
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
-      <c r="B52" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H52" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="I52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K52" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="L52" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="M52" s="16" t="s">
-        <v>102</v>
-      </c>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="Q52" s="7" t="s">
@@ -3892,7 +3958,7 @@
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="26"/>
+      <c r="U52" s="25"/>
       <c r="V52" s="6"/>
       <c r="W52" s="14" t="s">
         <v>6</v>
@@ -3919,45 +3985,19 @@
       <c r="AE52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="I53" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="J53" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="K53" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="L53" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="A53" s="7"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="6"/>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
       <c r="Q53" s="7"/>
@@ -3985,31 +4025,17 @@
       <c r="AE53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
-        <v>55</v>
-      </c>
+      <c r="A54" s="7"/>
       <c r="B54" s="7"/>
-      <c r="C54" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>59</v>
-      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="20"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="I54" s="21" t="s">
-        <v>114</v>
-      </c>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
       <c r="J54" s="11"/>
-      <c r="K54" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="K54" s="6"/>
       <c r="L54" s="11"/>
       <c r="M54" s="6"/>
       <c r="N54" s="11"/>
@@ -4560,17 +4586,17 @@
       <c r="U3" s="6"/>
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
-      <c r="X3" s="8" t="s">
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="Y3" s="7" t="s">
+      <c r="AA3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="Z3" s="8" t="s">
+      <c r="AB3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
       <c r="AC3" s="6"/>
       <c r="AD3" s="6"/>
       <c r="AE3" s="6"/>
@@ -4625,20 +4651,20 @@
       <c r="T4" s="7"/>
       <c r="U4" s="9"/>
       <c r="V4" s="6"/>
-      <c r="W4" s="6" t="s">
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="X4" s="9" t="s">
+      <c r="Z4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="Y4" s="7" t="s">
+      <c r="AA4" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AB4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
       <c r="AD4" s="6"/>
       <c r="AE4" s="6"/>
@@ -4690,15 +4716,15 @@
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="6" t="s">
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="X5" s="7" t="s">
+      <c r="Z5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="6"/>
@@ -5008,22 +5034,22 @@
         <v>84</v>
       </c>
       <c r="X11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y11" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z11" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="Y11" s="14" t="s">
+      <c r="AA11" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="Z11" s="14" t="s">
+      <c r="AB11" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AA11" s="14" t="s">
+      <c r="AC11" s="16" t="s">
         <v>87</v>
-      </c>
-      <c r="AB11" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="AC11" s="16" t="s">
-        <v>89</v>
       </c>
       <c r="AD11" s="6"/>
       <c r="AE11" s="6"/>
@@ -5089,23 +5115,23 @@
       <c r="W12" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="X12" s="17" t="s">
+      <c r="X12" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y12" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z12" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="Y12" s="14" t="s">
+      <c r="AA12" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="Z12" s="14" t="s">
+      <c r="AB12" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="AA12" s="14" t="s">
+      <c r="AC12" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="AB12" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC12" s="16" t="s">
-        <v>102</v>
       </c>
       <c r="AD12" s="6"/>
       <c r="AE12" s="6"/>
@@ -5172,19 +5198,19 @@
         <v>108</v>
       </c>
       <c r="X13" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y13" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="Z13" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="Y13" s="14" t="s">
+      <c r="AA13" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="Z13" s="14" t="s">
+      <c r="AB13" s="14" t="s">
         <v>111</v>
-      </c>
-      <c r="AA13" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="AB13" s="14" t="s">
-        <v>113</v>
       </c>
       <c r="AC13" s="6"/>
       <c r="AD13" s="6"/>
@@ -5434,9 +5460,7 @@
       <c r="F19" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="14" t="s">
-        <v>155</v>
-      </c>
+      <c r="G19" s="6"/>
       <c r="H19" s="14" t="s">
         <v>137</v>
       </c>
@@ -5516,7 +5540,9 @@
       <c r="F20" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="G20" s="6"/>
+      <c r="G20" s="14" t="s">
+        <v>155</v>
+      </c>
       <c r="H20" s="14" t="s">
         <v>138</v>
       </c>
@@ -5862,26 +5888,24 @@
       <c r="F27" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="6"/>
+      <c r="H27" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="I27" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H27" s="14" t="s">
+      <c r="J27" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="K27" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="L27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K27" s="7" t="s">
+      <c r="M27" s="7" t="s">
         <v>136</v>
-      </c>
-      <c r="L27" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="M27" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
@@ -5918,26 +5942,26 @@
       <c r="F28" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="I28" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="J28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="K28" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="L28" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K28" s="14" t="s">
+      <c r="M28" s="14" t="s">
         <v>21</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="M28" s="14" t="s">
-        <v>156</v>
       </c>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
@@ -5976,21 +6000,19 @@
       <c r="F29" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="6"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="J29" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="K29" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="J29" s="14" t="s">
+      <c r="L29" s="14" t="s">
         <v>168</v>
-      </c>
-      <c r="K29" s="6"/>
-      <c r="L29" s="14" t="s">
-        <v>169</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>43</v>
@@ -6251,7 +6273,7 @@
         <v>177</v>
       </c>
       <c r="AA35" s="7" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AB35" s="6"/>
       <c r="AC35" s="6"/>
@@ -6261,10 +6283,10 @@
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="7"/>
       <c r="B36" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>179</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>180</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>152</v>
@@ -6273,7 +6295,7 @@
         <v>8</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>154</v>
@@ -6291,7 +6313,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M36" s="14" t="s">
         <v>156</v>
@@ -6315,13 +6337,13 @@
         <v>153</v>
       </c>
       <c r="W36" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="X36" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="X36" s="9" t="s">
+      <c r="Y36" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="Y36" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="Z36" s="7" t="s">
         <v>177</v>
@@ -6339,19 +6361,19 @@
         <v>43</v>
       </c>
       <c r="B37" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="D37" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="E37" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="14" t="s">
-        <v>189</v>
-      </c>
       <c r="F37" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>165</v>
@@ -6393,10 +6415,10 @@
         <v>161</v>
       </c>
       <c r="W37" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="X37" s="26" t="s">
         <v>190</v>
-      </c>
-      <c r="X37" s="25" t="s">
-        <v>191</v>
       </c>
       <c r="Y37" s="6"/>
       <c r="Z37" s="6"/>
@@ -6615,7 +6637,7 @@
         <v>177</v>
       </c>
       <c r="AA43" s="7" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -6663,13 +6685,13 @@
         <v>153</v>
       </c>
       <c r="W44" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="X44" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="X44" s="9" t="s">
+      <c r="Y44" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="Y44" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="Z44" s="7" t="s">
         <v>177</v>
@@ -6721,10 +6743,10 @@
         <v>161</v>
       </c>
       <c r="W45" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="X45" s="7" t="s">
         <v>190</v>
-      </c>
-      <c r="X45" s="7" t="s">
-        <v>191</v>
       </c>
       <c r="Y45" s="6"/>
       <c r="Z45" s="6"/>
@@ -6864,42 +6886,18 @@
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="7"/>
-      <c r="B50" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>128</v>
-      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
       <c r="Q50" s="7"/>
@@ -6934,42 +6932,18 @@
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="7"/>
-      <c r="B51" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="L51" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="M51" s="19" t="s">
-        <v>149</v>
-      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
       <c r="Q51" s="7"/>
@@ -7006,42 +6980,18 @@
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="7"/>
-      <c r="B52" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F52" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G52" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H52" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="I52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="K52" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="L52" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="M52" s="16" t="s">
-        <v>102</v>
-      </c>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="Q52" s="7" t="s">
@@ -7050,7 +7000,7 @@
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="26"/>
+      <c r="U52" s="25"/>
       <c r="V52" s="6"/>
       <c r="W52" s="14" t="s">
         <v>6</v>
@@ -7077,45 +7027,19 @@
       <c r="AE52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F53" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="I53" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="J53" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="K53" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="L53" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>43</v>
-      </c>
+      <c r="A53" s="7"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="6"/>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
       <c r="Q53" s="7"/>
@@ -7143,31 +7067,17 @@
       <c r="AE53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
-        <v>55</v>
-      </c>
+      <c r="A54" s="7"/>
       <c r="B54" s="7"/>
-      <c r="C54" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>59</v>
-      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="20"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="I54" s="21" t="s">
-        <v>114</v>
-      </c>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
       <c r="J54" s="11"/>
-      <c r="K54" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="K54" s="6"/>
       <c r="L54" s="11"/>
       <c r="M54" s="6"/>
       <c r="N54" s="11"/>
@@ -8778,10 +8688,10 @@
       <c r="U20" s="27"/>
       <c r="V20" s="6"/>
       <c r="W20" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="X20" s="27" t="s">
         <v>183</v>
-      </c>
-      <c r="X20" s="27" t="s">
-        <v>184</v>
       </c>
       <c r="Y20" s="7"/>
       <c r="Z20" s="6" t="s">
@@ -8840,7 +8750,7 @@
       <c r="U21" s="6"/>
       <c r="V21" s="7"/>
       <c r="W21" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="X21" s="6"/>
       <c r="Y21" s="7"/>
@@ -14040,4 +13950,2318 @@
     <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:AF62"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="1" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="4.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="7.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="17" style="1" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="22" style="2" width="7.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="31" style="2" width="3.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="5"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="7"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="7"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="11"/>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="6"/>
+      <c r="AE6" s="11"/>
+      <c r="AF6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="11"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="5"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="R10" s="7"/>
+      <c r="S10" s="14"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="14"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="14"/>
+      <c r="X10" s="14"/>
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="14"/>
+      <c r="AD10" s="14"/>
+      <c r="AE10" s="14"/>
+      <c r="AF10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="R11" s="7"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="14"/>
+      <c r="X11" s="14"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="15"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="R12" s="7"/>
+      <c r="S12" s="14"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="14"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="14"/>
+      <c r="X12" s="14"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="14"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="R13" s="7"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="14"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+      <c r="AA14" s="11"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="11"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="11"/>
+      <c r="AF14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="11"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="6"/>
+      <c r="AF15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="5"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AF17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="7"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="7"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="19"/>
+      <c r="AD19" s="19"/>
+      <c r="AE19" s="6"/>
+      <c r="AF19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="14"/>
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="11"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="7"/>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="21"/>
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="11"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="11"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="11"/>
+      <c r="AF22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="21"/>
+      <c r="Z23" s="21"/>
+      <c r="AA23" s="11"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="5"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="18"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AF25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="7"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
+      <c r="V27" s="7"/>
+      <c r="W27" s="6"/>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="6"/>
+      <c r="AD27" s="6"/>
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="R28" s="20"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="6"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
+      <c r="V29" s="6"/>
+      <c r="W29" s="7"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="7"/>
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="6"/>
+      <c r="AD29" s="6"/>
+      <c r="AE29" s="6"/>
+      <c r="AF29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="11"/>
+      <c r="O30" s="11"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="7"/>
+      <c r="AA30" s="11"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="11"/>
+      <c r="AD30" s="6"/>
+      <c r="AE30" s="11"/>
+      <c r="AF30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="7"/>
+      <c r="AA31" s="11"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="5"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="4"/>
+      <c r="AC33" s="4"/>
+      <c r="AD33" s="4"/>
+      <c r="AE33" s="4"/>
+      <c r="AF33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="7"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="7"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
+      <c r="V35" s="7"/>
+      <c r="W35" s="7"/>
+      <c r="X35" s="14"/>
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="7"/>
+      <c r="AA35" s="7"/>
+      <c r="AB35" s="7"/>
+      <c r="AC35" s="6"/>
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="6"/>
+      <c r="AF35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="17"/>
+      <c r="W36" s="14"/>
+      <c r="X36" s="19"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="7"/>
+      <c r="AA36" s="7"/>
+      <c r="AB36" s="14"/>
+      <c r="AC36" s="6"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="6"/>
+      <c r="AF36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="24"/>
+      <c r="Y37" s="26"/>
+      <c r="Z37" s="6"/>
+      <c r="AA37" s="6"/>
+      <c r="AB37" s="6"/>
+      <c r="AC37" s="6"/>
+      <c r="AD37" s="6"/>
+      <c r="AE37" s="6"/>
+      <c r="AF37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="11"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="11"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="20"/>
+      <c r="AA38" s="11"/>
+      <c r="AB38" s="6"/>
+      <c r="AC38" s="11"/>
+      <c r="AD38" s="6"/>
+      <c r="AE38" s="11"/>
+      <c r="AF38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="11"/>
+      <c r="AB39" s="6"/>
+      <c r="AC39" s="6"/>
+      <c r="AD39" s="6"/>
+      <c r="AE39" s="6"/>
+      <c r="AF39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="22"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="13"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="5"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="4"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="4"/>
+      <c r="AF41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="7"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="7"/>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="6"/>
+      <c r="AF42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
+      <c r="V43" s="7"/>
+      <c r="W43" s="7"/>
+      <c r="X43" s="14"/>
+      <c r="Y43" s="14"/>
+      <c r="Z43" s="7"/>
+      <c r="AA43" s="7"/>
+      <c r="AB43" s="7"/>
+      <c r="AC43" s="6"/>
+      <c r="AD43" s="6"/>
+      <c r="AE43" s="6"/>
+      <c r="AF43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="14"/>
+      <c r="T44" s="14"/>
+      <c r="U44" s="14"/>
+      <c r="V44" s="17"/>
+      <c r="W44" s="14"/>
+      <c r="X44" s="19"/>
+      <c r="Y44" s="9"/>
+      <c r="Z44" s="7"/>
+      <c r="AA44" s="7"/>
+      <c r="AB44" s="14"/>
+      <c r="AC44" s="6"/>
+      <c r="AD44" s="6"/>
+      <c r="AE44" s="6"/>
+      <c r="AF44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="14"/>
+      <c r="T45" s="14"/>
+      <c r="U45" s="14"/>
+      <c r="V45" s="14"/>
+      <c r="W45" s="14"/>
+      <c r="X45" s="24"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="6"/>
+      <c r="AA45" s="6"/>
+      <c r="AB45" s="6"/>
+      <c r="AC45" s="6"/>
+      <c r="AD45" s="6"/>
+      <c r="AE45" s="6"/>
+      <c r="AF45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="20"/>
+      <c r="W46" s="20"/>
+      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
+      <c r="Z46" s="20"/>
+      <c r="AA46" s="11"/>
+      <c r="AB46" s="6"/>
+      <c r="AC46" s="11"/>
+      <c r="AD46" s="6"/>
+      <c r="AE46" s="11"/>
+      <c r="AF46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="20"/>
+      <c r="AA47" s="11"/>
+      <c r="AB47" s="6"/>
+      <c r="AC47" s="6"/>
+      <c r="AD47" s="6"/>
+      <c r="AE47" s="6"/>
+      <c r="AF47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="13"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="5"/>
+      <c r="R49" s="3"/>
+      <c r="X49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="7"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="7"/>
+      <c r="T50" s="7"/>
+      <c r="U50" s="7"/>
+      <c r="V50" s="6"/>
+      <c r="W50" s="6"/>
+      <c r="X50" s="14"/>
+      <c r="Y50" s="14"/>
+      <c r="Z50" s="14"/>
+      <c r="AA50" s="14"/>
+      <c r="AB50" s="14"/>
+      <c r="AC50" s="14"/>
+      <c r="AD50" s="7"/>
+      <c r="AE50" s="7"/>
+      <c r="AF50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+      <c r="U51" s="7"/>
+      <c r="V51" s="6"/>
+      <c r="W51" s="6"/>
+      <c r="X51" s="14"/>
+      <c r="Y51" s="14"/>
+      <c r="Z51" s="14"/>
+      <c r="AA51" s="14"/>
+      <c r="AB51" s="14"/>
+      <c r="AC51" s="14"/>
+      <c r="AD51" s="14"/>
+      <c r="AE51" s="7"/>
+      <c r="AF51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="R52" s="7"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
+      <c r="U52" s="7"/>
+      <c r="V52" s="25"/>
+      <c r="W52" s="6"/>
+      <c r="X52" s="14"/>
+      <c r="Y52" s="17"/>
+      <c r="Z52" s="14"/>
+      <c r="AA52" s="14"/>
+      <c r="AB52" s="14"/>
+      <c r="AC52" s="14"/>
+      <c r="AD52" s="14"/>
+      <c r="AE52" s="7"/>
+      <c r="AF52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="R53" s="7"/>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
+      <c r="U53" s="7"/>
+      <c r="V53" s="7"/>
+      <c r="W53" s="7"/>
+      <c r="X53" s="7"/>
+      <c r="Y53" s="14"/>
+      <c r="Z53" s="14"/>
+      <c r="AA53" s="14"/>
+      <c r="AB53" s="14"/>
+      <c r="AC53" s="7"/>
+      <c r="AD53" s="7"/>
+      <c r="AE53" s="7"/>
+      <c r="AF53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="R54" s="7"/>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
+      <c r="U54" s="7"/>
+      <c r="V54" s="7"/>
+      <c r="W54" s="7"/>
+      <c r="X54" s="7"/>
+      <c r="Y54" s="7"/>
+      <c r="Z54" s="7"/>
+      <c r="AA54" s="11"/>
+      <c r="AB54" s="6"/>
+      <c r="AC54" s="11"/>
+      <c r="AD54" s="6"/>
+      <c r="AE54" s="11"/>
+      <c r="AF54" s="11"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="R55" s="7"/>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
+      <c r="U55" s="7"/>
+      <c r="V55" s="7"/>
+      <c r="W55" s="7"/>
+      <c r="X55" s="7"/>
+      <c r="Y55" s="7"/>
+      <c r="Z55" s="7"/>
+      <c r="AA55" s="11"/>
+      <c r="AB55" s="6"/>
+      <c r="AC55" s="6"/>
+      <c r="AD55" s="6"/>
+      <c r="AE55" s="6"/>
+      <c r="AF55" s="6"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="186">
+    <mergeCell ref="N3:O4"/>
+    <mergeCell ref="AE3:AF4"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="AD5:AF5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:F7"/>
+    <mergeCell ref="G6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:O7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="W6:X7"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="AB6:AB7"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="N11:O12"/>
+    <mergeCell ref="AE11:AF12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="AD13:AF13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:F15"/>
+    <mergeCell ref="G14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="R14:R15"/>
+    <mergeCell ref="S14:S15"/>
+    <mergeCell ref="T14:T15"/>
+    <mergeCell ref="U14:U15"/>
+    <mergeCell ref="V14:V15"/>
+    <mergeCell ref="W14:X15"/>
+    <mergeCell ref="Y14:Y15"/>
+    <mergeCell ref="Z14:Z15"/>
+    <mergeCell ref="AB14:AB15"/>
+    <mergeCell ref="AE14:AF14"/>
+    <mergeCell ref="AE15:AF15"/>
+    <mergeCell ref="N19:O20"/>
+    <mergeCell ref="AE19:AF20"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="AD21:AF21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="N22:O22"/>
+    <mergeCell ref="R22:R23"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="U22:U23"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="W22:X23"/>
+    <mergeCell ref="Y22:Y23"/>
+    <mergeCell ref="Z22:Z23"/>
+    <mergeCell ref="AB22:AB23"/>
+    <mergeCell ref="AE22:AF22"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="AE23:AF23"/>
+    <mergeCell ref="N27:O28"/>
+    <mergeCell ref="AE27:AF28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="AD29:AF29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="R30:R31"/>
+    <mergeCell ref="S30:S31"/>
+    <mergeCell ref="T30:T31"/>
+    <mergeCell ref="U30:U31"/>
+    <mergeCell ref="V30:V31"/>
+    <mergeCell ref="W30:X31"/>
+    <mergeCell ref="Y30:Y31"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="AB30:AB31"/>
+    <mergeCell ref="AE30:AF30"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="AE31:AF31"/>
+    <mergeCell ref="N35:O36"/>
+    <mergeCell ref="AE35:AF36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="AD37:AF37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="R38:R39"/>
+    <mergeCell ref="S38:S39"/>
+    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="U38:U39"/>
+    <mergeCell ref="V38:V39"/>
+    <mergeCell ref="W38:X39"/>
+    <mergeCell ref="Y38:Y39"/>
+    <mergeCell ref="Z38:Z39"/>
+    <mergeCell ref="AB38:AB39"/>
+    <mergeCell ref="AE38:AF38"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="AE39:AF39"/>
+    <mergeCell ref="N43:O44"/>
+    <mergeCell ref="AE43:AF44"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="AD45:AF45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="R46:R47"/>
+    <mergeCell ref="S46:S47"/>
+    <mergeCell ref="T46:T47"/>
+    <mergeCell ref="U46:U47"/>
+    <mergeCell ref="V46:V47"/>
+    <mergeCell ref="W46:X47"/>
+    <mergeCell ref="Y46:Y47"/>
+    <mergeCell ref="Z46:Z47"/>
+    <mergeCell ref="AB46:AB47"/>
+    <mergeCell ref="AE46:AF46"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="AE47:AF47"/>
+    <mergeCell ref="N51:O52"/>
+    <mergeCell ref="AE51:AF52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="AD53:AF53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="R54:R55"/>
+    <mergeCell ref="S54:S55"/>
+    <mergeCell ref="T54:T55"/>
+    <mergeCell ref="U54:U55"/>
+    <mergeCell ref="V54:V55"/>
+    <mergeCell ref="W54:X55"/>
+    <mergeCell ref="Y54:Y55"/>
+    <mergeCell ref="Z54:Z55"/>
+    <mergeCell ref="AB54:AB55"/>
+    <mergeCell ref="AE54:AF54"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="AE55:AF55"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2405" uniqueCount="230">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -611,16 +611,19 @@
     <t xml:space="preserve">C+End</t>
   </si>
   <si>
+    <t xml:space="preserve">Layer1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">標準(改変なし)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">標準（ahk）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　</t>
+  </si>
+  <si>
     <t xml:space="preserve"> (F14 or 変換 or 無変換) 修飾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layer1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">標準(改変なし)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">標準（ahk）</t>
   </si>
   <si>
     <t xml:space="preserve">US</t>
@@ -2531,8 +2534,12 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
+      <c r="H22" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>2</v>
+      </c>
       <c r="J22" s="11"/>
       <c r="K22" s="7" t="s">
         <v>55</v>
@@ -2579,8 +2586,8 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
       <c r="J23" s="11"/>
       <c r="K23" s="7"/>
       <c r="L23" s="6"/>
@@ -2614,7 +2621,7 @@
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
+      <c r="K24" s="0"/>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
@@ -2991,8 +2998,12 @@
         <v>60</v>
       </c>
       <c r="G30" s="20"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
+      <c r="H30" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="14" t="s">
+        <v>2</v>
+      </c>
       <c r="J30" s="11"/>
       <c r="K30" s="7" t="s">
         <v>55</v>
@@ -3035,8 +3046,8 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="20"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
       <c r="J31" s="11"/>
       <c r="K31" s="7"/>
       <c r="L31" s="6"/>
@@ -3820,9 +3831,7 @@
       <c r="O48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
-        <v>195</v>
-      </c>
+      <c r="A49" s="3"/>
       <c r="B49" s="18"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -3838,26 +3847,56 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7"/>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
+      <c r="A50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
@@ -3889,20 +3928,48 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="6"/>
+      <c r="A51" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>21</v>
+      </c>
       <c r="O51" s="6"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7"/>
@@ -3937,19 +4004,45 @@
       <c r="AE51" s="7"/>
     </row>
     <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+      <c r="A52" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="Q52" s="7" t="s">
@@ -3985,19 +4078,45 @@
       <c r="AE52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="6"/>
+      <c r="A53" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
       <c r="Q53" s="7"/>
@@ -4025,19 +4144,39 @@
       <c r="AE53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="7"/>
+      <c r="A54" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="G54" s="7"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
+      <c r="H54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="J54" s="11"/>
-      <c r="K54" s="6"/>
+      <c r="K54" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="L54" s="11"/>
-      <c r="M54" s="6"/>
+      <c r="M54" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="N54" s="11"/>
       <c r="O54" s="11"/>
       <c r="Q54" s="7"/>
@@ -4065,16 +4204,22 @@
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="20"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
       <c r="J55" s="11"/>
       <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
+      <c r="L55" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="O55" s="6"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7"/>
@@ -4424,7 +4569,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AE62"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="1" style="1" width="7.66"/>
@@ -4437,7 +4582,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4850,7 +4995,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -5031,13 +5176,13 @@
         <v>83</v>
       </c>
       <c r="W11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="X11" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y11" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="X11" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y11" s="16" t="s">
-        <v>89</v>
       </c>
       <c r="Z11" s="14" t="s">
         <v>85</v>
@@ -5053,6 +5198,9 @@
       </c>
       <c r="AD11" s="6"/>
       <c r="AE11" s="6"/>
+      <c r="AH11" s="16" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
@@ -5113,13 +5261,13 @@
         <v>95</v>
       </c>
       <c r="W12" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="X12" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y12" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="X12" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y12" s="16" t="s">
-        <v>102</v>
       </c>
       <c r="Z12" s="17" t="s">
         <v>97</v>
@@ -5135,6 +5283,9 @@
       </c>
       <c r="AD12" s="6"/>
       <c r="AE12" s="6"/>
+      <c r="AH12" s="16" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
@@ -5195,13 +5346,13 @@
         <v>107</v>
       </c>
       <c r="W13" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="X13" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y13" s="14" t="s">
         <v>108</v>
-      </c>
-      <c r="X13" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="Y13" s="14" t="s">
-        <v>113</v>
       </c>
       <c r="Z13" s="14" t="s">
         <v>109</v>
@@ -5215,6 +5366,9 @@
       <c r="AC13" s="6"/>
       <c r="AD13" s="6"/>
       <c r="AE13" s="6"/>
+      <c r="AH13" s="14" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
@@ -5924,6 +6078,9 @@
       <c r="AC27" s="6"/>
       <c r="AD27" s="6"/>
       <c r="AE27" s="6"/>
+      <c r="AF27" s="2" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
@@ -6863,7 +7020,7 @@
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="4"/>
@@ -6880,7 +7037,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W49" s="1"/>
     </row>
@@ -7479,7 +7636,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -7496,7 +7653,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="5"/>
       <c r="Q1" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
@@ -7646,7 +7803,7 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O3" s="6"/>
       <c r="Q3" s="6" t="s">
@@ -7814,7 +7971,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -8163,7 +8320,7 @@
         <v>37</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O11" s="6"/>
       <c r="Q11" s="7"/>
@@ -8327,7 +8484,7 @@
         <v>52</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>43</v>
@@ -8520,40 +8677,40 @@
         <v>116</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L18" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M18" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>6</v>
@@ -8588,10 +8745,10 @@
         <v>131</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>8</v>
@@ -8736,7 +8893,7 @@
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>43</v>
@@ -8910,40 +9067,40 @@
     <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M26" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>6</v>
@@ -8976,10 +9133,10 @@
         <v>131</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>8</v>
@@ -9004,7 +9161,7 @@
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O27" s="6"/>
       <c r="Q27" s="7"/>
@@ -9114,7 +9271,7 @@
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>43</v>
@@ -9263,7 +9420,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -9283,40 +9440,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -9328,40 +9485,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -9375,10 +9532,10 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>8</v>
@@ -9403,7 +9560,7 @@
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
@@ -9416,10 +9573,10 @@
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V35" s="6" t="s">
         <v>8</v>
@@ -9561,7 +9718,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -9757,7 +9914,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -9831,12 +9988,12 @@
         <v>138</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -9844,14 +10001,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -9901,7 +10058,7 @@
       <c r="W44" s="6"/>
       <c r="X44" s="27"/>
       <c r="Y44" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -9925,7 +10082,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -9942,10 +10099,10 @@
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -10084,7 +10241,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10652,7 +10809,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10815,7 +10972,7 @@
         <v>37</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O3" s="6"/>
       <c r="Q3" s="7"/>
@@ -10979,7 +11136,7 @@
         <v>52</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>43</v>
@@ -11135,7 +11292,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -11277,7 +11434,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>14</v>
@@ -11462,7 +11619,7 @@
         <v>7</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>43</v>
@@ -11733,7 +11890,7 @@
         <v>4</v>
       </c>
       <c r="AD18" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AE18" s="6" t="s">
         <v>6</v>
@@ -12583,7 +12740,7 @@
       <c r="N33" s="4"/>
       <c r="O33" s="5"/>
       <c r="Q33" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="4"/>
@@ -12603,40 +12760,40 @@
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>6</v>
@@ -12648,40 +12805,40 @@
         <v>2</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="S34" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="U34" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y34" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AB34" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AC34" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
@@ -12695,10 +12852,10 @@
         <v>131</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>8</v>
@@ -12723,7 +12880,7 @@
       </c>
       <c r="M35" s="6"/>
       <c r="N35" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O35" s="6"/>
       <c r="Q35" s="7" t="s">
@@ -12736,10 +12893,10 @@
         <v>131</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U35" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="V35" s="6" t="s">
         <v>8</v>
@@ -12881,7 +13038,7 @@
       <c r="J37" s="7"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>43</v>
@@ -13077,7 +13234,7 @@
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
       <c r="Q41" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R41" s="18"/>
       <c r="S41" s="4"/>
@@ -13151,12 +13308,12 @@
         <v>138</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O43" s="6"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="S43" s="6"/>
       <c r="T43" s="6"/>
@@ -13164,14 +13321,14 @@
       <c r="V43" s="6"/>
       <c r="W43" s="6"/>
       <c r="X43" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y43" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
@@ -13221,7 +13378,7 @@
       <c r="W44" s="6"/>
       <c r="X44" s="27"/>
       <c r="Y44" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
@@ -13245,7 +13402,7 @@
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>43</v>
@@ -13262,10 +13419,10 @@
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -13404,7 +13561,7 @@
       <c r="N49" s="4"/>
       <c r="O49" s="5"/>
       <c r="Q49" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14234,7 +14391,7 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -14365,7 +14522,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -14629,7 +14786,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="14"/>
@@ -14838,7 +14995,7 @@
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="31" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2405" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2406" uniqueCount="230">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -2532,7 +2532,9 @@
         <v>58</v>
       </c>
       <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="F22" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="G22" s="7"/>
       <c r="H22" s="14" t="s">
         <v>2</v>
@@ -2621,7 +2623,7 @@
       <c r="H24" s="12"/>
       <c r="I24" s="12"/>
       <c r="J24" s="12"/>
-      <c r="K24" s="0"/>
+      <c r="K24" s="2"/>
       <c r="L24" s="12"/>
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="214">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -556,10 +556,7 @@
     <t xml:space="preserve">WhDn</t>
   </si>
   <si>
-    <t xml:space="preserve">Find-Next</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find-Prev</t>
+    <t xml:space="preserve">Prev</t>
   </si>
   <si>
     <t xml:space="preserve">Replace</t>
@@ -590,12 +587,6 @@
   </si>
   <si>
     <t xml:space="preserve">Paste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Num</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C+”-”</t>
   </si>
   <si>
     <t xml:space="preserve">Space &amp; F13 修飾</t>
@@ -649,10 +640,25 @@
     <t xml:space="preserve">＼</t>
   </si>
   <si>
+    <t xml:space="preserve">Find-Next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find-Prev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+”-”</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pn</t>
   </si>
   <si>
     <t xml:space="preserve">Kana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カスタマイズ後</t>
   </si>
   <si>
     <t xml:space="preserve">設定変更</t>
@@ -1017,15 +1023,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1041,7 +1039,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4469,67 +4475,67 @@
       <c r="BG33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7" t="s">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7" t="s">
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="6" t="s">
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="N34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="O34" s="6"/>
-      <c r="P34" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6" t="s">
+        <v>123</v>
+      </c>
       <c r="R34" s="6"/>
-      <c r="S34" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="T34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="U34" s="6"/>
-      <c r="V34" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="W34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6" t="s">
+        <v>125</v>
+      </c>
       <c r="X34" s="6"/>
-      <c r="Y34" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="Z34" s="7"/>
-      <c r="AA34" s="7"/>
-      <c r="AB34" s="6" t="s">
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="AC34" s="6"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="AD34" s="6"/>
-      <c r="AE34" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="AG34" s="6"/>
-      <c r="AH34" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AI34" s="6"/>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="AJ34" s="6"/>
-      <c r="AK34" s="6" t="s">
-        <v>129</v>
-      </c>
+      <c r="AK34" s="6"/>
       <c r="AL34" s="6"/>
       <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
@@ -4593,67 +4599,67 @@
       <c r="CI34" s="7"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="14" t="s">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="14" t="s">
         <v>143</v>
       </c>
+      <c r="D35" s="14"/>
       <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="s">
+      <c r="F35" s="14" t="s">
         <v>144</v>
       </c>
+      <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="26" t="s">
+      <c r="I35" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="14" t="s">
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="14" t="s">
-        <v>180</v>
-      </c>
+      <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
-      <c r="R35" s="14"/>
-      <c r="S35" s="14" t="s">
+      <c r="R35" s="14" t="s">
         <v>147</v>
       </c>
+      <c r="S35" s="14"/>
       <c r="T35" s="14"/>
-      <c r="U35" s="14"/>
-      <c r="V35" s="14" t="s">
+      <c r="U35" s="14" t="s">
         <v>6</v>
       </c>
+      <c r="V35" s="14"/>
       <c r="W35" s="14"/>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="7" t="s">
+      <c r="X35" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Z35" s="7"/>
-      <c r="AA35" s="7"/>
-      <c r="AB35" s="6" t="s">
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="6" t="s">
         <v>42</v>
       </c>
+      <c r="AB35" s="6"/>
       <c r="AC35" s="6"/>
-      <c r="AD35" s="6"/>
-      <c r="AE35" s="7" t="s">
+      <c r="AD35" s="7" t="s">
         <v>148</v>
       </c>
+      <c r="AE35" s="7"/>
       <c r="AF35" s="7"/>
-      <c r="AG35" s="7"/>
-      <c r="AH35" s="14" t="s">
+      <c r="AG35" s="14" t="s">
         <v>149</v>
       </c>
+      <c r="AH35" s="14"/>
       <c r="AI35" s="14"/>
-      <c r="AJ35" s="14"/>
-      <c r="AK35" s="14" t="s">
+      <c r="AJ35" s="14" t="s">
         <v>150</v>
       </c>
+      <c r="AK35" s="14"/>
       <c r="AL35" s="14"/>
       <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
@@ -4717,31 +4723,31 @@
       <c r="CI35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7"/>
+      <c r="A36" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
-      <c r="J36" s="14" t="s">
-        <v>156</v>
-      </c>
+      <c r="J36" s="14"/>
       <c r="K36" s="14"/>
       <c r="L36" s="14"/>
-      <c r="M36" s="9" t="s">
+      <c r="M36" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
       <c r="P36" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q36" s="14"/>
       <c r="R36" s="14"/>
@@ -4755,11 +4761,11 @@
       </c>
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
-      <c r="Y36" s="7" t="s">
+      <c r="Y36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="Z36" s="7"/>
-      <c r="AA36" s="7"/>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="6"/>
       <c r="AB36" s="6" t="s">
         <v>42</v>
       </c>
@@ -4771,7 +4777,7 @@
       <c r="AF36" s="14"/>
       <c r="AG36" s="14"/>
       <c r="AH36" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AI36" s="14"/>
       <c r="AJ36" s="14"/>
@@ -4779,11 +4785,11 @@
         <v>160</v>
       </c>
       <c r="AL36" s="14"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="6"/>
-      <c r="AO36" s="6"/>
-      <c r="AP36" s="6"/>
-      <c r="AQ36" s="6"/>
+      <c r="AM36" s="14"/>
+      <c r="AN36" s="10"/>
+      <c r="AO36" s="10"/>
+      <c r="AP36" s="10"/>
+      <c r="AQ36" s="10"/>
       <c r="AS36" s="7"/>
       <c r="AT36" s="7"/>
       <c r="AU36" s="7"/>
@@ -4846,63 +4852,63 @@
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="7"/>
+      <c r="E37" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14" t="s">
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14" t="s">
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="N37" s="14"/>
       <c r="O37" s="14"/>
-      <c r="P37" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14" t="s">
+        <v>184</v>
+      </c>
       <c r="R37" s="14"/>
-      <c r="S37" s="6" t="s">
+      <c r="S37" s="14"/>
+      <c r="T37" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="T37" s="6"/>
-      <c r="U37" s="6"/>
-      <c r="V37" s="7" t="s">
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="W37" s="7"/>
       <c r="X37" s="7"/>
-      <c r="Y37" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z37" s="14"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="14" t="s">
+        <v>170</v>
+      </c>
       <c r="AA37" s="14"/>
-      <c r="AB37" s="14" t="s">
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="6"/>
+      <c r="AD37" s="21"/>
+      <c r="AE37" s="21"/>
       <c r="AF37" s="6"/>
       <c r="AG37" s="6"/>
-      <c r="AH37" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="AI37" s="14"/>
-      <c r="AJ37" s="14"/>
+      <c r="AH37" s="6"/>
+      <c r="AI37" s="6"/>
+      <c r="AJ37" s="6"/>
       <c r="AK37" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AL37" s="6"/>
+      <c r="AL37" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="AM37" s="6"/>
       <c r="AN37" s="6"/>
       <c r="AO37" s="6"/>
@@ -4967,50 +4973,60 @@
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
+      <c r="E38" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="F38" s="7"/>
-      <c r="G38" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="I38" s="7"/>
-      <c r="J38" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="J38" s="7"/>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
-      <c r="N38" s="7"/>
+      <c r="N38" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="O38" s="7"/>
-      <c r="P38" s="27" t="s">
+      <c r="P38" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
-      <c r="V38" s="7"/>
-      <c r="W38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="W38" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
-      <c r="Z38" s="7"/>
+      <c r="Z38" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="AA38" s="7"/>
-      <c r="AB38" s="12"/>
-      <c r="AC38" s="12"/>
-      <c r="AD38" s="12"/>
-      <c r="AE38" s="7" t="s">
+      <c r="AB38" s="7"/>
+      <c r="AC38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD38" s="7"/>
+      <c r="AE38" s="7"/>
+      <c r="AF38" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="AF38" s="7"/>
       <c r="AG38" s="7"/>
-      <c r="AH38" s="12"/>
+      <c r="AH38" s="7"/>
       <c r="AI38" s="12"/>
       <c r="AJ38" s="12"/>
-      <c r="AK38" s="6"/>
+      <c r="AK38" s="12"/>
       <c r="AL38" s="6"/>
-      <c r="AM38" s="12"/>
-      <c r="AN38" s="12"/>
+      <c r="AM38" s="6"/>
+      <c r="AN38" s="6"/>
       <c r="AO38" s="12"/>
       <c r="AP38" s="12"/>
       <c r="AQ38" s="12"/>
@@ -5076,25 +5092,25 @@
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
       <c r="O39" s="7"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="27"/>
-      <c r="U39" s="27"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
-      <c r="AB39" s="12"/>
-      <c r="AC39" s="12"/>
-      <c r="AD39" s="12"/>
+      <c r="AB39" s="7"/>
+      <c r="AC39" s="7"/>
+      <c r="AD39" s="7"/>
       <c r="AE39" s="7"/>
       <c r="AF39" s="7"/>
       <c r="AG39" s="7"/>
-      <c r="AH39" s="6"/>
+      <c r="AH39" s="7"/>
       <c r="AI39" s="6"/>
       <c r="AJ39" s="6"/>
       <c r="AK39" s="6"/>
@@ -5155,50 +5171,50 @@
       <c r="CI39" s="24"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="AD40" s="29"/>
-      <c r="AE40" s="29"/>
-      <c r="AF40" s="29"/>
-      <c r="AG40" s="29"/>
-      <c r="AH40" s="29"/>
-      <c r="AI40" s="29"/>
-      <c r="AJ40" s="29"/>
-      <c r="AK40" s="29"/>
-      <c r="AL40" s="29"/>
-      <c r="AM40" s="29"/>
-      <c r="AN40" s="29"/>
-      <c r="AO40" s="29"/>
-      <c r="AP40" s="29"/>
-      <c r="AQ40" s="30"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+      <c r="W40" s="27"/>
+      <c r="X40" s="27"/>
+      <c r="Y40" s="27"/>
+      <c r="Z40" s="27"/>
+      <c r="AA40" s="27"/>
+      <c r="AB40" s="27"/>
+      <c r="AC40" s="27"/>
+      <c r="AD40" s="27"/>
+      <c r="AE40" s="27"/>
+      <c r="AF40" s="27"/>
+      <c r="AG40" s="27"/>
+      <c r="AH40" s="27"/>
+      <c r="AI40" s="27"/>
+      <c r="AJ40" s="27"/>
+      <c r="AK40" s="27"/>
+      <c r="AL40" s="27"/>
+      <c r="AM40" s="27"/>
+      <c r="AN40" s="27"/>
+      <c r="AO40" s="27"/>
+      <c r="AP40" s="27"/>
+      <c r="AQ40" s="28"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -5392,50 +5408,50 @@
       <c r="AQ43" s="6"/>
       <c r="AS43" s="7"/>
       <c r="AT43" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="AU43" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="AV43" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="AW43" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="AU43" s="7" t="s">
+      <c r="AX43" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="AV43" s="7" t="s">
+      <c r="AY43" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="AW43" s="6" t="s">
+      <c r="AZ43" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="AX43" s="6" t="s">
+      <c r="BA43" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="AY43" s="6" t="s">
+      <c r="BB43" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="AZ43" s="6" t="s">
+      <c r="BC43" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="BA43" s="7" t="s">
+      <c r="BD43" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="BB43" s="6" t="s">
+      <c r="BE43" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="BC43" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="BD43" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="BE43" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="BF43" s="6"/>
       <c r="BG43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -5452,7 +5468,7 @@
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="19" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="T44" s="19"/>
       <c r="U44" s="19"/>
@@ -5482,7 +5498,7 @@
       <c r="AO44" s="6"/>
       <c r="AP44" s="6"/>
       <c r="AQ44" s="6"/>
-      <c r="AS44" s="27" t="s">
+      <c r="AS44" s="29" t="s">
         <v>91</v>
       </c>
       <c r="AT44" s="14" t="s">
@@ -5542,7 +5558,7 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="19" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="T45" s="19"/>
       <c r="U45" s="19"/>
@@ -5622,14 +5638,14 @@
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
-      <c r="P46" s="27" t="s">
+      <c r="P46" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
       <c r="V46" s="6"/>
       <c r="W46" s="6"/>
       <c r="X46" s="6"/>
@@ -5664,17 +5680,17 @@
       <c r="AV46" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AW46" s="27" t="s">
+      <c r="AW46" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="AX46" s="27" t="s">
+      <c r="AX46" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="AY46" s="27"/>
-      <c r="AZ46" s="27" t="s">
+      <c r="AY46" s="29"/>
+      <c r="AZ46" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="BA46" s="27" t="s">
+      <c r="BA46" s="29" t="s">
         <v>115</v>
       </c>
       <c r="BB46" s="12"/>
@@ -5702,12 +5718,12 @@
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="27"/>
-      <c r="R47" s="27"/>
-      <c r="S47" s="27"/>
-      <c r="T47" s="27"/>
-      <c r="U47" s="27"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+      <c r="T47" s="29"/>
+      <c r="U47" s="29"/>
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
       <c r="X47" s="6"/>
@@ -5736,9 +5752,9 @@
       <c r="AV47" s="7"/>
       <c r="AW47" s="7"/>
       <c r="AX47" s="7"/>
-      <c r="AY47" s="27"/>
-      <c r="AZ47" s="27"/>
-      <c r="BA47" s="27"/>
+      <c r="AY47" s="29"/>
+      <c r="AZ47" s="29"/>
+      <c r="BA47" s="29"/>
       <c r="BB47" s="12"/>
       <c r="BC47" s="6"/>
       <c r="BD47" s="6"/>
@@ -5747,49 +5763,49 @@
       <c r="BG47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
-      <c r="W48" s="29"/>
-      <c r="X48" s="29"/>
-      <c r="Y48" s="29"/>
-      <c r="Z48" s="29"/>
-      <c r="AA48" s="29"/>
-      <c r="AB48" s="29"/>
-      <c r="AC48" s="29"/>
-      <c r="AD48" s="29"/>
-      <c r="AE48" s="29"/>
-      <c r="AF48" s="29"/>
-      <c r="AG48" s="29"/>
-      <c r="AH48" s="29"/>
-      <c r="AI48" s="29"/>
-      <c r="AJ48" s="29"/>
-      <c r="AK48" s="29"/>
-      <c r="AL48" s="29"/>
-      <c r="AM48" s="29"/>
-      <c r="AN48" s="29"/>
-      <c r="AO48" s="29"/>
-      <c r="AP48" s="29"/>
-      <c r="AQ48" s="30"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+      <c r="K48" s="27"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="27"/>
+      <c r="P48" s="27"/>
+      <c r="Q48" s="27"/>
+      <c r="R48" s="27"/>
+      <c r="S48" s="27"/>
+      <c r="T48" s="27"/>
+      <c r="U48" s="27"/>
+      <c r="V48" s="27"/>
+      <c r="W48" s="27"/>
+      <c r="X48" s="27"/>
+      <c r="Y48" s="27"/>
+      <c r="Z48" s="27"/>
+      <c r="AA48" s="27"/>
+      <c r="AB48" s="27"/>
+      <c r="AC48" s="27"/>
+      <c r="AD48" s="27"/>
+      <c r="AE48" s="27"/>
+      <c r="AF48" s="27"/>
+      <c r="AG48" s="27"/>
+      <c r="AH48" s="27"/>
+      <c r="AI48" s="27"/>
+      <c r="AJ48" s="27"/>
+      <c r="AK48" s="27"/>
+      <c r="AL48" s="27"/>
+      <c r="AM48" s="27"/>
+      <c r="AN48" s="27"/>
+      <c r="AO48" s="27"/>
+      <c r="AP48" s="27"/>
+      <c r="AQ48" s="28"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
@@ -5836,7 +5852,7 @@
       <c r="AP49" s="4"/>
       <c r="AQ49" s="5"/>
       <c r="AS49" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AY49" s="1"/>
     </row>
@@ -6124,7 +6140,7 @@
       <c r="AT52" s="7"/>
       <c r="AU52" s="7"/>
       <c r="AV52" s="7"/>
-      <c r="AW52" s="31"/>
+      <c r="AW52" s="30"/>
       <c r="AX52" s="6"/>
       <c r="AY52" s="14" t="s">
         <v>6</v>
@@ -6723,7 +6739,7 @@
       <c r="AR62" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="638">
+  <mergeCells count="695">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
@@ -7227,6 +7243,20 @@
     <mergeCell ref="CA31:CC31"/>
     <mergeCell ref="CD31:CF31"/>
     <mergeCell ref="CG31:CI31"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="T34:V34"/>
+    <mergeCell ref="W34:Y34"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="AF34:AH34"/>
+    <mergeCell ref="AI34:AK34"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AO34:AQ34"/>
     <mergeCell ref="AT34:AV34"/>
     <mergeCell ref="AW34:AY34"/>
     <mergeCell ref="AZ34:BB34"/>
@@ -7241,7 +7271,20 @@
     <mergeCell ref="CA34:CC34"/>
     <mergeCell ref="CD34:CF34"/>
     <mergeCell ref="CG34:CI34"/>
-    <mergeCell ref="AM35:AQ36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="U35:W35"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AG35:AI35"/>
+    <mergeCell ref="AJ35:AL35"/>
+    <mergeCell ref="AM35:AQ35"/>
     <mergeCell ref="AS35:AT35"/>
     <mergeCell ref="AU35:AW35"/>
     <mergeCell ref="AX35:AZ35"/>
@@ -7256,6 +7299,20 @@
     <mergeCell ref="BY35:CA35"/>
     <mergeCell ref="CB35:CD35"/>
     <mergeCell ref="CE35:CI35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="P36:R36"/>
+    <mergeCell ref="S36:U36"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AB36:AD36"/>
+    <mergeCell ref="AE36:AG36"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="AK36:AM36"/>
+    <mergeCell ref="AN36:AQ36"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="AV36:AX36"/>
     <mergeCell ref="AY36:BA36"/>
@@ -7270,7 +7327,19 @@
     <mergeCell ref="BZ36:CB36"/>
     <mergeCell ref="CC36:CE36"/>
     <mergeCell ref="CF36:CI36"/>
-    <mergeCell ref="AK37:AQ37"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="W37:Y37"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="AC37:AE37"/>
+    <mergeCell ref="AF37:AH37"/>
+    <mergeCell ref="AI37:AK37"/>
+    <mergeCell ref="AL37:AQ37"/>
     <mergeCell ref="AS37:AV37"/>
     <mergeCell ref="AW37:AY37"/>
     <mergeCell ref="AZ37:BB37"/>
@@ -7285,15 +7354,17 @@
     <mergeCell ref="CA37:CC37"/>
     <mergeCell ref="CD37:CI37"/>
     <mergeCell ref="A38:A39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="P38:S39"/>
-    <mergeCell ref="V38:V39"/>
-    <mergeCell ref="Y38:Y39"/>
-    <mergeCell ref="AE38:AE39"/>
-    <mergeCell ref="AM38:AQ38"/>
+    <mergeCell ref="B38:D39"/>
+    <mergeCell ref="E38:G39"/>
+    <mergeCell ref="H38:J39"/>
+    <mergeCell ref="K38:M39"/>
+    <mergeCell ref="N38:V39"/>
+    <mergeCell ref="W38:Y39"/>
+    <mergeCell ref="Z38:AB39"/>
+    <mergeCell ref="AC38:AE39"/>
+    <mergeCell ref="AF38:AH39"/>
+    <mergeCell ref="AI38:AK38"/>
+    <mergeCell ref="AL38:AN38"/>
     <mergeCell ref="AS38:AS39"/>
     <mergeCell ref="AT38:AV39"/>
     <mergeCell ref="AW38:AY39"/>
@@ -7306,7 +7377,9 @@
     <mergeCell ref="BX38:BZ39"/>
     <mergeCell ref="CA38:CC38"/>
     <mergeCell ref="CD38:CF38"/>
-    <mergeCell ref="AM39:AQ39"/>
+    <mergeCell ref="AI39:AK39"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AO39:AQ39"/>
     <mergeCell ref="CA39:CC39"/>
     <mergeCell ref="CD39:CF39"/>
     <mergeCell ref="CG39:CI39"/>
@@ -8306,7 +8379,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
@@ -10608,11 +10681,11 @@
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
-      <c r="J34" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
+      <c r="J34" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
       <c r="M34" s="6" t="s">
         <v>121</v>
       </c>
@@ -10732,18 +10805,18 @@
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
-      <c r="J35" s="26" t="s">
+      <c r="J35" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="14" t="s">
         <v>178</v>
-      </c>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="14" t="s">
-        <v>179</v>
       </c>
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
       <c r="P35" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q35" s="14"/>
       <c r="R35" s="14"/>
@@ -10847,12 +10920,12 @@
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
@@ -10867,7 +10940,7 @@
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
       <c r="P36" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q36" s="14"/>
       <c r="R36" s="14"/>
@@ -10897,7 +10970,7 @@
       <c r="AF36" s="14"/>
       <c r="AG36" s="14"/>
       <c r="AH36" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AI36" s="14"/>
       <c r="AJ36" s="14"/>
@@ -10973,27 +11046,27 @@
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
       <c r="D37" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="14"/>
       <c r="G37" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K37" s="14"/>
       <c r="L37" s="14"/>
       <c r="M37" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N37" s="14"/>
       <c r="O37" s="14"/>
       <c r="P37" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q37" s="14"/>
       <c r="R37" s="14"/>
@@ -11008,7 +11081,7 @@
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="14" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="Z37" s="14"/>
       <c r="AA37" s="14"/>
@@ -11021,7 +11094,7 @@
       <c r="AF37" s="6"/>
       <c r="AG37" s="6"/>
       <c r="AH37" s="14" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="AI37" s="14"/>
       <c r="AJ37" s="14"/>
@@ -11108,14 +11181,14 @@
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
       <c r="O38" s="7"/>
-      <c r="P38" s="27" t="s">
+      <c r="P38" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="29"/>
       <c r="V38" s="7"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
@@ -11202,12 +11275,12 @@
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
       <c r="O39" s="7"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="27"/>
-      <c r="U39" s="27"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="29"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
@@ -11281,50 +11354,50 @@
       <c r="CI39" s="24"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="AD40" s="29"/>
-      <c r="AE40" s="29"/>
-      <c r="AF40" s="29"/>
-      <c r="AG40" s="29"/>
-      <c r="AH40" s="29"/>
-      <c r="AI40" s="29"/>
-      <c r="AJ40" s="29"/>
-      <c r="AK40" s="29"/>
-      <c r="AL40" s="29"/>
-      <c r="AM40" s="29"/>
-      <c r="AN40" s="29"/>
-      <c r="AO40" s="29"/>
-      <c r="AP40" s="29"/>
-      <c r="AQ40" s="30"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+      <c r="W40" s="27"/>
+      <c r="X40" s="27"/>
+      <c r="Y40" s="27"/>
+      <c r="Z40" s="27"/>
+      <c r="AA40" s="27"/>
+      <c r="AB40" s="27"/>
+      <c r="AC40" s="27"/>
+      <c r="AD40" s="27"/>
+      <c r="AE40" s="27"/>
+      <c r="AF40" s="27"/>
+      <c r="AG40" s="27"/>
+      <c r="AH40" s="27"/>
+      <c r="AI40" s="27"/>
+      <c r="AJ40" s="27"/>
+      <c r="AK40" s="27"/>
+      <c r="AL40" s="27"/>
+      <c r="AM40" s="27"/>
+      <c r="AN40" s="27"/>
+      <c r="AO40" s="27"/>
+      <c r="AP40" s="27"/>
+      <c r="AQ40" s="28"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -11518,50 +11591,50 @@
       <c r="AQ43" s="6"/>
       <c r="AS43" s="7"/>
       <c r="AT43" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="AU43" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="AV43" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="AW43" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="AU43" s="7" t="s">
+      <c r="AX43" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="AV43" s="7" t="s">
+      <c r="AY43" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="AW43" s="6" t="s">
+      <c r="AZ43" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="AX43" s="6" t="s">
+      <c r="BA43" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="AY43" s="6" t="s">
+      <c r="BB43" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="AZ43" s="6" t="s">
+      <c r="BC43" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="BA43" s="7" t="s">
+      <c r="BD43" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="BB43" s="6" t="s">
+      <c r="BE43" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="BC43" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="BD43" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="BE43" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="BF43" s="6"/>
       <c r="BG43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -11578,7 +11651,7 @@
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="19" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="T44" s="19"/>
       <c r="U44" s="19"/>
@@ -11608,7 +11681,7 @@
       <c r="AO44" s="6"/>
       <c r="AP44" s="6"/>
       <c r="AQ44" s="6"/>
-      <c r="AS44" s="27" t="s">
+      <c r="AS44" s="29" t="s">
         <v>91</v>
       </c>
       <c r="AT44" s="14" t="s">
@@ -11668,7 +11741,7 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="19" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="T45" s="19"/>
       <c r="U45" s="19"/>
@@ -11748,14 +11821,14 @@
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
-      <c r="P46" s="27" t="s">
+      <c r="P46" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
       <c r="V46" s="6"/>
       <c r="W46" s="6"/>
       <c r="X46" s="6"/>
@@ -11790,17 +11863,17 @@
       <c r="AV46" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AW46" s="27" t="s">
+      <c r="AW46" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="AX46" s="27" t="s">
+      <c r="AX46" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="AY46" s="27"/>
-      <c r="AZ46" s="27" t="s">
+      <c r="AY46" s="29"/>
+      <c r="AZ46" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="BA46" s="27" t="s">
+      <c r="BA46" s="29" t="s">
         <v>115</v>
       </c>
       <c r="BB46" s="12"/>
@@ -11828,12 +11901,12 @@
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="27"/>
-      <c r="R47" s="27"/>
-      <c r="S47" s="27"/>
-      <c r="T47" s="27"/>
-      <c r="U47" s="27"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+      <c r="T47" s="29"/>
+      <c r="U47" s="29"/>
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
       <c r="X47" s="6"/>
@@ -11862,9 +11935,9 @@
       <c r="AV47" s="7"/>
       <c r="AW47" s="7"/>
       <c r="AX47" s="7"/>
-      <c r="AY47" s="27"/>
-      <c r="AZ47" s="27"/>
-      <c r="BA47" s="27"/>
+      <c r="AY47" s="29"/>
+      <c r="AZ47" s="29"/>
+      <c r="BA47" s="29"/>
       <c r="BB47" s="12"/>
       <c r="BC47" s="6"/>
       <c r="BD47" s="6"/>
@@ -11873,49 +11946,49 @@
       <c r="BG47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
-      <c r="W48" s="29"/>
-      <c r="X48" s="29"/>
-      <c r="Y48" s="29"/>
-      <c r="Z48" s="29"/>
-      <c r="AA48" s="29"/>
-      <c r="AB48" s="29"/>
-      <c r="AC48" s="29"/>
-      <c r="AD48" s="29"/>
-      <c r="AE48" s="29"/>
-      <c r="AF48" s="29"/>
-      <c r="AG48" s="29"/>
-      <c r="AH48" s="29"/>
-      <c r="AI48" s="29"/>
-      <c r="AJ48" s="29"/>
-      <c r="AK48" s="29"/>
-      <c r="AL48" s="29"/>
-      <c r="AM48" s="29"/>
-      <c r="AN48" s="29"/>
-      <c r="AO48" s="29"/>
-      <c r="AP48" s="29"/>
-      <c r="AQ48" s="30"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+      <c r="K48" s="27"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="27"/>
+      <c r="P48" s="27"/>
+      <c r="Q48" s="27"/>
+      <c r="R48" s="27"/>
+      <c r="S48" s="27"/>
+      <c r="T48" s="27"/>
+      <c r="U48" s="27"/>
+      <c r="V48" s="27"/>
+      <c r="W48" s="27"/>
+      <c r="X48" s="27"/>
+      <c r="Y48" s="27"/>
+      <c r="Z48" s="27"/>
+      <c r="AA48" s="27"/>
+      <c r="AB48" s="27"/>
+      <c r="AC48" s="27"/>
+      <c r="AD48" s="27"/>
+      <c r="AE48" s="27"/>
+      <c r="AF48" s="27"/>
+      <c r="AG48" s="27"/>
+      <c r="AH48" s="27"/>
+      <c r="AI48" s="27"/>
+      <c r="AJ48" s="27"/>
+      <c r="AK48" s="27"/>
+      <c r="AL48" s="27"/>
+      <c r="AM48" s="27"/>
+      <c r="AN48" s="27"/>
+      <c r="AO48" s="27"/>
+      <c r="AP48" s="27"/>
+      <c r="AQ48" s="28"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
@@ -11962,7 +12035,7 @@
       <c r="AP49" s="4"/>
       <c r="AQ49" s="5"/>
       <c r="AS49" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AY49" s="1"/>
     </row>
@@ -12250,7 +12323,7 @@
       <c r="AT52" s="7"/>
       <c r="AU52" s="7"/>
       <c r="AV52" s="7"/>
-      <c r="AW52" s="31"/>
+      <c r="AW52" s="30"/>
       <c r="AX52" s="6"/>
       <c r="AY52" s="14" t="s">
         <v>6</v>
@@ -13931,7 +14004,7 @@
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
       <c r="AR5" s="32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
@@ -13975,7 +14048,9 @@
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+      <c r="L6" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="M6" s="7" t="s">
         <v>60</v>
       </c>
@@ -13985,21 +14060,23 @@
       </c>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7" t="s">
+      <c r="R6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="S6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7" t="s">
+      <c r="T6" s="7"/>
+      <c r="U6" s="7" t="s">
         <v>61</v>
       </c>
+      <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
@@ -14170,7 +14247,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>211</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -14734,7 +14811,7 @@
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
       <c r="AR13" s="32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
@@ -14822,7 +14899,9 @@
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+      <c r="L14" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="M14" s="7" t="s">
         <v>60</v>
       </c>
@@ -14832,7 +14911,9 @@
       </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
+      <c r="R14" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="S14" s="7"/>
       <c r="T14" s="7" t="s">
         <v>60</v>
@@ -14843,10 +14924,10 @@
       </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -15193,6 +15274,9 @@
       <c r="AO18" s="6"/>
       <c r="AP18" s="6"/>
       <c r="AQ18" s="6"/>
+      <c r="AR18" s="6" t="s">
+        <v>149</v>
+      </c>
       <c r="AT18" s="6"/>
       <c r="AU18" s="6" t="s">
         <v>130</v>
@@ -15331,6 +15415,9 @@
       <c r="AO19" s="6"/>
       <c r="AP19" s="6"/>
       <c r="AQ19" s="6"/>
+      <c r="AR19" s="6" t="s">
+        <v>150</v>
+      </c>
       <c r="AT19" s="6"/>
       <c r="AU19" s="6"/>
       <c r="AV19" s="7"/>
@@ -15455,6 +15542,9 @@
       <c r="AO20" s="10"/>
       <c r="AP20" s="10"/>
       <c r="AQ20" s="10"/>
+      <c r="AR20" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="AT20" s="7"/>
       <c r="AU20" s="7"/>
       <c r="AV20" s="7"/>
@@ -15587,6 +15677,9 @@
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
+      <c r="AR21" s="32" t="s">
+        <v>209</v>
+      </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
       <c r="AV21" s="7"/>
@@ -15669,7 +15762,9 @@
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="L22" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="M22" s="7" t="s">
         <v>60</v>
       </c>
@@ -15679,7 +15774,9 @@
       </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
+      <c r="R22" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="S22" s="7"/>
       <c r="T22" s="7" t="s">
         <v>60</v>
@@ -15690,39 +15787,34 @@
       </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y22" s="7"/>
+        <v>210</v>
+      </c>
+      <c r="Y22" s="7" t="s">
+        <v>210</v>
+      </c>
       <c r="Z22" s="7"/>
-      <c r="AA22" s="7" t="s">
+      <c r="AA22" s="7"/>
+      <c r="AB22" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="AB22" s="7"/>
       <c r="AC22" s="7"/>
-      <c r="AD22" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AD22" s="7"/>
       <c r="AE22" s="7"/>
       <c r="AF22" s="7"/>
-      <c r="AG22" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="AG22" s="7"/>
       <c r="AH22" s="7"/>
       <c r="AI22" s="7"/>
-      <c r="AJ22" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="AJ22" s="7"/>
       <c r="AK22" s="7"/>
       <c r="AL22" s="7"/>
-      <c r="AM22" s="7" t="s">
-        <v>114</v>
-      </c>
+      <c r="AM22" s="7"/>
       <c r="AN22" s="7"/>
       <c r="AO22" s="7"/>
-      <c r="AP22" s="7" t="s">
+      <c r="AP22" s="7"/>
+      <c r="AQ22" s="7"/>
+      <c r="AR22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="AQ22" s="7"/>
       <c r="AT22" s="7" t="s">
         <v>55</v>
       </c>
@@ -15825,6 +15917,7 @@
       <c r="AO23" s="7"/>
       <c r="AP23" s="7"/>
       <c r="AQ23" s="7"/>
+      <c r="AR23" s="6"/>
       <c r="AT23" s="7"/>
       <c r="AU23" s="7"/>
       <c r="AV23" s="7"/>
@@ -16047,6 +16140,9 @@
       <c r="AO26" s="6"/>
       <c r="AP26" s="6"/>
       <c r="AQ26" s="6"/>
+      <c r="AR26" s="6" t="s">
+        <v>149</v>
+      </c>
       <c r="AT26" s="7"/>
       <c r="AU26" s="7"/>
       <c r="AV26" s="7"/>
@@ -16159,6 +16255,9 @@
       <c r="AO27" s="6"/>
       <c r="AP27" s="6"/>
       <c r="AQ27" s="6"/>
+      <c r="AR27" s="6" t="s">
+        <v>150</v>
+      </c>
       <c r="AT27" s="7"/>
       <c r="AU27" s="7"/>
       <c r="AV27" s="7"/>
@@ -16281,6 +16380,9 @@
       <c r="AO28" s="10"/>
       <c r="AP28" s="10"/>
       <c r="AQ28" s="10"/>
+      <c r="AR28" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="AT28" s="7"/>
       <c r="AU28" s="7"/>
       <c r="AV28" s="7"/>
@@ -16401,6 +16503,9 @@
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
+      <c r="AR29" s="32" t="s">
+        <v>209</v>
+      </c>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
       <c r="AV29" s="7"/>
@@ -16471,7 +16576,9 @@
       </c>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
+      <c r="L30" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="M30" s="7" t="s">
         <v>60</v>
       </c>
@@ -16481,7 +16588,9 @@
       </c>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
+      <c r="R30" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="S30" s="7"/>
       <c r="T30" s="7" t="s">
         <v>60</v>
@@ -16492,39 +16601,34 @@
       </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="Y30" s="7"/>
+        <v>210</v>
+      </c>
+      <c r="Y30" s="7" t="s">
+        <v>210</v>
+      </c>
       <c r="Z30" s="7"/>
-      <c r="AA30" s="7" t="s">
+      <c r="AA30" s="7"/>
+      <c r="AB30" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="AB30" s="7"/>
       <c r="AC30" s="7"/>
-      <c r="AD30" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="AD30" s="7"/>
       <c r="AE30" s="7"/>
       <c r="AF30" s="7"/>
-      <c r="AG30" s="7" t="s">
-        <v>41</v>
-      </c>
+      <c r="AG30" s="7"/>
       <c r="AH30" s="7"/>
       <c r="AI30" s="7"/>
-      <c r="AJ30" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="AJ30" s="7"/>
       <c r="AK30" s="7"/>
       <c r="AL30" s="7"/>
-      <c r="AM30" s="7" t="s">
-        <v>114</v>
-      </c>
+      <c r="AM30" s="7"/>
       <c r="AN30" s="7"/>
       <c r="AO30" s="7"/>
-      <c r="AP30" s="7" t="s">
+      <c r="AP30" s="7"/>
+      <c r="AQ30" s="7"/>
+      <c r="AR30" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="AQ30" s="7"/>
       <c r="AT30" s="7" t="s">
         <v>55</v>
       </c>
@@ -16567,7 +16671,7 @@
       </c>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="BR30" s="7"/>
       <c r="BS30" s="7"/>
@@ -16645,6 +16749,7 @@
       <c r="AO31" s="7"/>
       <c r="AP31" s="7"/>
       <c r="AQ31" s="7"/>
+      <c r="AR31" s="6"/>
       <c r="AT31" s="7"/>
       <c r="AU31" s="7"/>
       <c r="AV31" s="7"/>
@@ -16795,73 +16900,76 @@
       <c r="BH33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7" t="s">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7" t="s">
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="6" t="s">
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="N34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="O34" s="6"/>
-      <c r="P34" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6" t="s">
+        <v>123</v>
+      </c>
       <c r="R34" s="6"/>
-      <c r="S34" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="T34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="U34" s="6"/>
-      <c r="V34" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="W34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6" t="s">
+        <v>125</v>
+      </c>
       <c r="X34" s="6"/>
-      <c r="Y34" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="Z34" s="7"/>
-      <c r="AA34" s="7"/>
-      <c r="AB34" s="6" t="s">
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="AC34" s="6"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6" t="s">
+        <v>127</v>
+      </c>
       <c r="AD34" s="6"/>
-      <c r="AE34" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6" t="s">
+        <v>128</v>
+      </c>
       <c r="AG34" s="6"/>
-      <c r="AH34" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AI34" s="6"/>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="6" t="s">
+        <v>129</v>
+      </c>
       <c r="AJ34" s="6"/>
-      <c r="AK34" s="6" t="s">
-        <v>129</v>
-      </c>
+      <c r="AK34" s="6"/>
       <c r="AL34" s="6"/>
       <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
       <c r="AO34" s="6"/>
       <c r="AP34" s="6"/>
       <c r="AQ34" s="6"/>
+      <c r="AR34" s="6" t="s">
+        <v>149</v>
+      </c>
       <c r="AT34" s="7"/>
       <c r="AU34" s="7" t="s">
         <v>130</v>
@@ -16903,73 +17011,76 @@
       <c r="BH34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="14" t="s">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="14" t="s">
         <v>143</v>
       </c>
+      <c r="D35" s="14"/>
       <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="s">
+      <c r="F35" s="14" t="s">
         <v>144</v>
       </c>
+      <c r="G35" s="14"/>
       <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="26" t="s">
+      <c r="I35" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="14" t="s">
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="14" t="s">
-        <v>180</v>
-      </c>
+      <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
-      <c r="R35" s="14"/>
-      <c r="S35" s="14" t="s">
+      <c r="R35" s="14" t="s">
         <v>147</v>
       </c>
+      <c r="S35" s="14"/>
       <c r="T35" s="14"/>
-      <c r="U35" s="14"/>
-      <c r="V35" s="14" t="s">
+      <c r="U35" s="14" t="s">
         <v>6</v>
       </c>
+      <c r="V35" s="14"/>
       <c r="W35" s="14"/>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="7" t="s">
+      <c r="X35" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Z35" s="7"/>
-      <c r="AA35" s="7"/>
-      <c r="AB35" s="6" t="s">
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="6" t="s">
         <v>42</v>
       </c>
+      <c r="AB35" s="6"/>
       <c r="AC35" s="6"/>
-      <c r="AD35" s="6"/>
-      <c r="AE35" s="7" t="s">
+      <c r="AD35" s="7" t="s">
         <v>148</v>
       </c>
+      <c r="AE35" s="7"/>
       <c r="AF35" s="7"/>
-      <c r="AG35" s="7"/>
-      <c r="AH35" s="14" t="s">
+      <c r="AG35" s="14" t="s">
         <v>149</v>
       </c>
+      <c r="AH35" s="14"/>
       <c r="AI35" s="14"/>
-      <c r="AJ35" s="14"/>
-      <c r="AK35" s="14" t="s">
+      <c r="AJ35" s="14" t="s">
         <v>150</v>
       </c>
+      <c r="AK35" s="14"/>
       <c r="AL35" s="14"/>
       <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
       <c r="AP35" s="6"/>
       <c r="AQ35" s="6"/>
+      <c r="AR35" s="6" t="s">
+        <v>150</v>
+      </c>
       <c r="AT35" s="7"/>
       <c r="AU35" s="7"/>
       <c r="AV35" s="7"/>
@@ -16995,31 +17106,31 @@
       <c r="BH35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7"/>
+      <c r="A36" s="7" t="s">
+        <v>91</v>
+      </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
-      <c r="J36" s="14" t="s">
-        <v>156</v>
-      </c>
+      <c r="J36" s="14"/>
       <c r="K36" s="14"/>
       <c r="L36" s="14"/>
-      <c r="M36" s="9" t="s">
+      <c r="M36" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="N36" s="9"/>
-      <c r="O36" s="9"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
       <c r="P36" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q36" s="14"/>
       <c r="R36" s="14"/>
@@ -17033,11 +17144,11 @@
       </c>
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
-      <c r="Y36" s="7" t="s">
+      <c r="Y36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="Z36" s="7"/>
-      <c r="AA36" s="7"/>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="6"/>
       <c r="AB36" s="6" t="s">
         <v>42</v>
       </c>
@@ -17049,7 +17160,7 @@
       <c r="AF36" s="14"/>
       <c r="AG36" s="14"/>
       <c r="AH36" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AI36" s="14"/>
       <c r="AJ36" s="14"/>
@@ -17057,12 +17168,15 @@
         <v>160</v>
       </c>
       <c r="AL36" s="14"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="6"/>
-      <c r="AO36" s="6"/>
-      <c r="AP36" s="6"/>
-      <c r="AQ36" s="6"/>
-      <c r="AT36" s="27" t="s">
+      <c r="AM36" s="14"/>
+      <c r="AN36" s="10"/>
+      <c r="AO36" s="10"/>
+      <c r="AP36" s="10"/>
+      <c r="AQ36" s="10"/>
+      <c r="AR36" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AT36" s="29" t="s">
         <v>91</v>
       </c>
       <c r="AU36" s="14" t="s">
@@ -17106,68 +17220,71 @@
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="7"/>
+      <c r="E37" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14" t="s">
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14" t="s">
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="N37" s="14"/>
       <c r="O37" s="14"/>
-      <c r="P37" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14" t="s">
+        <v>184</v>
+      </c>
       <c r="R37" s="14"/>
-      <c r="S37" s="6" t="s">
+      <c r="S37" s="14"/>
+      <c r="T37" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="T37" s="6"/>
-      <c r="U37" s="6"/>
-      <c r="V37" s="7" t="s">
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="W37" s="7"/>
       <c r="X37" s="7"/>
-      <c r="Y37" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z37" s="14"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="14" t="s">
+        <v>170</v>
+      </c>
       <c r="AA37" s="14"/>
-      <c r="AB37" s="14" t="s">
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="6"/>
+      <c r="AD37" s="21"/>
+      <c r="AE37" s="21"/>
       <c r="AF37" s="6"/>
       <c r="AG37" s="6"/>
-      <c r="AH37" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="AI37" s="14"/>
-      <c r="AJ37" s="14"/>
+      <c r="AH37" s="6"/>
+      <c r="AI37" s="6"/>
+      <c r="AJ37" s="6"/>
       <c r="AK37" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AL37" s="6"/>
+      <c r="AL37" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="AM37" s="6"/>
       <c r="AN37" s="6"/>
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
+      <c r="AR37" s="32" t="s">
+        <v>209</v>
+      </c>
       <c r="AT37" s="7" t="s">
         <v>43</v>
       </c>
@@ -17206,56 +17323,77 @@
       <c r="A38" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
+      <c r="B38" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>57</v>
+      </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7" t="s">
-        <v>57</v>
-      </c>
+      <c r="F38" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" s="7"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7" t="s">
-        <v>58</v>
-      </c>
+      <c r="I38" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J38" s="7"/>
       <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
+      <c r="L38" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>60</v>
+      </c>
       <c r="N38" s="7"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="27" t="s">
+      <c r="O38" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
-      <c r="V38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="W38" s="7"/>
-      <c r="X38" s="7"/>
-      <c r="Y38" s="7"/>
+      <c r="X38" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y38" s="7" t="s">
+        <v>210</v>
+      </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
-      <c r="AB38" s="12"/>
-      <c r="AC38" s="12"/>
-      <c r="AD38" s="12"/>
-      <c r="AE38" s="7" t="s">
+      <c r="AB38" s="7" t="s">
         <v>55</v>
       </c>
+      <c r="AC38" s="7"/>
+      <c r="AD38" s="7"/>
+      <c r="AE38" s="7"/>
       <c r="AF38" s="7"/>
       <c r="AG38" s="7"/>
-      <c r="AH38" s="12"/>
-      <c r="AI38" s="12"/>
-      <c r="AJ38" s="12"/>
-      <c r="AK38" s="6"/>
-      <c r="AL38" s="6"/>
-      <c r="AM38" s="12"/>
-      <c r="AN38" s="12"/>
-      <c r="AO38" s="12"/>
-      <c r="AP38" s="12"/>
-      <c r="AQ38" s="12"/>
+      <c r="AH38" s="7"/>
+      <c r="AI38" s="7"/>
+      <c r="AJ38" s="7"/>
+      <c r="AK38" s="7"/>
+      <c r="AL38" s="7"/>
+      <c r="AM38" s="7"/>
+      <c r="AN38" s="7"/>
+      <c r="AO38" s="7"/>
+      <c r="AP38" s="7"/>
+      <c r="AQ38" s="7"/>
+      <c r="AR38" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="AT38" s="7" t="s">
         <v>55</v>
       </c>
@@ -17266,17 +17404,17 @@
       <c r="AW38" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AX38" s="27" t="s">
+      <c r="AX38" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="AY38" s="27" t="s">
+      <c r="AY38" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="AZ38" s="27"/>
-      <c r="BA38" s="27" t="s">
+      <c r="AZ38" s="29"/>
+      <c r="BA38" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="BB38" s="27" t="s">
+      <c r="BB38" s="29" t="s">
         <v>115</v>
       </c>
       <c r="BC38" s="12"/>
@@ -17304,43 +17442,44 @@
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
       <c r="O39" s="7"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="27"/>
-      <c r="U39" s="27"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
       <c r="AA39" s="7"/>
-      <c r="AB39" s="12"/>
-      <c r="AC39" s="12"/>
-      <c r="AD39" s="12"/>
+      <c r="AB39" s="7"/>
+      <c r="AC39" s="7"/>
+      <c r="AD39" s="7"/>
       <c r="AE39" s="7"/>
       <c r="AF39" s="7"/>
       <c r="AG39" s="7"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="6"/>
-      <c r="AO39" s="6"/>
-      <c r="AP39" s="6"/>
-      <c r="AQ39" s="6"/>
+      <c r="AH39" s="7"/>
+      <c r="AI39" s="7"/>
+      <c r="AJ39" s="7"/>
+      <c r="AK39" s="7"/>
+      <c r="AL39" s="7"/>
+      <c r="AM39" s="7"/>
+      <c r="AN39" s="7"/>
+      <c r="AO39" s="7"/>
+      <c r="AP39" s="7"/>
+      <c r="AQ39" s="7"/>
+      <c r="AR39" s="6"/>
       <c r="AT39" s="7"/>
       <c r="AU39" s="7"/>
       <c r="AV39" s="7"/>
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
-      <c r="AZ39" s="27"/>
-      <c r="BA39" s="27"/>
-      <c r="BB39" s="27"/>
+      <c r="AZ39" s="29"/>
+      <c r="BA39" s="29"/>
+      <c r="BB39" s="29"/>
       <c r="BC39" s="12"/>
       <c r="BD39" s="6"/>
       <c r="BE39" s="6"/>
@@ -17349,50 +17488,50 @@
       <c r="BH39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
-      <c r="AA40" s="29"/>
-      <c r="AB40" s="29"/>
-      <c r="AC40" s="29"/>
-      <c r="AD40" s="29"/>
-      <c r="AE40" s="29"/>
-      <c r="AF40" s="29"/>
-      <c r="AG40" s="29"/>
-      <c r="AH40" s="29"/>
-      <c r="AI40" s="29"/>
-      <c r="AJ40" s="29"/>
-      <c r="AK40" s="29"/>
-      <c r="AL40" s="29"/>
-      <c r="AM40" s="29"/>
-      <c r="AN40" s="29"/>
-      <c r="AO40" s="29"/>
-      <c r="AP40" s="29"/>
-      <c r="AQ40" s="30"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+      <c r="W40" s="27"/>
+      <c r="X40" s="27"/>
+      <c r="Y40" s="27"/>
+      <c r="Z40" s="27"/>
+      <c r="AA40" s="27"/>
+      <c r="AB40" s="27"/>
+      <c r="AC40" s="27"/>
+      <c r="AD40" s="27"/>
+      <c r="AE40" s="27"/>
+      <c r="AF40" s="27"/>
+      <c r="AG40" s="27"/>
+      <c r="AH40" s="27"/>
+      <c r="AI40" s="27"/>
+      <c r="AJ40" s="27"/>
+      <c r="AK40" s="27"/>
+      <c r="AL40" s="27"/>
+      <c r="AM40" s="27"/>
+      <c r="AN40" s="27"/>
+      <c r="AO40" s="27"/>
+      <c r="AP40" s="27"/>
+      <c r="AQ40" s="28"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -17586,50 +17725,50 @@
       <c r="AQ43" s="6"/>
       <c r="AT43" s="7"/>
       <c r="AU43" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="AV43" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="AW43" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="AX43" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="AV43" s="7" t="s">
+      <c r="AY43" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="AW43" s="7" t="s">
+      <c r="AZ43" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="AX43" s="6" t="s">
+      <c r="BA43" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="AY43" s="6" t="s">
+      <c r="BB43" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="AZ43" s="6" t="s">
+      <c r="BC43" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="BA43" s="6" t="s">
+      <c r="BD43" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="BB43" s="7" t="s">
+      <c r="BE43" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="BC43" s="6" t="s">
+      <c r="BF43" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="BD43" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="BE43" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="BF43" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="BG43" s="6"/>
       <c r="BH43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="27" t="s">
+      <c r="A44" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -17646,7 +17785,7 @@
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="19" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="T44" s="19"/>
       <c r="U44" s="19"/>
@@ -17676,7 +17815,7 @@
       <c r="AO44" s="6"/>
       <c r="AP44" s="6"/>
       <c r="AQ44" s="6"/>
-      <c r="AT44" s="27" t="s">
+      <c r="AT44" s="29" t="s">
         <v>91</v>
       </c>
       <c r="AU44" s="14" t="s">
@@ -17736,7 +17875,7 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="S45" s="19" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="T45" s="19"/>
       <c r="U45" s="19"/>
@@ -17816,14 +17955,14 @@
       <c r="M46" s="7"/>
       <c r="N46" s="7"/>
       <c r="O46" s="7"/>
-      <c r="P46" s="27" t="s">
+      <c r="P46" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
       <c r="V46" s="6"/>
       <c r="W46" s="6"/>
       <c r="X46" s="6"/>
@@ -17858,17 +17997,17 @@
       <c r="AW46" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="AX46" s="27" t="s">
+      <c r="AX46" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="AY46" s="27" t="s">
+      <c r="AY46" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="AZ46" s="27"/>
-      <c r="BA46" s="27" t="s">
+      <c r="AZ46" s="29"/>
+      <c r="BA46" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="BB46" s="27" t="s">
+      <c r="BB46" s="29" t="s">
         <v>115</v>
       </c>
       <c r="BC46" s="12"/>
@@ -17896,12 +18035,12 @@
       <c r="M47" s="7"/>
       <c r="N47" s="7"/>
       <c r="O47" s="7"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="27"/>
-      <c r="R47" s="27"/>
-      <c r="S47" s="27"/>
-      <c r="T47" s="27"/>
-      <c r="U47" s="27"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+      <c r="T47" s="29"/>
+      <c r="U47" s="29"/>
       <c r="V47" s="6"/>
       <c r="W47" s="6"/>
       <c r="X47" s="6"/>
@@ -17930,9 +18069,9 @@
       <c r="AW47" s="7"/>
       <c r="AX47" s="7"/>
       <c r="AY47" s="7"/>
-      <c r="AZ47" s="27"/>
-      <c r="BA47" s="27"/>
-      <c r="BB47" s="27"/>
+      <c r="AZ47" s="29"/>
+      <c r="BA47" s="29"/>
+      <c r="BB47" s="29"/>
       <c r="BC47" s="12"/>
       <c r="BD47" s="6"/>
       <c r="BE47" s="6"/>
@@ -17941,49 +18080,49 @@
       <c r="BH47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29"/>
-      <c r="P48" s="29"/>
-      <c r="Q48" s="29"/>
-      <c r="R48" s="29"/>
-      <c r="S48" s="29"/>
-      <c r="T48" s="29"/>
-      <c r="U48" s="29"/>
-      <c r="V48" s="29"/>
-      <c r="W48" s="29"/>
-      <c r="X48" s="29"/>
-      <c r="Y48" s="29"/>
-      <c r="Z48" s="29"/>
-      <c r="AA48" s="29"/>
-      <c r="AB48" s="29"/>
-      <c r="AC48" s="29"/>
-      <c r="AD48" s="29"/>
-      <c r="AE48" s="29"/>
-      <c r="AF48" s="29"/>
-      <c r="AG48" s="29"/>
-      <c r="AH48" s="29"/>
-      <c r="AI48" s="29"/>
-      <c r="AJ48" s="29"/>
-      <c r="AK48" s="29"/>
-      <c r="AL48" s="29"/>
-      <c r="AM48" s="29"/>
-      <c r="AN48" s="29"/>
-      <c r="AO48" s="29"/>
-      <c r="AP48" s="29"/>
-      <c r="AQ48" s="30"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+      <c r="K48" s="27"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="27"/>
+      <c r="P48" s="27"/>
+      <c r="Q48" s="27"/>
+      <c r="R48" s="27"/>
+      <c r="S48" s="27"/>
+      <c r="T48" s="27"/>
+      <c r="U48" s="27"/>
+      <c r="V48" s="27"/>
+      <c r="W48" s="27"/>
+      <c r="X48" s="27"/>
+      <c r="Y48" s="27"/>
+      <c r="Z48" s="27"/>
+      <c r="AA48" s="27"/>
+      <c r="AB48" s="27"/>
+      <c r="AC48" s="27"/>
+      <c r="AD48" s="27"/>
+      <c r="AE48" s="27"/>
+      <c r="AF48" s="27"/>
+      <c r="AG48" s="27"/>
+      <c r="AH48" s="27"/>
+      <c r="AI48" s="27"/>
+      <c r="AJ48" s="27"/>
+      <c r="AK48" s="27"/>
+      <c r="AL48" s="27"/>
+      <c r="AM48" s="27"/>
+      <c r="AN48" s="27"/>
+      <c r="AO48" s="27"/>
+      <c r="AP48" s="27"/>
+      <c r="AQ48" s="28"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
@@ -18030,7 +18169,7 @@
       <c r="AP49" s="4"/>
       <c r="AQ49" s="5"/>
       <c r="AT49" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AZ49" s="1"/>
     </row>
@@ -18318,7 +18457,7 @@
       <c r="AU52" s="7"/>
       <c r="AV52" s="7"/>
       <c r="AW52" s="7"/>
-      <c r="AX52" s="31"/>
+      <c r="AX52" s="30"/>
       <c r="AY52" s="6"/>
       <c r="AZ52" s="14" t="s">
         <v>6</v>
@@ -18924,7 +19063,7 @@
       <c r="AS62" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="569">
+  <mergeCells count="624">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="H2:J2"/>
@@ -18987,7 +19126,7 @@
     <mergeCell ref="F6:H7"/>
     <mergeCell ref="I6:K7"/>
     <mergeCell ref="L6:Q7"/>
-    <mergeCell ref="R6:X7"/>
+    <mergeCell ref="R6:W7"/>
     <mergeCell ref="Y6:AA7"/>
     <mergeCell ref="AB6:AD7"/>
     <mergeCell ref="AE6:AG7"/>
@@ -19257,14 +19396,14 @@
     <mergeCell ref="F22:H23"/>
     <mergeCell ref="I22:K23"/>
     <mergeCell ref="L22:Q23"/>
-    <mergeCell ref="R22:W23"/>
-    <mergeCell ref="X22:Z23"/>
-    <mergeCell ref="AA22:AC23"/>
-    <mergeCell ref="AD22:AF23"/>
-    <mergeCell ref="AG22:AI23"/>
-    <mergeCell ref="AJ22:AL23"/>
-    <mergeCell ref="AM22:AO23"/>
-    <mergeCell ref="AP22:AQ23"/>
+    <mergeCell ref="R22:X23"/>
+    <mergeCell ref="Y22:AA23"/>
+    <mergeCell ref="AB22:AD23"/>
+    <mergeCell ref="AE22:AG23"/>
+    <mergeCell ref="AH22:AJ23"/>
+    <mergeCell ref="AK22:AM23"/>
+    <mergeCell ref="AN22:AQ23"/>
+    <mergeCell ref="AR22:AR23"/>
     <mergeCell ref="AT22:AT23"/>
     <mergeCell ref="AU22:AW23"/>
     <mergeCell ref="AX22:AZ23"/>
@@ -19395,14 +19534,14 @@
     <mergeCell ref="F30:H31"/>
     <mergeCell ref="I30:K31"/>
     <mergeCell ref="L30:Q31"/>
-    <mergeCell ref="R30:W31"/>
-    <mergeCell ref="X30:Z31"/>
-    <mergeCell ref="AA30:AC31"/>
-    <mergeCell ref="AD30:AF31"/>
-    <mergeCell ref="AG30:AI31"/>
-    <mergeCell ref="AJ30:AL31"/>
-    <mergeCell ref="AM30:AO31"/>
-    <mergeCell ref="AP30:AQ31"/>
+    <mergeCell ref="R30:X31"/>
+    <mergeCell ref="Y30:AA31"/>
+    <mergeCell ref="AB30:AD31"/>
+    <mergeCell ref="AE30:AG31"/>
+    <mergeCell ref="AH30:AJ31"/>
+    <mergeCell ref="AK30:AM31"/>
+    <mergeCell ref="AN30:AQ31"/>
+    <mergeCell ref="AR30:AR31"/>
     <mergeCell ref="AT30:AU31"/>
     <mergeCell ref="AV30:AX31"/>
     <mergeCell ref="AY30:BA31"/>
@@ -19416,20 +19555,76 @@
     <mergeCell ref="CC30:CE31"/>
     <mergeCell ref="CF30:CH31"/>
     <mergeCell ref="CI30:CJ31"/>
-    <mergeCell ref="AM35:AQ36"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="T34:V34"/>
+    <mergeCell ref="W34:Y34"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="AF34:AH34"/>
+    <mergeCell ref="AI34:AK34"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AO34:AQ34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="U35:W35"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AG35:AI35"/>
+    <mergeCell ref="AJ35:AL35"/>
+    <mergeCell ref="AM35:AQ35"/>
     <mergeCell ref="BG35:BH36"/>
-    <mergeCell ref="AK37:AQ37"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="P36:R36"/>
+    <mergeCell ref="S36:U36"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AB36:AD36"/>
+    <mergeCell ref="AE36:AG36"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="AK36:AM36"/>
+    <mergeCell ref="AN36:AQ36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="W37:Y37"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="AC37:AE37"/>
+    <mergeCell ref="AF37:AH37"/>
+    <mergeCell ref="AI37:AK37"/>
+    <mergeCell ref="AL37:AQ37"/>
     <mergeCell ref="BF37:BH37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="M38:M39"/>
-    <mergeCell ref="P38:S39"/>
-    <mergeCell ref="V38:V39"/>
-    <mergeCell ref="Y38:Y39"/>
-    <mergeCell ref="AE38:AE39"/>
-    <mergeCell ref="AM38:AQ38"/>
+    <mergeCell ref="A38:B39"/>
+    <mergeCell ref="C38:E39"/>
+    <mergeCell ref="F38:H39"/>
+    <mergeCell ref="I38:K39"/>
+    <mergeCell ref="L38:Q39"/>
+    <mergeCell ref="R38:X39"/>
+    <mergeCell ref="Y38:AA39"/>
+    <mergeCell ref="AB38:AD39"/>
+    <mergeCell ref="AE38:AG39"/>
+    <mergeCell ref="AH38:AJ39"/>
+    <mergeCell ref="AK38:AM39"/>
+    <mergeCell ref="AN38:AQ39"/>
+    <mergeCell ref="AR38:AR39"/>
     <mergeCell ref="AT38:AT39"/>
     <mergeCell ref="AU38:AU39"/>
     <mergeCell ref="AV38:AV39"/>
@@ -19440,7 +19635,6 @@
     <mergeCell ref="BB38:BB39"/>
     <mergeCell ref="BD38:BD39"/>
     <mergeCell ref="BG38:BH38"/>
-    <mergeCell ref="AM39:AQ39"/>
     <mergeCell ref="BG39:BH39"/>
     <mergeCell ref="AM43:AQ44"/>
     <mergeCell ref="BG43:BH44"/>
@@ -19787,7 +19981,7 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -19901,24 +20095,24 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="30"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="27"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="27"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -20182,7 +20376,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="32" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="14"/>
@@ -20296,20 +20490,20 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="30"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="28"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4"/>
@@ -20391,7 +20585,7 @@
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="34" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -20410,7 +20604,7 @@
       <c r="AF19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="27"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -20493,7 +20687,7 @@
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="27"/>
+      <c r="V22" s="29"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
       <c r="Y22" s="35"/>
@@ -20525,8 +20719,8 @@
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
       <c r="X23" s="7"/>
       <c r="Y23" s="35"/>
       <c r="Z23" s="35"/>
@@ -20539,20 +20733,20 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="30"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="28"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
@@ -20666,7 +20860,7 @@
       <c r="M28" s="14"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="R28" s="27"/>
+      <c r="R28" s="29"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -20720,8 +20914,8 @@
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="12"/>
@@ -20734,9 +20928,9 @@
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="27"/>
-      <c r="W30" s="27"/>
-      <c r="X30" s="27"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="12"/>
@@ -20753,7 +20947,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="27"/>
+      <c r="G31" s="29"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="12"/>
@@ -20768,7 +20962,7 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="27"/>
+      <c r="X31" s="29"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="7"/>
       <c r="AA31" s="12"/>
@@ -20780,20 +20974,20 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="30"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="28"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
@@ -20831,7 +21025,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="25"/>
+      <c r="D34" s="31"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -20863,7 +21057,7 @@
       <c r="A35" s="7"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
-      <c r="D35" s="26"/>
+      <c r="D35" s="25"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
       <c r="G35" s="14"/>
@@ -20907,7 +21101,7 @@
       <c r="M36" s="14"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="R36" s="27"/>
+      <c r="R36" s="29"/>
       <c r="S36" s="14"/>
       <c r="T36" s="14"/>
       <c r="U36" s="14"/>
@@ -20961,8 +21155,8 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="12"/>
@@ -20975,11 +21169,11 @@
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
-      <c r="V38" s="27"/>
-      <c r="W38" s="27"/>
-      <c r="X38" s="27"/>
-      <c r="Y38" s="27"/>
-      <c r="Z38" s="27"/>
+      <c r="V38" s="29"/>
+      <c r="W38" s="29"/>
+      <c r="X38" s="29"/>
+      <c r="Y38" s="29"/>
+      <c r="Z38" s="29"/>
       <c r="AA38" s="12"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="12"/>
@@ -20994,7 +21188,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="27"/>
+      <c r="G39" s="29"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="12"/>
@@ -21009,9 +21203,9 @@
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
-      <c r="X39" s="27"/>
-      <c r="Y39" s="27"/>
-      <c r="Z39" s="27"/>
+      <c r="X39" s="29"/>
+      <c r="Y39" s="29"/>
+      <c r="Z39" s="29"/>
       <c r="AA39" s="12"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
@@ -21020,20 +21214,20 @@
       <c r="AF39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="28"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="30"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="27"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="28"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="16"/>
@@ -21132,7 +21326,7 @@
       <c r="AF43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="27"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -21147,7 +21341,7 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
-      <c r="R44" s="27"/>
+      <c r="R44" s="29"/>
       <c r="S44" s="14"/>
       <c r="T44" s="14"/>
       <c r="U44" s="14"/>
@@ -21201,8 +21395,8 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
       <c r="J46" s="12"/>
@@ -21215,11 +21409,11 @@
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
-      <c r="X46" s="27"/>
-      <c r="Y46" s="27"/>
-      <c r="Z46" s="27"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+      <c r="X46" s="29"/>
+      <c r="Y46" s="29"/>
+      <c r="Z46" s="29"/>
       <c r="AA46" s="12"/>
       <c r="AB46" s="6"/>
       <c r="AC46" s="12"/>
@@ -21234,7 +21428,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="27"/>
+      <c r="G47" s="29"/>
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
       <c r="J47" s="12"/>
@@ -21249,9 +21443,9 @@
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
-      <c r="X47" s="27"/>
-      <c r="Y47" s="27"/>
-      <c r="Z47" s="27"/>
+      <c r="X47" s="29"/>
+      <c r="Y47" s="29"/>
+      <c r="Z47" s="29"/>
       <c r="AA47" s="12"/>
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
@@ -21260,21 +21454,21 @@
       <c r="AF47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="30"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+      <c r="K48" s="27"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="28"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
@@ -21379,7 +21573,7 @@
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
-      <c r="V52" s="31"/>
+      <c r="V52" s="30"/>
       <c r="W52" s="6"/>
       <c r="X52" s="14"/>
       <c r="Y52" s="15"/>
@@ -21428,7 +21622,7 @@
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="27"/>
+      <c r="E54" s="29"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
       <c r="H54" s="35"/>
@@ -21460,8 +21654,8 @@
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
       <c r="G55" s="7"/>
       <c r="H55" s="35"/>
       <c r="I55" s="35"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="198">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -457,6 +457,12 @@
     <t xml:space="preserve">SC+→</t>
   </si>
   <si>
+    <t xml:space="preserve">C+Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+End</t>
+  </si>
+  <si>
     <t xml:space="preserve">C+a</t>
   </si>
   <si>
@@ -505,10 +511,10 @@
     <t xml:space="preserve">C+←</t>
   </si>
   <si>
-    <t xml:space="preserve">10Key</t>
+    <t xml:space="preserve">Mouse</t>
   </si>
   <si>
-    <t xml:space="preserve">Mouse</t>
+    <t xml:space="preserve">10Key</t>
   </si>
   <si>
     <t xml:space="preserve">S+End</t>
@@ -945,12 +951,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3325,12 +3331,16 @@
       </c>
       <c r="BW19" s="18"/>
       <c r="BX19" s="18"/>
-      <c r="BY19" s="7"/>
-      <c r="BZ19" s="7"/>
-      <c r="CA19" s="7"/>
-      <c r="CB19" s="7"/>
-      <c r="CC19" s="7"/>
-      <c r="CD19" s="7"/>
+      <c r="BY19" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="BZ19" s="19"/>
+      <c r="CA19" s="19"/>
+      <c r="CB19" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="CC19" s="10"/>
+      <c r="CD19" s="10"/>
       <c r="CE19" s="6"/>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
@@ -3344,32 +3354,32 @@
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
       <c r="G20" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
       <c r="P20" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
       <c r="S20" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
@@ -3394,12 +3404,12 @@
       <c r="AF20" s="13"/>
       <c r="AG20" s="13"/>
       <c r="AH20" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI20" s="13"/>
       <c r="AJ20" s="13"/>
       <c r="AK20" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL20" s="13"/>
       <c r="AM20" s="13"/>
@@ -3411,42 +3421,42 @@
       <c r="AT20" s="7"/>
       <c r="AU20" s="7"/>
       <c r="AV20" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AW20" s="13"/>
       <c r="AX20" s="13"/>
       <c r="AY20" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AZ20" s="13"/>
       <c r="BA20" s="13"/>
       <c r="BB20" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BC20" s="13"/>
       <c r="BD20" s="13"/>
       <c r="BE20" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF20" s="13"/>
       <c r="BG20" s="13"/>
       <c r="BH20" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BI20" s="13"/>
       <c r="BJ20" s="13"/>
-      <c r="BK20" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="BL20" s="20"/>
-      <c r="BM20" s="20"/>
+      <c r="BK20" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="BL20" s="19"/>
+      <c r="BM20" s="19"/>
       <c r="BN20" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BO20" s="8"/>
       <c r="BP20" s="8"/>
       <c r="BQ20" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BR20" s="6"/>
       <c r="BS20" s="6"/>
@@ -3479,53 +3489,55 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
       <c r="Q21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R21" s="13"/>
       <c r="S21" s="13"/>
       <c r="T21" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
-      <c r="Z21" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA21" s="13"/>
-      <c r="AB21" s="13"/>
+      <c r="Z21" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA21" s="7"/>
+      <c r="AB21" s="7"/>
       <c r="AC21" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD21" s="21"/>
       <c r="AE21" s="21"/>
-      <c r="AF21" s="6"/>
-      <c r="AG21" s="6"/>
-      <c r="AH21" s="6"/>
+      <c r="AF21" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG21" s="13"/>
+      <c r="AH21" s="13"/>
       <c r="AI21" s="6"/>
       <c r="AJ21" s="6"/>
       <c r="AK21" s="6" t="s">
@@ -3544,43 +3556,45 @@
       <c r="AU21" s="7"/>
       <c r="AV21" s="7"/>
       <c r="AW21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AX21" s="13"/>
       <c r="AY21" s="13"/>
       <c r="AZ21" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BA21" s="13"/>
       <c r="BB21" s="13"/>
       <c r="BC21" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BD21" s="13"/>
       <c r="BE21" s="13"/>
       <c r="BF21" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BG21" s="13"/>
       <c r="BH21" s="13"/>
       <c r="BI21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BJ21" s="13"/>
       <c r="BK21" s="13"/>
       <c r="BL21" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM21" s="10"/>
       <c r="BN21" s="10"/>
       <c r="BO21" s="18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BP21" s="18"/>
       <c r="BQ21" s="18"/>
-      <c r="BR21" s="7"/>
-      <c r="BS21" s="7"/>
-      <c r="BT21" s="7"/>
+      <c r="BR21" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="BS21" s="18"/>
+      <c r="BT21" s="18"/>
       <c r="BU21" s="7"/>
       <c r="BV21" s="7"/>
       <c r="BW21" s="7"/>
@@ -3856,7 +3870,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -3900,9 +3914,6 @@
       <c r="AO25" s="4"/>
       <c r="AP25" s="4"/>
       <c r="AQ25" s="5"/>
-      <c r="AR25" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AS25" s="15"/>
       <c r="AT25" s="15"/>
       <c r="AU25" s="4"/>
@@ -4117,12 +4128,12 @@
       <c r="BH27" s="7"/>
       <c r="BI27" s="7"/>
       <c r="BJ27" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BK27" s="7"/>
       <c r="BL27" s="7"/>
       <c r="BM27" s="22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BN27" s="22"/>
       <c r="BO27" s="22"/>
@@ -4132,7 +4143,7 @@
       <c r="BQ27" s="7"/>
       <c r="BR27" s="7"/>
       <c r="BS27" s="22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BT27" s="22"/>
       <c r="BU27" s="22"/>
@@ -4158,32 +4169,32 @@
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
-      <c r="M28" s="19" t="s">
+      <c r="M28" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
       <c r="P28" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
       <c r="S28" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
@@ -4208,12 +4219,12 @@
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
       <c r="AH28" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI28" s="13"/>
       <c r="AJ28" s="13"/>
       <c r="AK28" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL28" s="13"/>
       <c r="AM28" s="13"/>
@@ -4240,7 +4251,7 @@
       <c r="BI28" s="7"/>
       <c r="BJ28" s="7"/>
       <c r="BK28" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BL28" s="7"/>
       <c r="BM28" s="7"/>
@@ -4281,53 +4292,55 @@
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="H29" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
       <c r="K29" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
       <c r="N29" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
       <c r="Q29" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R29" s="13"/>
       <c r="S29" s="13"/>
       <c r="T29" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
       <c r="W29" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
-      <c r="Z29" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA29" s="13"/>
-      <c r="AB29" s="13"/>
+      <c r="Z29" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA29" s="7"/>
+      <c r="AB29" s="7"/>
       <c r="AC29" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD29" s="21"/>
       <c r="AE29" s="21"/>
-      <c r="AF29" s="6"/>
-      <c r="AG29" s="6"/>
-      <c r="AH29" s="6"/>
+      <c r="AF29" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG29" s="13"/>
+      <c r="AH29" s="13"/>
       <c r="AI29" s="6"/>
       <c r="AJ29" s="6"/>
       <c r="AK29" s="6" t="s">
@@ -4361,7 +4374,7 @@
       <c r="BJ29" s="7"/>
       <c r="BK29" s="7"/>
       <c r="BL29" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BM29" s="7"/>
       <c r="BN29" s="7"/>
@@ -4489,7 +4502,7 @@
       <c r="CB30" s="11"/>
       <c r="CC30" s="11"/>
       <c r="CD30" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="CE30" s="6"/>
       <c r="CF30" s="6"/>
@@ -4576,17 +4589,17 @@
       <c r="BY31" s="7"/>
       <c r="BZ31" s="7"/>
       <c r="CA31" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="CB31" s="6"/>
       <c r="CC31" s="6"/>
       <c r="CD31" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="CE31" s="6"/>
       <c r="CF31" s="6"/>
       <c r="CG31" s="24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="CH31" s="24"/>
       <c r="CI31" s="24"/>
@@ -4635,6 +4648,8 @@
       <c r="AO32" s="12"/>
       <c r="AP32" s="12"/>
       <c r="AQ32" s="12"/>
+      <c r="AS32" s="12"/>
+      <c r="AT32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
@@ -4680,8 +4695,8 @@
       <c r="AO33" s="4"/>
       <c r="AP33" s="4"/>
       <c r="AQ33" s="5"/>
-      <c r="AS33" s="3"/>
-      <c r="AT33" s="15"/>
+      <c r="AS33" s="4"/>
+      <c r="AT33" s="5"/>
       <c r="AU33" s="4"/>
       <c r="AV33" s="4"/>
       <c r="AW33" s="4"/>
@@ -4709,7 +4724,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
@@ -4834,17 +4849,17 @@
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
       <c r="L35" s="25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
       <c r="O35" s="13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
@@ -4951,30 +4966,30 @@
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
       <c r="G36" s="13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
-      <c r="M36" s="19" t="s">
+      <c r="M36" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
       <c r="P36" s="13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
       <c r="S36" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
@@ -4999,12 +5014,12 @@
       <c r="AF36" s="13"/>
       <c r="AG36" s="13"/>
       <c r="AH36" s="13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AI36" s="13"/>
       <c r="AJ36" s="13"/>
       <c r="AK36" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL36" s="13"/>
       <c r="AM36" s="13"/>
@@ -5076,53 +5091,55 @@
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
       <c r="H37" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
       <c r="K37" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L37" s="13"/>
       <c r="M37" s="13"/>
       <c r="N37" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
       <c r="Q37" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="R37" s="13"/>
       <c r="S37" s="13"/>
       <c r="T37" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
       <c r="W37" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
-      <c r="Z37" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA37" s="13"/>
-      <c r="AB37" s="13"/>
+      <c r="Z37" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA37" s="7"/>
+      <c r="AB37" s="7"/>
       <c r="AC37" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD37" s="21"/>
       <c r="AE37" s="21"/>
-      <c r="AF37" s="6"/>
-      <c r="AG37" s="6"/>
-      <c r="AH37" s="6"/>
+      <c r="AF37" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG37" s="13"/>
+      <c r="AH37" s="13"/>
       <c r="AI37" s="6"/>
       <c r="AJ37" s="6"/>
       <c r="AK37" s="6" t="s">
@@ -5428,7 +5445,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -5773,32 +5790,32 @@
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E44" s="13"/>
       <c r="F44" s="13"/>
       <c r="G44" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
       <c r="J44" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K44" s="13"/>
       <c r="L44" s="13"/>
-      <c r="M44" s="19" t="s">
+      <c r="M44" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N44" s="19"/>
-      <c r="O44" s="19"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
       <c r="P44" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q44" s="13"/>
       <c r="R44" s="13"/>
       <c r="S44" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="6"/>
@@ -5823,12 +5840,12 @@
       <c r="AF44" s="13"/>
       <c r="AG44" s="13"/>
       <c r="AH44" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI44" s="13"/>
       <c r="AJ44" s="13"/>
       <c r="AK44" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL44" s="13"/>
       <c r="AM44" s="13"/>
@@ -5842,32 +5859,32 @@
       <c r="AT44" s="7"/>
       <c r="AU44" s="7"/>
       <c r="AV44" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AW44" s="13"/>
       <c r="AX44" s="13"/>
       <c r="AY44" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="BC44" s="13"/>
       <c r="BD44" s="13"/>
-      <c r="BE44" s="19" t="s">
+      <c r="BE44" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="BF44" s="19"/>
-      <c r="BG44" s="19"/>
+      <c r="BF44" s="20"/>
+      <c r="BG44" s="20"/>
       <c r="BH44" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BI44" s="13"/>
       <c r="BJ44" s="13"/>
       <c r="BK44" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="BL44" s="6"/>
       <c r="BM44" s="6"/>
@@ -5892,12 +5909,12 @@
       <c r="BX44" s="13"/>
       <c r="BY44" s="13"/>
       <c r="BZ44" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="CA44" s="13"/>
       <c r="CB44" s="13"/>
       <c r="CC44" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="CD44" s="13"/>
       <c r="CE44" s="13"/>
@@ -5914,53 +5931,55 @@
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
       <c r="H45" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
       <c r="K45" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L45" s="13"/>
       <c r="M45" s="13"/>
       <c r="N45" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O45" s="13"/>
       <c r="P45" s="13"/>
       <c r="Q45" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R45" s="13"/>
       <c r="S45" s="13"/>
       <c r="T45" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
       <c r="W45" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
-      <c r="Z45" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA45" s="13"/>
-      <c r="AB45" s="13"/>
+      <c r="Z45" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA45" s="7"/>
+      <c r="AB45" s="7"/>
       <c r="AC45" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD45" s="21"/>
       <c r="AE45" s="21"/>
-      <c r="AF45" s="6"/>
-      <c r="AG45" s="6"/>
-      <c r="AH45" s="6"/>
+      <c r="AF45" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="AG45" s="13"/>
+      <c r="AH45" s="13"/>
       <c r="AI45" s="6"/>
       <c r="AJ45" s="6"/>
       <c r="AK45" s="6" t="s">
@@ -5981,53 +6000,55 @@
       <c r="AU45" s="7"/>
       <c r="AV45" s="7"/>
       <c r="AW45" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
       <c r="AZ45" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
       <c r="BC45" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BD45" s="13"/>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BG45" s="13"/>
       <c r="BH45" s="13"/>
       <c r="BI45" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BJ45" s="13"/>
       <c r="BK45" s="13"/>
       <c r="BL45" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BM45" s="7"/>
       <c r="BN45" s="7"/>
       <c r="BO45" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BP45" s="7"/>
       <c r="BQ45" s="7"/>
-      <c r="BR45" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="BS45" s="13"/>
-      <c r="BT45" s="13"/>
+      <c r="BR45" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="BS45" s="7"/>
+      <c r="BT45" s="7"/>
       <c r="BU45" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="BV45" s="21"/>
       <c r="BW45" s="21"/>
-      <c r="BX45" s="6"/>
-      <c r="BY45" s="6"/>
-      <c r="BZ45" s="6"/>
+      <c r="BX45" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="BY45" s="13"/>
+      <c r="BZ45" s="13"/>
       <c r="CA45" s="6"/>
       <c r="CB45" s="6"/>
       <c r="CC45" s="6" t="s">
@@ -8424,8 +8445,8 @@
       <c r="CI7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0"/>
-      <c r="B8" s="0"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
@@ -8469,8 +8490,8 @@
       <c r="AQ8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0"/>
-      <c r="B9" s="0"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
         <v>57</v>
       </c>
@@ -8650,7 +8671,7 @@
       <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
@@ -8744,7 +8765,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
@@ -9413,7 +9434,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>108</v>
@@ -9619,7 +9640,7 @@
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -9674,7 +9695,7 @@
       <c r="CC19" s="7"/>
       <c r="CD19" s="7"/>
       <c r="CE19" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
@@ -9688,32 +9709,32 @@
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
       <c r="G20" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
       <c r="P20" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
       <c r="S20" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
@@ -9738,7 +9759,7 @@
       <c r="AF20" s="13"/>
       <c r="AG20" s="13"/>
       <c r="AH20" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI20" s="13"/>
       <c r="AJ20" s="13"/>
@@ -9755,42 +9776,42 @@
       <c r="AT20" s="7"/>
       <c r="AU20" s="7"/>
       <c r="AV20" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AW20" s="13"/>
       <c r="AX20" s="13"/>
       <c r="AY20" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AZ20" s="13"/>
       <c r="BA20" s="13"/>
       <c r="BB20" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BC20" s="13"/>
       <c r="BD20" s="13"/>
       <c r="BE20" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BF20" s="13"/>
       <c r="BG20" s="13"/>
       <c r="BH20" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BI20" s="13"/>
       <c r="BJ20" s="13"/>
-      <c r="BK20" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="BL20" s="20"/>
-      <c r="BM20" s="20"/>
+      <c r="BK20" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="BL20" s="19"/>
+      <c r="BM20" s="19"/>
       <c r="BN20" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BO20" s="8"/>
       <c r="BP20" s="8"/>
       <c r="BQ20" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BR20" s="6"/>
       <c r="BS20" s="6"/>
@@ -9825,47 +9846,47 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
       <c r="Q21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R21" s="13"/>
       <c r="S21" s="13"/>
       <c r="T21" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AA21" s="13"/>
       <c r="AB21" s="13"/>
       <c r="AC21" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD21" s="21"/>
       <c r="AE21" s="21"/>
@@ -9892,37 +9913,37 @@
       <c r="AU21" s="7"/>
       <c r="AV21" s="7"/>
       <c r="AW21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AX21" s="13"/>
       <c r="AY21" s="13"/>
       <c r="AZ21" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BA21" s="13"/>
       <c r="BB21" s="13"/>
       <c r="BC21" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BD21" s="13"/>
       <c r="BE21" s="13"/>
       <c r="BF21" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BG21" s="13"/>
       <c r="BH21" s="13"/>
       <c r="BI21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BJ21" s="13"/>
       <c r="BK21" s="13"/>
       <c r="BL21" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM21" s="10"/>
       <c r="BN21" s="10"/>
       <c r="BO21" s="18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BP21" s="18"/>
       <c r="BQ21" s="18"/>
@@ -10208,7 +10229,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -10455,7 +10476,7 @@
       <c r="AK27" s="13"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -10479,12 +10500,12 @@
       <c r="BH27" s="7"/>
       <c r="BI27" s="7"/>
       <c r="BJ27" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BK27" s="7"/>
       <c r="BL27" s="7"/>
       <c r="BM27" s="22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BN27" s="22"/>
       <c r="BO27" s="22"/>
@@ -10494,7 +10515,7 @@
       <c r="BQ27" s="7"/>
       <c r="BR27" s="7"/>
       <c r="BS27" s="22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BT27" s="22"/>
       <c r="BU27" s="22"/>
@@ -10508,7 +10529,7 @@
       <c r="CC27" s="7"/>
       <c r="CD27" s="7"/>
       <c r="CE27" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CF27" s="6"/>
       <c r="CG27" s="6"/>
@@ -10522,32 +10543,32 @@
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
-      <c r="M28" s="19" t="s">
+      <c r="M28" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
       <c r="P28" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
       <c r="S28" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
@@ -10572,7 +10593,7 @@
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
       <c r="AH28" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI28" s="13"/>
       <c r="AJ28" s="13"/>
@@ -10604,7 +10625,7 @@
       <c r="BI28" s="7"/>
       <c r="BJ28" s="7"/>
       <c r="BK28" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BL28" s="7"/>
       <c r="BM28" s="7"/>
@@ -10647,47 +10668,47 @@
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="H29" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
       <c r="K29" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
       <c r="N29" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
       <c r="Q29" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R29" s="13"/>
       <c r="S29" s="13"/>
       <c r="T29" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
       <c r="W29" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AA29" s="13"/>
       <c r="AB29" s="13"/>
       <c r="AC29" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD29" s="21"/>
       <c r="AE29" s="21"/>
@@ -10729,7 +10750,7 @@
       <c r="BJ29" s="7"/>
       <c r="BK29" s="7"/>
       <c r="BL29" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BM29" s="7"/>
       <c r="BN29" s="7"/>
@@ -10869,7 +10890,7 @@
       <c r="CB30" s="11"/>
       <c r="CC30" s="11"/>
       <c r="CD30" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="CE30" s="6"/>
       <c r="CF30" s="6"/>
@@ -10964,17 +10985,17 @@
       <c r="BY31" s="7"/>
       <c r="BZ31" s="7"/>
       <c r="CA31" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="CB31" s="6"/>
       <c r="CC31" s="6"/>
       <c r="CD31" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="CE31" s="6"/>
       <c r="CF31" s="6"/>
       <c r="CG31" s="24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="CH31" s="24"/>
       <c r="CI31" s="24"/>
@@ -11280,7 +11301,7 @@
       <c r="AK35" s="13"/>
       <c r="AL35" s="13"/>
       <c r="AM35" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -11337,7 +11358,7 @@
       <c r="CC35" s="7"/>
       <c r="CD35" s="7"/>
       <c r="CE35" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="CF35" s="6"/>
       <c r="CG35" s="6"/>
@@ -11351,32 +11372,32 @@
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
       <c r="G36" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
       <c r="J36" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
-      <c r="M36" s="19" t="s">
+      <c r="M36" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
       <c r="P36" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
       <c r="S36" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
@@ -11401,7 +11422,7 @@
       <c r="AF36" s="13"/>
       <c r="AG36" s="13"/>
       <c r="AH36" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI36" s="13"/>
       <c r="AJ36" s="13"/>
@@ -11480,47 +11501,47 @@
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
       <c r="H37" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
       <c r="K37" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L37" s="13"/>
       <c r="M37" s="13"/>
       <c r="N37" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
       <c r="Q37" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R37" s="13"/>
       <c r="S37" s="13"/>
       <c r="T37" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
       <c r="W37" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AA37" s="13"/>
       <c r="AB37" s="13"/>
       <c r="AC37" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD37" s="21"/>
       <c r="AE37" s="21"/>
@@ -12891,7 +12912,7 @@
       <c r="AP1" s="4"/>
       <c r="AQ1" s="5"/>
       <c r="AT1" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -13085,14 +13106,14 @@
       <c r="AX3" s="6"/>
       <c r="AY3" s="6"/>
       <c r="AZ3" s="6"/>
-      <c r="BA3" s="20" t="s">
-        <v>166</v>
+      <c r="BA3" s="19" t="s">
+        <v>168</v>
       </c>
       <c r="BB3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="BC3" s="20" t="s">
-        <v>167</v>
+      <c r="BC3" s="19" t="s">
+        <v>169</v>
       </c>
       <c r="BD3" s="6"/>
       <c r="BE3" s="6"/>
@@ -13171,10 +13192,10 @@
       <c r="AP4" s="9"/>
       <c r="AQ4" s="9"/>
       <c r="AR4" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AT4" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AU4" s="7"/>
       <c r="AV4" s="7"/>
@@ -13182,7 +13203,7 @@
       <c r="AX4" s="8"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="BA4" s="8" t="s">
         <v>54</v>
@@ -13272,7 +13293,7 @@
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
       <c r="AR5" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
@@ -13281,10 +13302,10 @@
       <c r="AX5" s="7"/>
       <c r="AY5" s="7"/>
       <c r="AZ5" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BA5" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BB5" s="7"/>
       <c r="BC5" s="7"/>
@@ -13341,10 +13362,10 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
@@ -13387,7 +13408,7 @@
       <c r="AW6" s="7"/>
       <c r="AX6" s="7"/>
       <c r="AY6" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AZ6" s="7"/>
       <c r="BA6" s="7"/>
@@ -13396,7 +13417,7 @@
       <c r="BD6" s="6"/>
       <c r="BE6" s="11"/>
       <c r="BF6" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="BG6" s="11"/>
       <c r="BH6" s="11"/>
@@ -13458,13 +13479,13 @@
       <c r="BC7" s="11"/>
       <c r="BD7" s="6"/>
       <c r="BE7" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BG7" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="BH7" s="6"/>
     </row>
@@ -13515,7 +13536,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -13936,7 +13957,7 @@
       <c r="AP12" s="9"/>
       <c r="AQ12" s="9"/>
       <c r="AR12" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AT12" s="7"/>
       <c r="AU12" s="7"/>
@@ -14079,7 +14100,7 @@
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
       <c r="AR13" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
@@ -14192,10 +14213,10 @@
       </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -14474,7 +14495,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>108</v>
@@ -14747,32 +14768,32 @@
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
       <c r="G20" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
-      <c r="M20" s="19" t="s">
+      <c r="M20" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
       <c r="P20" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
       <c r="S20" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
@@ -14797,12 +14818,12 @@
       <c r="AF20" s="13"/>
       <c r="AG20" s="13"/>
       <c r="AH20" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI20" s="13"/>
       <c r="AJ20" s="13"/>
       <c r="AK20" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL20" s="13"/>
       <c r="AM20" s="13"/>
@@ -14811,48 +14832,48 @@
       <c r="AP20" s="9"/>
       <c r="AQ20" s="9"/>
       <c r="AR20" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AT20" s="7"/>
       <c r="AU20" s="7"/>
       <c r="AV20" s="7"/>
       <c r="AW20" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AX20" s="13"/>
       <c r="AY20" s="13"/>
       <c r="AZ20" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BA20" s="13"/>
       <c r="BB20" s="13"/>
       <c r="BC20" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BD20" s="13"/>
       <c r="BE20" s="13"/>
       <c r="BF20" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BG20" s="13"/>
       <c r="BH20" s="13"/>
       <c r="BI20" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="BJ20" s="13"/>
       <c r="BK20" s="13"/>
-      <c r="BL20" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="BM20" s="20"/>
-      <c r="BN20" s="20"/>
+      <c r="BL20" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="BM20" s="19"/>
+      <c r="BN20" s="19"/>
       <c r="BO20" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BP20" s="8"/>
       <c r="BQ20" s="8"/>
       <c r="BR20" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BS20" s="6"/>
       <c r="BT20" s="6"/>
@@ -14885,47 +14906,47 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
       <c r="K21" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O21" s="13"/>
       <c r="P21" s="13"/>
       <c r="Q21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R21" s="13"/>
       <c r="S21" s="13"/>
       <c r="T21" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
       <c r="W21" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AA21" s="13"/>
       <c r="AB21" s="13"/>
       <c r="AC21" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD21" s="21"/>
       <c r="AE21" s="21"/>
@@ -14946,44 +14967,44 @@
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
       <c r="AR21" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
       <c r="AV21" s="7"/>
       <c r="AW21" s="7"/>
       <c r="AX21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AY21" s="13"/>
       <c r="AZ21" s="13"/>
       <c r="BA21" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="BB21" s="13"/>
       <c r="BC21" s="13"/>
       <c r="BD21" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="BE21" s="13"/>
       <c r="BF21" s="13"/>
       <c r="BG21" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="BH21" s="13"/>
       <c r="BI21" s="13"/>
       <c r="BJ21" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BK21" s="13"/>
       <c r="BL21" s="13"/>
       <c r="BM21" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BN21" s="10"/>
       <c r="BO21" s="10"/>
       <c r="BP21" s="18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BQ21" s="18"/>
       <c r="BR21" s="18"/>
@@ -15055,10 +15076,10 @@
       </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
@@ -15277,7 +15298,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -15544,12 +15565,12 @@
       <c r="BI27" s="7"/>
       <c r="BJ27" s="7"/>
       <c r="BK27" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="BL27" s="7"/>
       <c r="BM27" s="7"/>
       <c r="BN27" s="22" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="BO27" s="22"/>
       <c r="BP27" s="22"/>
@@ -15559,7 +15580,7 @@
       <c r="BR27" s="7"/>
       <c r="BS27" s="7"/>
       <c r="BT27" s="22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="BU27" s="22"/>
       <c r="BV27" s="22"/>
@@ -15585,32 +15606,32 @@
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K28" s="13"/>
       <c r="L28" s="13"/>
-      <c r="M28" s="19" t="s">
+      <c r="M28" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
       <c r="P28" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
       <c r="S28" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
@@ -15635,12 +15656,12 @@
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
       <c r="AH28" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AI28" s="13"/>
       <c r="AJ28" s="13"/>
       <c r="AK28" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL28" s="13"/>
       <c r="AM28" s="13"/>
@@ -15649,7 +15670,7 @@
       <c r="AP28" s="9"/>
       <c r="AQ28" s="9"/>
       <c r="AR28" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AT28" s="7"/>
       <c r="AU28" s="7"/>
@@ -15670,7 +15691,7 @@
       <c r="BJ28" s="7"/>
       <c r="BK28" s="7"/>
       <c r="BL28" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BM28" s="7"/>
       <c r="BN28" s="7"/>
@@ -15711,47 +15732,47 @@
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="H29" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
       <c r="K29" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L29" s="13"/>
       <c r="M29" s="13"/>
       <c r="N29" s="13" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O29" s="13"/>
       <c r="P29" s="13"/>
       <c r="Q29" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R29" s="13"/>
       <c r="S29" s="13"/>
       <c r="T29" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U29" s="7"/>
       <c r="V29" s="7"/>
       <c r="W29" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AA29" s="13"/>
       <c r="AB29" s="13"/>
       <c r="AC29" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD29" s="21"/>
       <c r="AE29" s="21"/>
@@ -15772,7 +15793,7 @@
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
       <c r="AR29" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
@@ -15794,7 +15815,7 @@
       <c r="BK29" s="7"/>
       <c r="BL29" s="7"/>
       <c r="BM29" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BN29" s="7"/>
       <c r="BO29" s="7"/>
@@ -15869,10 +15890,10 @@
       </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -15939,7 +15960,7 @@
       </c>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BR30" s="7"/>
       <c r="BS30" s="7"/>
@@ -16180,7 +16201,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
@@ -16292,17 +16313,17 @@
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
       <c r="L35" s="25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
       <c r="O35" s="13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P35" s="13"/>
       <c r="Q35" s="13"/>
@@ -16380,30 +16401,30 @@
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E36" s="13"/>
       <c r="F36" s="13"/>
       <c r="G36" s="13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
       <c r="K36" s="13"/>
       <c r="L36" s="13"/>
-      <c r="M36" s="19" t="s">
+      <c r="M36" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
       <c r="P36" s="13" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
       <c r="S36" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="6"/>
@@ -16428,12 +16449,12 @@
       <c r="AF36" s="13"/>
       <c r="AG36" s="13"/>
       <c r="AH36" s="13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AI36" s="13"/>
       <c r="AJ36" s="13"/>
       <c r="AK36" s="13" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AL36" s="13"/>
       <c r="AM36" s="13"/>
@@ -16442,34 +16463,34 @@
       <c r="AP36" s="9"/>
       <c r="AQ36" s="9"/>
       <c r="AR36" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AT36" s="30" t="s">
         <v>82</v>
       </c>
       <c r="AU36" s="13" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AV36" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AW36" s="13" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AX36" s="14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AY36" s="13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AZ36" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="BA36" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="BB36" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BC36" s="7" t="s">
         <v>142</v>
@@ -16490,47 +16511,47 @@
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
       <c r="H37" s="13" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
       <c r="K37" s="13" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L37" s="13"/>
       <c r="M37" s="13"/>
       <c r="N37" s="13" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O37" s="13"/>
       <c r="P37" s="13"/>
       <c r="Q37" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="R37" s="13"/>
       <c r="S37" s="13"/>
       <c r="T37" s="7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="U37" s="7"/>
       <c r="V37" s="7"/>
       <c r="W37" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AA37" s="13"/>
       <c r="AB37" s="13"/>
       <c r="AC37" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AD37" s="21"/>
       <c r="AE37" s="21"/>
@@ -16551,31 +16572,31 @@
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
       <c r="AR37" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AT37" s="7" t="s">
         <v>33</v>
       </c>
       <c r="AU37" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AV37" s="13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AW37" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="AX37" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AY37" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="AX37" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="AY37" s="13" t="s">
-        <v>151</v>
-      </c>
       <c r="AZ37" s="18" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BA37" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BB37" s="7" t="s">
         <v>143</v>
@@ -16634,10 +16655,10 @@
       </c>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -17880,9 +17901,9 @@
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
-      <c r="Y3" s="20"/>
+      <c r="Y3" s="19"/>
       <c r="Z3" s="7"/>
-      <c r="AA3" s="20"/>
+      <c r="AA3" s="19"/>
       <c r="AB3" s="6"/>
       <c r="AC3" s="6"/>
       <c r="AD3" s="6"/>
@@ -17932,7 +17953,7 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
       <c r="P4" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
@@ -17993,7 +18014,7 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -18124,7 +18145,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -18327,7 +18348,7 @@
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="P12" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="R12" s="7"/>
       <c r="S12" s="13"/>
@@ -18388,7 +18409,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="29" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="13"/>
@@ -18597,7 +18618,7 @@
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="32" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="long_press_shift(JP)" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="long_press_shift(US)" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="md770-jp" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="_" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="long_press_shift(JP)_2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="long_press_shift(US)" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="md770-jp" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="_" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="205">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -583,6 +584,24 @@
     <t xml:space="preserve">Space &amp; F13 修飾</t>
   </si>
   <si>
+    <t xml:space="preserve">10Key Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SelMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CurMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cursor Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t xml:space="preserve"> (</t>
   </si>
   <si>
@@ -877,7 +896,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -994,6 +1013,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1011,10 +1038,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7556,6 +7579,6205 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:CI56"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="2" style="1" width="2.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="4.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="6.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="46" style="1" width="2.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="87" min="49" style="2" width="2.04"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
+      <c r="AJ1" s="4"/>
+      <c r="AK1" s="4"/>
+      <c r="AL1" s="4"/>
+      <c r="AM1" s="4"/>
+      <c r="AN1" s="4"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="5"/>
+      <c r="AS1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
+      <c r="AV1" s="4"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
+      <c r="AY1" s="4"/>
+      <c r="AZ1" s="4"/>
+      <c r="BA1" s="4"/>
+      <c r="BB1" s="4"/>
+      <c r="BC1" s="4"/>
+      <c r="BD1" s="4"/>
+      <c r="BE1" s="4"/>
+      <c r="BF1" s="4"/>
+      <c r="BG1" s="5"/>
+    </row>
+    <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP2" s="6"/>
+      <c r="AQ2" s="6"/>
+      <c r="AS2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX2" s="6"/>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA2" s="6"/>
+      <c r="BB2" s="6"/>
+      <c r="BC2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD2" s="6"/>
+      <c r="BE2" s="6"/>
+      <c r="BF2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG2" s="6"/>
+      <c r="BH2" s="6"/>
+      <c r="BI2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ2" s="6"/>
+      <c r="BK2" s="6"/>
+      <c r="BL2" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM2" s="6"/>
+      <c r="BN2" s="6"/>
+      <c r="BO2" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BP2" s="6"/>
+      <c r="BQ2" s="6"/>
+      <c r="BR2" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BS2" s="6"/>
+      <c r="BT2" s="6"/>
+      <c r="BU2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV2" s="6"/>
+      <c r="BW2" s="6"/>
+      <c r="BX2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="BY2" s="6"/>
+      <c r="BZ2" s="6"/>
+      <c r="CA2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="CB2" s="6"/>
+      <c r="CC2" s="6"/>
+      <c r="CD2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="CE2" s="6"/>
+      <c r="CF2" s="6"/>
+      <c r="CG2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="CH2" s="6"/>
+      <c r="CI2" s="6"/>
+    </row>
+    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="6"/>
+      <c r="AJ3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK3" s="6"/>
+      <c r="AL3" s="6"/>
+      <c r="AM3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN3" s="6"/>
+      <c r="AO3" s="6"/>
+      <c r="AP3" s="6"/>
+      <c r="AQ3" s="6"/>
+      <c r="AS3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT3" s="6"/>
+      <c r="AU3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AV3" s="6"/>
+      <c r="AW3" s="6"/>
+      <c r="AX3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY3" s="6"/>
+      <c r="AZ3" s="6"/>
+      <c r="BA3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="BB3" s="6"/>
+      <c r="BC3" s="6"/>
+      <c r="BD3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="BE3" s="6"/>
+      <c r="BF3" s="6"/>
+      <c r="BG3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="BH3" s="6"/>
+      <c r="BI3" s="6"/>
+      <c r="BJ3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BK3" s="6"/>
+      <c r="BL3" s="6"/>
+      <c r="BM3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN3" s="6"/>
+      <c r="BO3" s="6"/>
+      <c r="BP3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="BQ3" s="6"/>
+      <c r="BR3" s="6"/>
+      <c r="BS3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="BT3" s="6"/>
+      <c r="BU3" s="6"/>
+      <c r="BV3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="BW3" s="6"/>
+      <c r="BX3" s="6"/>
+      <c r="BY3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="BZ3" s="6"/>
+      <c r="CA3" s="6"/>
+      <c r="CB3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="CC3" s="6"/>
+      <c r="CD3" s="6"/>
+      <c r="CE3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="CF3" s="6"/>
+      <c r="CG3" s="6"/>
+      <c r="CH3" s="6"/>
+      <c r="CI3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="6"/>
+      <c r="AN4" s="9"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AS4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT4" s="7"/>
+      <c r="AU4" s="7"/>
+      <c r="AV4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="AW4" s="6"/>
+      <c r="AX4" s="6"/>
+      <c r="AY4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="AZ4" s="6"/>
+      <c r="BA4" s="6"/>
+      <c r="BB4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="BC4" s="6"/>
+      <c r="BD4" s="6"/>
+      <c r="BE4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="BF4" s="8"/>
+      <c r="BG4" s="8"/>
+      <c r="BH4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="BI4" s="6"/>
+      <c r="BJ4" s="6"/>
+      <c r="BK4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL4" s="6"/>
+      <c r="BM4" s="6"/>
+      <c r="BN4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="BO4" s="8"/>
+      <c r="BP4" s="8"/>
+      <c r="BQ4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="BR4" s="6"/>
+      <c r="BS4" s="6"/>
+      <c r="BT4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="BU4" s="6"/>
+      <c r="BV4" s="6"/>
+      <c r="BW4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="BX4" s="6"/>
+      <c r="BY4" s="6"/>
+      <c r="BZ4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="CA4" s="6"/>
+      <c r="CB4" s="6"/>
+      <c r="CC4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="CD4" s="6"/>
+      <c r="CE4" s="6"/>
+      <c r="CF4" s="9"/>
+      <c r="CG4" s="9"/>
+      <c r="CH4" s="9"/>
+      <c r="CI4" s="9"/>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG5" s="6"/>
+      <c r="AH5" s="6"/>
+      <c r="AI5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ5" s="6"/>
+      <c r="AK5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM5" s="6"/>
+      <c r="AN5" s="6"/>
+      <c r="AO5" s="6"/>
+      <c r="AP5" s="6"/>
+      <c r="AQ5" s="6"/>
+      <c r="AS5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="AT5" s="7"/>
+      <c r="AU5" s="7"/>
+      <c r="AV5" s="7"/>
+      <c r="AW5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX5" s="7"/>
+      <c r="AY5" s="7"/>
+      <c r="AZ5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="BA5" s="7"/>
+      <c r="BB5" s="7"/>
+      <c r="BC5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="BD5" s="7"/>
+      <c r="BE5" s="7"/>
+      <c r="BF5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="BG5" s="7"/>
+      <c r="BH5" s="7"/>
+      <c r="BI5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="BJ5" s="7"/>
+      <c r="BK5" s="7"/>
+      <c r="BL5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="BM5" s="7"/>
+      <c r="BN5" s="7"/>
+      <c r="BO5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="BP5" s="7"/>
+      <c r="BQ5" s="7"/>
+      <c r="BR5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="BS5" s="7"/>
+      <c r="BT5" s="7"/>
+      <c r="BU5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="BV5" s="6"/>
+      <c r="BW5" s="6"/>
+      <c r="BX5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BY5" s="6"/>
+      <c r="BZ5" s="6"/>
+      <c r="CA5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB5" s="6"/>
+      <c r="CC5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CD5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CE5" s="6"/>
+      <c r="CF5" s="6"/>
+      <c r="CG5" s="6"/>
+      <c r="CH5" s="6"/>
+      <c r="CI5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA6" s="10"/>
+      <c r="AB6" s="10"/>
+      <c r="AC6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG6" s="7"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="11"/>
+      <c r="AJ6" s="11"/>
+      <c r="AK6" s="11"/>
+      <c r="AL6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM6" s="6"/>
+      <c r="AN6" s="6"/>
+      <c r="AO6" s="11"/>
+      <c r="AP6" s="11"/>
+      <c r="AQ6" s="11"/>
+      <c r="AS6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU6" s="7"/>
+      <c r="AV6" s="7"/>
+      <c r="AW6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX6" s="7"/>
+      <c r="AY6" s="7"/>
+      <c r="AZ6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="BA6" s="7"/>
+      <c r="BB6" s="7"/>
+      <c r="BC6" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="BD6" s="7"/>
+      <c r="BE6" s="7"/>
+      <c r="BF6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="BG6" s="7"/>
+      <c r="BH6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="BI6" s="7"/>
+      <c r="BJ6" s="7"/>
+      <c r="BK6" s="7"/>
+      <c r="BL6" s="7"/>
+      <c r="BM6" s="7"/>
+      <c r="BN6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="BO6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="BP6" s="7"/>
+      <c r="BQ6" s="7"/>
+      <c r="BR6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="BS6" s="7"/>
+      <c r="BT6" s="7"/>
+      <c r="BU6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="BV6" s="7"/>
+      <c r="BW6" s="7"/>
+      <c r="BX6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="BY6" s="7"/>
+      <c r="BZ6" s="7"/>
+      <c r="CA6" s="11"/>
+      <c r="CB6" s="11"/>
+      <c r="CC6" s="11"/>
+      <c r="CD6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="CE6" s="6"/>
+      <c r="CF6" s="6"/>
+      <c r="CG6" s="11"/>
+      <c r="CH6" s="11"/>
+      <c r="CI6" s="11"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="7"/>
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ7" s="6"/>
+      <c r="AK7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM7" s="6"/>
+      <c r="AN7" s="6"/>
+      <c r="AO7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP7" s="6"/>
+      <c r="AQ7" s="6"/>
+      <c r="AS7" s="7"/>
+      <c r="AT7" s="7"/>
+      <c r="AU7" s="7"/>
+      <c r="AV7" s="7"/>
+      <c r="AW7" s="7"/>
+      <c r="AX7" s="7"/>
+      <c r="AY7" s="7"/>
+      <c r="AZ7" s="7"/>
+      <c r="BA7" s="7"/>
+      <c r="BB7" s="7"/>
+      <c r="BC7" s="7"/>
+      <c r="BD7" s="7"/>
+      <c r="BE7" s="7"/>
+      <c r="BF7" s="7"/>
+      <c r="BG7" s="7"/>
+      <c r="BH7" s="7"/>
+      <c r="BI7" s="7"/>
+      <c r="BJ7" s="7"/>
+      <c r="BK7" s="7"/>
+      <c r="BL7" s="7"/>
+      <c r="BM7" s="7"/>
+      <c r="BN7" s="7"/>
+      <c r="BO7" s="7"/>
+      <c r="BP7" s="7"/>
+      <c r="BQ7" s="7"/>
+      <c r="BR7" s="7"/>
+      <c r="BS7" s="7"/>
+      <c r="BT7" s="7"/>
+      <c r="BU7" s="7"/>
+      <c r="BV7" s="7"/>
+      <c r="BW7" s="7"/>
+      <c r="BX7" s="7"/>
+      <c r="BY7" s="7"/>
+      <c r="BZ7" s="7"/>
+      <c r="CA7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="CB7" s="6"/>
+      <c r="CC7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="CD7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="CE7" s="6"/>
+      <c r="CF7" s="6"/>
+      <c r="CG7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="CH7" s="6"/>
+      <c r="CI7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="4"/>
+      <c r="AG9" s="4"/>
+      <c r="AH9" s="4"/>
+      <c r="AI9" s="4"/>
+      <c r="AJ9" s="4"/>
+      <c r="AK9" s="4"/>
+      <c r="AL9" s="4"/>
+      <c r="AM9" s="4"/>
+      <c r="AN9" s="4"/>
+      <c r="AO9" s="4"/>
+      <c r="AP9" s="4"/>
+      <c r="AQ9" s="5"/>
+      <c r="AS9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AT9" s="4"/>
+      <c r="AU9" s="4"/>
+      <c r="AV9" s="4"/>
+      <c r="AW9" s="4"/>
+      <c r="AX9" s="4"/>
+      <c r="AY9" s="4"/>
+      <c r="AZ9" s="4"/>
+      <c r="BA9" s="4"/>
+      <c r="BB9" s="4"/>
+      <c r="BC9" s="4"/>
+      <c r="BD9" s="4"/>
+      <c r="BE9" s="4"/>
+      <c r="BF9" s="4"/>
+      <c r="BG9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="6"/>
+      <c r="AK10" s="6"/>
+      <c r="AL10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="6"/>
+      <c r="AN10" s="6"/>
+      <c r="AO10" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP10" s="6"/>
+      <c r="AQ10" s="6"/>
+      <c r="AS10" s="6"/>
+      <c r="AT10" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AU10" s="13"/>
+      <c r="AV10" s="13"/>
+      <c r="AW10" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="AX10" s="13"/>
+      <c r="AY10" s="13"/>
+      <c r="AZ10" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA10" s="13"/>
+      <c r="BB10" s="13"/>
+      <c r="BC10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="BD10" s="13"/>
+      <c r="BE10" s="13"/>
+      <c r="BF10" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="BG10" s="13"/>
+      <c r="BH10" s="13"/>
+      <c r="BI10" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="BJ10" s="13"/>
+      <c r="BK10" s="13"/>
+      <c r="BL10" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="BM10" s="13"/>
+      <c r="BN10" s="13"/>
+      <c r="BO10" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="BP10" s="13"/>
+      <c r="BQ10" s="13"/>
+      <c r="BR10" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS10" s="13"/>
+      <c r="BT10" s="13"/>
+      <c r="BU10" s="6"/>
+      <c r="BV10" s="6"/>
+      <c r="BW10" s="6"/>
+      <c r="BX10" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="BY10" s="13"/>
+      <c r="BZ10" s="13"/>
+      <c r="CA10" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="CB10" s="13"/>
+      <c r="CC10" s="13"/>
+      <c r="CD10" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="CE10" s="13"/>
+      <c r="CF10" s="13"/>
+      <c r="CG10" s="6"/>
+      <c r="CH10" s="6"/>
+      <c r="CI10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="6"/>
+      <c r="AJ11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AK11" s="6"/>
+      <c r="AL11" s="6"/>
+      <c r="AM11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN11" s="6"/>
+      <c r="AO11" s="6"/>
+      <c r="AP11" s="6"/>
+      <c r="AQ11" s="6"/>
+      <c r="AS11" s="6"/>
+      <c r="AT11" s="6"/>
+      <c r="AU11" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="AV11" s="13"/>
+      <c r="AW11" s="13"/>
+      <c r="AX11" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY11" s="13"/>
+      <c r="AZ11" s="13"/>
+      <c r="BA11" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB11" s="13"/>
+      <c r="BC11" s="13"/>
+      <c r="BD11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="BE11" s="13"/>
+      <c r="BF11" s="13"/>
+      <c r="BG11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="BH11" s="13"/>
+      <c r="BI11" s="13"/>
+      <c r="BJ11" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="BK11" s="13"/>
+      <c r="BL11" s="13"/>
+      <c r="BM11" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="BN11" s="13"/>
+      <c r="BO11" s="13"/>
+      <c r="BP11" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="BQ11" s="13"/>
+      <c r="BR11" s="13"/>
+      <c r="BS11" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="BT11" s="13"/>
+      <c r="BU11" s="13"/>
+      <c r="BV11" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="BW11" s="13"/>
+      <c r="BX11" s="13"/>
+      <c r="BY11" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="BZ11" s="13"/>
+      <c r="CA11" s="13"/>
+      <c r="CB11" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="CC11" s="13"/>
+      <c r="CD11" s="13"/>
+      <c r="CE11" s="6"/>
+      <c r="CF11" s="6"/>
+      <c r="CG11" s="6"/>
+      <c r="CH11" s="6"/>
+      <c r="CI11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI12" s="6"/>
+      <c r="AJ12" s="6"/>
+      <c r="AK12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL12" s="6"/>
+      <c r="AM12" s="6"/>
+      <c r="AN12" s="9"/>
+      <c r="AO12" s="9"/>
+      <c r="AP12" s="9"/>
+      <c r="AQ12" s="9"/>
+      <c r="AS12" s="7"/>
+      <c r="AT12" s="7"/>
+      <c r="AU12" s="7"/>
+      <c r="AV12" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW12" s="13"/>
+      <c r="AX12" s="13"/>
+      <c r="AY12" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ12" s="13"/>
+      <c r="BA12" s="13"/>
+      <c r="BB12" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="BC12" s="13"/>
+      <c r="BD12" s="13"/>
+      <c r="BE12" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="BF12" s="14"/>
+      <c r="BG12" s="14"/>
+      <c r="BH12" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="BI12" s="13"/>
+      <c r="BJ12" s="13"/>
+      <c r="BK12" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="BL12" s="13"/>
+      <c r="BM12" s="13"/>
+      <c r="BN12" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="BO12" s="14"/>
+      <c r="BP12" s="14"/>
+      <c r="BQ12" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="BR12" s="13"/>
+      <c r="BS12" s="13"/>
+      <c r="BT12" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="BU12" s="13"/>
+      <c r="BV12" s="13"/>
+      <c r="BW12" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="BX12" s="13"/>
+      <c r="BY12" s="13"/>
+      <c r="BZ12" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="CA12" s="13"/>
+      <c r="CB12" s="13"/>
+      <c r="CC12" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="CD12" s="13"/>
+      <c r="CE12" s="13"/>
+      <c r="CF12" s="9"/>
+      <c r="CG12" s="9"/>
+      <c r="CH12" s="9"/>
+      <c r="CI12" s="9"/>
+    </row>
+    <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="6"/>
+      <c r="AI13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ13" s="6"/>
+      <c r="AK13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM13" s="6"/>
+      <c r="AN13" s="6"/>
+      <c r="AO13" s="6"/>
+      <c r="AP13" s="6"/>
+      <c r="AQ13" s="6"/>
+      <c r="AS13" s="7"/>
+      <c r="AT13" s="7"/>
+      <c r="AU13" s="7"/>
+      <c r="AV13" s="7"/>
+      <c r="AW13" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="AX13" s="13"/>
+      <c r="AY13" s="13"/>
+      <c r="AZ13" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="BA13" s="13"/>
+      <c r="BB13" s="13"/>
+      <c r="BC13" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="BD13" s="13"/>
+      <c r="BE13" s="13"/>
+      <c r="BF13" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="BG13" s="13"/>
+      <c r="BH13" s="13"/>
+      <c r="BI13" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="BJ13" s="13"/>
+      <c r="BK13" s="13"/>
+      <c r="BL13" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="BM13" s="13"/>
+      <c r="BN13" s="13"/>
+      <c r="BO13" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="BP13" s="13"/>
+      <c r="BQ13" s="13"/>
+      <c r="BR13" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="BS13" s="13"/>
+      <c r="BT13" s="13"/>
+      <c r="BU13" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="BV13" s="13"/>
+      <c r="BW13" s="13"/>
+      <c r="BX13" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="BY13" s="13"/>
+      <c r="BZ13" s="13"/>
+      <c r="CA13" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="CB13" s="13"/>
+      <c r="CC13" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="CD13" s="6"/>
+      <c r="CE13" s="6"/>
+      <c r="CF13" s="6"/>
+      <c r="CG13" s="6"/>
+      <c r="CH13" s="6"/>
+      <c r="CI13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="W14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG14" s="7"/>
+      <c r="AH14" s="7"/>
+      <c r="AI14" s="11"/>
+      <c r="AJ14" s="11"/>
+      <c r="AK14" s="11"/>
+      <c r="AL14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM14" s="6"/>
+      <c r="AN14" s="6"/>
+      <c r="AO14" s="11"/>
+      <c r="AP14" s="11"/>
+      <c r="AQ14" s="11"/>
+      <c r="AS14" s="7"/>
+      <c r="AT14" s="7"/>
+      <c r="AU14" s="7"/>
+      <c r="AV14" s="7"/>
+      <c r="AW14" s="7"/>
+      <c r="AX14" s="7"/>
+      <c r="AY14" s="7"/>
+      <c r="AZ14" s="7"/>
+      <c r="BA14" s="7"/>
+      <c r="BB14" s="7"/>
+      <c r="BC14" s="7"/>
+      <c r="BD14" s="7"/>
+      <c r="BE14" s="7"/>
+      <c r="BF14" s="7"/>
+      <c r="BG14" s="7"/>
+      <c r="BH14" s="7"/>
+      <c r="BI14" s="7"/>
+      <c r="BJ14" s="7"/>
+      <c r="BK14" s="7"/>
+      <c r="BL14" s="7"/>
+      <c r="BM14" s="7"/>
+      <c r="BN14" s="7"/>
+      <c r="BO14" s="7"/>
+      <c r="BP14" s="7"/>
+      <c r="BQ14" s="7"/>
+      <c r="BR14" s="7"/>
+      <c r="BS14" s="7"/>
+      <c r="BT14" s="7"/>
+      <c r="BU14" s="7"/>
+      <c r="BV14" s="7"/>
+      <c r="BW14" s="7"/>
+      <c r="BX14" s="7"/>
+      <c r="BY14" s="7"/>
+      <c r="BZ14" s="7"/>
+      <c r="CA14" s="11"/>
+      <c r="CB14" s="11"/>
+      <c r="CC14" s="11"/>
+      <c r="CD14" s="6"/>
+      <c r="CE14" s="6"/>
+      <c r="CF14" s="6"/>
+      <c r="CG14" s="11"/>
+      <c r="CH14" s="11"/>
+      <c r="CI14" s="11"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ15" s="6"/>
+      <c r="AK15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM15" s="6"/>
+      <c r="AN15" s="6"/>
+      <c r="AO15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AP15" s="6"/>
+      <c r="AQ15" s="6"/>
+      <c r="AS15" s="7"/>
+      <c r="AT15" s="7"/>
+      <c r="AU15" s="7"/>
+      <c r="AV15" s="7"/>
+      <c r="AW15" s="7"/>
+      <c r="AX15" s="7"/>
+      <c r="AY15" s="7"/>
+      <c r="AZ15" s="7"/>
+      <c r="BA15" s="7"/>
+      <c r="BB15" s="7"/>
+      <c r="BC15" s="7"/>
+      <c r="BD15" s="7"/>
+      <c r="BE15" s="7"/>
+      <c r="BF15" s="7"/>
+      <c r="BG15" s="7"/>
+      <c r="BH15" s="7"/>
+      <c r="BI15" s="7"/>
+      <c r="BJ15" s="7"/>
+      <c r="BK15" s="7"/>
+      <c r="BL15" s="7"/>
+      <c r="BM15" s="7"/>
+      <c r="BN15" s="7"/>
+      <c r="BO15" s="7"/>
+      <c r="BP15" s="7"/>
+      <c r="BQ15" s="7"/>
+      <c r="BR15" s="7"/>
+      <c r="BS15" s="7"/>
+      <c r="BT15" s="7"/>
+      <c r="BU15" s="7"/>
+      <c r="BV15" s="7"/>
+      <c r="BW15" s="7"/>
+      <c r="BX15" s="7"/>
+      <c r="BY15" s="7"/>
+      <c r="BZ15" s="7"/>
+      <c r="CA15" s="6"/>
+      <c r="CB15" s="6"/>
+      <c r="CC15" s="6"/>
+      <c r="CD15" s="6"/>
+      <c r="CE15" s="6"/>
+      <c r="CF15" s="6"/>
+      <c r="CG15" s="6"/>
+      <c r="CH15" s="6"/>
+      <c r="CI15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
+      <c r="AA16" s="12"/>
+      <c r="AB16" s="12"/>
+      <c r="AC16" s="12"/>
+      <c r="AD16" s="12"/>
+      <c r="AE16" s="12"/>
+      <c r="AF16" s="12"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="12"/>
+      <c r="AI16" s="12"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AF17" s="4"/>
+      <c r="AG17" s="4"/>
+      <c r="AH17" s="4"/>
+      <c r="AI17" s="4"/>
+      <c r="AJ17" s="4"/>
+      <c r="AK17" s="4"/>
+      <c r="AL17" s="4"/>
+      <c r="AM17" s="4"/>
+      <c r="AN17" s="4"/>
+      <c r="AO17" s="4"/>
+      <c r="AP17" s="4"/>
+      <c r="AQ17" s="5"/>
+      <c r="AS17" s="15"/>
+      <c r="AT17" s="15"/>
+      <c r="AU17" s="4"/>
+      <c r="AV17" s="4"/>
+      <c r="AW17" s="4"/>
+      <c r="AX17" s="4"/>
+      <c r="AY17" s="4"/>
+      <c r="AZ17" s="4"/>
+      <c r="BA17" s="4"/>
+      <c r="BB17" s="4"/>
+      <c r="BC17" s="4"/>
+      <c r="BD17" s="4"/>
+      <c r="BE17" s="4"/>
+      <c r="BF17" s="4"/>
+      <c r="BG17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AJ18" s="6"/>
+      <c r="AK18" s="6"/>
+      <c r="AL18" s="6"/>
+      <c r="AM18" s="6"/>
+      <c r="AN18" s="6"/>
+      <c r="AO18" s="6"/>
+      <c r="AP18" s="6"/>
+      <c r="AQ18" s="6"/>
+      <c r="AS18" s="6"/>
+      <c r="AT18" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="AU18" s="6"/>
+      <c r="AV18" s="6"/>
+      <c r="AW18" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="AX18" s="6"/>
+      <c r="AY18" s="6"/>
+      <c r="AZ18" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA18" s="6"/>
+      <c r="BB18" s="6"/>
+      <c r="BC18" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD18" s="6"/>
+      <c r="BE18" s="6"/>
+      <c r="BF18" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG18" s="6"/>
+      <c r="BH18" s="6"/>
+      <c r="BI18" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="BJ18" s="6"/>
+      <c r="BK18" s="6"/>
+      <c r="BL18" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="BM18" s="6"/>
+      <c r="BN18" s="6"/>
+      <c r="BO18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="BP18" s="6"/>
+      <c r="BQ18" s="6"/>
+      <c r="BR18" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="BS18" s="6"/>
+      <c r="BT18" s="6"/>
+      <c r="BU18" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="BV18" s="16"/>
+      <c r="BW18" s="16"/>
+      <c r="BX18" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="BY18" s="17"/>
+      <c r="BZ18" s="17"/>
+      <c r="CA18" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="CB18" s="17"/>
+      <c r="CC18" s="17"/>
+      <c r="CD18" s="6"/>
+      <c r="CE18" s="6"/>
+      <c r="CF18" s="6"/>
+      <c r="CG18" s="6"/>
+      <c r="CH18" s="6"/>
+      <c r="CI18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="13"/>
+      <c r="AG19" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH19" s="29"/>
+      <c r="AI19" s="29"/>
+      <c r="AJ19" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK19" s="29"/>
+      <c r="AL19" s="29"/>
+      <c r="AM19" s="6"/>
+      <c r="AN19" s="6"/>
+      <c r="AO19" s="6"/>
+      <c r="AP19" s="6"/>
+      <c r="AQ19" s="6"/>
+      <c r="AS19" s="6"/>
+      <c r="AT19" s="6"/>
+      <c r="AU19" s="7"/>
+      <c r="AV19" s="7"/>
+      <c r="AW19" s="7"/>
+      <c r="AX19" s="7"/>
+      <c r="AY19" s="7"/>
+      <c r="AZ19" s="7"/>
+      <c r="BA19" s="7"/>
+      <c r="BB19" s="7"/>
+      <c r="BC19" s="7"/>
+      <c r="BD19" s="7"/>
+      <c r="BE19" s="7"/>
+      <c r="BF19" s="7"/>
+      <c r="BG19" s="7"/>
+      <c r="BH19" s="7"/>
+      <c r="BI19" s="7"/>
+      <c r="BJ19" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="BK19" s="13"/>
+      <c r="BL19" s="13"/>
+      <c r="BM19" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="BN19" s="13"/>
+      <c r="BO19" s="13"/>
+      <c r="BP19" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="BQ19" s="6"/>
+      <c r="BR19" s="6"/>
+      <c r="BS19" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="BT19" s="6"/>
+      <c r="BU19" s="6"/>
+      <c r="BV19" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="BW19" s="18"/>
+      <c r="BX19" s="18"/>
+      <c r="BY19" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="BZ19" s="19"/>
+      <c r="CA19" s="19"/>
+      <c r="CB19" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="CC19" s="10"/>
+      <c r="CD19" s="10"/>
+      <c r="CE19" s="6"/>
+      <c r="CF19" s="6"/>
+      <c r="CG19" s="6"/>
+      <c r="CH19" s="6"/>
+      <c r="CI19" s="6"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W20" s="8"/>
+      <c r="X20" s="8"/>
+      <c r="Y20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF20" s="13"/>
+      <c r="AG20" s="13"/>
+      <c r="AH20" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="AI20" s="13"/>
+      <c r="AJ20" s="13"/>
+      <c r="AK20" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL20" s="13"/>
+      <c r="AM20" s="13"/>
+      <c r="AN20" s="9"/>
+      <c r="AO20" s="9"/>
+      <c r="AP20" s="9"/>
+      <c r="AQ20" s="9"/>
+      <c r="AS20" s="7"/>
+      <c r="AT20" s="7"/>
+      <c r="AU20" s="7"/>
+      <c r="AV20" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="AW20" s="13"/>
+      <c r="AX20" s="13"/>
+      <c r="AY20" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="AZ20" s="13"/>
+      <c r="BA20" s="13"/>
+      <c r="BB20" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="BC20" s="13"/>
+      <c r="BD20" s="13"/>
+      <c r="BE20" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="BF20" s="13"/>
+      <c r="BG20" s="13"/>
+      <c r="BH20" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BI20" s="13"/>
+      <c r="BJ20" s="13"/>
+      <c r="BK20" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="BL20" s="19"/>
+      <c r="BM20" s="19"/>
+      <c r="BN20" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="BO20" s="8"/>
+      <c r="BP20" s="8"/>
+      <c r="BQ20" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BR20" s="6"/>
+      <c r="BS20" s="6"/>
+      <c r="BT20" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="BU20" s="6"/>
+      <c r="BV20" s="6"/>
+      <c r="BW20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BX20" s="13"/>
+      <c r="BY20" s="13"/>
+      <c r="BZ20" s="7"/>
+      <c r="CA20" s="7"/>
+      <c r="CB20" s="7"/>
+      <c r="CC20" s="7"/>
+      <c r="CD20" s="7"/>
+      <c r="CE20" s="7"/>
+      <c r="CF20" s="9"/>
+      <c r="CG20" s="9"/>
+      <c r="CH20" s="9"/>
+      <c r="CI20" s="9"/>
+    </row>
+    <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="U21" s="7"/>
+      <c r="V21" s="7"/>
+      <c r="W21" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA21" s="7"/>
+      <c r="AB21" s="7"/>
+      <c r="AC21" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD21" s="21"/>
+      <c r="AE21" s="21"/>
+      <c r="AF21" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="AG21" s="13"/>
+      <c r="AH21" s="13"/>
+      <c r="AI21" s="6"/>
+      <c r="AJ21" s="6"/>
+      <c r="AK21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM21" s="6"/>
+      <c r="AN21" s="6"/>
+      <c r="AO21" s="6"/>
+      <c r="AP21" s="6"/>
+      <c r="AQ21" s="6"/>
+      <c r="AS21" s="7"/>
+      <c r="AT21" s="7"/>
+      <c r="AU21" s="7"/>
+      <c r="AV21" s="7"/>
+      <c r="AW21" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="AX21" s="13"/>
+      <c r="AY21" s="13"/>
+      <c r="AZ21" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="BA21" s="13"/>
+      <c r="BB21" s="13"/>
+      <c r="BC21" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="BD21" s="13"/>
+      <c r="BE21" s="13"/>
+      <c r="BF21" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="BG21" s="13"/>
+      <c r="BH21" s="13"/>
+      <c r="BI21" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="BJ21" s="13"/>
+      <c r="BK21" s="13"/>
+      <c r="BL21" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM21" s="10"/>
+      <c r="BN21" s="10"/>
+      <c r="BO21" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="BP21" s="18"/>
+      <c r="BQ21" s="18"/>
+      <c r="BR21" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="BS21" s="18"/>
+      <c r="BT21" s="18"/>
+      <c r="BU21" s="7"/>
+      <c r="BV21" s="7"/>
+      <c r="BW21" s="7"/>
+      <c r="BX21" s="6"/>
+      <c r="BY21" s="6"/>
+      <c r="BZ21" s="6"/>
+      <c r="CA21" s="6"/>
+      <c r="CB21" s="6"/>
+      <c r="CC21" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="CD21" s="6"/>
+      <c r="CE21" s="6"/>
+      <c r="CF21" s="6"/>
+      <c r="CG21" s="6"/>
+      <c r="CH21" s="6"/>
+      <c r="CI21" s="6"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
+      <c r="V22" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="W22" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="X22" s="7"/>
+      <c r="Y22" s="7"/>
+      <c r="Z22" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="7"/>
+      <c r="AB22" s="7"/>
+      <c r="AC22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD22" s="7"/>
+      <c r="AE22" s="7"/>
+      <c r="AF22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG22" s="7"/>
+      <c r="AH22" s="7"/>
+      <c r="AI22" s="11"/>
+      <c r="AJ22" s="11"/>
+      <c r="AK22" s="11"/>
+      <c r="AL22" s="6"/>
+      <c r="AM22" s="6"/>
+      <c r="AN22" s="6"/>
+      <c r="AO22" s="11"/>
+      <c r="AP22" s="11"/>
+      <c r="AQ22" s="11"/>
+      <c r="AS22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT22" s="7"/>
+      <c r="AU22" s="7"/>
+      <c r="AV22" s="7"/>
+      <c r="AW22" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX22" s="7"/>
+      <c r="AY22" s="7"/>
+      <c r="AZ22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="BA22" s="7"/>
+      <c r="BB22" s="7"/>
+      <c r="BC22" s="7"/>
+      <c r="BD22" s="7"/>
+      <c r="BE22" s="7"/>
+      <c r="BF22" s="7"/>
+      <c r="BG22" s="7"/>
+      <c r="BH22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="BI22" s="7"/>
+      <c r="BJ22" s="7"/>
+      <c r="BK22" s="7"/>
+      <c r="BL22" s="7"/>
+      <c r="BM22" s="7"/>
+      <c r="BN22" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="BO22" s="7"/>
+      <c r="BP22" s="7"/>
+      <c r="BQ22" s="7"/>
+      <c r="BR22" s="7"/>
+      <c r="BS22" s="7"/>
+      <c r="BT22" s="7"/>
+      <c r="BU22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="BV22" s="7"/>
+      <c r="BW22" s="7"/>
+      <c r="BX22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="BY22" s="7"/>
+      <c r="BZ22" s="7"/>
+      <c r="CA22" s="11"/>
+      <c r="CB22" s="11"/>
+      <c r="CC22" s="11"/>
+      <c r="CD22" s="6"/>
+      <c r="CE22" s="6"/>
+      <c r="CF22" s="6"/>
+      <c r="CG22" s="11"/>
+      <c r="CH22" s="11"/>
+      <c r="CI22" s="11"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
+      <c r="V23" s="7"/>
+      <c r="W23" s="7"/>
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7"/>
+      <c r="Z23" s="7"/>
+      <c r="AA23" s="7"/>
+      <c r="AB23" s="7"/>
+      <c r="AC23" s="7"/>
+      <c r="AD23" s="7"/>
+      <c r="AE23" s="7"/>
+      <c r="AF23" s="7"/>
+      <c r="AG23" s="7"/>
+      <c r="AH23" s="7"/>
+      <c r="AI23" s="6"/>
+      <c r="AJ23" s="6"/>
+      <c r="AK23" s="6"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="6"/>
+      <c r="AN23" s="6"/>
+      <c r="AO23" s="6"/>
+      <c r="AP23" s="6"/>
+      <c r="AQ23" s="6"/>
+      <c r="AS23" s="7"/>
+      <c r="AT23" s="7"/>
+      <c r="AU23" s="7"/>
+      <c r="AV23" s="7"/>
+      <c r="AW23" s="7"/>
+      <c r="AX23" s="7"/>
+      <c r="AY23" s="7"/>
+      <c r="AZ23" s="7"/>
+      <c r="BA23" s="7"/>
+      <c r="BB23" s="7"/>
+      <c r="BC23" s="7"/>
+      <c r="BD23" s="7"/>
+      <c r="BE23" s="7"/>
+      <c r="BF23" s="7"/>
+      <c r="BG23" s="7"/>
+      <c r="BH23" s="7"/>
+      <c r="BI23" s="7"/>
+      <c r="BJ23" s="7"/>
+      <c r="BK23" s="7"/>
+      <c r="BL23" s="7"/>
+      <c r="BM23" s="7"/>
+      <c r="BN23" s="7"/>
+      <c r="BO23" s="7"/>
+      <c r="BP23" s="7"/>
+      <c r="BQ23" s="7"/>
+      <c r="BR23" s="7"/>
+      <c r="BS23" s="7"/>
+      <c r="BT23" s="7"/>
+      <c r="BU23" s="7"/>
+      <c r="BV23" s="7"/>
+      <c r="BW23" s="7"/>
+      <c r="BX23" s="7"/>
+      <c r="BY23" s="7"/>
+      <c r="BZ23" s="7"/>
+      <c r="CA23" s="6"/>
+      <c r="CB23" s="6"/>
+      <c r="CC23" s="6"/>
+      <c r="CD23" s="6"/>
+      <c r="CE23" s="6"/>
+      <c r="CF23" s="6"/>
+      <c r="CG23" s="6"/>
+      <c r="CH23" s="6"/>
+      <c r="CI23" s="6"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="12"/>
+      <c r="AA24" s="12"/>
+      <c r="AB24" s="12"/>
+      <c r="AC24" s="12"/>
+      <c r="AD24" s="12"/>
+      <c r="AE24" s="12"/>
+      <c r="AF24" s="12"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="12"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AF25" s="4"/>
+      <c r="AG25" s="4"/>
+      <c r="AH25" s="4"/>
+      <c r="AI25" s="4"/>
+      <c r="AJ25" s="4"/>
+      <c r="AK25" s="4"/>
+      <c r="AL25" s="4"/>
+      <c r="AM25" s="4"/>
+      <c r="AN25" s="4"/>
+      <c r="AO25" s="4"/>
+      <c r="AP25" s="4"/>
+      <c r="AQ25" s="5"/>
+      <c r="AS25" s="15"/>
+      <c r="AT25" s="15"/>
+      <c r="AU25" s="4"/>
+      <c r="AV25" s="4"/>
+      <c r="AW25" s="4"/>
+      <c r="AX25" s="4"/>
+      <c r="AY25" s="4"/>
+      <c r="AZ25" s="4"/>
+      <c r="BA25" s="4"/>
+      <c r="BB25" s="4"/>
+      <c r="BC25" s="4"/>
+      <c r="BD25" s="4"/>
+      <c r="BE25" s="4"/>
+      <c r="BF25" s="4"/>
+      <c r="BG25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="U26" s="6"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="6"/>
+      <c r="AI26" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AJ26" s="6"/>
+      <c r="AK26" s="6"/>
+      <c r="AL26" s="6"/>
+      <c r="AM26" s="6"/>
+      <c r="AN26" s="6"/>
+      <c r="AO26" s="6"/>
+      <c r="AP26" s="6"/>
+      <c r="AQ26" s="6"/>
+      <c r="AS26" s="7"/>
+      <c r="AT26" s="7"/>
+      <c r="AU26" s="7"/>
+      <c r="AV26" s="7"/>
+      <c r="AW26" s="7"/>
+      <c r="AX26" s="7"/>
+      <c r="AY26" s="7"/>
+      <c r="AZ26" s="7"/>
+      <c r="BA26" s="7"/>
+      <c r="BB26" s="7"/>
+      <c r="BC26" s="7"/>
+      <c r="BD26" s="7"/>
+      <c r="BE26" s="7"/>
+      <c r="BF26" s="7"/>
+      <c r="BG26" s="7"/>
+      <c r="BH26" s="7"/>
+      <c r="BI26" s="7"/>
+      <c r="BJ26" s="7"/>
+      <c r="BK26" s="7"/>
+      <c r="BL26" s="7"/>
+      <c r="BM26" s="7"/>
+      <c r="BN26" s="7"/>
+      <c r="BO26" s="7"/>
+      <c r="BP26" s="7"/>
+      <c r="BQ26" s="7"/>
+      <c r="BR26" s="7"/>
+      <c r="BS26" s="7"/>
+      <c r="BT26" s="7"/>
+      <c r="BU26" s="7"/>
+      <c r="BV26" s="7"/>
+      <c r="BW26" s="7"/>
+      <c r="BX26" s="7"/>
+      <c r="BY26" s="7"/>
+      <c r="BZ26" s="7"/>
+      <c r="CA26" s="7"/>
+      <c r="CB26" s="7"/>
+      <c r="CC26" s="7"/>
+      <c r="CD26" s="7"/>
+      <c r="CE26" s="7"/>
+      <c r="CF26" s="7"/>
+      <c r="CG26" s="7"/>
+      <c r="CH26" s="7"/>
+      <c r="CI26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S27" s="13"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y27" s="6"/>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="6"/>
+      <c r="AD27" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AE27" s="7"/>
+      <c r="AF27" s="7"/>
+      <c r="AG27" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH27" s="13"/>
+      <c r="AI27" s="13"/>
+      <c r="AJ27" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="AK27" s="13"/>
+      <c r="AL27" s="13"/>
+      <c r="AM27" s="6"/>
+      <c r="AN27" s="6"/>
+      <c r="AO27" s="6"/>
+      <c r="AP27" s="6"/>
+      <c r="AQ27" s="6"/>
+      <c r="AS27" s="7"/>
+      <c r="AT27" s="7"/>
+      <c r="AU27" s="7"/>
+      <c r="AV27" s="7"/>
+      <c r="AW27" s="7"/>
+      <c r="AX27" s="7"/>
+      <c r="AY27" s="7"/>
+      <c r="AZ27" s="7"/>
+      <c r="BA27" s="7"/>
+      <c r="BB27" s="7"/>
+      <c r="BC27" s="7"/>
+      <c r="BD27" s="7"/>
+      <c r="BE27" s="7"/>
+      <c r="BF27" s="7"/>
+      <c r="BG27" s="7"/>
+      <c r="BH27" s="7"/>
+      <c r="BI27" s="7"/>
+      <c r="BJ27" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="BK27" s="7"/>
+      <c r="BL27" s="7"/>
+      <c r="BM27" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="BN27" s="22"/>
+      <c r="BO27" s="22"/>
+      <c r="BP27" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="BQ27" s="7"/>
+      <c r="BR27" s="7"/>
+      <c r="BS27" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="BT27" s="22"/>
+      <c r="BU27" s="22"/>
+      <c r="BV27" s="7"/>
+      <c r="BW27" s="7"/>
+      <c r="BX27" s="7"/>
+      <c r="BY27" s="7"/>
+      <c r="BZ27" s="7"/>
+      <c r="CA27" s="7"/>
+      <c r="CB27" s="7"/>
+      <c r="CC27" s="7"/>
+      <c r="CD27" s="7"/>
+      <c r="CE27" s="7"/>
+      <c r="CF27" s="7"/>
+      <c r="CG27" s="7"/>
+      <c r="CH27" s="7"/>
+      <c r="CI27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6"/>
+      <c r="V28" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W28" s="8"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF28" s="13"/>
+      <c r="AG28" s="13"/>
+      <c r="AH28" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="AI28" s="13"/>
+      <c r="AJ28" s="13"/>
+      <c r="AK28" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL28" s="13"/>
+      <c r="AM28" s="13"/>
+      <c r="AN28" s="9"/>
+      <c r="AO28" s="9"/>
+      <c r="AP28" s="9"/>
+      <c r="AQ28" s="9"/>
+      <c r="AS28" s="7"/>
+      <c r="AT28" s="7"/>
+      <c r="AU28" s="7"/>
+      <c r="AV28" s="7"/>
+      <c r="AW28" s="7"/>
+      <c r="AX28" s="7"/>
+      <c r="AY28" s="7"/>
+      <c r="AZ28" s="7"/>
+      <c r="BA28" s="7"/>
+      <c r="BB28" s="7"/>
+      <c r="BC28" s="7"/>
+      <c r="BD28" s="7"/>
+      <c r="BE28" s="8"/>
+      <c r="BF28" s="8"/>
+      <c r="BG28" s="8"/>
+      <c r="BH28" s="7"/>
+      <c r="BI28" s="7"/>
+      <c r="BJ28" s="7"/>
+      <c r="BK28" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="BL28" s="7"/>
+      <c r="BM28" s="7"/>
+      <c r="BN28" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="BO28" s="8"/>
+      <c r="BP28" s="8"/>
+      <c r="BQ28" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="BR28" s="7"/>
+      <c r="BS28" s="7"/>
+      <c r="BT28" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="BU28" s="7"/>
+      <c r="BV28" s="7"/>
+      <c r="BW28" s="7"/>
+      <c r="BX28" s="7"/>
+      <c r="BY28" s="7"/>
+      <c r="BZ28" s="7"/>
+      <c r="CA28" s="7"/>
+      <c r="CB28" s="7"/>
+      <c r="CC28" s="7"/>
+      <c r="CD28" s="7"/>
+      <c r="CE28" s="7"/>
+      <c r="CF28" s="23"/>
+      <c r="CG28" s="23"/>
+      <c r="CH28" s="23"/>
+      <c r="CI28" s="23"/>
+    </row>
+    <row r="29" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="U29" s="7"/>
+      <c r="V29" s="7"/>
+      <c r="W29" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="X29" s="7"/>
+      <c r="Y29" s="7"/>
+      <c r="Z29" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA29" s="7"/>
+      <c r="AB29" s="7"/>
+      <c r="AC29" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD29" s="21"/>
+      <c r="AE29" s="21"/>
+      <c r="AF29" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="AG29" s="13"/>
+      <c r="AH29" s="13"/>
+      <c r="AI29" s="6"/>
+      <c r="AJ29" s="6"/>
+      <c r="AK29" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL29" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM29" s="6"/>
+      <c r="AN29" s="6"/>
+      <c r="AO29" s="6"/>
+      <c r="AP29" s="6"/>
+      <c r="AQ29" s="6"/>
+      <c r="AS29" s="7"/>
+      <c r="AT29" s="7"/>
+      <c r="AU29" s="7"/>
+      <c r="AV29" s="7"/>
+      <c r="AW29" s="7"/>
+      <c r="AX29" s="7"/>
+      <c r="AY29" s="7"/>
+      <c r="AZ29" s="7"/>
+      <c r="BA29" s="7"/>
+      <c r="BB29" s="7"/>
+      <c r="BC29" s="7"/>
+      <c r="BD29" s="7"/>
+      <c r="BE29" s="7"/>
+      <c r="BF29" s="7"/>
+      <c r="BG29" s="7"/>
+      <c r="BH29" s="7"/>
+      <c r="BI29" s="7"/>
+      <c r="BJ29" s="7"/>
+      <c r="BK29" s="7"/>
+      <c r="BL29" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="BM29" s="7"/>
+      <c r="BN29" s="7"/>
+      <c r="BO29" s="7"/>
+      <c r="BP29" s="7"/>
+      <c r="BQ29" s="7"/>
+      <c r="BR29" s="7"/>
+      <c r="BS29" s="7"/>
+      <c r="BT29" s="7"/>
+      <c r="BU29" s="7"/>
+      <c r="BV29" s="7"/>
+      <c r="BW29" s="7"/>
+      <c r="BX29" s="7"/>
+      <c r="BY29" s="7"/>
+      <c r="BZ29" s="7"/>
+      <c r="CA29" s="7"/>
+      <c r="CB29" s="7"/>
+      <c r="CC29" s="7"/>
+      <c r="CD29" s="7"/>
+      <c r="CE29" s="7"/>
+      <c r="CF29" s="7"/>
+      <c r="CG29" s="7"/>
+      <c r="CH29" s="7"/>
+      <c r="CI29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
+      <c r="V30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="W30" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="X30" s="7"/>
+      <c r="Y30" s="7"/>
+      <c r="Z30" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA30" s="7"/>
+      <c r="AB30" s="7"/>
+      <c r="AC30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD30" s="7"/>
+      <c r="AE30" s="7"/>
+      <c r="AF30" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG30" s="7"/>
+      <c r="AH30" s="7"/>
+      <c r="AI30" s="11"/>
+      <c r="AJ30" s="11"/>
+      <c r="AK30" s="11"/>
+      <c r="AL30" s="6"/>
+      <c r="AM30" s="6"/>
+      <c r="AN30" s="6"/>
+      <c r="AO30" s="11"/>
+      <c r="AP30" s="11"/>
+      <c r="AQ30" s="11"/>
+      <c r="AS30" s="7"/>
+      <c r="AT30" s="7"/>
+      <c r="AU30" s="7"/>
+      <c r="AV30" s="7"/>
+      <c r="AW30" s="7"/>
+      <c r="AX30" s="7"/>
+      <c r="AY30" s="7"/>
+      <c r="AZ30" s="7"/>
+      <c r="BA30" s="7"/>
+      <c r="BB30" s="7"/>
+      <c r="BC30" s="7"/>
+      <c r="BD30" s="7"/>
+      <c r="BE30" s="7"/>
+      <c r="BF30" s="7"/>
+      <c r="BG30" s="7"/>
+      <c r="BH30" s="7"/>
+      <c r="BI30" s="7"/>
+      <c r="BJ30" s="7"/>
+      <c r="BK30" s="7"/>
+      <c r="BL30" s="7"/>
+      <c r="BM30" s="7"/>
+      <c r="BN30" s="7"/>
+      <c r="BO30" s="7"/>
+      <c r="BP30" s="7"/>
+      <c r="BQ30" s="7"/>
+      <c r="BR30" s="7"/>
+      <c r="BS30" s="7"/>
+      <c r="BT30" s="7"/>
+      <c r="BU30" s="7"/>
+      <c r="BV30" s="7"/>
+      <c r="BW30" s="7"/>
+      <c r="BX30" s="7"/>
+      <c r="BY30" s="7"/>
+      <c r="BZ30" s="7"/>
+      <c r="CA30" s="11"/>
+      <c r="CB30" s="11"/>
+      <c r="CC30" s="11"/>
+      <c r="CD30" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE30" s="6"/>
+      <c r="CF30" s="6"/>
+      <c r="CG30" s="11"/>
+      <c r="CH30" s="11"/>
+      <c r="CI30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
+      <c r="V31" s="7"/>
+      <c r="W31" s="7"/>
+      <c r="X31" s="7"/>
+      <c r="Y31" s="7"/>
+      <c r="Z31" s="7"/>
+      <c r="AA31" s="7"/>
+      <c r="AB31" s="7"/>
+      <c r="AC31" s="7"/>
+      <c r="AD31" s="7"/>
+      <c r="AE31" s="7"/>
+      <c r="AF31" s="7"/>
+      <c r="AG31" s="7"/>
+      <c r="AH31" s="7"/>
+      <c r="AI31" s="6"/>
+      <c r="AJ31" s="6"/>
+      <c r="AK31" s="6"/>
+      <c r="AL31" s="6"/>
+      <c r="AM31" s="6"/>
+      <c r="AN31" s="6"/>
+      <c r="AO31" s="6"/>
+      <c r="AP31" s="6"/>
+      <c r="AQ31" s="6"/>
+      <c r="AS31" s="7"/>
+      <c r="AT31" s="7"/>
+      <c r="AU31" s="7"/>
+      <c r="AV31" s="7"/>
+      <c r="AW31" s="7"/>
+      <c r="AX31" s="7"/>
+      <c r="AY31" s="7"/>
+      <c r="AZ31" s="7"/>
+      <c r="BA31" s="7"/>
+      <c r="BB31" s="7"/>
+      <c r="BC31" s="7"/>
+      <c r="BD31" s="7"/>
+      <c r="BE31" s="7"/>
+      <c r="BF31" s="7"/>
+      <c r="BG31" s="7"/>
+      <c r="BH31" s="7"/>
+      <c r="BI31" s="7"/>
+      <c r="BJ31" s="7"/>
+      <c r="BK31" s="7"/>
+      <c r="BL31" s="7"/>
+      <c r="BM31" s="7"/>
+      <c r="BN31" s="7"/>
+      <c r="BO31" s="7"/>
+      <c r="BP31" s="7"/>
+      <c r="BQ31" s="7"/>
+      <c r="BR31" s="7"/>
+      <c r="BS31" s="7"/>
+      <c r="BT31" s="7"/>
+      <c r="BU31" s="7"/>
+      <c r="BV31" s="7"/>
+      <c r="BW31" s="7"/>
+      <c r="BX31" s="7"/>
+      <c r="BY31" s="7"/>
+      <c r="BZ31" s="7"/>
+      <c r="CA31" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="CB31" s="6"/>
+      <c r="CC31" s="6"/>
+      <c r="CD31" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="CE31" s="6"/>
+      <c r="CF31" s="6"/>
+      <c r="CG31" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="CH31" s="24"/>
+      <c r="CI31" s="24"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="12"/>
+      <c r="U32" s="12"/>
+      <c r="V32" s="12"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="12"/>
+      <c r="Y32" s="12"/>
+      <c r="Z32" s="12"/>
+      <c r="AA32" s="12"/>
+      <c r="AB32" s="12"/>
+      <c r="AC32" s="12"/>
+      <c r="AD32" s="12"/>
+      <c r="AE32" s="12"/>
+      <c r="AF32" s="12"/>
+      <c r="AG32" s="12"/>
+      <c r="AH32" s="12"/>
+      <c r="AI32" s="12"/>
+      <c r="AJ32" s="12"/>
+      <c r="AK32" s="12"/>
+      <c r="AL32" s="12"/>
+      <c r="AM32" s="12"/>
+      <c r="AN32" s="12"/>
+      <c r="AO32" s="12"/>
+      <c r="AP32" s="12"/>
+      <c r="AQ32" s="12"/>
+      <c r="AS32" s="12"/>
+      <c r="AT32" s="12"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4"/>
+      <c r="V33" s="4"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="4"/>
+      <c r="AA33" s="4"/>
+      <c r="AB33" s="4"/>
+      <c r="AC33" s="4"/>
+      <c r="AD33" s="4"/>
+      <c r="AE33" s="4"/>
+      <c r="AF33" s="4"/>
+      <c r="AG33" s="4"/>
+      <c r="AH33" s="4"/>
+      <c r="AI33" s="4"/>
+      <c r="AJ33" s="4"/>
+      <c r="AK33" s="4"/>
+      <c r="AL33" s="4"/>
+      <c r="AM33" s="4"/>
+      <c r="AN33" s="4"/>
+      <c r="AO33" s="4"/>
+      <c r="AP33" s="4"/>
+      <c r="AQ33" s="5"/>
+      <c r="AS33" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="AT33" s="5"/>
+      <c r="AU33" s="4"/>
+      <c r="AV33" s="4"/>
+      <c r="AW33" s="4"/>
+      <c r="AX33" s="4"/>
+      <c r="AY33" s="4"/>
+      <c r="AZ33" s="4"/>
+      <c r="BA33" s="4"/>
+      <c r="BB33" s="4"/>
+      <c r="BC33" s="4"/>
+      <c r="BD33" s="4"/>
+      <c r="BE33" s="4"/>
+      <c r="BF33" s="4"/>
+      <c r="BG33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="6"/>
+      <c r="AL34" s="6"/>
+      <c r="AM34" s="6"/>
+      <c r="AN34" s="6"/>
+      <c r="AO34" s="6"/>
+      <c r="AP34" s="6"/>
+      <c r="AQ34" s="6"/>
+      <c r="AS34" s="7"/>
+      <c r="AT34" s="7"/>
+      <c r="AU34" s="7"/>
+      <c r="AV34" s="7"/>
+      <c r="AW34" s="7"/>
+      <c r="AX34" s="7"/>
+      <c r="AY34" s="7"/>
+      <c r="AZ34" s="7"/>
+      <c r="BA34" s="7"/>
+      <c r="BB34" s="7"/>
+      <c r="BC34" s="7"/>
+      <c r="BD34" s="7"/>
+      <c r="BE34" s="7"/>
+      <c r="BF34" s="7"/>
+      <c r="BG34" s="7"/>
+      <c r="BH34" s="7"/>
+      <c r="BI34" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="BJ34" s="13"/>
+      <c r="BK34" s="13"/>
+      <c r="BL34" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM34" s="13"/>
+      <c r="BN34" s="13"/>
+      <c r="BO34" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BP34" s="13"/>
+      <c r="BQ34" s="13"/>
+      <c r="BR34" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BS34" s="13"/>
+      <c r="BT34" s="13"/>
+      <c r="BU34" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV34" s="13"/>
+      <c r="BW34" s="13"/>
+      <c r="BX34" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="BY34" s="13"/>
+      <c r="BZ34" s="13"/>
+      <c r="CA34" s="7"/>
+      <c r="CB34" s="7"/>
+      <c r="CC34" s="7"/>
+      <c r="CD34" s="7"/>
+      <c r="CE34" s="7"/>
+      <c r="CF34" s="7"/>
+      <c r="CG34" s="7"/>
+      <c r="CH34" s="7"/>
+      <c r="CI34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S35" s="13"/>
+      <c r="T35" s="13"/>
+      <c r="U35" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB35" s="13"/>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="13"/>
+      <c r="AG35" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH35" s="29"/>
+      <c r="AI35" s="29"/>
+      <c r="AJ35" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK35" s="29"/>
+      <c r="AL35" s="29"/>
+      <c r="AM35" s="6"/>
+      <c r="AN35" s="6"/>
+      <c r="AO35" s="6"/>
+      <c r="AP35" s="6"/>
+      <c r="AQ35" s="6"/>
+      <c r="AS35" s="7"/>
+      <c r="AT35" s="7"/>
+      <c r="AU35" s="7"/>
+      <c r="AV35" s="7"/>
+      <c r="AW35" s="7"/>
+      <c r="AX35" s="7"/>
+      <c r="AY35" s="7"/>
+      <c r="AZ35" s="7"/>
+      <c r="BA35" s="7"/>
+      <c r="BB35" s="7"/>
+      <c r="BC35" s="7"/>
+      <c r="BD35" s="7"/>
+      <c r="BE35" s="7"/>
+      <c r="BF35" s="7"/>
+      <c r="BG35" s="7"/>
+      <c r="BH35" s="7"/>
+      <c r="BI35" s="7"/>
+      <c r="BJ35" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="BK35" s="13"/>
+      <c r="BL35" s="13"/>
+      <c r="BM35" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN35" s="13"/>
+      <c r="BO35" s="13"/>
+      <c r="BP35" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ35" s="13"/>
+      <c r="BR35" s="13"/>
+      <c r="BS35" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT35" s="13"/>
+      <c r="BU35" s="13"/>
+      <c r="BV35" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="BW35" s="13"/>
+      <c r="BX35" s="13"/>
+      <c r="BY35" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="BZ35" s="13"/>
+      <c r="CA35" s="13"/>
+      <c r="CB35" s="7"/>
+      <c r="CC35" s="7"/>
+      <c r="CD35" s="7"/>
+      <c r="CE35" s="7"/>
+      <c r="CF35" s="7"/>
+      <c r="CG35" s="7"/>
+      <c r="CH35" s="7"/>
+      <c r="CI35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6"/>
+      <c r="V36" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W36" s="8"/>
+      <c r="X36" s="8"/>
+      <c r="Y36" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="6"/>
+      <c r="AB36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC36" s="6"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="13"/>
+      <c r="AH36" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="AI36" s="29"/>
+      <c r="AJ36" s="29"/>
+      <c r="AK36" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="AL36" s="13"/>
+      <c r="AM36" s="13"/>
+      <c r="AN36" s="9"/>
+      <c r="AO36" s="9"/>
+      <c r="AP36" s="9"/>
+      <c r="AQ36" s="9"/>
+      <c r="AS36" s="7"/>
+      <c r="AT36" s="7"/>
+      <c r="AU36" s="7"/>
+      <c r="AV36" s="7"/>
+      <c r="AW36" s="7"/>
+      <c r="AX36" s="7"/>
+      <c r="AY36" s="7"/>
+      <c r="AZ36" s="7"/>
+      <c r="BA36" s="7"/>
+      <c r="BB36" s="7"/>
+      <c r="BC36" s="7"/>
+      <c r="BD36" s="7"/>
+      <c r="BE36" s="8"/>
+      <c r="BF36" s="8"/>
+      <c r="BG36" s="8"/>
+      <c r="BH36" s="7"/>
+      <c r="BI36" s="7"/>
+      <c r="BJ36" s="7"/>
+      <c r="BK36" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="BL36" s="13"/>
+      <c r="BM36" s="13"/>
+      <c r="BN36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO36" s="14"/>
+      <c r="BP36" s="14"/>
+      <c r="BQ36" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR36" s="13"/>
+      <c r="BS36" s="13"/>
+      <c r="BT36" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU36" s="13"/>
+      <c r="BV36" s="13"/>
+      <c r="BW36" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BX36" s="13"/>
+      <c r="BY36" s="13"/>
+      <c r="BZ36" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="CA36" s="13"/>
+      <c r="CB36" s="13"/>
+      <c r="CC36" s="7"/>
+      <c r="CD36" s="7"/>
+      <c r="CE36" s="7"/>
+      <c r="CF36" s="23"/>
+      <c r="CG36" s="23"/>
+      <c r="CH36" s="23"/>
+      <c r="CI36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="U37" s="7"/>
+      <c r="V37" s="7"/>
+      <c r="W37" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="X37" s="7"/>
+      <c r="Y37" s="7"/>
+      <c r="Z37" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA37" s="7"/>
+      <c r="AB37" s="7"/>
+      <c r="AC37" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD37" s="21"/>
+      <c r="AE37" s="21"/>
+      <c r="AF37" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="AG37" s="13"/>
+      <c r="AH37" s="13"/>
+      <c r="AI37" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="AJ37" s="29"/>
+      <c r="AK37" s="29"/>
+      <c r="AL37" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM37" s="6"/>
+      <c r="AN37" s="6"/>
+      <c r="AO37" s="6"/>
+      <c r="AP37" s="6"/>
+      <c r="AQ37" s="6"/>
+      <c r="AS37" s="7"/>
+      <c r="AT37" s="7"/>
+      <c r="AU37" s="7"/>
+      <c r="AV37" s="7"/>
+      <c r="AW37" s="7"/>
+      <c r="AX37" s="7"/>
+      <c r="AY37" s="7"/>
+      <c r="AZ37" s="7"/>
+      <c r="BA37" s="7"/>
+      <c r="BB37" s="7"/>
+      <c r="BC37" s="7"/>
+      <c r="BD37" s="7"/>
+      <c r="BE37" s="7"/>
+      <c r="BF37" s="7"/>
+      <c r="BG37" s="7"/>
+      <c r="BH37" s="7"/>
+      <c r="BI37" s="7"/>
+      <c r="BJ37" s="7"/>
+      <c r="BK37" s="7"/>
+      <c r="BL37" s="7"/>
+      <c r="BM37" s="7"/>
+      <c r="BN37" s="7"/>
+      <c r="BO37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP37" s="13"/>
+      <c r="BQ37" s="13"/>
+      <c r="BR37" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="BS37" s="13"/>
+      <c r="BT37" s="13"/>
+      <c r="BU37" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="BV37" s="13"/>
+      <c r="BW37" s="13"/>
+      <c r="BX37" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="BY37" s="13"/>
+      <c r="BZ37" s="13"/>
+      <c r="CA37" s="7"/>
+      <c r="CB37" s="7"/>
+      <c r="CC37" s="7"/>
+      <c r="CD37" s="7"/>
+      <c r="CE37" s="7"/>
+      <c r="CF37" s="7"/>
+      <c r="CG37" s="7"/>
+      <c r="CH37" s="7"/>
+      <c r="CI37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
+      <c r="V38" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="W38" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="X38" s="7"/>
+      <c r="Y38" s="7"/>
+      <c r="Z38" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA38" s="7"/>
+      <c r="AB38" s="7"/>
+      <c r="AC38" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD38" s="7"/>
+      <c r="AE38" s="7"/>
+      <c r="AF38" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG38" s="7"/>
+      <c r="AH38" s="7"/>
+      <c r="AI38" s="11"/>
+      <c r="AJ38" s="11"/>
+      <c r="AK38" s="11"/>
+      <c r="AL38" s="6"/>
+      <c r="AM38" s="6"/>
+      <c r="AN38" s="6"/>
+      <c r="AO38" s="11"/>
+      <c r="AP38" s="11"/>
+      <c r="AQ38" s="11"/>
+      <c r="AS38" s="7"/>
+      <c r="AT38" s="7"/>
+      <c r="AU38" s="7"/>
+      <c r="AV38" s="7"/>
+      <c r="AW38" s="7"/>
+      <c r="AX38" s="7"/>
+      <c r="AY38" s="7"/>
+      <c r="AZ38" s="7"/>
+      <c r="BA38" s="7"/>
+      <c r="BB38" s="7"/>
+      <c r="BC38" s="7"/>
+      <c r="BD38" s="7"/>
+      <c r="BE38" s="7"/>
+      <c r="BF38" s="7"/>
+      <c r="BG38" s="7"/>
+      <c r="BH38" s="7"/>
+      <c r="BI38" s="7"/>
+      <c r="BJ38" s="7"/>
+      <c r="BK38" s="7"/>
+      <c r="BL38" s="7"/>
+      <c r="BM38" s="7"/>
+      <c r="BN38" s="7"/>
+      <c r="BO38" s="7"/>
+      <c r="BP38" s="7"/>
+      <c r="BQ38" s="7"/>
+      <c r="BR38" s="7"/>
+      <c r="BS38" s="7"/>
+      <c r="BT38" s="7"/>
+      <c r="BU38" s="7"/>
+      <c r="BV38" s="7"/>
+      <c r="BW38" s="7"/>
+      <c r="BX38" s="7"/>
+      <c r="BY38" s="7"/>
+      <c r="BZ38" s="7"/>
+      <c r="CA38" s="11"/>
+      <c r="CB38" s="11"/>
+      <c r="CC38" s="11"/>
+      <c r="CD38" s="6"/>
+      <c r="CE38" s="6"/>
+      <c r="CF38" s="6"/>
+      <c r="CG38" s="11"/>
+      <c r="CH38" s="11"/>
+      <c r="CI38" s="11"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
+      <c r="V39" s="7"/>
+      <c r="W39" s="7"/>
+      <c r="X39" s="7"/>
+      <c r="Y39" s="7"/>
+      <c r="Z39" s="7"/>
+      <c r="AA39" s="7"/>
+      <c r="AB39" s="7"/>
+      <c r="AC39" s="7"/>
+      <c r="AD39" s="7"/>
+      <c r="AE39" s="7"/>
+      <c r="AF39" s="7"/>
+      <c r="AG39" s="7"/>
+      <c r="AH39" s="7"/>
+      <c r="AI39" s="6"/>
+      <c r="AJ39" s="6"/>
+      <c r="AK39" s="6"/>
+      <c r="AL39" s="6"/>
+      <c r="AM39" s="6"/>
+      <c r="AN39" s="6"/>
+      <c r="AO39" s="6"/>
+      <c r="AP39" s="6"/>
+      <c r="AQ39" s="6"/>
+      <c r="AS39" s="7"/>
+      <c r="AT39" s="7"/>
+      <c r="AU39" s="7"/>
+      <c r="AV39" s="7"/>
+      <c r="AW39" s="7"/>
+      <c r="AX39" s="7"/>
+      <c r="AY39" s="7"/>
+      <c r="AZ39" s="7"/>
+      <c r="BA39" s="7"/>
+      <c r="BB39" s="7"/>
+      <c r="BC39" s="7"/>
+      <c r="BD39" s="7"/>
+      <c r="BE39" s="7"/>
+      <c r="BF39" s="7"/>
+      <c r="BG39" s="7"/>
+      <c r="BH39" s="7"/>
+      <c r="BI39" s="7"/>
+      <c r="BJ39" s="7"/>
+      <c r="BK39" s="7"/>
+      <c r="BL39" s="7"/>
+      <c r="BM39" s="7"/>
+      <c r="BN39" s="7"/>
+      <c r="BO39" s="7"/>
+      <c r="BP39" s="7"/>
+      <c r="BQ39" s="7"/>
+      <c r="BR39" s="7"/>
+      <c r="BS39" s="7"/>
+      <c r="BT39" s="7"/>
+      <c r="BU39" s="7"/>
+      <c r="BV39" s="7"/>
+      <c r="BW39" s="7"/>
+      <c r="BX39" s="7"/>
+      <c r="BY39" s="7"/>
+      <c r="BZ39" s="7"/>
+      <c r="CA39" s="6"/>
+      <c r="CB39" s="6"/>
+      <c r="CC39" s="6"/>
+      <c r="CD39" s="6"/>
+      <c r="CE39" s="6"/>
+      <c r="CF39" s="6"/>
+      <c r="CG39" s="24"/>
+      <c r="CH39" s="24"/>
+      <c r="CI39" s="24"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="27"/>
+      <c r="I40" s="27"/>
+      <c r="J40" s="27"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+      <c r="W40" s="27"/>
+      <c r="X40" s="27"/>
+      <c r="Y40" s="27"/>
+      <c r="Z40" s="27"/>
+      <c r="AA40" s="27"/>
+      <c r="AB40" s="27"/>
+      <c r="AC40" s="27"/>
+      <c r="AD40" s="27"/>
+      <c r="AE40" s="27"/>
+      <c r="AF40" s="27"/>
+      <c r="AG40" s="27"/>
+      <c r="AH40" s="27"/>
+      <c r="AI40" s="27"/>
+      <c r="AJ40" s="27"/>
+      <c r="AK40" s="27"/>
+      <c r="AL40" s="27"/>
+      <c r="AM40" s="27"/>
+      <c r="AN40" s="27"/>
+      <c r="AO40" s="27"/>
+      <c r="AP40" s="27"/>
+      <c r="AQ40" s="28"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="4"/>
+      <c r="AA41" s="4"/>
+      <c r="AB41" s="4"/>
+      <c r="AC41" s="4"/>
+      <c r="AD41" s="4"/>
+      <c r="AE41" s="4"/>
+      <c r="AF41" s="4"/>
+      <c r="AG41" s="4"/>
+      <c r="AH41" s="4"/>
+      <c r="AI41" s="4"/>
+      <c r="AJ41" s="4"/>
+      <c r="AK41" s="4"/>
+      <c r="AL41" s="4"/>
+      <c r="AM41" s="4"/>
+      <c r="AN41" s="4"/>
+      <c r="AO41" s="4"/>
+      <c r="AP41" s="4"/>
+      <c r="AQ41" s="5"/>
+      <c r="AS41" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="AT41" s="15"/>
+      <c r="AU41" s="4"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="4"/>
+      <c r="AX41" s="4"/>
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="4"/>
+      <c r="BA41" s="4"/>
+      <c r="BB41" s="4"/>
+      <c r="BC41" s="4"/>
+      <c r="BD41" s="4"/>
+      <c r="BE41" s="4"/>
+      <c r="BF41" s="4"/>
+      <c r="BG41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="6"/>
+      <c r="AF42" s="6"/>
+      <c r="AG42" s="6"/>
+      <c r="AH42" s="6"/>
+      <c r="AI42" s="6"/>
+      <c r="AJ42" s="6"/>
+      <c r="AK42" s="6"/>
+      <c r="AL42" s="6"/>
+      <c r="AM42" s="6"/>
+      <c r="AN42" s="6"/>
+      <c r="AO42" s="6"/>
+      <c r="AP42" s="6"/>
+      <c r="AQ42" s="6"/>
+      <c r="AS42" s="6"/>
+      <c r="AT42" s="6"/>
+      <c r="AU42" s="6"/>
+      <c r="AV42" s="6"/>
+      <c r="AW42" s="6"/>
+      <c r="AX42" s="6"/>
+      <c r="AY42" s="6"/>
+      <c r="AZ42" s="6"/>
+      <c r="BA42" s="6"/>
+      <c r="BB42" s="6"/>
+      <c r="BC42" s="6"/>
+      <c r="BD42" s="6"/>
+      <c r="BE42" s="6"/>
+      <c r="BF42" s="6"/>
+      <c r="BG42" s="6"/>
+      <c r="BH42" s="6"/>
+      <c r="BI42" s="6"/>
+      <c r="BJ42" s="6"/>
+      <c r="BK42" s="6"/>
+      <c r="BL42" s="6"/>
+      <c r="BM42" s="6"/>
+      <c r="BN42" s="6"/>
+      <c r="BO42" s="6"/>
+      <c r="BP42" s="6"/>
+      <c r="BQ42" s="6"/>
+      <c r="BR42" s="6"/>
+      <c r="BS42" s="6"/>
+      <c r="BT42" s="6"/>
+      <c r="BU42" s="6"/>
+      <c r="BV42" s="6"/>
+      <c r="BW42" s="6"/>
+      <c r="BX42" s="6"/>
+      <c r="BY42" s="6"/>
+      <c r="BZ42" s="6"/>
+      <c r="CA42" s="6"/>
+      <c r="CB42" s="6"/>
+      <c r="CC42" s="6"/>
+      <c r="CD42" s="6"/>
+      <c r="CE42" s="6"/>
+      <c r="CF42" s="6"/>
+      <c r="CG42" s="6"/>
+      <c r="CH42" s="6"/>
+      <c r="CI42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="13"/>
+      <c r="R43" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="S43" s="13"/>
+      <c r="T43" s="13"/>
+      <c r="U43" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="V43" s="13"/>
+      <c r="W43" s="13"/>
+      <c r="X43" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y43" s="6"/>
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AB43" s="7"/>
+      <c r="AC43" s="7"/>
+      <c r="AD43" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="AE43" s="7"/>
+      <c r="AF43" s="7"/>
+      <c r="AG43" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH43" s="29"/>
+      <c r="AI43" s="29"/>
+      <c r="AJ43" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK43" s="29"/>
+      <c r="AL43" s="29"/>
+      <c r="AM43" s="6"/>
+      <c r="AN43" s="6"/>
+      <c r="AO43" s="6"/>
+      <c r="AP43" s="6"/>
+      <c r="AQ43" s="6"/>
+      <c r="AS43" s="6"/>
+      <c r="AT43" s="6"/>
+      <c r="AU43" s="6"/>
+      <c r="AV43" s="6"/>
+      <c r="AW43" s="6"/>
+      <c r="AX43" s="29"/>
+      <c r="AY43" s="29"/>
+      <c r="AZ43" s="29"/>
+      <c r="BA43" s="6"/>
+      <c r="BB43" s="6"/>
+      <c r="BC43" s="6"/>
+      <c r="BD43" s="6"/>
+      <c r="BE43" s="6"/>
+      <c r="BF43" s="6"/>
+      <c r="BG43" s="6"/>
+      <c r="BH43" s="6"/>
+      <c r="BI43" s="6"/>
+      <c r="BJ43" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="BK43" s="13"/>
+      <c r="BL43" s="13"/>
+      <c r="BM43" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="BN43" s="13"/>
+      <c r="BO43" s="13"/>
+      <c r="BP43" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="BQ43" s="6"/>
+      <c r="BR43" s="6"/>
+      <c r="BS43" s="6"/>
+      <c r="BT43" s="6"/>
+      <c r="BU43" s="6"/>
+      <c r="BV43" s="7"/>
+      <c r="BW43" s="7"/>
+      <c r="BX43" s="7"/>
+      <c r="BY43" s="13"/>
+      <c r="BZ43" s="13"/>
+      <c r="CA43" s="13"/>
+      <c r="CB43" s="13"/>
+      <c r="CC43" s="13"/>
+      <c r="CD43" s="13"/>
+      <c r="CE43" s="6"/>
+      <c r="CF43" s="6"/>
+      <c r="CG43" s="6"/>
+      <c r="CH43" s="6"/>
+      <c r="CI43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q44" s="13"/>
+      <c r="R44" s="13"/>
+      <c r="S44" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
+      <c r="V44" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W44" s="8"/>
+      <c r="X44" s="8"/>
+      <c r="Y44" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z44" s="6"/>
+      <c r="AA44" s="6"/>
+      <c r="AB44" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC44" s="6"/>
+      <c r="AD44" s="6"/>
+      <c r="AE44" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="AF44" s="13"/>
+      <c r="AG44" s="13"/>
+      <c r="AH44" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="AI44" s="29"/>
+      <c r="AJ44" s="29"/>
+      <c r="AK44" s="13"/>
+      <c r="AL44" s="13"/>
+      <c r="AM44" s="13"/>
+      <c r="AN44" s="9"/>
+      <c r="AO44" s="9"/>
+      <c r="AP44" s="9"/>
+      <c r="AQ44" s="9"/>
+      <c r="AS44" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT44" s="7"/>
+      <c r="AU44" s="7"/>
+      <c r="AV44" s="6"/>
+      <c r="AW44" s="6"/>
+      <c r="AX44" s="6"/>
+      <c r="AY44" s="6"/>
+      <c r="AZ44" s="6"/>
+      <c r="BA44" s="6"/>
+      <c r="BB44" s="6"/>
+      <c r="BC44" s="6"/>
+      <c r="BD44" s="6"/>
+      <c r="BE44" s="8"/>
+      <c r="BF44" s="8"/>
+      <c r="BG44" s="8"/>
+      <c r="BH44" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BI44" s="13"/>
+      <c r="BJ44" s="13"/>
+      <c r="BK44" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="BL44" s="19"/>
+      <c r="BM44" s="19"/>
+      <c r="BN44" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="BO44" s="8"/>
+      <c r="BP44" s="8"/>
+      <c r="BQ44" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="BR44" s="6"/>
+      <c r="BS44" s="6"/>
+      <c r="BT44" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="BU44" s="6"/>
+      <c r="BV44" s="6"/>
+      <c r="BW44" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="BX44" s="13"/>
+      <c r="BY44" s="13"/>
+      <c r="BZ44" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="CA44" s="29"/>
+      <c r="CB44" s="29"/>
+      <c r="CC44" s="13"/>
+      <c r="CD44" s="13"/>
+      <c r="CE44" s="13"/>
+      <c r="CF44" s="9"/>
+      <c r="CG44" s="9"/>
+      <c r="CH44" s="9"/>
+      <c r="CI44" s="9"/>
+    </row>
+    <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="O45" s="13"/>
+      <c r="P45" s="13"/>
+      <c r="Q45" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="R45" s="13"/>
+      <c r="S45" s="13"/>
+      <c r="T45" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="U45" s="7"/>
+      <c r="V45" s="7"/>
+      <c r="W45" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="X45" s="7"/>
+      <c r="Y45" s="7"/>
+      <c r="Z45" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA45" s="7"/>
+      <c r="AB45" s="7"/>
+      <c r="AC45" s="21"/>
+      <c r="AD45" s="21"/>
+      <c r="AE45" s="21"/>
+      <c r="AF45" s="13"/>
+      <c r="AG45" s="13"/>
+      <c r="AH45" s="13"/>
+      <c r="AI45" s="6"/>
+      <c r="AJ45" s="6"/>
+      <c r="AK45" s="6"/>
+      <c r="AL45" s="6"/>
+      <c r="AM45" s="6"/>
+      <c r="AN45" s="6"/>
+      <c r="AO45" s="6"/>
+      <c r="AP45" s="6"/>
+      <c r="AQ45" s="6"/>
+      <c r="AS45" s="7"/>
+      <c r="AT45" s="7"/>
+      <c r="AU45" s="7"/>
+      <c r="AV45" s="7"/>
+      <c r="AW45" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="AX45" s="13"/>
+      <c r="AY45" s="13"/>
+      <c r="AZ45" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="BA45" s="13"/>
+      <c r="BB45" s="13"/>
+      <c r="BC45" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="BD45" s="13"/>
+      <c r="BE45" s="13"/>
+      <c r="BF45" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="BG45" s="13"/>
+      <c r="BH45" s="13"/>
+      <c r="BI45" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="BJ45" s="13"/>
+      <c r="BK45" s="13"/>
+      <c r="BL45" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="BM45" s="10"/>
+      <c r="BN45" s="10"/>
+      <c r="BO45" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="BP45" s="30"/>
+      <c r="BQ45" s="30"/>
+      <c r="BR45" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="BS45" s="30"/>
+      <c r="BT45" s="30"/>
+      <c r="BU45" s="21"/>
+      <c r="BV45" s="21"/>
+      <c r="BW45" s="21"/>
+      <c r="BX45" s="13"/>
+      <c r="BY45" s="13"/>
+      <c r="BZ45" s="13"/>
+      <c r="CA45" s="6"/>
+      <c r="CB45" s="6"/>
+      <c r="CC45" s="6"/>
+      <c r="CD45" s="6"/>
+      <c r="CE45" s="6"/>
+      <c r="CF45" s="6"/>
+      <c r="CG45" s="6"/>
+      <c r="CH45" s="6"/>
+      <c r="CI45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="7"/>
+      <c r="J46" s="7"/>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
+      <c r="W46" s="7"/>
+      <c r="X46" s="7"/>
+      <c r="Y46" s="7"/>
+      <c r="Z46" s="7"/>
+      <c r="AA46" s="7"/>
+      <c r="AB46" s="7"/>
+      <c r="AC46" s="7"/>
+      <c r="AD46" s="7"/>
+      <c r="AE46" s="7"/>
+      <c r="AF46" s="7"/>
+      <c r="AG46" s="7"/>
+      <c r="AH46" s="7"/>
+      <c r="AI46" s="11"/>
+      <c r="AJ46" s="11"/>
+      <c r="AK46" s="11"/>
+      <c r="AL46" s="6"/>
+      <c r="AM46" s="6"/>
+      <c r="AN46" s="6"/>
+      <c r="AO46" s="11"/>
+      <c r="AP46" s="11"/>
+      <c r="AQ46" s="11"/>
+      <c r="AS46" s="7"/>
+      <c r="AT46" s="7"/>
+      <c r="AU46" s="7"/>
+      <c r="AV46" s="7"/>
+      <c r="AW46" s="7"/>
+      <c r="AX46" s="7"/>
+      <c r="AY46" s="7"/>
+      <c r="AZ46" s="7"/>
+      <c r="BA46" s="7"/>
+      <c r="BB46" s="7"/>
+      <c r="BC46" s="7"/>
+      <c r="BD46" s="7"/>
+      <c r="BE46" s="7"/>
+      <c r="BF46" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="BG46" s="7"/>
+      <c r="BH46" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="BI46" s="7"/>
+      <c r="BJ46" s="7"/>
+      <c r="BK46" s="7"/>
+      <c r="BL46" s="7"/>
+      <c r="BM46" s="7"/>
+      <c r="BN46" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="BO46" s="7"/>
+      <c r="BP46" s="7"/>
+      <c r="BQ46" s="7"/>
+      <c r="BR46" s="7"/>
+      <c r="BS46" s="7"/>
+      <c r="BT46" s="7"/>
+      <c r="BU46" s="7"/>
+      <c r="BV46" s="7"/>
+      <c r="BW46" s="7"/>
+      <c r="BX46" s="7"/>
+      <c r="BY46" s="7"/>
+      <c r="BZ46" s="7"/>
+      <c r="CA46" s="11"/>
+      <c r="CB46" s="11"/>
+      <c r="CC46" s="11"/>
+      <c r="CD46" s="6"/>
+      <c r="CE46" s="6"/>
+      <c r="CF46" s="6"/>
+      <c r="CG46" s="11"/>
+      <c r="CH46" s="11"/>
+      <c r="CI46" s="11"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="7"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
+      <c r="W47" s="7"/>
+      <c r="X47" s="7"/>
+      <c r="Y47" s="7"/>
+      <c r="Z47" s="7"/>
+      <c r="AA47" s="7"/>
+      <c r="AB47" s="7"/>
+      <c r="AC47" s="7"/>
+      <c r="AD47" s="7"/>
+      <c r="AE47" s="7"/>
+      <c r="AF47" s="7"/>
+      <c r="AG47" s="7"/>
+      <c r="AH47" s="7"/>
+      <c r="AI47" s="6"/>
+      <c r="AJ47" s="6"/>
+      <c r="AK47" s="6"/>
+      <c r="AL47" s="6"/>
+      <c r="AM47" s="6"/>
+      <c r="AN47" s="6"/>
+      <c r="AO47" s="6"/>
+      <c r="AP47" s="6"/>
+      <c r="AQ47" s="6"/>
+      <c r="AS47" s="7"/>
+      <c r="AT47" s="7"/>
+      <c r="AU47" s="7"/>
+      <c r="AV47" s="7"/>
+      <c r="AW47" s="7"/>
+      <c r="AX47" s="7"/>
+      <c r="AY47" s="7"/>
+      <c r="AZ47" s="7"/>
+      <c r="BA47" s="7"/>
+      <c r="BB47" s="7"/>
+      <c r="BC47" s="7"/>
+      <c r="BD47" s="7"/>
+      <c r="BE47" s="7"/>
+      <c r="BF47" s="7"/>
+      <c r="BG47" s="7"/>
+      <c r="BH47" s="7"/>
+      <c r="BI47" s="7"/>
+      <c r="BJ47" s="7"/>
+      <c r="BK47" s="7"/>
+      <c r="BL47" s="7"/>
+      <c r="BM47" s="7"/>
+      <c r="BN47" s="7"/>
+      <c r="BO47" s="7"/>
+      <c r="BP47" s="7"/>
+      <c r="BQ47" s="7"/>
+      <c r="BR47" s="7"/>
+      <c r="BS47" s="7"/>
+      <c r="BT47" s="7"/>
+      <c r="BU47" s="7"/>
+      <c r="BV47" s="7"/>
+      <c r="BW47" s="7"/>
+      <c r="BX47" s="7"/>
+      <c r="BY47" s="7"/>
+      <c r="BZ47" s="7"/>
+      <c r="CA47" s="6"/>
+      <c r="CB47" s="6"/>
+      <c r="CC47" s="6"/>
+      <c r="CD47" s="6"/>
+      <c r="CE47" s="6"/>
+      <c r="CF47" s="6"/>
+      <c r="CG47" s="6"/>
+      <c r="CH47" s="6"/>
+      <c r="CI47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="27"/>
+      <c r="I48" s="27"/>
+      <c r="J48" s="27"/>
+      <c r="K48" s="27"/>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="27"/>
+      <c r="P48" s="27"/>
+      <c r="Q48" s="27"/>
+      <c r="R48" s="27"/>
+      <c r="S48" s="27"/>
+      <c r="T48" s="27"/>
+      <c r="U48" s="27"/>
+      <c r="V48" s="27"/>
+      <c r="W48" s="27"/>
+      <c r="X48" s="27"/>
+      <c r="Y48" s="27"/>
+      <c r="Z48" s="27"/>
+      <c r="AA48" s="27"/>
+      <c r="AB48" s="27"/>
+      <c r="AC48" s="27"/>
+      <c r="AD48" s="27"/>
+      <c r="AE48" s="27"/>
+      <c r="AF48" s="27"/>
+      <c r="AG48" s="27"/>
+      <c r="AH48" s="27"/>
+      <c r="AI48" s="27"/>
+      <c r="AJ48" s="27"/>
+      <c r="AK48" s="27"/>
+      <c r="AL48" s="27"/>
+      <c r="AM48" s="27"/>
+      <c r="AN48" s="27"/>
+      <c r="AO48" s="27"/>
+      <c r="AP48" s="27"/>
+      <c r="AQ48" s="28"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="4"/>
+      <c r="AC49" s="4"/>
+      <c r="AD49" s="4"/>
+      <c r="AE49" s="4"/>
+      <c r="AF49" s="4"/>
+      <c r="AG49" s="4"/>
+      <c r="AH49" s="4"/>
+      <c r="AI49" s="4"/>
+      <c r="AJ49" s="4"/>
+      <c r="AK49" s="4"/>
+      <c r="AL49" s="4"/>
+      <c r="AM49" s="4"/>
+      <c r="AN49" s="4"/>
+      <c r="AO49" s="4"/>
+      <c r="AP49" s="4"/>
+      <c r="AQ49" s="5"/>
+      <c r="AS49" s="3"/>
+      <c r="AY49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="2"/>
+      <c r="U50" s="2"/>
+      <c r="V50" s="2"/>
+      <c r="W50" s="2"/>
+      <c r="X50" s="2"/>
+      <c r="Y50" s="2"/>
+      <c r="Z50" s="2"/>
+      <c r="AA50" s="2"/>
+      <c r="AB50" s="2"/>
+      <c r="AC50" s="2"/>
+      <c r="AD50" s="2"/>
+      <c r="AE50" s="2"/>
+      <c r="AF50" s="2"/>
+      <c r="AG50" s="2"/>
+      <c r="AH50" s="2"/>
+      <c r="AI50" s="2"/>
+      <c r="AJ50" s="2"/>
+      <c r="AK50" s="2"/>
+      <c r="AL50" s="2"/>
+      <c r="AM50" s="2"/>
+      <c r="AN50" s="2"/>
+      <c r="AO50" s="2"/>
+      <c r="AP50" s="2"/>
+      <c r="AQ50" s="2"/>
+      <c r="AR50" s="2"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
+      <c r="T51" s="2"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="2"/>
+      <c r="W51" s="2"/>
+      <c r="X51" s="2"/>
+      <c r="Y51" s="2"/>
+      <c r="Z51" s="2"/>
+      <c r="AA51" s="2"/>
+      <c r="AB51" s="2"/>
+      <c r="AC51" s="2"/>
+      <c r="AD51" s="2"/>
+      <c r="AE51" s="2"/>
+      <c r="AF51" s="2"/>
+      <c r="AG51" s="2"/>
+      <c r="AH51" s="2"/>
+      <c r="AI51" s="2"/>
+      <c r="AJ51" s="2"/>
+      <c r="AK51" s="2"/>
+      <c r="AL51" s="2"/>
+      <c r="AM51" s="2"/>
+      <c r="AN51" s="2"/>
+      <c r="AO51" s="2"/>
+      <c r="AP51" s="2"/>
+      <c r="AQ51" s="2"/>
+      <c r="AR51" s="2"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="2"/>
+      <c r="X52" s="2"/>
+      <c r="Y52" s="2"/>
+      <c r="Z52" s="2"/>
+      <c r="AA52" s="2"/>
+      <c r="AB52" s="2"/>
+      <c r="AC52" s="2"/>
+      <c r="AD52" s="2"/>
+      <c r="AE52" s="2"/>
+      <c r="AF52" s="2"/>
+      <c r="AG52" s="2"/>
+      <c r="AH52" s="2"/>
+      <c r="AI52" s="2"/>
+      <c r="AJ52" s="2"/>
+      <c r="AK52" s="2"/>
+      <c r="AL52" s="2"/>
+      <c r="AM52" s="2"/>
+      <c r="AN52" s="2"/>
+      <c r="AO52" s="2"/>
+      <c r="AP52" s="2"/>
+      <c r="AQ52" s="2"/>
+      <c r="AR52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="2"/>
+      <c r="T53" s="2"/>
+      <c r="U53" s="2"/>
+      <c r="V53" s="2"/>
+      <c r="W53" s="2"/>
+      <c r="X53" s="2"/>
+      <c r="Y53" s="2"/>
+      <c r="Z53" s="2"/>
+      <c r="AA53" s="2"/>
+      <c r="AB53" s="2"/>
+      <c r="AC53" s="2"/>
+      <c r="AD53" s="2"/>
+      <c r="AE53" s="2"/>
+      <c r="AF53" s="2"/>
+      <c r="AG53" s="2"/>
+      <c r="AH53" s="2"/>
+      <c r="AI53" s="2"/>
+      <c r="AJ53" s="2"/>
+      <c r="AK53" s="2"/>
+      <c r="AL53" s="2"/>
+      <c r="AM53" s="2"/>
+      <c r="AN53" s="2"/>
+      <c r="AO53" s="2"/>
+      <c r="AP53" s="2"/>
+      <c r="AQ53" s="2"/>
+      <c r="AR53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2"/>
+      <c r="Y54" s="2"/>
+      <c r="Z54" s="2"/>
+      <c r="AA54" s="2"/>
+      <c r="AB54" s="2"/>
+      <c r="AC54" s="2"/>
+      <c r="AD54" s="2"/>
+      <c r="AE54" s="2"/>
+      <c r="AF54" s="2"/>
+      <c r="AG54" s="2"/>
+      <c r="AH54" s="2"/>
+      <c r="AI54" s="2"/>
+      <c r="AJ54" s="2"/>
+      <c r="AK54" s="2"/>
+      <c r="AL54" s="2"/>
+      <c r="AM54" s="2"/>
+      <c r="AN54" s="2"/>
+      <c r="AO54" s="2"/>
+      <c r="AP54" s="2"/>
+      <c r="AQ54" s="2"/>
+      <c r="AR54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+      <c r="T55" s="2"/>
+      <c r="U55" s="2"/>
+      <c r="V55" s="2"/>
+      <c r="W55" s="2"/>
+      <c r="X55" s="2"/>
+      <c r="Y55" s="2"/>
+      <c r="Z55" s="2"/>
+      <c r="AA55" s="2"/>
+      <c r="AB55" s="2"/>
+      <c r="AC55" s="2"/>
+      <c r="AD55" s="2"/>
+      <c r="AE55" s="2"/>
+      <c r="AF55" s="2"/>
+      <c r="AG55" s="2"/>
+      <c r="AH55" s="2"/>
+      <c r="AI55" s="2"/>
+      <c r="AJ55" s="2"/>
+      <c r="AK55" s="2"/>
+      <c r="AL55" s="2"/>
+      <c r="AM55" s="2"/>
+      <c r="AN55" s="2"/>
+      <c r="AO55" s="2"/>
+      <c r="AP55" s="2"/>
+      <c r="AQ55" s="2"/>
+      <c r="AR55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="2"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="2"/>
+      <c r="Z56" s="2"/>
+      <c r="AA56" s="2"/>
+      <c r="AB56" s="2"/>
+      <c r="AC56" s="2"/>
+      <c r="AD56" s="2"/>
+      <c r="AE56" s="2"/>
+      <c r="AF56" s="2"/>
+      <c r="AG56" s="2"/>
+      <c r="AH56" s="2"/>
+      <c r="AI56" s="2"/>
+      <c r="AJ56" s="2"/>
+      <c r="AK56" s="2"/>
+      <c r="AL56" s="2"/>
+      <c r="AM56" s="2"/>
+      <c r="AN56" s="2"/>
+      <c r="AO56" s="2"/>
+      <c r="AP56" s="2"/>
+      <c r="AQ56" s="2"/>
+      <c r="AR56" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="840">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AW2:AY2"/>
+    <mergeCell ref="AZ2:BB2"/>
+    <mergeCell ref="BC2:BE2"/>
+    <mergeCell ref="BF2:BH2"/>
+    <mergeCell ref="BI2:BK2"/>
+    <mergeCell ref="BL2:BN2"/>
+    <mergeCell ref="BO2:BQ2"/>
+    <mergeCell ref="BR2:BT2"/>
+    <mergeCell ref="BU2:BW2"/>
+    <mergeCell ref="BX2:BZ2"/>
+    <mergeCell ref="CA2:CC2"/>
+    <mergeCell ref="CD2:CF2"/>
+    <mergeCell ref="CG2:CI2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AL3"/>
+    <mergeCell ref="AM3:AQ3"/>
+    <mergeCell ref="AS3:AT3"/>
+    <mergeCell ref="AU3:AW3"/>
+    <mergeCell ref="AX3:AZ3"/>
+    <mergeCell ref="BA3:BC3"/>
+    <mergeCell ref="BD3:BF3"/>
+    <mergeCell ref="BG3:BI3"/>
+    <mergeCell ref="BJ3:BL3"/>
+    <mergeCell ref="BM3:BO3"/>
+    <mergeCell ref="BP3:BR3"/>
+    <mergeCell ref="BS3:BU3"/>
+    <mergeCell ref="BV3:BX3"/>
+    <mergeCell ref="BY3:CA3"/>
+    <mergeCell ref="CB3:CD3"/>
+    <mergeCell ref="CE3:CI3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="Y4:AA4"/>
+    <mergeCell ref="AB4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="AH4:AJ4"/>
+    <mergeCell ref="AK4:AM4"/>
+    <mergeCell ref="AN4:AQ4"/>
+    <mergeCell ref="AS4:AU4"/>
+    <mergeCell ref="AV4:AX4"/>
+    <mergeCell ref="AY4:BA4"/>
+    <mergeCell ref="BB4:BD4"/>
+    <mergeCell ref="BE4:BG4"/>
+    <mergeCell ref="BH4:BJ4"/>
+    <mergeCell ref="BK4:BM4"/>
+    <mergeCell ref="BN4:BP4"/>
+    <mergeCell ref="BQ4:BS4"/>
+    <mergeCell ref="BT4:BV4"/>
+    <mergeCell ref="BW4:BY4"/>
+    <mergeCell ref="BZ4:CB4"/>
+    <mergeCell ref="CC4:CE4"/>
+    <mergeCell ref="CF4:CI4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="W5:Y5"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AF5:AH5"/>
+    <mergeCell ref="AI5:AK5"/>
+    <mergeCell ref="AL5:AQ5"/>
+    <mergeCell ref="AS5:AV5"/>
+    <mergeCell ref="AW5:AY5"/>
+    <mergeCell ref="AZ5:BB5"/>
+    <mergeCell ref="BC5:BE5"/>
+    <mergeCell ref="BF5:BH5"/>
+    <mergeCell ref="BI5:BK5"/>
+    <mergeCell ref="BL5:BN5"/>
+    <mergeCell ref="BO5:BQ5"/>
+    <mergeCell ref="BR5:BT5"/>
+    <mergeCell ref="BU5:BW5"/>
+    <mergeCell ref="BX5:BZ5"/>
+    <mergeCell ref="CA5:CC5"/>
+    <mergeCell ref="CD5:CI5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:D7"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="H6:J7"/>
+    <mergeCell ref="K6:M7"/>
+    <mergeCell ref="N6:V7"/>
+    <mergeCell ref="W6:Y7"/>
+    <mergeCell ref="Z6:AB7"/>
+    <mergeCell ref="AC6:AE7"/>
+    <mergeCell ref="AF6:AH7"/>
+    <mergeCell ref="AI6:AK6"/>
+    <mergeCell ref="AL6:AN6"/>
+    <mergeCell ref="AS6:AS7"/>
+    <mergeCell ref="AT6:AV7"/>
+    <mergeCell ref="AW6:AY7"/>
+    <mergeCell ref="AZ6:BB7"/>
+    <mergeCell ref="BC6:BE7"/>
+    <mergeCell ref="BF6:BN7"/>
+    <mergeCell ref="BO6:BQ7"/>
+    <mergeCell ref="BR6:BT7"/>
+    <mergeCell ref="BU6:BW7"/>
+    <mergeCell ref="BX6:BZ7"/>
+    <mergeCell ref="CA6:CC6"/>
+    <mergeCell ref="CD6:CF6"/>
+    <mergeCell ref="AI7:AK7"/>
+    <mergeCell ref="AL7:AN7"/>
+    <mergeCell ref="AO7:AQ7"/>
+    <mergeCell ref="CA7:CC7"/>
+    <mergeCell ref="CD7:CF7"/>
+    <mergeCell ref="CG7:CI7"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="W10:Y10"/>
+    <mergeCell ref="Z10:AB10"/>
+    <mergeCell ref="AC10:AE10"/>
+    <mergeCell ref="AF10:AH10"/>
+    <mergeCell ref="AI10:AK10"/>
+    <mergeCell ref="AL10:AN10"/>
+    <mergeCell ref="AO10:AQ10"/>
+    <mergeCell ref="AT10:AV10"/>
+    <mergeCell ref="AW10:AY10"/>
+    <mergeCell ref="AZ10:BB10"/>
+    <mergeCell ref="BC10:BE10"/>
+    <mergeCell ref="BF10:BH10"/>
+    <mergeCell ref="BI10:BK10"/>
+    <mergeCell ref="BL10:BN10"/>
+    <mergeCell ref="BO10:BQ10"/>
+    <mergeCell ref="BR10:BT10"/>
+    <mergeCell ref="BU10:BW10"/>
+    <mergeCell ref="BX10:BZ10"/>
+    <mergeCell ref="CA10:CC10"/>
+    <mergeCell ref="CD10:CF10"/>
+    <mergeCell ref="CG10:CI10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="R11:T11"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="X11:Z11"/>
+    <mergeCell ref="AA11:AC11"/>
+    <mergeCell ref="AD11:AF11"/>
+    <mergeCell ref="AG11:AI11"/>
+    <mergeCell ref="AJ11:AL11"/>
+    <mergeCell ref="AM11:AQ11"/>
+    <mergeCell ref="AS11:AT11"/>
+    <mergeCell ref="AU11:AW11"/>
+    <mergeCell ref="AX11:AZ11"/>
+    <mergeCell ref="BA11:BC11"/>
+    <mergeCell ref="BD11:BF11"/>
+    <mergeCell ref="BG11:BI11"/>
+    <mergeCell ref="BJ11:BL11"/>
+    <mergeCell ref="BM11:BO11"/>
+    <mergeCell ref="BP11:BR11"/>
+    <mergeCell ref="BS11:BU11"/>
+    <mergeCell ref="BV11:BX11"/>
+    <mergeCell ref="BY11:CA11"/>
+    <mergeCell ref="CB11:CD11"/>
+    <mergeCell ref="CE11:CI11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="P12:R12"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="V12:X12"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB12:AD12"/>
+    <mergeCell ref="AE12:AG12"/>
+    <mergeCell ref="AH12:AJ12"/>
+    <mergeCell ref="AK12:AM12"/>
+    <mergeCell ref="AN12:AQ12"/>
+    <mergeCell ref="AS12:AU12"/>
+    <mergeCell ref="AV12:AX12"/>
+    <mergeCell ref="AY12:BA12"/>
+    <mergeCell ref="BB12:BD12"/>
+    <mergeCell ref="BE12:BG12"/>
+    <mergeCell ref="BH12:BJ12"/>
+    <mergeCell ref="BK12:BM12"/>
+    <mergeCell ref="BN12:BP12"/>
+    <mergeCell ref="BQ12:BS12"/>
+    <mergeCell ref="BT12:BV12"/>
+    <mergeCell ref="BW12:BY12"/>
+    <mergeCell ref="BZ12:CB12"/>
+    <mergeCell ref="CC12:CE12"/>
+    <mergeCell ref="CF12:CI12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="W13:Y13"/>
+    <mergeCell ref="Z13:AB13"/>
+    <mergeCell ref="AC13:AE13"/>
+    <mergeCell ref="AF13:AH13"/>
+    <mergeCell ref="AI13:AK13"/>
+    <mergeCell ref="AL13:AQ13"/>
+    <mergeCell ref="AS13:AV13"/>
+    <mergeCell ref="AW13:AY13"/>
+    <mergeCell ref="AZ13:BB13"/>
+    <mergeCell ref="BC13:BE13"/>
+    <mergeCell ref="BF13:BH13"/>
+    <mergeCell ref="BI13:BK13"/>
+    <mergeCell ref="BL13:BN13"/>
+    <mergeCell ref="BO13:BQ13"/>
+    <mergeCell ref="BR13:BT13"/>
+    <mergeCell ref="BU13:BW13"/>
+    <mergeCell ref="BX13:BZ13"/>
+    <mergeCell ref="CA13:CC13"/>
+    <mergeCell ref="CD13:CI13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:D15"/>
+    <mergeCell ref="E14:G15"/>
+    <mergeCell ref="H14:J15"/>
+    <mergeCell ref="K14:M15"/>
+    <mergeCell ref="N14:V15"/>
+    <mergeCell ref="W14:Y15"/>
+    <mergeCell ref="Z14:AB15"/>
+    <mergeCell ref="AC14:AE15"/>
+    <mergeCell ref="AF14:AH15"/>
+    <mergeCell ref="AI14:AK14"/>
+    <mergeCell ref="AL14:AN14"/>
+    <mergeCell ref="AS14:AS15"/>
+    <mergeCell ref="AT14:AV15"/>
+    <mergeCell ref="AW14:AY15"/>
+    <mergeCell ref="AZ14:BB15"/>
+    <mergeCell ref="BC14:BE15"/>
+    <mergeCell ref="BF14:BN15"/>
+    <mergeCell ref="BO14:BQ15"/>
+    <mergeCell ref="BR14:BT15"/>
+    <mergeCell ref="BU14:BW15"/>
+    <mergeCell ref="BX14:BZ15"/>
+    <mergeCell ref="CA14:CC14"/>
+    <mergeCell ref="CD14:CF14"/>
+    <mergeCell ref="AI15:AK15"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AO15:AQ15"/>
+    <mergeCell ref="CA15:CC15"/>
+    <mergeCell ref="CD15:CF15"/>
+    <mergeCell ref="CG15:CI15"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="W18:Y18"/>
+    <mergeCell ref="Z18:AB18"/>
+    <mergeCell ref="AC18:AE18"/>
+    <mergeCell ref="AF18:AH18"/>
+    <mergeCell ref="AI18:AK18"/>
+    <mergeCell ref="AL18:AN18"/>
+    <mergeCell ref="AO18:AQ18"/>
+    <mergeCell ref="AT18:AV18"/>
+    <mergeCell ref="AW18:AY18"/>
+    <mergeCell ref="AZ18:BB18"/>
+    <mergeCell ref="BC18:BE18"/>
+    <mergeCell ref="BF18:BH18"/>
+    <mergeCell ref="BI18:BK18"/>
+    <mergeCell ref="BL18:BN18"/>
+    <mergeCell ref="BO18:BQ18"/>
+    <mergeCell ref="BR18:BT18"/>
+    <mergeCell ref="BU18:BW18"/>
+    <mergeCell ref="BX18:BZ18"/>
+    <mergeCell ref="CA18:CC18"/>
+    <mergeCell ref="CD18:CF18"/>
+    <mergeCell ref="CG18:CI18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="AA19:AC19"/>
+    <mergeCell ref="AD19:AF19"/>
+    <mergeCell ref="AG19:AI19"/>
+    <mergeCell ref="AJ19:AL19"/>
+    <mergeCell ref="AM19:AQ19"/>
+    <mergeCell ref="AS19:AT19"/>
+    <mergeCell ref="AU19:AW19"/>
+    <mergeCell ref="AX19:AZ19"/>
+    <mergeCell ref="BA19:BC19"/>
+    <mergeCell ref="BD19:BF19"/>
+    <mergeCell ref="BG19:BI19"/>
+    <mergeCell ref="BJ19:BL19"/>
+    <mergeCell ref="BM19:BO19"/>
+    <mergeCell ref="BP19:BR19"/>
+    <mergeCell ref="BS19:BU19"/>
+    <mergeCell ref="BV19:BX19"/>
+    <mergeCell ref="BY19:CA19"/>
+    <mergeCell ref="CB19:CD19"/>
+    <mergeCell ref="CE19:CI19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="V20:X20"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="AB20:AD20"/>
+    <mergeCell ref="AE20:AG20"/>
+    <mergeCell ref="AH20:AJ20"/>
+    <mergeCell ref="AK20:AM20"/>
+    <mergeCell ref="AN20:AQ20"/>
+    <mergeCell ref="AS20:AU20"/>
+    <mergeCell ref="AV20:AX20"/>
+    <mergeCell ref="AY20:BA20"/>
+    <mergeCell ref="BB20:BD20"/>
+    <mergeCell ref="BE20:BG20"/>
+    <mergeCell ref="BH20:BJ20"/>
+    <mergeCell ref="BK20:BM20"/>
+    <mergeCell ref="BN20:BP20"/>
+    <mergeCell ref="BQ20:BS20"/>
+    <mergeCell ref="BT20:BV20"/>
+    <mergeCell ref="BW20:BY20"/>
+    <mergeCell ref="BZ20:CB20"/>
+    <mergeCell ref="CC20:CE20"/>
+    <mergeCell ref="CF20:CI20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="T21:V21"/>
+    <mergeCell ref="W21:Y21"/>
+    <mergeCell ref="Z21:AB21"/>
+    <mergeCell ref="AC21:AE21"/>
+    <mergeCell ref="AF21:AH21"/>
+    <mergeCell ref="AI21:AK21"/>
+    <mergeCell ref="AL21:AQ21"/>
+    <mergeCell ref="AS21:AV21"/>
+    <mergeCell ref="AW21:AY21"/>
+    <mergeCell ref="AZ21:BB21"/>
+    <mergeCell ref="BC21:BE21"/>
+    <mergeCell ref="BF21:BH21"/>
+    <mergeCell ref="BI21:BK21"/>
+    <mergeCell ref="BL21:BN21"/>
+    <mergeCell ref="BO21:BQ21"/>
+    <mergeCell ref="BR21:BT21"/>
+    <mergeCell ref="BU21:BW21"/>
+    <mergeCell ref="BX21:BZ21"/>
+    <mergeCell ref="CA21:CC21"/>
+    <mergeCell ref="CD21:CI21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:D23"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="H22:J23"/>
+    <mergeCell ref="K22:M23"/>
+    <mergeCell ref="N22:V23"/>
+    <mergeCell ref="W22:Y23"/>
+    <mergeCell ref="Z22:AB23"/>
+    <mergeCell ref="AC22:AE23"/>
+    <mergeCell ref="AF22:AH23"/>
+    <mergeCell ref="AI22:AK22"/>
+    <mergeCell ref="AL22:AN22"/>
+    <mergeCell ref="AS22:AS23"/>
+    <mergeCell ref="AT22:AV23"/>
+    <mergeCell ref="AW22:AY23"/>
+    <mergeCell ref="AZ22:BB23"/>
+    <mergeCell ref="BC22:BE23"/>
+    <mergeCell ref="BF22:BN23"/>
+    <mergeCell ref="BO22:BQ23"/>
+    <mergeCell ref="BR22:BT23"/>
+    <mergeCell ref="BU22:BW23"/>
+    <mergeCell ref="BX22:BZ23"/>
+    <mergeCell ref="CA22:CC22"/>
+    <mergeCell ref="CD22:CF22"/>
+    <mergeCell ref="AI23:AK23"/>
+    <mergeCell ref="AL23:AN23"/>
+    <mergeCell ref="AO23:AQ23"/>
+    <mergeCell ref="CA23:CC23"/>
+    <mergeCell ref="CD23:CF23"/>
+    <mergeCell ref="CG23:CI23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="T26:V26"/>
+    <mergeCell ref="W26:Y26"/>
+    <mergeCell ref="Z26:AB26"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="AF26:AH26"/>
+    <mergeCell ref="AI26:AK26"/>
+    <mergeCell ref="AL26:AN26"/>
+    <mergeCell ref="AO26:AQ26"/>
+    <mergeCell ref="AT26:AV26"/>
+    <mergeCell ref="AW26:AY26"/>
+    <mergeCell ref="AZ26:BB26"/>
+    <mergeCell ref="BC26:BE26"/>
+    <mergeCell ref="BF26:BH26"/>
+    <mergeCell ref="BI26:BK26"/>
+    <mergeCell ref="BL26:BN26"/>
+    <mergeCell ref="BO26:BQ26"/>
+    <mergeCell ref="BR26:BT26"/>
+    <mergeCell ref="BU26:BW26"/>
+    <mergeCell ref="BX26:BZ26"/>
+    <mergeCell ref="CA26:CC26"/>
+    <mergeCell ref="CD26:CF26"/>
+    <mergeCell ref="CG26:CI26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="R27:T27"/>
+    <mergeCell ref="U27:W27"/>
+    <mergeCell ref="X27:Z27"/>
+    <mergeCell ref="AA27:AC27"/>
+    <mergeCell ref="AD27:AF27"/>
+    <mergeCell ref="AG27:AI27"/>
+    <mergeCell ref="AJ27:AL27"/>
+    <mergeCell ref="AM27:AQ27"/>
+    <mergeCell ref="AS27:AT27"/>
+    <mergeCell ref="AU27:AW27"/>
+    <mergeCell ref="AX27:AZ27"/>
+    <mergeCell ref="BA27:BC27"/>
+    <mergeCell ref="BD27:BF27"/>
+    <mergeCell ref="BG27:BI27"/>
+    <mergeCell ref="BJ27:BL27"/>
+    <mergeCell ref="BM27:BO27"/>
+    <mergeCell ref="BP27:BR27"/>
+    <mergeCell ref="BS27:BU27"/>
+    <mergeCell ref="BV27:BX27"/>
+    <mergeCell ref="BY27:CA27"/>
+    <mergeCell ref="CB27:CD27"/>
+    <mergeCell ref="CE27:CI27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="P28:R28"/>
+    <mergeCell ref="S28:U28"/>
+    <mergeCell ref="V28:X28"/>
+    <mergeCell ref="Y28:AA28"/>
+    <mergeCell ref="AB28:AD28"/>
+    <mergeCell ref="AE28:AG28"/>
+    <mergeCell ref="AH28:AJ28"/>
+    <mergeCell ref="AK28:AM28"/>
+    <mergeCell ref="AN28:AQ28"/>
+    <mergeCell ref="AS28:AU28"/>
+    <mergeCell ref="AV28:AX28"/>
+    <mergeCell ref="AY28:BA28"/>
+    <mergeCell ref="BB28:BD28"/>
+    <mergeCell ref="BE28:BG28"/>
+    <mergeCell ref="BH28:BJ28"/>
+    <mergeCell ref="BK28:BM28"/>
+    <mergeCell ref="BN28:BP28"/>
+    <mergeCell ref="BQ28:BS28"/>
+    <mergeCell ref="BT28:BV28"/>
+    <mergeCell ref="BW28:BY28"/>
+    <mergeCell ref="BZ28:CB28"/>
+    <mergeCell ref="CC28:CE28"/>
+    <mergeCell ref="CF28:CI28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="K29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="T29:V29"/>
+    <mergeCell ref="W29:Y29"/>
+    <mergeCell ref="Z29:AB29"/>
+    <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="AF29:AH29"/>
+    <mergeCell ref="AI29:AK29"/>
+    <mergeCell ref="AL29:AQ29"/>
+    <mergeCell ref="AS29:AV29"/>
+    <mergeCell ref="AW29:AY29"/>
+    <mergeCell ref="AZ29:BB29"/>
+    <mergeCell ref="BC29:BE29"/>
+    <mergeCell ref="BF29:BH29"/>
+    <mergeCell ref="BI29:BK29"/>
+    <mergeCell ref="BL29:BN29"/>
+    <mergeCell ref="BO29:BQ29"/>
+    <mergeCell ref="BR29:BT29"/>
+    <mergeCell ref="BU29:BW29"/>
+    <mergeCell ref="BX29:BZ29"/>
+    <mergeCell ref="CA29:CC29"/>
+    <mergeCell ref="CD29:CI29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:D31"/>
+    <mergeCell ref="E30:G31"/>
+    <mergeCell ref="H30:J31"/>
+    <mergeCell ref="K30:M31"/>
+    <mergeCell ref="N30:V31"/>
+    <mergeCell ref="W30:Y31"/>
+    <mergeCell ref="Z30:AB31"/>
+    <mergeCell ref="AC30:AE31"/>
+    <mergeCell ref="AF30:AH31"/>
+    <mergeCell ref="AI30:AK30"/>
+    <mergeCell ref="AL30:AN30"/>
+    <mergeCell ref="AS30:AS31"/>
+    <mergeCell ref="AT30:AV31"/>
+    <mergeCell ref="AW30:AY31"/>
+    <mergeCell ref="AZ30:BB31"/>
+    <mergeCell ref="BC30:BE31"/>
+    <mergeCell ref="BF30:BN31"/>
+    <mergeCell ref="BO30:BQ31"/>
+    <mergeCell ref="BR30:BT31"/>
+    <mergeCell ref="BU30:BW31"/>
+    <mergeCell ref="BX30:BZ31"/>
+    <mergeCell ref="CA30:CC30"/>
+    <mergeCell ref="CD30:CF30"/>
+    <mergeCell ref="AI31:AK31"/>
+    <mergeCell ref="AL31:AN31"/>
+    <mergeCell ref="AO31:AQ31"/>
+    <mergeCell ref="CA31:CC31"/>
+    <mergeCell ref="CD31:CF31"/>
+    <mergeCell ref="CG31:CI31"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="K34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="T34:V34"/>
+    <mergeCell ref="W34:Y34"/>
+    <mergeCell ref="Z34:AB34"/>
+    <mergeCell ref="AC34:AE34"/>
+    <mergeCell ref="AF34:AH34"/>
+    <mergeCell ref="AI34:AK34"/>
+    <mergeCell ref="AL34:AN34"/>
+    <mergeCell ref="AO34:AQ34"/>
+    <mergeCell ref="AT34:AV34"/>
+    <mergeCell ref="AW34:AY34"/>
+    <mergeCell ref="AZ34:BB34"/>
+    <mergeCell ref="BC34:BE34"/>
+    <mergeCell ref="BF34:BH34"/>
+    <mergeCell ref="BI34:BK34"/>
+    <mergeCell ref="BL34:BN34"/>
+    <mergeCell ref="BO34:BQ34"/>
+    <mergeCell ref="BR34:BT34"/>
+    <mergeCell ref="BU34:BW34"/>
+    <mergeCell ref="BX34:BZ34"/>
+    <mergeCell ref="CA34:CC34"/>
+    <mergeCell ref="CD34:CF34"/>
+    <mergeCell ref="CG34:CI34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="U35:W35"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="AA35:AC35"/>
+    <mergeCell ref="AD35:AF35"/>
+    <mergeCell ref="AG35:AI35"/>
+    <mergeCell ref="AJ35:AL35"/>
+    <mergeCell ref="AM35:AQ35"/>
+    <mergeCell ref="AS35:AT35"/>
+    <mergeCell ref="AU35:AW35"/>
+    <mergeCell ref="AX35:AZ35"/>
+    <mergeCell ref="BA35:BC35"/>
+    <mergeCell ref="BD35:BF35"/>
+    <mergeCell ref="BG35:BI35"/>
+    <mergeCell ref="BJ35:BL35"/>
+    <mergeCell ref="BM35:BO35"/>
+    <mergeCell ref="BP35:BR35"/>
+    <mergeCell ref="BS35:BU35"/>
+    <mergeCell ref="BV35:BX35"/>
+    <mergeCell ref="BY35:CA35"/>
+    <mergeCell ref="CB35:CD35"/>
+    <mergeCell ref="CE35:CI35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="P36:R36"/>
+    <mergeCell ref="S36:U36"/>
+    <mergeCell ref="V36:X36"/>
+    <mergeCell ref="Y36:AA36"/>
+    <mergeCell ref="AB36:AD36"/>
+    <mergeCell ref="AE36:AG36"/>
+    <mergeCell ref="AH36:AJ36"/>
+    <mergeCell ref="AK36:AM36"/>
+    <mergeCell ref="AN36:AQ36"/>
+    <mergeCell ref="AS36:AU36"/>
+    <mergeCell ref="AV36:AX36"/>
+    <mergeCell ref="AY36:BA36"/>
+    <mergeCell ref="BB36:BD36"/>
+    <mergeCell ref="BE36:BG36"/>
+    <mergeCell ref="BH36:BJ36"/>
+    <mergeCell ref="BK36:BM36"/>
+    <mergeCell ref="BN36:BP36"/>
+    <mergeCell ref="BQ36:BS36"/>
+    <mergeCell ref="BT36:BV36"/>
+    <mergeCell ref="BW36:BY36"/>
+    <mergeCell ref="BZ36:CB36"/>
+    <mergeCell ref="CC36:CE36"/>
+    <mergeCell ref="CF36:CI36"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="H37:J37"/>
+    <mergeCell ref="K37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="T37:V37"/>
+    <mergeCell ref="W37:Y37"/>
+    <mergeCell ref="Z37:AB37"/>
+    <mergeCell ref="AC37:AE37"/>
+    <mergeCell ref="AF37:AH37"/>
+    <mergeCell ref="AI37:AK37"/>
+    <mergeCell ref="AL37:AQ37"/>
+    <mergeCell ref="AS37:AV37"/>
+    <mergeCell ref="AW37:AY37"/>
+    <mergeCell ref="AZ37:BB37"/>
+    <mergeCell ref="BC37:BE37"/>
+    <mergeCell ref="BF37:BH37"/>
+    <mergeCell ref="BI37:BK37"/>
+    <mergeCell ref="BL37:BN37"/>
+    <mergeCell ref="BO37:BQ37"/>
+    <mergeCell ref="BR37:BT37"/>
+    <mergeCell ref="BU37:BW37"/>
+    <mergeCell ref="BX37:BZ37"/>
+    <mergeCell ref="CA37:CC37"/>
+    <mergeCell ref="CD37:CI37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:D39"/>
+    <mergeCell ref="E38:G39"/>
+    <mergeCell ref="H38:J39"/>
+    <mergeCell ref="K38:M39"/>
+    <mergeCell ref="N38:V39"/>
+    <mergeCell ref="W38:Y39"/>
+    <mergeCell ref="Z38:AB39"/>
+    <mergeCell ref="AC38:AE39"/>
+    <mergeCell ref="AF38:AH39"/>
+    <mergeCell ref="AI38:AK38"/>
+    <mergeCell ref="AL38:AN38"/>
+    <mergeCell ref="AS38:AS39"/>
+    <mergeCell ref="AT38:AV39"/>
+    <mergeCell ref="AW38:AY39"/>
+    <mergeCell ref="AZ38:BB39"/>
+    <mergeCell ref="BC38:BE39"/>
+    <mergeCell ref="BF38:BN39"/>
+    <mergeCell ref="BO38:BQ39"/>
+    <mergeCell ref="BR38:BT39"/>
+    <mergeCell ref="BU38:BW39"/>
+    <mergeCell ref="BX38:BZ39"/>
+    <mergeCell ref="CA38:CC38"/>
+    <mergeCell ref="CD38:CF38"/>
+    <mergeCell ref="AI39:AK39"/>
+    <mergeCell ref="AL39:AN39"/>
+    <mergeCell ref="AO39:AQ39"/>
+    <mergeCell ref="CA39:CC39"/>
+    <mergeCell ref="CD39:CF39"/>
+    <mergeCell ref="CG39:CI39"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="K42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="T42:V42"/>
+    <mergeCell ref="W42:Y42"/>
+    <mergeCell ref="Z42:AB42"/>
+    <mergeCell ref="AC42:AE42"/>
+    <mergeCell ref="AF42:AH42"/>
+    <mergeCell ref="AI42:AK42"/>
+    <mergeCell ref="AL42:AN42"/>
+    <mergeCell ref="AO42:AQ42"/>
+    <mergeCell ref="AT42:AV42"/>
+    <mergeCell ref="AW42:AY42"/>
+    <mergeCell ref="AZ42:BB42"/>
+    <mergeCell ref="BC42:BE42"/>
+    <mergeCell ref="BF42:BH42"/>
+    <mergeCell ref="BI42:BK42"/>
+    <mergeCell ref="BL42:BN42"/>
+    <mergeCell ref="BO42:BQ42"/>
+    <mergeCell ref="BR42:BT42"/>
+    <mergeCell ref="BU42:BW42"/>
+    <mergeCell ref="BX42:BZ42"/>
+    <mergeCell ref="CA42:CC42"/>
+    <mergeCell ref="CD42:CF42"/>
+    <mergeCell ref="CG42:CI42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="O43:Q43"/>
+    <mergeCell ref="R43:T43"/>
+    <mergeCell ref="U43:W43"/>
+    <mergeCell ref="X43:Z43"/>
+    <mergeCell ref="AA43:AC43"/>
+    <mergeCell ref="AD43:AF43"/>
+    <mergeCell ref="AG43:AI43"/>
+    <mergeCell ref="AJ43:AL43"/>
+    <mergeCell ref="AM43:AQ43"/>
+    <mergeCell ref="AS43:AT43"/>
+    <mergeCell ref="AU43:AW43"/>
+    <mergeCell ref="AX43:AZ43"/>
+    <mergeCell ref="BA43:BC43"/>
+    <mergeCell ref="BD43:BF43"/>
+    <mergeCell ref="BG43:BI43"/>
+    <mergeCell ref="BJ43:BL43"/>
+    <mergeCell ref="BM43:BO43"/>
+    <mergeCell ref="BP43:BR43"/>
+    <mergeCell ref="BS43:BU43"/>
+    <mergeCell ref="BV43:BX43"/>
+    <mergeCell ref="BY43:CA43"/>
+    <mergeCell ref="CB43:CD43"/>
+    <mergeCell ref="CE43:CI43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="G44:I44"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="P44:R44"/>
+    <mergeCell ref="S44:U44"/>
+    <mergeCell ref="V44:X44"/>
+    <mergeCell ref="Y44:AA44"/>
+    <mergeCell ref="AB44:AD44"/>
+    <mergeCell ref="AE44:AG44"/>
+    <mergeCell ref="AH44:AJ44"/>
+    <mergeCell ref="AK44:AM44"/>
+    <mergeCell ref="AN44:AQ44"/>
+    <mergeCell ref="AS44:AU44"/>
+    <mergeCell ref="AV44:AX44"/>
+    <mergeCell ref="AY44:BA44"/>
+    <mergeCell ref="BB44:BD44"/>
+    <mergeCell ref="BE44:BG44"/>
+    <mergeCell ref="BH44:BJ44"/>
+    <mergeCell ref="BK44:BM44"/>
+    <mergeCell ref="BN44:BP44"/>
+    <mergeCell ref="BQ44:BS44"/>
+    <mergeCell ref="BT44:BV44"/>
+    <mergeCell ref="BW44:BY44"/>
+    <mergeCell ref="BZ44:CB44"/>
+    <mergeCell ref="CC44:CE44"/>
+    <mergeCell ref="CF44:CI44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="K45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="T45:V45"/>
+    <mergeCell ref="W45:Y45"/>
+    <mergeCell ref="Z45:AB45"/>
+    <mergeCell ref="AC45:AE45"/>
+    <mergeCell ref="AF45:AH45"/>
+    <mergeCell ref="AI45:AK45"/>
+    <mergeCell ref="AL45:AQ45"/>
+    <mergeCell ref="AS45:AV45"/>
+    <mergeCell ref="AW45:AY45"/>
+    <mergeCell ref="AZ45:BB45"/>
+    <mergeCell ref="BC45:BE45"/>
+    <mergeCell ref="BF45:BH45"/>
+    <mergeCell ref="BI45:BK45"/>
+    <mergeCell ref="BL45:BN45"/>
+    <mergeCell ref="BO45:BQ45"/>
+    <mergeCell ref="BR45:BT45"/>
+    <mergeCell ref="BU45:BW45"/>
+    <mergeCell ref="BX45:BZ45"/>
+    <mergeCell ref="CA45:CC45"/>
+    <mergeCell ref="CD45:CI45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:D47"/>
+    <mergeCell ref="E46:G47"/>
+    <mergeCell ref="H46:J47"/>
+    <mergeCell ref="K46:M47"/>
+    <mergeCell ref="N46:V47"/>
+    <mergeCell ref="W46:Y47"/>
+    <mergeCell ref="Z46:AB47"/>
+    <mergeCell ref="AC46:AE47"/>
+    <mergeCell ref="AF46:AH47"/>
+    <mergeCell ref="AI46:AK46"/>
+    <mergeCell ref="AL46:AN46"/>
+    <mergeCell ref="AS46:AS47"/>
+    <mergeCell ref="AT46:AV47"/>
+    <mergeCell ref="AW46:AY47"/>
+    <mergeCell ref="AZ46:BB47"/>
+    <mergeCell ref="BC46:BE47"/>
+    <mergeCell ref="BF46:BN47"/>
+    <mergeCell ref="BO46:BQ47"/>
+    <mergeCell ref="BR46:BT47"/>
+    <mergeCell ref="BU46:BW47"/>
+    <mergeCell ref="BX46:BZ47"/>
+    <mergeCell ref="CA46:CC46"/>
+    <mergeCell ref="CD46:CF46"/>
+    <mergeCell ref="AI47:AK47"/>
+    <mergeCell ref="AL47:AN47"/>
+    <mergeCell ref="AO47:AQ47"/>
+    <mergeCell ref="CA47:CC47"/>
+    <mergeCell ref="CD47:CF47"/>
+    <mergeCell ref="CG47:CI47"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,標準"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,標準"&amp;12ページ &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:CI47"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -8676,7 +14898,7 @@
       <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
@@ -8770,7 +14992,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
@@ -9439,7 +15661,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -9645,7 +15867,7 @@
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -9700,7 +15922,7 @@
       <c r="CC19" s="7"/>
       <c r="CD19" s="7"/>
       <c r="CE19" s="6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
@@ -10481,7 +16703,7 @@
       <c r="AK27" s="13"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -10534,7 +16756,7 @@
       <c r="CC27" s="7"/>
       <c r="CD27" s="7"/>
       <c r="CE27" s="6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="CF27" s="6"/>
       <c r="CG27" s="6"/>
@@ -11306,7 +17528,7 @@
       <c r="AK35" s="13"/>
       <c r="AL35" s="13"/>
       <c r="AM35" s="6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -11363,7 +17585,7 @@
       <c r="CC35" s="7"/>
       <c r="CD35" s="7"/>
       <c r="CE35" s="6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="CF35" s="6"/>
       <c r="CG35" s="6"/>
@@ -12854,7 +19076,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -12917,7 +19139,7 @@
       <c r="AP1" s="4"/>
       <c r="AQ1" s="5"/>
       <c r="AT1" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -13200,7 +19422,7 @@
         <v>161</v>
       </c>
       <c r="AT4" s="7" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="AU4" s="7"/>
       <c r="AV4" s="7"/>
@@ -13208,7 +19430,7 @@
       <c r="AX4" s="8"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="BA4" s="8" t="s">
         <v>56</v>
@@ -13297,8 +19519,8 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
-      <c r="AR5" s="29" t="s">
-        <v>192</v>
+      <c r="AR5" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
@@ -13307,7 +19529,7 @@
       <c r="AX5" s="7"/>
       <c r="AY5" s="7"/>
       <c r="AZ5" s="6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="BA5" s="7" t="s">
         <v>172</v>
@@ -13367,10 +19589,10 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
@@ -13413,7 +19635,7 @@
       <c r="AW6" s="7"/>
       <c r="AX6" s="7"/>
       <c r="AY6" s="7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="AZ6" s="7"/>
       <c r="BA6" s="7"/>
@@ -13422,7 +19644,7 @@
       <c r="BD6" s="6"/>
       <c r="BE6" s="11"/>
       <c r="BF6" s="6" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="BG6" s="11"/>
       <c r="BH6" s="11"/>
@@ -13487,7 +19709,7 @@
         <v>172</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="BG7" s="6" t="s">
         <v>173</v>
@@ -13541,7 +19763,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -14104,8 +20326,8 @@
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
-      <c r="AR13" s="29" t="s">
-        <v>192</v>
+      <c r="AR13" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
@@ -14218,10 +20440,10 @@
       </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -14500,7 +20722,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -14971,8 +21193,8 @@
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
-      <c r="AR21" s="29" t="s">
-        <v>192</v>
+      <c r="AR21" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
@@ -15081,10 +21303,10 @@
       </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
@@ -15797,8 +22019,8 @@
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
-      <c r="AR29" s="29" t="s">
-        <v>192</v>
+      <c r="AR29" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
@@ -15895,10 +22117,10 @@
       </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -15965,7 +22187,7 @@
       </c>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="BR30" s="7"/>
       <c r="BS30" s="7"/>
@@ -16470,7 +22692,7 @@
       <c r="AR36" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="AT36" s="30" t="s">
+      <c r="AT36" s="32" t="s">
         <v>34</v>
       </c>
       <c r="AU36" s="13" t="s">
@@ -16576,8 +22798,8 @@
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
-      <c r="AR37" s="29" t="s">
-        <v>192</v>
+      <c r="AR37" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="AT37" s="7" t="s">
         <v>35</v>
@@ -16660,10 +22882,10 @@
       </c>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -16698,17 +22920,17 @@
       <c r="AW38" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AX38" s="30" t="s">
+      <c r="AX38" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="AY38" s="30" t="s">
+      <c r="AY38" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="AZ38" s="30"/>
-      <c r="BA38" s="30" t="s">
+      <c r="AZ38" s="32"/>
+      <c r="BA38" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="BB38" s="30" t="s">
+      <c r="BB38" s="32" t="s">
         <v>107</v>
       </c>
       <c r="BC38" s="11"/>
@@ -16771,9 +22993,9 @@
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
-      <c r="AZ39" s="30"/>
-      <c r="BA39" s="30"/>
-      <c r="BB39" s="30"/>
+      <c r="AZ39" s="32"/>
+      <c r="BA39" s="32"/>
+      <c r="BB39" s="32"/>
       <c r="BC39" s="11"/>
       <c r="BD39" s="6"/>
       <c r="BE39" s="6"/>
@@ -17737,7 +23959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -18018,8 +24240,8 @@
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="29" t="s">
-        <v>192</v>
+      <c r="P5" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -18150,7 +24372,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -18305,7 +24527,7 @@
       <c r="Z11" s="13"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="13"/>
-      <c r="AC11" s="31"/>
+      <c r="AC11" s="33"/>
       <c r="AD11" s="21"/>
       <c r="AE11" s="6"/>
       <c r="AF11" s="6"/>
@@ -18413,8 +24635,8 @@
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
-      <c r="P13" s="29" t="s">
-        <v>192</v>
+      <c r="P13" s="31" t="s">
+        <v>198</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="13"/>
@@ -18622,8 +24844,8 @@
       <c r="M19" s="13"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
-      <c r="P19" s="32" t="s">
-        <v>198</v>
+      <c r="P19" s="34" t="s">
+        <v>204</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -18642,7 +24864,7 @@
       <c r="AF19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -18725,11 +24947,11 @@
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="30"/>
+      <c r="V22" s="32"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
-      <c r="Y22" s="33"/>
-      <c r="Z22" s="33"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="11"/>
@@ -18757,11 +24979,11 @@
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
       <c r="X23" s="7"/>
-      <c r="Y23" s="33"/>
-      <c r="Z23" s="33"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
@@ -18898,7 +25120,7 @@
       <c r="M28" s="13"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="R28" s="30"/>
+      <c r="R28" s="32"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -18952,8 +25174,8 @@
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="11"/>
@@ -18966,9 +25188,9 @@
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="30"/>
-      <c r="X30" s="30"/>
+      <c r="V30" s="32"/>
+      <c r="W30" s="32"/>
+      <c r="X30" s="32"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="11"/>
@@ -18985,7 +25207,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="30"/>
+      <c r="G31" s="32"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="11"/>
@@ -19000,7 +25222,7 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="30"/>
+      <c r="X31" s="32"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="7"/>
       <c r="AA31" s="11"/>
@@ -19063,7 +25285,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -19139,7 +25361,7 @@
       <c r="M36" s="13"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="R36" s="30"/>
+      <c r="R36" s="32"/>
       <c r="S36" s="13"/>
       <c r="T36" s="13"/>
       <c r="U36" s="13"/>
@@ -19178,7 +25400,7 @@
       <c r="V37" s="13"/>
       <c r="W37" s="13"/>
       <c r="X37" s="18"/>
-      <c r="Y37" s="35"/>
+      <c r="Y37" s="36"/>
       <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
@@ -19193,8 +25415,8 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="11"/>
@@ -19207,11 +25429,11 @@
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
-      <c r="V38" s="30"/>
-      <c r="W38" s="30"/>
-      <c r="X38" s="30"/>
-      <c r="Y38" s="30"/>
-      <c r="Z38" s="30"/>
+      <c r="V38" s="32"/>
+      <c r="W38" s="32"/>
+      <c r="X38" s="32"/>
+      <c r="Y38" s="32"/>
+      <c r="Z38" s="32"/>
       <c r="AA38" s="11"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="11"/>
@@ -19226,7 +25448,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="30"/>
+      <c r="G39" s="32"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="11"/>
@@ -19241,9 +25463,9 @@
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
-      <c r="X39" s="30"/>
-      <c r="Y39" s="30"/>
-      <c r="Z39" s="30"/>
+      <c r="X39" s="32"/>
+      <c r="Y39" s="32"/>
+      <c r="Z39" s="32"/>
       <c r="AA39" s="11"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
@@ -19364,7 +25586,7 @@
       <c r="AF43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="30"/>
+      <c r="A44" s="32"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -19379,7 +25601,7 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
-      <c r="R44" s="30"/>
+      <c r="R44" s="32"/>
       <c r="S44" s="13"/>
       <c r="T44" s="13"/>
       <c r="U44" s="13"/>
@@ -19433,8 +25655,8 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
       <c r="J46" s="11"/>
@@ -19447,11 +25669,11 @@
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="32"/>
+      <c r="X46" s="32"/>
+      <c r="Y46" s="32"/>
+      <c r="Z46" s="32"/>
       <c r="AA46" s="11"/>
       <c r="AB46" s="6"/>
       <c r="AC46" s="11"/>
@@ -19466,7 +25688,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="30"/>
+      <c r="G47" s="32"/>
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
       <c r="J47" s="11"/>
@@ -19481,9 +25703,9 @@
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
-      <c r="X47" s="30"/>
-      <c r="Y47" s="30"/>
-      <c r="Z47" s="30"/>
+      <c r="X47" s="32"/>
+      <c r="Y47" s="32"/>
+      <c r="Z47" s="32"/>
       <c r="AA47" s="11"/>
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
@@ -19611,7 +25833,7 @@
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
-      <c r="V52" s="36"/>
+      <c r="V52" s="37"/>
       <c r="W52" s="6"/>
       <c r="X52" s="13"/>
       <c r="Y52" s="14"/>
@@ -19660,11 +25882,11 @@
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="30"/>
+      <c r="E54" s="32"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
       <c r="J54" s="11"/>
       <c r="K54" s="6"/>
       <c r="L54" s="11"/>
@@ -19692,11 +25914,11 @@
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="33"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="35"/>
       <c r="J55" s="11"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="208">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -584,13 +584,17 @@
     <t xml:space="preserve">Space &amp; F13 修飾</t>
   </si>
   <si>
+    <t xml:space="preserve">SelMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StdMode</t>
+  </si>
+  <si>
     <t xml:space="preserve">10Key Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">SelMode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CurMode</t>
+    <t xml:space="preserve">SelCur
+Togle</t>
   </si>
   <si>
     <t xml:space="preserve">Cursor Mode</t>
@@ -599,7 +603,49 @@
     <t xml:space="preserve">Select Mode</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">CurMode</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">C+x
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">CurMode</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">C+c
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">CurMode</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve"> (</t>
@@ -896,7 +942,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1015,6 +1061,14 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -8353,11 +8407,11 @@
       </c>
       <c r="BV6" s="7"/>
       <c r="BW6" s="7"/>
-      <c r="BX6" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="BY6" s="7"/>
-      <c r="BZ6" s="7"/>
+      <c r="BX6" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="BY6" s="29"/>
+      <c r="BZ6" s="29"/>
       <c r="CA6" s="11"/>
       <c r="CB6" s="11"/>
       <c r="CC6" s="11"/>
@@ -8453,9 +8507,9 @@
       <c r="BU7" s="7"/>
       <c r="BV7" s="7"/>
       <c r="BW7" s="7"/>
-      <c r="BX7" s="7"/>
-      <c r="BY7" s="7"/>
-      <c r="BZ7" s="7"/>
+      <c r="BX7" s="29"/>
+      <c r="BY7" s="29"/>
+      <c r="BZ7" s="29"/>
       <c r="CA7" s="6" t="s">
         <v>56</v>
       </c>
@@ -9738,11 +9792,11 @@
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
-      <c r="J20" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
+      <c r="J20" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
       <c r="M20" s="20" t="s">
         <v>7</v>
       </c>
@@ -10553,11 +10607,11 @@
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
-      <c r="J28" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
+      <c r="J28" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
       <c r="M28" s="20" t="s">
         <v>7</v>
       </c>
@@ -10607,7 +10661,9 @@
       <c r="AO28" s="9"/>
       <c r="AP28" s="9"/>
       <c r="AQ28" s="9"/>
-      <c r="AS28" s="7"/>
+      <c r="AS28" s="7" t="s">
+        <v>187</v>
+      </c>
       <c r="AT28" s="7"/>
       <c r="AU28" s="7"/>
       <c r="AV28" s="7"/>
@@ -10852,7 +10908,9 @@
       <c r="BC30" s="7"/>
       <c r="BD30" s="7"/>
       <c r="BE30" s="7"/>
-      <c r="BF30" s="7"/>
+      <c r="BF30" s="7" t="s">
+        <v>187</v>
+      </c>
       <c r="BG30" s="7"/>
       <c r="BH30" s="7"/>
       <c r="BI30" s="7"/>
@@ -10870,9 +10928,11 @@
       <c r="BU30" s="7"/>
       <c r="BV30" s="7"/>
       <c r="BW30" s="7"/>
-      <c r="BX30" s="7"/>
-      <c r="BY30" s="7"/>
-      <c r="BZ30" s="7"/>
+      <c r="BX30" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="BY30" s="29"/>
+      <c r="BZ30" s="29"/>
       <c r="CA30" s="11"/>
       <c r="CB30" s="11"/>
       <c r="CC30" s="11"/>
@@ -10960,9 +11020,9 @@
       <c r="BU31" s="7"/>
       <c r="BV31" s="7"/>
       <c r="BW31" s="7"/>
-      <c r="BX31" s="7"/>
-      <c r="BY31" s="7"/>
-      <c r="BZ31" s="7"/>
+      <c r="BX31" s="29"/>
+      <c r="BY31" s="29"/>
+      <c r="BZ31" s="29"/>
       <c r="CA31" s="6" t="s">
         <v>172</v>
       </c>
@@ -11071,7 +11131,7 @@
       <c r="AP33" s="4"/>
       <c r="AQ33" s="5"/>
       <c r="AS33" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AT33" s="5"/>
       <c r="AU33" s="4"/>
@@ -11395,7 +11455,7 @@
       <c r="AF36" s="13"/>
       <c r="AG36" s="13"/>
       <c r="AH36" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AI36" s="29"/>
       <c r="AJ36" s="29"/>
@@ -11408,7 +11468,9 @@
       <c r="AO36" s="9"/>
       <c r="AP36" s="9"/>
       <c r="AQ36" s="9"/>
-      <c r="AS36" s="7"/>
+      <c r="AS36" s="7" t="s">
+        <v>187</v>
+      </c>
       <c r="AT36" s="7"/>
       <c r="AU36" s="7"/>
       <c r="AV36" s="7"/>
@@ -11521,11 +11583,9 @@
       </c>
       <c r="AG37" s="13"/>
       <c r="AH37" s="13"/>
-      <c r="AI37" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="AJ37" s="29"/>
-      <c r="AK37" s="29"/>
+      <c r="AI37" s="6"/>
+      <c r="AJ37" s="6"/>
+      <c r="AK37" s="6"/>
       <c r="AL37" s="6" t="s">
         <v>35</v>
       </c>
@@ -11586,7 +11646,7 @@
       <c r="CH37" s="7"/>
       <c r="CI37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
         <v>46</v>
       </c>
@@ -11636,11 +11696,11 @@
       </c>
       <c r="AD38" s="7"/>
       <c r="AE38" s="7"/>
-      <c r="AF38" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG38" s="7"/>
-      <c r="AH38" s="7"/>
+      <c r="AF38" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="AG38" s="30"/>
+      <c r="AH38" s="30"/>
       <c r="AI38" s="11"/>
       <c r="AJ38" s="11"/>
       <c r="AK38" s="11"/>
@@ -11663,7 +11723,9 @@
       <c r="BC38" s="7"/>
       <c r="BD38" s="7"/>
       <c r="BE38" s="7"/>
-      <c r="BF38" s="7"/>
+      <c r="BF38" s="7" t="s">
+        <v>187</v>
+      </c>
       <c r="BG38" s="7"/>
       <c r="BH38" s="7"/>
       <c r="BI38" s="7"/>
@@ -11681,9 +11743,11 @@
       <c r="BU38" s="7"/>
       <c r="BV38" s="7"/>
       <c r="BW38" s="7"/>
-      <c r="BX38" s="7"/>
-      <c r="BY38" s="7"/>
-      <c r="BZ38" s="7"/>
+      <c r="BX38" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="BY38" s="29"/>
+      <c r="BZ38" s="29"/>
       <c r="CA38" s="11"/>
       <c r="CB38" s="11"/>
       <c r="CC38" s="11"/>
@@ -11726,9 +11790,9 @@
       <c r="AC39" s="7"/>
       <c r="AD39" s="7"/>
       <c r="AE39" s="7"/>
-      <c r="AF39" s="7"/>
-      <c r="AG39" s="7"/>
-      <c r="AH39" s="7"/>
+      <c r="AF39" s="30"/>
+      <c r="AG39" s="30"/>
+      <c r="AH39" s="30"/>
       <c r="AI39" s="6"/>
       <c r="AJ39" s="6"/>
       <c r="AK39" s="6"/>
@@ -11769,9 +11833,9 @@
       <c r="BU39" s="7"/>
       <c r="BV39" s="7"/>
       <c r="BW39" s="7"/>
-      <c r="BX39" s="7"/>
-      <c r="BY39" s="7"/>
-      <c r="BZ39" s="7"/>
+      <c r="BX39" s="29"/>
+      <c r="BY39" s="29"/>
+      <c r="BZ39" s="29"/>
       <c r="CA39" s="6"/>
       <c r="CB39" s="6"/>
       <c r="CC39" s="6"/>
@@ -11826,7 +11890,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -11871,7 +11935,7 @@
       <c r="AP41" s="4"/>
       <c r="AQ41" s="5"/>
       <c r="AS41" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AT41" s="15"/>
       <c r="AU41" s="4"/>
@@ -11979,21 +12043,23 @@
     <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13"/>
-      <c r="Q43" s="13"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
+      <c r="Q43" s="6"/>
       <c r="R43" s="13" t="s">
         <v>138</v>
       </c>
@@ -12039,12 +12105,14 @@
       <c r="AU43" s="6"/>
       <c r="AV43" s="6"/>
       <c r="AW43" s="6"/>
-      <c r="AX43" s="29"/>
-      <c r="AY43" s="29"/>
-      <c r="AZ43" s="29"/>
-      <c r="BA43" s="6"/>
-      <c r="BB43" s="6"/>
-      <c r="BC43" s="6"/>
+      <c r="AX43" s="6"/>
+      <c r="AY43" s="6"/>
+      <c r="AZ43" s="6"/>
+      <c r="BA43" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="BB43" s="29"/>
+      <c r="BC43" s="29"/>
       <c r="BD43" s="6"/>
       <c r="BE43" s="6"/>
       <c r="BF43" s="6"/>
@@ -12069,15 +12137,15 @@
       <c r="BS43" s="6"/>
       <c r="BT43" s="6"/>
       <c r="BU43" s="6"/>
-      <c r="BV43" s="7"/>
-      <c r="BW43" s="7"/>
-      <c r="BX43" s="7"/>
-      <c r="BY43" s="13"/>
-      <c r="BZ43" s="13"/>
-      <c r="CA43" s="13"/>
-      <c r="CB43" s="13"/>
-      <c r="CC43" s="13"/>
-      <c r="CD43" s="13"/>
+      <c r="BV43" s="6"/>
+      <c r="BW43" s="6"/>
+      <c r="BX43" s="6"/>
+      <c r="BY43" s="6"/>
+      <c r="BZ43" s="6"/>
+      <c r="CA43" s="6"/>
+      <c r="CB43" s="6"/>
+      <c r="CC43" s="6"/>
+      <c r="CD43" s="6"/>
       <c r="CE43" s="6"/>
       <c r="CF43" s="6"/>
       <c r="CG43" s="6"/>
@@ -12090,15 +12158,15 @@
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="13"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
       <c r="M44" s="20"/>
       <c r="N44" s="20"/>
       <c r="O44" s="20"/>
@@ -12128,18 +12196,18 @@
       <c r="AC44" s="6"/>
       <c r="AD44" s="6"/>
       <c r="AE44" s="13" t="s">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="AF44" s="13"/>
       <c r="AG44" s="13"/>
       <c r="AH44" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AI44" s="29"/>
       <c r="AJ44" s="29"/>
-      <c r="AK44" s="13"/>
-      <c r="AL44" s="13"/>
-      <c r="AM44" s="13"/>
+      <c r="AK44" s="6"/>
+      <c r="AL44" s="6"/>
+      <c r="AM44" s="6"/>
       <c r="AN44" s="9"/>
       <c r="AO44" s="9"/>
       <c r="AP44" s="9"/>
@@ -12192,13 +12260,13 @@
       <c r="BX44" s="13"/>
       <c r="BY44" s="13"/>
       <c r="BZ44" s="29" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="CA44" s="29"/>
       <c r="CB44" s="29"/>
-      <c r="CC44" s="13"/>
-      <c r="CD44" s="13"/>
-      <c r="CE44" s="13"/>
+      <c r="CC44" s="6"/>
+      <c r="CD44" s="6"/>
+      <c r="CE44" s="6"/>
       <c r="CF44" s="9"/>
       <c r="CG44" s="9"/>
       <c r="CH44" s="9"/>
@@ -12249,12 +12317,12 @@
       </c>
       <c r="AA45" s="7"/>
       <c r="AB45" s="7"/>
-      <c r="AC45" s="21"/>
-      <c r="AD45" s="21"/>
-      <c r="AE45" s="21"/>
-      <c r="AF45" s="13"/>
-      <c r="AG45" s="13"/>
-      <c r="AH45" s="13"/>
+      <c r="AC45" s="6"/>
+      <c r="AD45" s="6"/>
+      <c r="AE45" s="6"/>
+      <c r="AF45" s="6"/>
+      <c r="AG45" s="6"/>
+      <c r="AH45" s="6"/>
       <c r="AI45" s="6"/>
       <c r="AJ45" s="6"/>
       <c r="AK45" s="6"/>
@@ -12273,16 +12341,16 @@
       </c>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
-      <c r="AZ45" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="BA45" s="13"/>
-      <c r="BB45" s="13"/>
-      <c r="BC45" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="BD45" s="13"/>
-      <c r="BE45" s="13"/>
+      <c r="AZ45" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="BA45" s="31"/>
+      <c r="BB45" s="31"/>
+      <c r="BC45" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="BD45" s="31"/>
+      <c r="BE45" s="31"/>
       <c r="BF45" s="13" t="s">
         <v>157</v>
       </c>
@@ -12298,22 +12366,22 @@
       </c>
       <c r="BM45" s="10"/>
       <c r="BN45" s="10"/>
-      <c r="BO45" s="30" t="s">
+      <c r="BO45" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="BP45" s="30"/>
-      <c r="BQ45" s="30"/>
-      <c r="BR45" s="30" t="s">
+      <c r="BP45" s="32"/>
+      <c r="BQ45" s="32"/>
+      <c r="BR45" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="BS45" s="30"/>
-      <c r="BT45" s="30"/>
-      <c r="BU45" s="21"/>
-      <c r="BV45" s="21"/>
-      <c r="BW45" s="21"/>
-      <c r="BX45" s="13"/>
-      <c r="BY45" s="13"/>
-      <c r="BZ45" s="13"/>
+      <c r="BS45" s="32"/>
+      <c r="BT45" s="32"/>
+      <c r="BU45" s="6"/>
+      <c r="BV45" s="6"/>
+      <c r="BW45" s="6"/>
+      <c r="BX45" s="6"/>
+      <c r="BY45" s="6"/>
+      <c r="BZ45" s="6"/>
       <c r="CA45" s="6"/>
       <c r="CB45" s="6"/>
       <c r="CC45" s="6"/>
@@ -12356,9 +12424,11 @@
       <c r="AC46" s="7"/>
       <c r="AD46" s="7"/>
       <c r="AE46" s="7"/>
-      <c r="AF46" s="7"/>
-      <c r="AG46" s="7"/>
-      <c r="AH46" s="7"/>
+      <c r="AF46" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="AG46" s="29"/>
+      <c r="AH46" s="29"/>
       <c r="AI46" s="11"/>
       <c r="AJ46" s="11"/>
       <c r="AK46" s="11"/>
@@ -12405,9 +12475,11 @@
       <c r="BU46" s="7"/>
       <c r="BV46" s="7"/>
       <c r="BW46" s="7"/>
-      <c r="BX46" s="7"/>
-      <c r="BY46" s="7"/>
-      <c r="BZ46" s="7"/>
+      <c r="BX46" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="BY46" s="29"/>
+      <c r="BZ46" s="29"/>
       <c r="CA46" s="11"/>
       <c r="CB46" s="11"/>
       <c r="CC46" s="11"/>
@@ -12450,9 +12522,9 @@
       <c r="AC47" s="7"/>
       <c r="AD47" s="7"/>
       <c r="AE47" s="7"/>
-      <c r="AF47" s="7"/>
-      <c r="AG47" s="7"/>
-      <c r="AH47" s="7"/>
+      <c r="AF47" s="29"/>
+      <c r="AG47" s="29"/>
+      <c r="AH47" s="29"/>
       <c r="AI47" s="6"/>
       <c r="AJ47" s="6"/>
       <c r="AK47" s="6"/>
@@ -12493,9 +12565,9 @@
       <c r="BU47" s="7"/>
       <c r="BV47" s="7"/>
       <c r="BW47" s="7"/>
-      <c r="BX47" s="7"/>
-      <c r="BY47" s="7"/>
-      <c r="BZ47" s="7"/>
+      <c r="BX47" s="29"/>
+      <c r="BY47" s="29"/>
+      <c r="BZ47" s="29"/>
       <c r="CA47" s="6"/>
       <c r="CB47" s="6"/>
       <c r="CC47" s="6"/>
@@ -14898,7 +14970,7 @@
       <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
@@ -14992,7 +15064,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
@@ -15661,7 +15733,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -15867,7 +15939,7 @@
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -15922,7 +15994,7 @@
       <c r="CC19" s="7"/>
       <c r="CD19" s="7"/>
       <c r="CE19" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
@@ -16703,7 +16775,7 @@
       <c r="AK27" s="13"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -16756,7 +16828,7 @@
       <c r="CC27" s="7"/>
       <c r="CD27" s="7"/>
       <c r="CE27" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="CF27" s="6"/>
       <c r="CG27" s="6"/>
@@ -17528,7 +17600,7 @@
       <c r="AK35" s="13"/>
       <c r="AL35" s="13"/>
       <c r="AM35" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -17585,7 +17657,7 @@
       <c r="CC35" s="7"/>
       <c r="CD35" s="7"/>
       <c r="CE35" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="CF35" s="6"/>
       <c r="CG35" s="6"/>
@@ -19139,7 +19211,7 @@
       <c r="AP1" s="4"/>
       <c r="AQ1" s="5"/>
       <c r="AT1" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -19422,7 +19494,7 @@
         <v>161</v>
       </c>
       <c r="AT4" s="7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AU4" s="7"/>
       <c r="AV4" s="7"/>
@@ -19430,7 +19502,7 @@
       <c r="AX4" s="8"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="BA4" s="8" t="s">
         <v>56</v>
@@ -19519,8 +19591,8 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
-      <c r="AR5" s="31" t="s">
-        <v>198</v>
+      <c r="AR5" s="33" t="s">
+        <v>201</v>
       </c>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
@@ -19529,7 +19601,7 @@
       <c r="AX5" s="7"/>
       <c r="AY5" s="7"/>
       <c r="AZ5" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="BA5" s="7" t="s">
         <v>172</v>
@@ -19589,10 +19661,10 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
@@ -19635,7 +19707,7 @@
       <c r="AW6" s="7"/>
       <c r="AX6" s="7"/>
       <c r="AY6" s="7" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AZ6" s="7"/>
       <c r="BA6" s="7"/>
@@ -19644,7 +19716,7 @@
       <c r="BD6" s="6"/>
       <c r="BE6" s="11"/>
       <c r="BF6" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="BG6" s="11"/>
       <c r="BH6" s="11"/>
@@ -19709,7 +19781,7 @@
         <v>172</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="BG7" s="6" t="s">
         <v>173</v>
@@ -19763,7 +19835,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -20326,8 +20398,8 @@
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
-      <c r="AR13" s="31" t="s">
-        <v>198</v>
+      <c r="AR13" s="33" t="s">
+        <v>201</v>
       </c>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
@@ -20440,10 +20512,10 @@
       </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -20722,7 +20794,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -21193,8 +21265,8 @@
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
-      <c r="AR21" s="31" t="s">
-        <v>198</v>
+      <c r="AR21" s="33" t="s">
+        <v>201</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
@@ -21303,10 +21375,10 @@
       </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
@@ -22019,8 +22091,8 @@
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
-      <c r="AR29" s="31" t="s">
-        <v>198</v>
+      <c r="AR29" s="33" t="s">
+        <v>201</v>
       </c>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
@@ -22117,10 +22189,10 @@
       </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -22187,7 +22259,7 @@
       </c>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="BR30" s="7"/>
       <c r="BS30" s="7"/>
@@ -22692,7 +22764,7 @@
       <c r="AR36" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="AT36" s="32" t="s">
+      <c r="AT36" s="34" t="s">
         <v>34</v>
       </c>
       <c r="AU36" s="13" t="s">
@@ -22798,8 +22870,8 @@
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
-      <c r="AR37" s="31" t="s">
-        <v>198</v>
+      <c r="AR37" s="33" t="s">
+        <v>201</v>
       </c>
       <c r="AT37" s="7" t="s">
         <v>35</v>
@@ -22882,10 +22954,10 @@
       </c>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -22920,17 +22992,17 @@
       <c r="AW38" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AX38" s="32" t="s">
+      <c r="AX38" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="AY38" s="32" t="s">
+      <c r="AY38" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="AZ38" s="32"/>
-      <c r="BA38" s="32" t="s">
+      <c r="AZ38" s="34"/>
+      <c r="BA38" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="BB38" s="32" t="s">
+      <c r="BB38" s="34" t="s">
         <v>107</v>
       </c>
       <c r="BC38" s="11"/>
@@ -22993,9 +23065,9 @@
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
-      <c r="AZ39" s="32"/>
-      <c r="BA39" s="32"/>
-      <c r="BB39" s="32"/>
+      <c r="AZ39" s="34"/>
+      <c r="BA39" s="34"/>
+      <c r="BB39" s="34"/>
       <c r="BC39" s="11"/>
       <c r="BD39" s="6"/>
       <c r="BE39" s="6"/>
@@ -24240,8 +24312,8 @@
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="31" t="s">
-        <v>198</v>
+      <c r="P5" s="33" t="s">
+        <v>201</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -24372,7 +24444,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -24527,7 +24599,7 @@
       <c r="Z11" s="13"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="13"/>
-      <c r="AC11" s="33"/>
+      <c r="AC11" s="35"/>
       <c r="AD11" s="21"/>
       <c r="AE11" s="6"/>
       <c r="AF11" s="6"/>
@@ -24635,8 +24707,8 @@
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
-      <c r="P13" s="31" t="s">
-        <v>198</v>
+      <c r="P13" s="33" t="s">
+        <v>201</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="13"/>
@@ -24844,8 +24916,8 @@
       <c r="M19" s="13"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
-      <c r="P19" s="34" t="s">
-        <v>204</v>
+      <c r="P19" s="36" t="s">
+        <v>207</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -24864,7 +24936,7 @@
       <c r="AF19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32"/>
+      <c r="A20" s="34"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -24947,11 +25019,11 @@
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="32"/>
+      <c r="V22" s="34"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
+      <c r="Y22" s="37"/>
+      <c r="Z22" s="37"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="11"/>
@@ -24979,11 +25051,11 @@
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="32"/>
+      <c r="V23" s="34"/>
+      <c r="W23" s="34"/>
       <c r="X23" s="7"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
+      <c r="Y23" s="37"/>
+      <c r="Z23" s="37"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
@@ -25120,7 +25192,7 @@
       <c r="M28" s="13"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="R28" s="32"/>
+      <c r="R28" s="34"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -25174,8 +25246,8 @@
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="11"/>
@@ -25188,9 +25260,9 @@
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="32"/>
-      <c r="W30" s="32"/>
-      <c r="X30" s="32"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="X30" s="34"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="11"/>
@@ -25207,7 +25279,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="32"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="11"/>
@@ -25222,7 +25294,7 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="32"/>
+      <c r="X31" s="34"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="7"/>
       <c r="AA31" s="11"/>
@@ -25285,7 +25357,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="30"/>
+      <c r="D34" s="32"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -25361,7 +25433,7 @@
       <c r="M36" s="13"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="R36" s="32"/>
+      <c r="R36" s="34"/>
       <c r="S36" s="13"/>
       <c r="T36" s="13"/>
       <c r="U36" s="13"/>
@@ -25400,7 +25472,7 @@
       <c r="V37" s="13"/>
       <c r="W37" s="13"/>
       <c r="X37" s="18"/>
-      <c r="Y37" s="36"/>
+      <c r="Y37" s="38"/>
       <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
@@ -25415,8 +25487,8 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="11"/>
@@ -25429,11 +25501,11 @@
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
-      <c r="V38" s="32"/>
-      <c r="W38" s="32"/>
-      <c r="X38" s="32"/>
-      <c r="Y38" s="32"/>
-      <c r="Z38" s="32"/>
+      <c r="V38" s="34"/>
+      <c r="W38" s="34"/>
+      <c r="X38" s="34"/>
+      <c r="Y38" s="34"/>
+      <c r="Z38" s="34"/>
       <c r="AA38" s="11"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="11"/>
@@ -25448,7 +25520,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="32"/>
+      <c r="G39" s="34"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="11"/>
@@ -25463,9 +25535,9 @@
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
-      <c r="X39" s="32"/>
-      <c r="Y39" s="32"/>
-      <c r="Z39" s="32"/>
+      <c r="X39" s="34"/>
+      <c r="Y39" s="34"/>
+      <c r="Z39" s="34"/>
       <c r="AA39" s="11"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
@@ -25586,7 +25658,7 @@
       <c r="AF43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="32"/>
+      <c r="A44" s="34"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -25601,7 +25673,7 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
-      <c r="R44" s="32"/>
+      <c r="R44" s="34"/>
       <c r="S44" s="13"/>
       <c r="T44" s="13"/>
       <c r="U44" s="13"/>
@@ -25655,8 +25727,8 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
       <c r="J46" s="11"/>
@@ -25669,11 +25741,11 @@
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
-      <c r="V46" s="32"/>
-      <c r="W46" s="32"/>
-      <c r="X46" s="32"/>
-      <c r="Y46" s="32"/>
-      <c r="Z46" s="32"/>
+      <c r="V46" s="34"/>
+      <c r="W46" s="34"/>
+      <c r="X46" s="34"/>
+      <c r="Y46" s="34"/>
+      <c r="Z46" s="34"/>
       <c r="AA46" s="11"/>
       <c r="AB46" s="6"/>
       <c r="AC46" s="11"/>
@@ -25688,7 +25760,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="32"/>
+      <c r="G47" s="34"/>
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
       <c r="J47" s="11"/>
@@ -25703,9 +25775,9 @@
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
-      <c r="X47" s="32"/>
-      <c r="Y47" s="32"/>
-      <c r="Z47" s="32"/>
+      <c r="X47" s="34"/>
+      <c r="Y47" s="34"/>
+      <c r="Z47" s="34"/>
       <c r="AA47" s="11"/>
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
@@ -25833,7 +25905,7 @@
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
-      <c r="V52" s="37"/>
+      <c r="V52" s="39"/>
       <c r="W52" s="6"/>
       <c r="X52" s="13"/>
       <c r="Y52" s="14"/>
@@ -25882,11 +25954,11 @@
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="32"/>
+      <c r="E54" s="34"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
+      <c r="H54" s="37"/>
+      <c r="I54" s="37"/>
       <c r="J54" s="11"/>
       <c r="K54" s="6"/>
       <c r="L54" s="11"/>
@@ -25914,11 +25986,11 @@
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
+      <c r="H55" s="37"/>
+      <c r="I55" s="37"/>
       <c r="J55" s="11"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="211">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -584,23 +584,36 @@
     <t xml:space="preserve">Space &amp; F13 修飾</t>
   </si>
   <si>
-    <t xml:space="preserve">SelMode</t>
+    <t xml:space="preserve">SelCur
+Togle</t>
   </si>
   <si>
-    <t xml:space="preserve">StdMode</t>
+    <t xml:space="preserve">Select
+Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stdard
+Mode</t>
   </si>
   <si>
     <t xml:space="preserve">10Key Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">SelCur
-Togle</t>
+    <t xml:space="preserve">SelMode</t>
   </si>
   <si>
     <t xml:space="preserve">Cursor Mode</t>
   </si>
   <si>
     <t xml:space="preserve">Select Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal
+Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cursor
+Mode</t>
   </si>
   <si>
     <t xml:space="preserve">CurMode</t>
@@ -942,7 +955,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1060,10 +1073,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8392,26 +8413,26 @@
       <c r="BN6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="BO6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="BP6" s="7"/>
-      <c r="BQ6" s="7"/>
-      <c r="BR6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="BS6" s="7"/>
-      <c r="BT6" s="7"/>
+      <c r="BO6" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="BP6" s="29"/>
+      <c r="BQ6" s="29"/>
+      <c r="BR6" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="BS6" s="29"/>
+      <c r="BT6" s="29"/>
       <c r="BU6" s="7" t="s">
         <v>49</v>
       </c>
       <c r="BV6" s="7"/>
       <c r="BW6" s="7"/>
-      <c r="BX6" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="BY6" s="29"/>
-      <c r="BZ6" s="29"/>
+      <c r="BX6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="BY6" s="7"/>
+      <c r="BZ6" s="7"/>
       <c r="CA6" s="11"/>
       <c r="CB6" s="11"/>
       <c r="CC6" s="11"/>
@@ -8498,18 +8519,18 @@
       <c r="BL7" s="7"/>
       <c r="BM7" s="7"/>
       <c r="BN7" s="7"/>
-      <c r="BO7" s="7"/>
-      <c r="BP7" s="7"/>
-      <c r="BQ7" s="7"/>
-      <c r="BR7" s="7"/>
-      <c r="BS7" s="7"/>
-      <c r="BT7" s="7"/>
+      <c r="BO7" s="29"/>
+      <c r="BP7" s="29"/>
+      <c r="BQ7" s="29"/>
+      <c r="BR7" s="29"/>
+      <c r="BS7" s="29"/>
+      <c r="BT7" s="29"/>
       <c r="BU7" s="7"/>
       <c r="BV7" s="7"/>
       <c r="BW7" s="7"/>
-      <c r="BX7" s="29"/>
-      <c r="BY7" s="29"/>
-      <c r="BZ7" s="29"/>
+      <c r="BX7" s="7"/>
+      <c r="BY7" s="7"/>
+      <c r="BZ7" s="7"/>
       <c r="CA7" s="6" t="s">
         <v>56</v>
       </c>
@@ -9703,16 +9724,16 @@
       </c>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
-      <c r="AG19" s="29" t="s">
+      <c r="AG19" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="AH19" s="29"/>
-      <c r="AI19" s="29"/>
-      <c r="AJ19" s="29" t="s">
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="30"/>
+      <c r="AJ19" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="AK19" s="29"/>
-      <c r="AL19" s="29"/>
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="30"/>
       <c r="AM19" s="6"/>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -9793,7 +9814,7 @@
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
       <c r="J20" s="29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
@@ -10608,7 +10629,7 @@
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
       <c r="J28" s="29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K28" s="29"/>
       <c r="L28" s="29"/>
@@ -10661,11 +10682,11 @@
       <c r="AO28" s="9"/>
       <c r="AP28" s="9"/>
       <c r="AQ28" s="9"/>
-      <c r="AS28" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="AT28" s="7"/>
-      <c r="AU28" s="7"/>
+      <c r="AS28" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="AT28" s="31"/>
+      <c r="AU28" s="31"/>
       <c r="AV28" s="7"/>
       <c r="AW28" s="7"/>
       <c r="AX28" s="7"/>
@@ -10831,7 +10852,7 @@
       <c r="CH29" s="7"/>
       <c r="CI29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
         <v>46</v>
       </c>
@@ -10908,17 +10929,17 @@
       <c r="BC30" s="7"/>
       <c r="BD30" s="7"/>
       <c r="BE30" s="7"/>
-      <c r="BF30" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="BG30" s="7"/>
-      <c r="BH30" s="7"/>
-      <c r="BI30" s="7"/>
-      <c r="BJ30" s="7"/>
-      <c r="BK30" s="7"/>
-      <c r="BL30" s="7"/>
-      <c r="BM30" s="7"/>
-      <c r="BN30" s="7"/>
+      <c r="BF30" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="BG30" s="31"/>
+      <c r="BH30" s="31"/>
+      <c r="BI30" s="31"/>
+      <c r="BJ30" s="31"/>
+      <c r="BK30" s="31"/>
+      <c r="BL30" s="31"/>
+      <c r="BM30" s="31"/>
+      <c r="BN30" s="31"/>
       <c r="BO30" s="7"/>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7"/>
@@ -10928,11 +10949,11 @@
       <c r="BU30" s="7"/>
       <c r="BV30" s="7"/>
       <c r="BW30" s="7"/>
-      <c r="BX30" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="BY30" s="29"/>
-      <c r="BZ30" s="29"/>
+      <c r="BX30" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="BY30" s="32"/>
+      <c r="BZ30" s="32"/>
       <c r="CA30" s="11"/>
       <c r="CB30" s="11"/>
       <c r="CC30" s="11"/>
@@ -11002,15 +11023,15 @@
       <c r="BC31" s="7"/>
       <c r="BD31" s="7"/>
       <c r="BE31" s="7"/>
-      <c r="BF31" s="7"/>
-      <c r="BG31" s="7"/>
-      <c r="BH31" s="7"/>
-      <c r="BI31" s="7"/>
-      <c r="BJ31" s="7"/>
-      <c r="BK31" s="7"/>
-      <c r="BL31" s="7"/>
-      <c r="BM31" s="7"/>
-      <c r="BN31" s="7"/>
+      <c r="BF31" s="31"/>
+      <c r="BG31" s="31"/>
+      <c r="BH31" s="31"/>
+      <c r="BI31" s="31"/>
+      <c r="BJ31" s="31"/>
+      <c r="BK31" s="31"/>
+      <c r="BL31" s="31"/>
+      <c r="BM31" s="31"/>
+      <c r="BN31" s="31"/>
       <c r="BO31" s="7"/>
       <c r="BP31" s="7"/>
       <c r="BQ31" s="7"/>
@@ -11020,9 +11041,9 @@
       <c r="BU31" s="7"/>
       <c r="BV31" s="7"/>
       <c r="BW31" s="7"/>
-      <c r="BX31" s="29"/>
-      <c r="BY31" s="29"/>
-      <c r="BZ31" s="29"/>
+      <c r="BX31" s="32"/>
+      <c r="BY31" s="32"/>
+      <c r="BZ31" s="32"/>
       <c r="CA31" s="6" t="s">
         <v>172</v>
       </c>
@@ -11131,7 +11152,7 @@
       <c r="AP33" s="4"/>
       <c r="AQ33" s="5"/>
       <c r="AS33" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AT33" s="5"/>
       <c r="AU33" s="4"/>
@@ -11327,16 +11348,16 @@
       </c>
       <c r="AE35" s="13"/>
       <c r="AF35" s="13"/>
-      <c r="AG35" s="29" t="s">
+      <c r="AG35" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="AH35" s="29"/>
-      <c r="AI35" s="29"/>
-      <c r="AJ35" s="29" t="s">
+      <c r="AH35" s="30"/>
+      <c r="AI35" s="30"/>
+      <c r="AJ35" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="AK35" s="29"/>
-      <c r="AL35" s="29"/>
+      <c r="AK35" s="30"/>
+      <c r="AL35" s="30"/>
       <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -11454,11 +11475,11 @@
       </c>
       <c r="AF36" s="13"/>
       <c r="AG36" s="13"/>
-      <c r="AH36" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="AI36" s="29"/>
-      <c r="AJ36" s="29"/>
+      <c r="AH36" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI36" s="30"/>
+      <c r="AJ36" s="30"/>
       <c r="AK36" s="13" t="s">
         <v>153</v>
       </c>
@@ -11468,11 +11489,11 @@
       <c r="AO36" s="9"/>
       <c r="AP36" s="9"/>
       <c r="AQ36" s="9"/>
-      <c r="AS36" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="AT36" s="7"/>
-      <c r="AU36" s="7"/>
+      <c r="AS36" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="AT36" s="31"/>
+      <c r="AU36" s="31"/>
       <c r="AV36" s="7"/>
       <c r="AW36" s="7"/>
       <c r="AX36" s="7"/>
@@ -11696,11 +11717,11 @@
       </c>
       <c r="AD38" s="7"/>
       <c r="AE38" s="7"/>
-      <c r="AF38" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="AG38" s="30"/>
-      <c r="AH38" s="30"/>
+      <c r="AF38" s="29" t="s">
+        <v>186</v>
+      </c>
+      <c r="AG38" s="29"/>
+      <c r="AH38" s="29"/>
       <c r="AI38" s="11"/>
       <c r="AJ38" s="11"/>
       <c r="AK38" s="11"/>
@@ -11723,17 +11744,17 @@
       <c r="BC38" s="7"/>
       <c r="BD38" s="7"/>
       <c r="BE38" s="7"/>
-      <c r="BF38" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="BG38" s="7"/>
-      <c r="BH38" s="7"/>
-      <c r="BI38" s="7"/>
-      <c r="BJ38" s="7"/>
-      <c r="BK38" s="7"/>
-      <c r="BL38" s="7"/>
-      <c r="BM38" s="7"/>
-      <c r="BN38" s="7"/>
+      <c r="BF38" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="BG38" s="31"/>
+      <c r="BH38" s="31"/>
+      <c r="BI38" s="31"/>
+      <c r="BJ38" s="31"/>
+      <c r="BK38" s="31"/>
+      <c r="BL38" s="31"/>
+      <c r="BM38" s="31"/>
+      <c r="BN38" s="31"/>
       <c r="BO38" s="7"/>
       <c r="BP38" s="7"/>
       <c r="BQ38" s="7"/>
@@ -11743,11 +11764,11 @@
       <c r="BU38" s="7"/>
       <c r="BV38" s="7"/>
       <c r="BW38" s="7"/>
-      <c r="BX38" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="BY38" s="29"/>
-      <c r="BZ38" s="29"/>
+      <c r="BX38" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="BY38" s="32"/>
+      <c r="BZ38" s="32"/>
       <c r="CA38" s="11"/>
       <c r="CB38" s="11"/>
       <c r="CC38" s="11"/>
@@ -11790,9 +11811,9 @@
       <c r="AC39" s="7"/>
       <c r="AD39" s="7"/>
       <c r="AE39" s="7"/>
-      <c r="AF39" s="30"/>
-      <c r="AG39" s="30"/>
-      <c r="AH39" s="30"/>
+      <c r="AF39" s="29"/>
+      <c r="AG39" s="29"/>
+      <c r="AH39" s="29"/>
       <c r="AI39" s="6"/>
       <c r="AJ39" s="6"/>
       <c r="AK39" s="6"/>
@@ -11815,15 +11836,15 @@
       <c r="BC39" s="7"/>
       <c r="BD39" s="7"/>
       <c r="BE39" s="7"/>
-      <c r="BF39" s="7"/>
-      <c r="BG39" s="7"/>
-      <c r="BH39" s="7"/>
-      <c r="BI39" s="7"/>
-      <c r="BJ39" s="7"/>
-      <c r="BK39" s="7"/>
-      <c r="BL39" s="7"/>
-      <c r="BM39" s="7"/>
-      <c r="BN39" s="7"/>
+      <c r="BF39" s="31"/>
+      <c r="BG39" s="31"/>
+      <c r="BH39" s="31"/>
+      <c r="BI39" s="31"/>
+      <c r="BJ39" s="31"/>
+      <c r="BK39" s="31"/>
+      <c r="BL39" s="31"/>
+      <c r="BM39" s="31"/>
+      <c r="BN39" s="31"/>
       <c r="BO39" s="7"/>
       <c r="BP39" s="7"/>
       <c r="BQ39" s="7"/>
@@ -11833,9 +11854,9 @@
       <c r="BU39" s="7"/>
       <c r="BV39" s="7"/>
       <c r="BW39" s="7"/>
-      <c r="BX39" s="29"/>
-      <c r="BY39" s="29"/>
-      <c r="BZ39" s="29"/>
+      <c r="BX39" s="32"/>
+      <c r="BY39" s="32"/>
+      <c r="BZ39" s="32"/>
       <c r="CA39" s="6"/>
       <c r="CB39" s="6"/>
       <c r="CC39" s="6"/>
@@ -11890,7 +11911,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -11935,7 +11956,7 @@
       <c r="AP41" s="4"/>
       <c r="AQ41" s="5"/>
       <c r="AS41" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AT41" s="15"/>
       <c r="AU41" s="4"/>
@@ -12049,14 +12070,14 @@
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
-      <c r="I43" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
@@ -12085,16 +12106,16 @@
       </c>
       <c r="AE43" s="7"/>
       <c r="AF43" s="7"/>
-      <c r="AG43" s="29" t="s">
+      <c r="AG43" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="AH43" s="29"/>
-      <c r="AI43" s="29"/>
-      <c r="AJ43" s="29" t="s">
+      <c r="AH43" s="30"/>
+      <c r="AI43" s="30"/>
+      <c r="AJ43" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="AK43" s="29"/>
-      <c r="AL43" s="29"/>
+      <c r="AK43" s="30"/>
+      <c r="AL43" s="30"/>
       <c r="AM43" s="6"/>
       <c r="AN43" s="6"/>
       <c r="AO43" s="6"/>
@@ -12108,14 +12129,14 @@
       <c r="AX43" s="6"/>
       <c r="AY43" s="6"/>
       <c r="AZ43" s="6"/>
-      <c r="BA43" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="BB43" s="29"/>
-      <c r="BC43" s="29"/>
-      <c r="BD43" s="6"/>
-      <c r="BE43" s="6"/>
-      <c r="BF43" s="6"/>
+      <c r="BA43" s="6"/>
+      <c r="BB43" s="6"/>
+      <c r="BC43" s="6"/>
+      <c r="BD43" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="BE43" s="32"/>
+      <c r="BF43" s="32"/>
       <c r="BG43" s="6"/>
       <c r="BH43" s="6"/>
       <c r="BI43" s="6"/>
@@ -12164,9 +12185,11 @@
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
+      <c r="J44" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="K44" s="32"/>
+      <c r="L44" s="32"/>
       <c r="M44" s="20"/>
       <c r="N44" s="20"/>
       <c r="O44" s="20"/>
@@ -12200,11 +12223,11 @@
       </c>
       <c r="AF44" s="13"/>
       <c r="AG44" s="13"/>
-      <c r="AH44" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="AI44" s="29"/>
-      <c r="AJ44" s="29"/>
+      <c r="AH44" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI44" s="30"/>
+      <c r="AJ44" s="30"/>
       <c r="AK44" s="6"/>
       <c r="AL44" s="6"/>
       <c r="AM44" s="6"/>
@@ -12223,9 +12246,11 @@
       <c r="AY44" s="6"/>
       <c r="AZ44" s="6"/>
       <c r="BA44" s="6"/>
-      <c r="BB44" s="6"/>
-      <c r="BC44" s="6"/>
-      <c r="BD44" s="6"/>
+      <c r="BB44" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="BC44" s="32"/>
+      <c r="BD44" s="32"/>
       <c r="BE44" s="8"/>
       <c r="BF44" s="8"/>
       <c r="BG44" s="8"/>
@@ -12259,11 +12284,11 @@
       </c>
       <c r="BX44" s="13"/>
       <c r="BY44" s="13"/>
-      <c r="BZ44" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="CA44" s="29"/>
-      <c r="CB44" s="29"/>
+      <c r="BZ44" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="CA44" s="30"/>
+      <c r="CB44" s="30"/>
       <c r="CC44" s="6"/>
       <c r="CD44" s="6"/>
       <c r="CE44" s="6"/>
@@ -12341,16 +12366,16 @@
       </c>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
-      <c r="AZ45" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="BA45" s="31"/>
-      <c r="BB45" s="31"/>
-      <c r="BC45" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="BD45" s="31"/>
-      <c r="BE45" s="31"/>
+      <c r="AZ45" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="BA45" s="33"/>
+      <c r="BB45" s="33"/>
+      <c r="BC45" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="BD45" s="33"/>
+      <c r="BE45" s="33"/>
       <c r="BF45" s="13" t="s">
         <v>157</v>
       </c>
@@ -12366,16 +12391,16 @@
       </c>
       <c r="BM45" s="10"/>
       <c r="BN45" s="10"/>
-      <c r="BO45" s="32" t="s">
+      <c r="BO45" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="BP45" s="32"/>
-      <c r="BQ45" s="32"/>
-      <c r="BR45" s="32" t="s">
+      <c r="BP45" s="34"/>
+      <c r="BQ45" s="34"/>
+      <c r="BR45" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="BS45" s="32"/>
-      <c r="BT45" s="32"/>
+      <c r="BS45" s="34"/>
+      <c r="BT45" s="34"/>
       <c r="BU45" s="6"/>
       <c r="BV45" s="6"/>
       <c r="BW45" s="6"/>
@@ -12392,7 +12417,7 @@
       <c r="CH45" s="6"/>
       <c r="CI45" s="6"/>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -12424,11 +12449,11 @@
       <c r="AC46" s="7"/>
       <c r="AD46" s="7"/>
       <c r="AE46" s="7"/>
-      <c r="AF46" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="AG46" s="29"/>
-      <c r="AH46" s="29"/>
+      <c r="AF46" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="AG46" s="32"/>
+      <c r="AH46" s="32"/>
       <c r="AI46" s="11"/>
       <c r="AJ46" s="11"/>
       <c r="AK46" s="11"/>
@@ -12475,11 +12500,11 @@
       <c r="BU46" s="7"/>
       <c r="BV46" s="7"/>
       <c r="BW46" s="7"/>
-      <c r="BX46" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="BY46" s="29"/>
-      <c r="BZ46" s="29"/>
+      <c r="BX46" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="BY46" s="32"/>
+      <c r="BZ46" s="32"/>
       <c r="CA46" s="11"/>
       <c r="CB46" s="11"/>
       <c r="CC46" s="11"/>
@@ -12522,9 +12547,9 @@
       <c r="AC47" s="7"/>
       <c r="AD47" s="7"/>
       <c r="AE47" s="7"/>
-      <c r="AF47" s="29"/>
-      <c r="AG47" s="29"/>
-      <c r="AH47" s="29"/>
+      <c r="AF47" s="32"/>
+      <c r="AG47" s="32"/>
+      <c r="AH47" s="32"/>
       <c r="AI47" s="6"/>
       <c r="AJ47" s="6"/>
       <c r="AK47" s="6"/>
@@ -12565,9 +12590,9 @@
       <c r="BU47" s="7"/>
       <c r="BV47" s="7"/>
       <c r="BW47" s="7"/>
-      <c r="BX47" s="29"/>
-      <c r="BY47" s="29"/>
-      <c r="BZ47" s="29"/>
+      <c r="BX47" s="32"/>
+      <c r="BY47" s="32"/>
+      <c r="BZ47" s="32"/>
       <c r="CA47" s="6"/>
       <c r="CB47" s="6"/>
       <c r="CC47" s="6"/>
@@ -14970,7 +14995,7 @@
       <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
@@ -15064,7 +15089,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
@@ -15733,7 +15758,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -15939,7 +15964,7 @@
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -15994,7 +16019,7 @@
       <c r="CC19" s="7"/>
       <c r="CD19" s="7"/>
       <c r="CE19" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
@@ -16775,7 +16800,7 @@
       <c r="AK27" s="13"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -16828,7 +16853,7 @@
       <c r="CC27" s="7"/>
       <c r="CD27" s="7"/>
       <c r="CE27" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="CF27" s="6"/>
       <c r="CG27" s="6"/>
@@ -17600,7 +17625,7 @@
       <c r="AK35" s="13"/>
       <c r="AL35" s="13"/>
       <c r="AM35" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -17657,7 +17682,7 @@
       <c r="CC35" s="7"/>
       <c r="CD35" s="7"/>
       <c r="CE35" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="CF35" s="6"/>
       <c r="CG35" s="6"/>
@@ -19211,7 +19236,7 @@
       <c r="AP1" s="4"/>
       <c r="AQ1" s="5"/>
       <c r="AT1" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -19494,7 +19519,7 @@
         <v>161</v>
       </c>
       <c r="AT4" s="7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AU4" s="7"/>
       <c r="AV4" s="7"/>
@@ -19502,7 +19527,7 @@
       <c r="AX4" s="8"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="BA4" s="8" t="s">
         <v>56</v>
@@ -19591,8 +19616,8 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
-      <c r="AR5" s="33" t="s">
-        <v>201</v>
+      <c r="AR5" s="35" t="s">
+        <v>204</v>
       </c>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
@@ -19601,7 +19626,7 @@
       <c r="AX5" s="7"/>
       <c r="AY5" s="7"/>
       <c r="AZ5" s="6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="BA5" s="7" t="s">
         <v>172</v>
@@ -19661,10 +19686,10 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
@@ -19707,7 +19732,7 @@
       <c r="AW6" s="7"/>
       <c r="AX6" s="7"/>
       <c r="AY6" s="7" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AZ6" s="7"/>
       <c r="BA6" s="7"/>
@@ -19716,7 +19741,7 @@
       <c r="BD6" s="6"/>
       <c r="BE6" s="11"/>
       <c r="BF6" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="BG6" s="11"/>
       <c r="BH6" s="11"/>
@@ -19781,7 +19806,7 @@
         <v>172</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="BG7" s="6" t="s">
         <v>173</v>
@@ -19835,7 +19860,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -20398,8 +20423,8 @@
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
-      <c r="AR13" s="33" t="s">
-        <v>201</v>
+      <c r="AR13" s="35" t="s">
+        <v>204</v>
       </c>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
@@ -20512,10 +20537,10 @@
       </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -20794,7 +20819,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -21265,8 +21290,8 @@
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
-      <c r="AR21" s="33" t="s">
-        <v>201</v>
+      <c r="AR21" s="35" t="s">
+        <v>204</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
@@ -21375,10 +21400,10 @@
       </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
@@ -22091,8 +22116,8 @@
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
-      <c r="AR29" s="33" t="s">
-        <v>201</v>
+      <c r="AR29" s="35" t="s">
+        <v>204</v>
       </c>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
@@ -22189,10 +22214,10 @@
       </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -22259,7 +22284,7 @@
       </c>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="BR30" s="7"/>
       <c r="BS30" s="7"/>
@@ -22764,7 +22789,7 @@
       <c r="AR36" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="AT36" s="34" t="s">
+      <c r="AT36" s="36" t="s">
         <v>34</v>
       </c>
       <c r="AU36" s="13" t="s">
@@ -22870,8 +22895,8 @@
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
-      <c r="AR37" s="33" t="s">
-        <v>201</v>
+      <c r="AR37" s="35" t="s">
+        <v>204</v>
       </c>
       <c r="AT37" s="7" t="s">
         <v>35</v>
@@ -22954,10 +22979,10 @@
       </c>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -22992,17 +23017,17 @@
       <c r="AW38" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AX38" s="34" t="s">
+      <c r="AX38" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="AY38" s="34" t="s">
+      <c r="AY38" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="AZ38" s="34"/>
-      <c r="BA38" s="34" t="s">
+      <c r="AZ38" s="36"/>
+      <c r="BA38" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="BB38" s="34" t="s">
+      <c r="BB38" s="36" t="s">
         <v>107</v>
       </c>
       <c r="BC38" s="11"/>
@@ -23065,9 +23090,9 @@
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
-      <c r="AZ39" s="34"/>
-      <c r="BA39" s="34"/>
-      <c r="BB39" s="34"/>
+      <c r="AZ39" s="36"/>
+      <c r="BA39" s="36"/>
+      <c r="BB39" s="36"/>
       <c r="BC39" s="11"/>
       <c r="BD39" s="6"/>
       <c r="BE39" s="6"/>
@@ -24312,8 +24337,8 @@
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="33" t="s">
-        <v>201</v>
+      <c r="P5" s="35" t="s">
+        <v>204</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -24444,7 +24469,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -24599,7 +24624,7 @@
       <c r="Z11" s="13"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="13"/>
-      <c r="AC11" s="35"/>
+      <c r="AC11" s="37"/>
       <c r="AD11" s="21"/>
       <c r="AE11" s="6"/>
       <c r="AF11" s="6"/>
@@ -24707,8 +24732,8 @@
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
-      <c r="P13" s="33" t="s">
-        <v>201</v>
+      <c r="P13" s="35" t="s">
+        <v>204</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="13"/>
@@ -24916,8 +24941,8 @@
       <c r="M19" s="13"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
-      <c r="P19" s="36" t="s">
-        <v>207</v>
+      <c r="P19" s="38" t="s">
+        <v>210</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -24936,7 +24961,7 @@
       <c r="AF19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -25019,11 +25044,11 @@
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="34"/>
+      <c r="V22" s="36"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
-      <c r="Y22" s="37"/>
-      <c r="Z22" s="37"/>
+      <c r="Y22" s="39"/>
+      <c r="Z22" s="39"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="11"/>
@@ -25051,11 +25076,11 @@
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="34"/>
-      <c r="W23" s="34"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="36"/>
       <c r="X23" s="7"/>
-      <c r="Y23" s="37"/>
-      <c r="Z23" s="37"/>
+      <c r="Y23" s="39"/>
+      <c r="Z23" s="39"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
@@ -25192,7 +25217,7 @@
       <c r="M28" s="13"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="R28" s="34"/>
+      <c r="R28" s="36"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -25246,8 +25271,8 @@
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="11"/>
@@ -25260,9 +25285,9 @@
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="34"/>
-      <c r="W30" s="34"/>
-      <c r="X30" s="34"/>
+      <c r="V30" s="36"/>
+      <c r="W30" s="36"/>
+      <c r="X30" s="36"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="11"/>
@@ -25279,7 +25304,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="34"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="11"/>
@@ -25294,7 +25319,7 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="34"/>
+      <c r="X31" s="36"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="7"/>
       <c r="AA31" s="11"/>
@@ -25357,7 +25382,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="32"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -25433,7 +25458,7 @@
       <c r="M36" s="13"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="R36" s="34"/>
+      <c r="R36" s="36"/>
       <c r="S36" s="13"/>
       <c r="T36" s="13"/>
       <c r="U36" s="13"/>
@@ -25472,7 +25497,7 @@
       <c r="V37" s="13"/>
       <c r="W37" s="13"/>
       <c r="X37" s="18"/>
-      <c r="Y37" s="38"/>
+      <c r="Y37" s="40"/>
       <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
@@ -25487,8 +25512,8 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="11"/>
@@ -25501,11 +25526,11 @@
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
-      <c r="V38" s="34"/>
-      <c r="W38" s="34"/>
-      <c r="X38" s="34"/>
-      <c r="Y38" s="34"/>
-      <c r="Z38" s="34"/>
+      <c r="V38" s="36"/>
+      <c r="W38" s="36"/>
+      <c r="X38" s="36"/>
+      <c r="Y38" s="36"/>
+      <c r="Z38" s="36"/>
       <c r="AA38" s="11"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="11"/>
@@ -25520,7 +25545,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="34"/>
+      <c r="G39" s="36"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="11"/>
@@ -25535,9 +25560,9 @@
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
-      <c r="X39" s="34"/>
-      <c r="Y39" s="34"/>
-      <c r="Z39" s="34"/>
+      <c r="X39" s="36"/>
+      <c r="Y39" s="36"/>
+      <c r="Z39" s="36"/>
       <c r="AA39" s="11"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
@@ -25658,7 +25683,7 @@
       <c r="AF43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="34"/>
+      <c r="A44" s="36"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -25673,7 +25698,7 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
-      <c r="R44" s="34"/>
+      <c r="R44" s="36"/>
       <c r="S44" s="13"/>
       <c r="T44" s="13"/>
       <c r="U44" s="13"/>
@@ -25727,8 +25752,8 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
       <c r="J46" s="11"/>
@@ -25741,11 +25766,11 @@
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
-      <c r="V46" s="34"/>
-      <c r="W46" s="34"/>
-      <c r="X46" s="34"/>
-      <c r="Y46" s="34"/>
-      <c r="Z46" s="34"/>
+      <c r="V46" s="36"/>
+      <c r="W46" s="36"/>
+      <c r="X46" s="36"/>
+      <c r="Y46" s="36"/>
+      <c r="Z46" s="36"/>
       <c r="AA46" s="11"/>
       <c r="AB46" s="6"/>
       <c r="AC46" s="11"/>
@@ -25760,7 +25785,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="34"/>
+      <c r="G47" s="36"/>
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
       <c r="J47" s="11"/>
@@ -25775,9 +25800,9 @@
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
-      <c r="X47" s="34"/>
-      <c r="Y47" s="34"/>
-      <c r="Z47" s="34"/>
+      <c r="X47" s="36"/>
+      <c r="Y47" s="36"/>
+      <c r="Z47" s="36"/>
       <c r="AA47" s="11"/>
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
@@ -25905,7 +25930,7 @@
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
-      <c r="V52" s="39"/>
+      <c r="V52" s="41"/>
       <c r="W52" s="6"/>
       <c r="X52" s="13"/>
       <c r="Y52" s="14"/>
@@ -25954,11 +25979,11 @@
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="34"/>
+      <c r="E54" s="36"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="37"/>
-      <c r="I54" s="37"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
       <c r="J54" s="11"/>
       <c r="K54" s="6"/>
       <c r="L54" s="11"/>
@@ -25986,11 +26011,11 @@
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="37"/>
-      <c r="I55" s="37"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
       <c r="J55" s="11"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="210">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -592,7 +592,7 @@
 Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">Stdard
+    <t xml:space="preserve">Standard
 Mode</t>
   </si>
   <si>
@@ -614,9 +614,6 @@
   <si>
     <t xml:space="preserve">Cursor
 Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CurMode</t>
   </si>
   <si>
     <r>
@@ -7658,7 +7655,9 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="2" style="1" width="2.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="2" style="1" width="2.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="2.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="35" style="1" width="2.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="4.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="6.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="46" style="1" width="2.04"/>
@@ -10535,26 +10534,26 @@
       </c>
       <c r="Y27" s="6"/>
       <c r="Z27" s="6"/>
-      <c r="AA27" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB27" s="6"/>
-      <c r="AC27" s="6"/>
-      <c r="AD27" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="AE27" s="7"/>
-      <c r="AF27" s="7"/>
-      <c r="AG27" s="13" t="s">
+      <c r="AA27" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AH27" s="13"/>
-      <c r="AI27" s="13"/>
-      <c r="AJ27" s="13" t="s">
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AK27" s="13"/>
-      <c r="AL27" s="13"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="13"/>
+      <c r="AG27" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
       <c r="AM27" s="6"/>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -10940,20 +10939,22 @@
       <c r="BL30" s="31"/>
       <c r="BM30" s="31"/>
       <c r="BN30" s="31"/>
-      <c r="BO30" s="7"/>
-      <c r="BP30" s="7"/>
-      <c r="BQ30" s="7"/>
-      <c r="BR30" s="7"/>
-      <c r="BS30" s="7"/>
-      <c r="BT30" s="7"/>
+      <c r="BO30" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="BP30" s="32"/>
+      <c r="BQ30" s="32"/>
+      <c r="BR30" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="BS30" s="32"/>
+      <c r="BT30" s="32"/>
       <c r="BU30" s="7"/>
       <c r="BV30" s="7"/>
       <c r="BW30" s="7"/>
-      <c r="BX30" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="BY30" s="32"/>
-      <c r="BZ30" s="32"/>
+      <c r="BX30" s="7"/>
+      <c r="BY30" s="7"/>
+      <c r="BZ30" s="7"/>
       <c r="CA30" s="11"/>
       <c r="CB30" s="11"/>
       <c r="CC30" s="11"/>
@@ -11032,18 +11033,18 @@
       <c r="BL31" s="31"/>
       <c r="BM31" s="31"/>
       <c r="BN31" s="31"/>
-      <c r="BO31" s="7"/>
-      <c r="BP31" s="7"/>
-      <c r="BQ31" s="7"/>
-      <c r="BR31" s="7"/>
-      <c r="BS31" s="7"/>
-      <c r="BT31" s="7"/>
+      <c r="BO31" s="32"/>
+      <c r="BP31" s="32"/>
+      <c r="BQ31" s="32"/>
+      <c r="BR31" s="32"/>
+      <c r="BS31" s="32"/>
+      <c r="BT31" s="32"/>
       <c r="BU31" s="7"/>
       <c r="BV31" s="7"/>
       <c r="BW31" s="7"/>
-      <c r="BX31" s="32"/>
-      <c r="BY31" s="32"/>
-      <c r="BZ31" s="32"/>
+      <c r="BX31" s="7"/>
+      <c r="BY31" s="7"/>
+      <c r="BZ31" s="7"/>
       <c r="CA31" s="6" t="s">
         <v>172</v>
       </c>
@@ -11435,11 +11436,11 @@
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
-      <c r="J36" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
+      <c r="J36" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
       <c r="M36" s="20" t="s">
         <v>7</v>
       </c>
@@ -11717,11 +11718,11 @@
       </c>
       <c r="AD38" s="7"/>
       <c r="AE38" s="7"/>
-      <c r="AF38" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="AG38" s="29"/>
-      <c r="AH38" s="29"/>
+      <c r="AF38" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG38" s="7"/>
+      <c r="AH38" s="7"/>
       <c r="AI38" s="11"/>
       <c r="AJ38" s="11"/>
       <c r="AK38" s="11"/>
@@ -11755,20 +11756,22 @@
       <c r="BL38" s="31"/>
       <c r="BM38" s="31"/>
       <c r="BN38" s="31"/>
-      <c r="BO38" s="7"/>
-      <c r="BP38" s="7"/>
-      <c r="BQ38" s="7"/>
-      <c r="BR38" s="7"/>
-      <c r="BS38" s="7"/>
-      <c r="BT38" s="7"/>
+      <c r="BO38" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="BP38" s="32"/>
+      <c r="BQ38" s="32"/>
+      <c r="BR38" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="BS38" s="32"/>
+      <c r="BT38" s="32"/>
       <c r="BU38" s="7"/>
       <c r="BV38" s="7"/>
       <c r="BW38" s="7"/>
-      <c r="BX38" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="BY38" s="32"/>
-      <c r="BZ38" s="32"/>
+      <c r="BX38" s="7"/>
+      <c r="BY38" s="7"/>
+      <c r="BZ38" s="7"/>
       <c r="CA38" s="11"/>
       <c r="CB38" s="11"/>
       <c r="CC38" s="11"/>
@@ -11811,9 +11814,9 @@
       <c r="AC39" s="7"/>
       <c r="AD39" s="7"/>
       <c r="AE39" s="7"/>
-      <c r="AF39" s="29"/>
-      <c r="AG39" s="29"/>
-      <c r="AH39" s="29"/>
+      <c r="AF39" s="7"/>
+      <c r="AG39" s="7"/>
+      <c r="AH39" s="7"/>
       <c r="AI39" s="6"/>
       <c r="AJ39" s="6"/>
       <c r="AK39" s="6"/>
@@ -11845,18 +11848,18 @@
       <c r="BL39" s="31"/>
       <c r="BM39" s="31"/>
       <c r="BN39" s="31"/>
-      <c r="BO39" s="7"/>
-      <c r="BP39" s="7"/>
-      <c r="BQ39" s="7"/>
-      <c r="BR39" s="7"/>
-      <c r="BS39" s="7"/>
-      <c r="BT39" s="7"/>
+      <c r="BO39" s="32"/>
+      <c r="BP39" s="32"/>
+      <c r="BQ39" s="32"/>
+      <c r="BR39" s="32"/>
+      <c r="BS39" s="32"/>
+      <c r="BT39" s="32"/>
       <c r="BU39" s="7"/>
       <c r="BV39" s="7"/>
       <c r="BW39" s="7"/>
-      <c r="BX39" s="32"/>
-      <c r="BY39" s="32"/>
-      <c r="BZ39" s="32"/>
+      <c r="BX39" s="7"/>
+      <c r="BY39" s="7"/>
+      <c r="BZ39" s="7"/>
       <c r="CA39" s="6"/>
       <c r="CB39" s="6"/>
       <c r="CC39" s="6"/>
@@ -12174,11 +12177,11 @@
       <c r="CI43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
+      <c r="A44" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -12223,11 +12226,11 @@
       </c>
       <c r="AF44" s="13"/>
       <c r="AG44" s="13"/>
-      <c r="AH44" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="AI44" s="30"/>
-      <c r="AJ44" s="30"/>
+      <c r="AH44" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="AI44" s="32"/>
+      <c r="AJ44" s="32"/>
       <c r="AK44" s="6"/>
       <c r="AL44" s="6"/>
       <c r="AM44" s="6"/>
@@ -12235,11 +12238,11 @@
       <c r="AO44" s="9"/>
       <c r="AP44" s="9"/>
       <c r="AQ44" s="9"/>
-      <c r="AS44" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="AT44" s="7"/>
-      <c r="AU44" s="7"/>
+      <c r="AS44" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="AT44" s="31"/>
+      <c r="AU44" s="31"/>
       <c r="AV44" s="6"/>
       <c r="AW44" s="6"/>
       <c r="AX44" s="6"/>
@@ -12284,11 +12287,11 @@
       </c>
       <c r="BX44" s="13"/>
       <c r="BY44" s="13"/>
-      <c r="BZ44" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="CA44" s="30"/>
-      <c r="CB44" s="30"/>
+      <c r="BZ44" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="CA44" s="32"/>
+      <c r="CB44" s="32"/>
       <c r="CC44" s="6"/>
       <c r="CD44" s="6"/>
       <c r="CE44" s="6"/>
@@ -12367,12 +12370,12 @@
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
       <c r="AZ45" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BA45" s="33"/>
       <c r="BB45" s="33"/>
       <c r="BC45" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BD45" s="33"/>
       <c r="BE45" s="33"/>
@@ -12431,29 +12434,33 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
-      <c r="U46" s="7"/>
-      <c r="V46" s="7"/>
-      <c r="W46" s="7"/>
-      <c r="X46" s="7"/>
-      <c r="Y46" s="7"/>
-      <c r="Z46" s="7"/>
-      <c r="AA46" s="7"/>
-      <c r="AB46" s="7"/>
+      <c r="N46" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="31"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="X46" s="32"/>
+      <c r="Y46" s="32"/>
+      <c r="Z46" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="AA46" s="32"/>
+      <c r="AB46" s="32"/>
       <c r="AC46" s="7"/>
       <c r="AD46" s="7"/>
       <c r="AE46" s="7"/>
-      <c r="AF46" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="AG46" s="32"/>
-      <c r="AH46" s="32"/>
+      <c r="AF46" s="7"/>
+      <c r="AG46" s="7"/>
+      <c r="AH46" s="7"/>
       <c r="AI46" s="11"/>
       <c r="AJ46" s="11"/>
       <c r="AK46" s="11"/>
@@ -12476,35 +12483,33 @@
       <c r="BC46" s="7"/>
       <c r="BD46" s="7"/>
       <c r="BE46" s="7"/>
-      <c r="BF46" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="BG46" s="7"/>
-      <c r="BH46" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="BI46" s="7"/>
-      <c r="BJ46" s="7"/>
-      <c r="BK46" s="7"/>
-      <c r="BL46" s="7"/>
-      <c r="BM46" s="7"/>
-      <c r="BN46" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="BO46" s="7"/>
-      <c r="BP46" s="7"/>
-      <c r="BQ46" s="7"/>
-      <c r="BR46" s="7"/>
-      <c r="BS46" s="7"/>
-      <c r="BT46" s="7"/>
+      <c r="BF46" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="BG46" s="31"/>
+      <c r="BH46" s="31"/>
+      <c r="BI46" s="31"/>
+      <c r="BJ46" s="31"/>
+      <c r="BK46" s="31"/>
+      <c r="BL46" s="31"/>
+      <c r="BM46" s="31"/>
+      <c r="BN46" s="31"/>
+      <c r="BO46" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="BP46" s="32"/>
+      <c r="BQ46" s="32"/>
+      <c r="BR46" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="BS46" s="32"/>
+      <c r="BT46" s="32"/>
       <c r="BU46" s="7"/>
       <c r="BV46" s="7"/>
       <c r="BW46" s="7"/>
-      <c r="BX46" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="BY46" s="32"/>
-      <c r="BZ46" s="32"/>
+      <c r="BX46" s="7"/>
+      <c r="BY46" s="7"/>
+      <c r="BZ46" s="7"/>
       <c r="CA46" s="11"/>
       <c r="CB46" s="11"/>
       <c r="CC46" s="11"/>
@@ -12529,27 +12534,27 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="7"/>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="7"/>
-      <c r="X47" s="7"/>
-      <c r="Y47" s="7"/>
-      <c r="Z47" s="7"/>
-      <c r="AA47" s="7"/>
-      <c r="AB47" s="7"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="31"/>
+      <c r="S47" s="31"/>
+      <c r="T47" s="31"/>
+      <c r="U47" s="31"/>
+      <c r="V47" s="31"/>
+      <c r="W47" s="32"/>
+      <c r="X47" s="32"/>
+      <c r="Y47" s="32"/>
+      <c r="Z47" s="32"/>
+      <c r="AA47" s="32"/>
+      <c r="AB47" s="32"/>
       <c r="AC47" s="7"/>
       <c r="AD47" s="7"/>
       <c r="AE47" s="7"/>
-      <c r="AF47" s="32"/>
-      <c r="AG47" s="32"/>
-      <c r="AH47" s="32"/>
+      <c r="AF47" s="7"/>
+      <c r="AG47" s="7"/>
+      <c r="AH47" s="7"/>
       <c r="AI47" s="6"/>
       <c r="AJ47" s="6"/>
       <c r="AK47" s="6"/>
@@ -12572,27 +12577,27 @@
       <c r="BC47" s="7"/>
       <c r="BD47" s="7"/>
       <c r="BE47" s="7"/>
-      <c r="BF47" s="7"/>
-      <c r="BG47" s="7"/>
-      <c r="BH47" s="7"/>
-      <c r="BI47" s="7"/>
-      <c r="BJ47" s="7"/>
-      <c r="BK47" s="7"/>
-      <c r="BL47" s="7"/>
-      <c r="BM47" s="7"/>
-      <c r="BN47" s="7"/>
-      <c r="BO47" s="7"/>
-      <c r="BP47" s="7"/>
-      <c r="BQ47" s="7"/>
-      <c r="BR47" s="7"/>
-      <c r="BS47" s="7"/>
-      <c r="BT47" s="7"/>
+      <c r="BF47" s="31"/>
+      <c r="BG47" s="31"/>
+      <c r="BH47" s="31"/>
+      <c r="BI47" s="31"/>
+      <c r="BJ47" s="31"/>
+      <c r="BK47" s="31"/>
+      <c r="BL47" s="31"/>
+      <c r="BM47" s="31"/>
+      <c r="BN47" s="31"/>
+      <c r="BO47" s="32"/>
+      <c r="BP47" s="32"/>
+      <c r="BQ47" s="32"/>
+      <c r="BR47" s="32"/>
+      <c r="BS47" s="32"/>
+      <c r="BT47" s="32"/>
       <c r="BU47" s="7"/>
       <c r="BV47" s="7"/>
       <c r="BW47" s="7"/>
-      <c r="BX47" s="32"/>
-      <c r="BY47" s="32"/>
-      <c r="BZ47" s="32"/>
+      <c r="BX47" s="7"/>
+      <c r="BY47" s="7"/>
+      <c r="BZ47" s="7"/>
       <c r="CA47" s="6"/>
       <c r="CB47" s="6"/>
       <c r="CC47" s="6"/>
@@ -14995,7 +15000,7 @@
       <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
@@ -15089,7 +15094,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
@@ -15758,7 +15763,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -15964,7 +15969,7 @@
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -16019,7 +16024,7 @@
       <c r="CC19" s="7"/>
       <c r="CD19" s="7"/>
       <c r="CE19" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
@@ -16800,7 +16805,7 @@
       <c r="AK27" s="13"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -16853,7 +16858,7 @@
       <c r="CC27" s="7"/>
       <c r="CD27" s="7"/>
       <c r="CE27" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CF27" s="6"/>
       <c r="CG27" s="6"/>
@@ -17625,7 +17630,7 @@
       <c r="AK35" s="13"/>
       <c r="AL35" s="13"/>
       <c r="AM35" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -17682,7 +17687,7 @@
       <c r="CC35" s="7"/>
       <c r="CD35" s="7"/>
       <c r="CE35" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="CF35" s="6"/>
       <c r="CG35" s="6"/>
@@ -19236,7 +19241,7 @@
       <c r="AP1" s="4"/>
       <c r="AQ1" s="5"/>
       <c r="AT1" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -19519,7 +19524,7 @@
         <v>161</v>
       </c>
       <c r="AT4" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AU4" s="7"/>
       <c r="AV4" s="7"/>
@@ -19527,7 +19532,7 @@
       <c r="AX4" s="8"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BA4" s="8" t="s">
         <v>56</v>
@@ -19617,7 +19622,7 @@
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
       <c r="AR5" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
@@ -19626,7 +19631,7 @@
       <c r="AX5" s="7"/>
       <c r="AY5" s="7"/>
       <c r="AZ5" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BA5" s="7" t="s">
         <v>172</v>
@@ -19686,10 +19691,10 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
@@ -19732,7 +19737,7 @@
       <c r="AW6" s="7"/>
       <c r="AX6" s="7"/>
       <c r="AY6" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AZ6" s="7"/>
       <c r="BA6" s="7"/>
@@ -19741,7 +19746,7 @@
       <c r="BD6" s="6"/>
       <c r="BE6" s="11"/>
       <c r="BF6" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BG6" s="11"/>
       <c r="BH6" s="11"/>
@@ -19806,7 +19811,7 @@
         <v>172</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BG7" s="6" t="s">
         <v>173</v>
@@ -19860,7 +19865,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -20424,7 +20429,7 @@
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
       <c r="AR13" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
@@ -20537,10 +20542,10 @@
       </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -20819,7 +20824,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -21291,7 +21296,7 @@
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
       <c r="AR21" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
@@ -21400,10 +21405,10 @@
       </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
@@ -22117,7 +22122,7 @@
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
       <c r="AR29" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
@@ -22214,10 +22219,10 @@
       </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -22284,7 +22289,7 @@
       </c>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BR30" s="7"/>
       <c r="BS30" s="7"/>
@@ -22896,7 +22901,7 @@
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
       <c r="AR37" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AT37" s="7" t="s">
         <v>35</v>
@@ -22979,10 +22984,10 @@
       </c>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -24338,7 +24343,7 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -24469,7 +24474,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -24733,7 +24738,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="13"/>
@@ -24942,7 +24947,7 @@
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="38" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="214">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -584,12 +584,27 @@
     <t xml:space="preserve">Space &amp; F13 修飾</t>
   </si>
   <si>
+    <t xml:space="preserve">sShift</t>
+  </si>
+  <si>
     <t xml:space="preserve">SelCur
 Togle</t>
   </si>
   <si>
+    <t xml:space="preserve">F14修飾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SC+p</t>
+  </si>
+  <si>
     <t xml:space="preserve">Select
 Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+Space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S+Tab</t>
   </si>
   <si>
     <t xml:space="preserve">Standard
@@ -599,17 +614,13 @@
     <t xml:space="preserve">10Key Mode</t>
   </si>
   <si>
-    <t xml:space="preserve">SelMode</t>
+    <t xml:space="preserve">Backspace</t>
   </si>
   <si>
     <t xml:space="preserve">Cursor Mode</t>
   </si>
   <si>
     <t xml:space="preserve">Select Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normal
-Mode</t>
   </si>
   <si>
     <t xml:space="preserve">Cursor
@@ -952,7 +963,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1073,15 +1084,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5589,9 +5604,7 @@
       <c r="AO41" s="4"/>
       <c r="AP41" s="4"/>
       <c r="AQ41" s="5"/>
-      <c r="AS41" s="15" t="s">
-        <v>50</v>
-      </c>
+      <c r="AS41" s="15"/>
       <c r="AT41" s="15"/>
       <c r="AU41" s="4"/>
       <c r="AV41" s="4"/>
@@ -5676,64 +5689,40 @@
       <c r="AP42" s="6"/>
       <c r="AQ42" s="6"/>
       <c r="AS42" s="6"/>
-      <c r="AT42" s="6" t="s">
-        <v>109</v>
-      </c>
+      <c r="AT42" s="6"/>
       <c r="AU42" s="6"/>
       <c r="AV42" s="6"/>
-      <c r="AW42" s="6" t="s">
-        <v>110</v>
-      </c>
+      <c r="AW42" s="6"/>
       <c r="AX42" s="6"/>
       <c r="AY42" s="6"/>
-      <c r="AZ42" s="6" t="s">
-        <v>111</v>
-      </c>
+      <c r="AZ42" s="6"/>
       <c r="BA42" s="6"/>
       <c r="BB42" s="6"/>
-      <c r="BC42" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="BC42" s="6"/>
       <c r="BD42" s="6"/>
       <c r="BE42" s="6"/>
-      <c r="BF42" s="6" t="s">
-        <v>113</v>
-      </c>
+      <c r="BF42" s="6"/>
       <c r="BG42" s="6"/>
       <c r="BH42" s="6"/>
-      <c r="BI42" s="6" t="s">
-        <v>114</v>
-      </c>
+      <c r="BI42" s="6"/>
       <c r="BJ42" s="6"/>
       <c r="BK42" s="6"/>
-      <c r="BL42" s="6" t="s">
-        <v>115</v>
-      </c>
+      <c r="BL42" s="6"/>
       <c r="BM42" s="6"/>
       <c r="BN42" s="6"/>
-      <c r="BO42" s="6" t="s">
-        <v>116</v>
-      </c>
+      <c r="BO42" s="6"/>
       <c r="BP42" s="6"/>
       <c r="BQ42" s="6"/>
-      <c r="BR42" s="6" t="s">
-        <v>117</v>
-      </c>
+      <c r="BR42" s="6"/>
       <c r="BS42" s="6"/>
       <c r="BT42" s="6"/>
-      <c r="BU42" s="6" t="s">
-        <v>118</v>
-      </c>
+      <c r="BU42" s="6"/>
       <c r="BV42" s="6"/>
       <c r="BW42" s="6"/>
-      <c r="BX42" s="6" t="s">
-        <v>119</v>
-      </c>
+      <c r="BX42" s="6"/>
       <c r="BY42" s="6"/>
       <c r="BZ42" s="6"/>
-      <c r="CA42" s="6" t="s">
-        <v>120</v>
-      </c>
+      <c r="CA42" s="6"/>
       <c r="CB42" s="6"/>
       <c r="CC42" s="6"/>
       <c r="CD42" s="6"/>
@@ -5813,75 +5802,75 @@
       <c r="AO43" s="6"/>
       <c r="AP43" s="6"/>
       <c r="AQ43" s="6"/>
-      <c r="AS43" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT43" s="6"/>
-      <c r="AU43" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="AV43" s="13"/>
-      <c r="AW43" s="13"/>
-      <c r="AX43" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="AY43" s="13"/>
-      <c r="AZ43" s="13"/>
-      <c r="BA43" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="BB43" s="13"/>
-      <c r="BC43" s="13"/>
-      <c r="BD43" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="BE43" s="13"/>
-      <c r="BF43" s="13"/>
-      <c r="BG43" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="BH43" s="13"/>
-      <c r="BI43" s="13"/>
-      <c r="BJ43" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="BK43" s="13"/>
-      <c r="BL43" s="13"/>
-      <c r="BM43" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="BN43" s="13"/>
-      <c r="BO43" s="13"/>
-      <c r="BP43" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="BQ43" s="6"/>
-      <c r="BR43" s="6"/>
-      <c r="BS43" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="BT43" s="6"/>
-      <c r="BU43" s="6"/>
+      <c r="AS43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT43" s="7"/>
+      <c r="AU43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV43" s="7"/>
+      <c r="AW43" s="7"/>
+      <c r="AX43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AY43" s="7"/>
+      <c r="AZ43" s="7"/>
+      <c r="BA43" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BB43" s="7"/>
+      <c r="BC43" s="7"/>
+      <c r="BD43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BE43" s="7"/>
+      <c r="BF43" s="7"/>
+      <c r="BG43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH43" s="7"/>
+      <c r="BI43" s="7"/>
+      <c r="BJ43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BK43" s="7"/>
+      <c r="BL43" s="7"/>
+      <c r="BM43" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BN43" s="7"/>
+      <c r="BO43" s="7"/>
+      <c r="BP43" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BQ43" s="7"/>
+      <c r="BR43" s="7"/>
+      <c r="BS43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BT43" s="7"/>
+      <c r="BU43" s="7"/>
       <c r="BV43" s="7" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="BW43" s="7"/>
       <c r="BX43" s="7"/>
-      <c r="BY43" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="BZ43" s="13"/>
-      <c r="CA43" s="13"/>
-      <c r="CB43" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="CC43" s="13"/>
-      <c r="CD43" s="13"/>
-      <c r="CE43" s="6"/>
-      <c r="CF43" s="6"/>
-      <c r="CG43" s="6"/>
-      <c r="CH43" s="6"/>
-      <c r="CI43" s="6"/>
+      <c r="BY43" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="BZ43" s="7"/>
+      <c r="CA43" s="7"/>
+      <c r="CB43" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="CC43" s="7"/>
+      <c r="CD43" s="7"/>
+      <c r="CE43" s="7"/>
+      <c r="CF43" s="7"/>
+      <c r="CG43" s="7"/>
+      <c r="CH43" s="7"/>
+      <c r="CI43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
@@ -5954,74 +5943,74 @@
       <c r="AP44" s="9"/>
       <c r="AQ44" s="9"/>
       <c r="AS44" s="7" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="AT44" s="7"/>
       <c r="AU44" s="7"/>
-      <c r="AV44" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="AW44" s="13"/>
-      <c r="AX44" s="13"/>
-      <c r="AY44" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="AZ44" s="13"/>
-      <c r="BA44" s="13"/>
-      <c r="BB44" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="BC44" s="13"/>
-      <c r="BD44" s="13"/>
+      <c r="AV44" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW44" s="7"/>
+      <c r="AX44" s="7"/>
+      <c r="AY44" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ44" s="7"/>
+      <c r="BA44" s="7"/>
+      <c r="BB44" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC44" s="7"/>
+      <c r="BD44" s="7"/>
       <c r="BE44" s="20" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="BF44" s="20"/>
       <c r="BG44" s="20"/>
-      <c r="BH44" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="BI44" s="13"/>
-      <c r="BJ44" s="13"/>
-      <c r="BK44" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="BL44" s="6"/>
-      <c r="BM44" s="6"/>
+      <c r="BH44" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BI44" s="7"/>
+      <c r="BJ44" s="7"/>
+      <c r="BK44" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BL44" s="7"/>
+      <c r="BM44" s="7"/>
       <c r="BN44" s="8" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="BO44" s="8"/>
       <c r="BP44" s="8"/>
-      <c r="BQ44" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="BR44" s="6"/>
-      <c r="BS44" s="6"/>
-      <c r="BT44" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="BU44" s="6"/>
-      <c r="BV44" s="6"/>
-      <c r="BW44" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="BX44" s="13"/>
-      <c r="BY44" s="13"/>
-      <c r="BZ44" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="CA44" s="13"/>
-      <c r="CB44" s="13"/>
-      <c r="CC44" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="CD44" s="13"/>
-      <c r="CE44" s="13"/>
-      <c r="CF44" s="9"/>
-      <c r="CG44" s="9"/>
-      <c r="CH44" s="9"/>
-      <c r="CI44" s="9"/>
+      <c r="BQ44" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="BR44" s="7"/>
+      <c r="BS44" s="7"/>
+      <c r="BT44" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="BU44" s="7"/>
+      <c r="BV44" s="7"/>
+      <c r="BW44" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BX44" s="7"/>
+      <c r="BY44" s="7"/>
+      <c r="BZ44" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="CA44" s="7"/>
+      <c r="CB44" s="7"/>
+      <c r="CC44" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="CD44" s="7"/>
+      <c r="CE44" s="7"/>
+      <c r="CF44" s="23"/>
+      <c r="CG44" s="23"/>
+      <c r="CH44" s="23"/>
+      <c r="CI44" s="23"/>
     </row>
     <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="7" t="s">
@@ -6086,7 +6075,7 @@
         <v>35</v>
       </c>
       <c r="AL45" s="6" t="s">
-        <v>35</v>
+        <v>186</v>
       </c>
       <c r="AM45" s="6"/>
       <c r="AN45" s="6"/>
@@ -6094,74 +6083,74 @@
       <c r="AP45" s="6"/>
       <c r="AQ45" s="6"/>
       <c r="AS45" s="7" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="AT45" s="7"/>
       <c r="AU45" s="7"/>
       <c r="AV45" s="7"/>
-      <c r="AW45" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="AX45" s="13"/>
-      <c r="AY45" s="13"/>
-      <c r="AZ45" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="BA45" s="13"/>
-      <c r="BB45" s="13"/>
-      <c r="BC45" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="BD45" s="13"/>
-      <c r="BE45" s="13"/>
-      <c r="BF45" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="BG45" s="13"/>
-      <c r="BH45" s="13"/>
-      <c r="BI45" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="BJ45" s="13"/>
-      <c r="BK45" s="13"/>
+      <c r="AW45" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX45" s="7"/>
+      <c r="AY45" s="7"/>
+      <c r="AZ45" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BA45" s="7"/>
+      <c r="BB45" s="7"/>
+      <c r="BC45" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BD45" s="7"/>
+      <c r="BE45" s="7"/>
+      <c r="BF45" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BG45" s="7"/>
+      <c r="BH45" s="7"/>
+      <c r="BI45" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="BJ45" s="7"/>
+      <c r="BK45" s="7"/>
       <c r="BL45" s="7" t="s">
-        <v>161</v>
+        <v>84</v>
       </c>
       <c r="BM45" s="7"/>
       <c r="BN45" s="7"/>
       <c r="BO45" s="7" t="s">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="BP45" s="7"/>
       <c r="BQ45" s="7"/>
       <c r="BR45" s="7" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="BS45" s="7"/>
       <c r="BT45" s="7"/>
-      <c r="BU45" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="BV45" s="21"/>
-      <c r="BW45" s="21"/>
-      <c r="BX45" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="BY45" s="13"/>
-      <c r="BZ45" s="13"/>
-      <c r="CA45" s="6"/>
-      <c r="CB45" s="6"/>
-      <c r="CC45" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="CD45" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="CE45" s="6"/>
-      <c r="CF45" s="6"/>
-      <c r="CG45" s="6"/>
-      <c r="CH45" s="6"/>
-      <c r="CI45" s="6"/>
+      <c r="BU45" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="BV45" s="7"/>
+      <c r="BW45" s="7"/>
+      <c r="BX45" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="BY45" s="7"/>
+      <c r="BZ45" s="7"/>
+      <c r="CA45" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="CB45" s="7"/>
+      <c r="CC45" s="7"/>
+      <c r="CD45" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="CE45" s="7"/>
+      <c r="CF45" s="7"/>
+      <c r="CG45" s="7"/>
+      <c r="CH45" s="7"/>
+      <c r="CI45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
@@ -6227,58 +6216,48 @@
       <c r="AO46" s="11"/>
       <c r="AP46" s="11"/>
       <c r="AQ46" s="11"/>
-      <c r="AS46" s="7" t="s">
-        <v>46</v>
-      </c>
+      <c r="AS46" s="7"/>
       <c r="AT46" s="7"/>
       <c r="AU46" s="7"/>
       <c r="AV46" s="7"/>
-      <c r="AW46" s="7" t="s">
-        <v>48</v>
-      </c>
+      <c r="AW46" s="7"/>
       <c r="AX46" s="7"/>
       <c r="AY46" s="7"/>
       <c r="AZ46" s="7" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="BA46" s="7"/>
       <c r="BB46" s="7"/>
-      <c r="BC46" s="7"/>
+      <c r="BC46" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="BD46" s="7"/>
       <c r="BE46" s="7"/>
       <c r="BF46" s="7" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="BG46" s="7"/>
-      <c r="BH46" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="BH46" s="7"/>
       <c r="BI46" s="7"/>
       <c r="BJ46" s="7"/>
       <c r="BK46" s="7"/>
       <c r="BL46" s="7"/>
       <c r="BM46" s="7"/>
-      <c r="BN46" s="7" t="s">
-        <v>53</v>
-      </c>
+      <c r="BN46" s="7"/>
       <c r="BO46" s="7" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="BP46" s="7"/>
       <c r="BQ46" s="7"/>
       <c r="BR46" s="7" t="s">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="BS46" s="7"/>
       <c r="BT46" s="7"/>
-      <c r="BU46" s="7" t="s">
-        <v>49</v>
-      </c>
+      <c r="BU46" s="7"/>
       <c r="BV46" s="7"/>
       <c r="BW46" s="7"/>
-      <c r="BX46" s="7" t="s">
-        <v>46</v>
-      </c>
+      <c r="BX46" s="7"/>
       <c r="BY46" s="7"/>
       <c r="BZ46" s="7"/>
       <c r="CA46" s="11"/>
@@ -8413,12 +8392,12 @@
         <v>53</v>
       </c>
       <c r="BO6" s="29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BP6" s="29"/>
       <c r="BQ6" s="29"/>
       <c r="BR6" s="29" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BS6" s="29"/>
       <c r="BT6" s="29"/>
@@ -9516,7 +9495,9 @@
       <c r="AO17" s="4"/>
       <c r="AP17" s="4"/>
       <c r="AQ17" s="5"/>
-      <c r="AS17" s="15"/>
+      <c r="AS17" s="15" t="s">
+        <v>188</v>
+      </c>
       <c r="AT17" s="15"/>
       <c r="AU17" s="4"/>
       <c r="AV17" s="4"/>
@@ -9674,30 +9655,30 @@
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="13" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
       <c r="I19" s="13" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="J19" s="13"/>
       <c r="K19" s="13"/>
       <c r="L19" s="13" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
-      <c r="O19" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
+      <c r="O19" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
       <c r="R19" s="13" t="s">
         <v>138</v>
       </c>
@@ -9723,16 +9704,16 @@
       </c>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
-      <c r="AG19" s="30" t="s">
+      <c r="AG19" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="AH19" s="30"/>
-      <c r="AI19" s="30"/>
-      <c r="AJ19" s="30" t="s">
+      <c r="AH19" s="31"/>
+      <c r="AI19" s="31"/>
+      <c r="AJ19" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="AK19" s="30"/>
-      <c r="AL19" s="30"/>
+      <c r="AK19" s="31"/>
+      <c r="AL19" s="31"/>
       <c r="AM19" s="6"/>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -9746,12 +9727,16 @@
       <c r="AX19" s="7"/>
       <c r="AY19" s="7"/>
       <c r="AZ19" s="7"/>
-      <c r="BA19" s="7"/>
-      <c r="BB19" s="7"/>
-      <c r="BC19" s="7"/>
-      <c r="BD19" s="7"/>
-      <c r="BE19" s="7"/>
-      <c r="BF19" s="7"/>
+      <c r="BA19" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="BB19" s="13"/>
+      <c r="BC19" s="13"/>
+      <c r="BD19" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BE19" s="13"/>
+      <c r="BF19" s="13"/>
       <c r="BG19" s="7"/>
       <c r="BH19" s="7"/>
       <c r="BI19" s="7"/>
@@ -9812,21 +9797,21 @@
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="13"/>
-      <c r="J20" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
+      <c r="J20" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
       <c r="M20" s="20" t="s">
         <v>7</v>
       </c>
       <c r="N20" s="20"/>
       <c r="O20" s="20"/>
-      <c r="P20" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
+      <c r="P20" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
       <c r="S20" s="6" t="s">
         <v>151</v>
       </c>
@@ -9869,31 +9854,25 @@
       <c r="AS20" s="7"/>
       <c r="AT20" s="7"/>
       <c r="AU20" s="7"/>
-      <c r="AV20" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="AW20" s="13"/>
-      <c r="AX20" s="13"/>
-      <c r="AY20" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="AZ20" s="13"/>
-      <c r="BA20" s="13"/>
+      <c r="AV20" s="7"/>
+      <c r="AW20" s="7"/>
+      <c r="AX20" s="7"/>
+      <c r="AY20" s="7"/>
+      <c r="AZ20" s="7"/>
+      <c r="BA20" s="7"/>
       <c r="BB20" s="13" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="BC20" s="13"/>
       <c r="BD20" s="13"/>
-      <c r="BE20" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="BF20" s="13"/>
-      <c r="BG20" s="13"/>
-      <c r="BH20" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="BI20" s="13"/>
-      <c r="BJ20" s="13"/>
+      <c r="BE20" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="BF20" s="32"/>
+      <c r="BG20" s="32"/>
+      <c r="BH20" s="7"/>
+      <c r="BI20" s="7"/>
+      <c r="BJ20" s="7"/>
       <c r="BK20" s="19" t="s">
         <v>158</v>
       </c>
@@ -10495,30 +10474,30 @@
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="13" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
       <c r="F27" s="13" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
       <c r="I27" s="13" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
       <c r="L27" s="13" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
-      <c r="O27" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
+      <c r="O27" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
       <c r="R27" s="13" t="s">
         <v>138</v>
       </c>
@@ -10544,16 +10523,16 @@
       </c>
       <c r="AE27" s="13"/>
       <c r="AF27" s="13"/>
-      <c r="AG27" s="30" t="s">
+      <c r="AG27" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="AH27" s="30"/>
-      <c r="AI27" s="30"/>
-      <c r="AJ27" s="30" t="s">
+      <c r="AH27" s="31"/>
+      <c r="AI27" s="31"/>
+      <c r="AJ27" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="AK27" s="30"/>
-      <c r="AL27" s="30"/>
+      <c r="AK27" s="31"/>
+      <c r="AL27" s="31"/>
       <c r="AM27" s="6"/>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -10627,21 +10606,21 @@
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="13"/>
-      <c r="J28" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
+      <c r="J28" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
       <c r="M28" s="20" t="s">
         <v>7</v>
       </c>
       <c r="N28" s="20"/>
       <c r="O28" s="20"/>
-      <c r="P28" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
+      <c r="P28" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
       <c r="S28" s="6" t="s">
         <v>151</v>
       </c>
@@ -10681,11 +10660,11 @@
       <c r="AO28" s="9"/>
       <c r="AP28" s="9"/>
       <c r="AQ28" s="9"/>
-      <c r="AS28" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="AT28" s="31"/>
-      <c r="AU28" s="31"/>
+      <c r="AS28" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="AT28" s="33"/>
+      <c r="AU28" s="33"/>
       <c r="AV28" s="7"/>
       <c r="AW28" s="7"/>
       <c r="AX28" s="7"/>
@@ -10872,7 +10851,7 @@
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
       <c r="N30" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O30" s="7"/>
       <c r="P30" s="7" t="s">
@@ -10928,27 +10907,27 @@
       <c r="BC30" s="7"/>
       <c r="BD30" s="7"/>
       <c r="BE30" s="7"/>
-      <c r="BF30" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="BG30" s="31"/>
-      <c r="BH30" s="31"/>
-      <c r="BI30" s="31"/>
-      <c r="BJ30" s="31"/>
-      <c r="BK30" s="31"/>
-      <c r="BL30" s="31"/>
-      <c r="BM30" s="31"/>
-      <c r="BN30" s="31"/>
-      <c r="BO30" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="BP30" s="32"/>
-      <c r="BQ30" s="32"/>
-      <c r="BR30" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="BS30" s="32"/>
-      <c r="BT30" s="32"/>
+      <c r="BF30" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="BG30" s="33"/>
+      <c r="BH30" s="33"/>
+      <c r="BI30" s="33"/>
+      <c r="BJ30" s="33"/>
+      <c r="BK30" s="33"/>
+      <c r="BL30" s="33"/>
+      <c r="BM30" s="33"/>
+      <c r="BN30" s="33"/>
+      <c r="BO30" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="BP30" s="30"/>
+      <c r="BQ30" s="30"/>
+      <c r="BR30" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="BS30" s="30"/>
+      <c r="BT30" s="30"/>
       <c r="BU30" s="7"/>
       <c r="BV30" s="7"/>
       <c r="BW30" s="7"/>
@@ -11024,21 +11003,21 @@
       <c r="BC31" s="7"/>
       <c r="BD31" s="7"/>
       <c r="BE31" s="7"/>
-      <c r="BF31" s="31"/>
-      <c r="BG31" s="31"/>
-      <c r="BH31" s="31"/>
-      <c r="BI31" s="31"/>
-      <c r="BJ31" s="31"/>
-      <c r="BK31" s="31"/>
-      <c r="BL31" s="31"/>
-      <c r="BM31" s="31"/>
-      <c r="BN31" s="31"/>
-      <c r="BO31" s="32"/>
-      <c r="BP31" s="32"/>
-      <c r="BQ31" s="32"/>
-      <c r="BR31" s="32"/>
-      <c r="BS31" s="32"/>
-      <c r="BT31" s="32"/>
+      <c r="BF31" s="33"/>
+      <c r="BG31" s="33"/>
+      <c r="BH31" s="33"/>
+      <c r="BI31" s="33"/>
+      <c r="BJ31" s="33"/>
+      <c r="BK31" s="33"/>
+      <c r="BL31" s="33"/>
+      <c r="BM31" s="33"/>
+      <c r="BN31" s="33"/>
+      <c r="BO31" s="30"/>
+      <c r="BP31" s="30"/>
+      <c r="BQ31" s="30"/>
+      <c r="BR31" s="30"/>
+      <c r="BS31" s="30"/>
+      <c r="BT31" s="30"/>
       <c r="BU31" s="7"/>
       <c r="BV31" s="7"/>
       <c r="BW31" s="7"/>
@@ -11109,7 +11088,9 @@
       <c r="AT32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3"/>
+      <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="15"/>
@@ -11153,7 +11134,7 @@
       <c r="AP33" s="4"/>
       <c r="AQ33" s="5"/>
       <c r="AS33" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="AT33" s="5"/>
       <c r="AU33" s="4"/>
@@ -11300,30 +11281,30 @@
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="13" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="13"/>
       <c r="F35" s="13" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
       <c r="I35" s="13" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="J35" s="13"/>
       <c r="K35" s="13"/>
       <c r="L35" s="13" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="13"/>
-      <c r="O35" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
+      <c r="O35" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
       <c r="R35" s="13" t="s">
         <v>138</v>
       </c>
@@ -11349,16 +11330,16 @@
       </c>
       <c r="AE35" s="13"/>
       <c r="AF35" s="13"/>
-      <c r="AG35" s="30" t="s">
+      <c r="AG35" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="AH35" s="30"/>
-      <c r="AI35" s="30"/>
-      <c r="AJ35" s="30" t="s">
+      <c r="AH35" s="31"/>
+      <c r="AI35" s="31"/>
+      <c r="AJ35" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="AK35" s="30"/>
-      <c r="AL35" s="30"/>
+      <c r="AK35" s="31"/>
+      <c r="AL35" s="31"/>
       <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -11436,21 +11417,21 @@
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="13"/>
-      <c r="J36" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
+      <c r="J36" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
       <c r="M36" s="20" t="s">
         <v>7</v>
       </c>
       <c r="N36" s="20"/>
       <c r="O36" s="20"/>
-      <c r="P36" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
+      <c r="P36" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="31"/>
       <c r="S36" s="6" t="s">
         <v>151</v>
       </c>
@@ -11476,11 +11457,11 @@
       </c>
       <c r="AF36" s="13"/>
       <c r="AG36" s="13"/>
-      <c r="AH36" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="AI36" s="30"/>
-      <c r="AJ36" s="30"/>
+      <c r="AH36" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="AI36" s="13"/>
+      <c r="AJ36" s="13"/>
       <c r="AK36" s="13" t="s">
         <v>153</v>
       </c>
@@ -11490,11 +11471,11 @@
       <c r="AO36" s="9"/>
       <c r="AP36" s="9"/>
       <c r="AQ36" s="9"/>
-      <c r="AS36" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="AT36" s="31"/>
-      <c r="AU36" s="31"/>
+      <c r="AS36" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="AT36" s="33"/>
+      <c r="AU36" s="33"/>
       <c r="AV36" s="7"/>
       <c r="AW36" s="7"/>
       <c r="AX36" s="7"/>
@@ -11607,7 +11588,9 @@
       <c r="AH37" s="13"/>
       <c r="AI37" s="6"/>
       <c r="AJ37" s="6"/>
-      <c r="AK37" s="6"/>
+      <c r="AK37" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="AL37" s="6" t="s">
         <v>35</v>
       </c>
@@ -11689,7 +11672,7 @@
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="7" t="s">
-        <v>6</v>
+        <v>195</v>
       </c>
       <c r="O38" s="7"/>
       <c r="P38" s="7" t="s">
@@ -11745,27 +11728,27 @@
       <c r="BC38" s="7"/>
       <c r="BD38" s="7"/>
       <c r="BE38" s="7"/>
-      <c r="BF38" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="BG38" s="31"/>
-      <c r="BH38" s="31"/>
-      <c r="BI38" s="31"/>
-      <c r="BJ38" s="31"/>
-      <c r="BK38" s="31"/>
-      <c r="BL38" s="31"/>
-      <c r="BM38" s="31"/>
-      <c r="BN38" s="31"/>
-      <c r="BO38" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="BP38" s="32"/>
-      <c r="BQ38" s="32"/>
-      <c r="BR38" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="BS38" s="32"/>
-      <c r="BT38" s="32"/>
+      <c r="BF38" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="BG38" s="33"/>
+      <c r="BH38" s="33"/>
+      <c r="BI38" s="33"/>
+      <c r="BJ38" s="33"/>
+      <c r="BK38" s="33"/>
+      <c r="BL38" s="33"/>
+      <c r="BM38" s="33"/>
+      <c r="BN38" s="33"/>
+      <c r="BO38" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="BP38" s="30"/>
+      <c r="BQ38" s="30"/>
+      <c r="BR38" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="BS38" s="30"/>
+      <c r="BT38" s="30"/>
       <c r="BU38" s="7"/>
       <c r="BV38" s="7"/>
       <c r="BW38" s="7"/>
@@ -11839,21 +11822,21 @@
       <c r="BC39" s="7"/>
       <c r="BD39" s="7"/>
       <c r="BE39" s="7"/>
-      <c r="BF39" s="31"/>
-      <c r="BG39" s="31"/>
-      <c r="BH39" s="31"/>
-      <c r="BI39" s="31"/>
-      <c r="BJ39" s="31"/>
-      <c r="BK39" s="31"/>
-      <c r="BL39" s="31"/>
-      <c r="BM39" s="31"/>
-      <c r="BN39" s="31"/>
-      <c r="BO39" s="32"/>
-      <c r="BP39" s="32"/>
-      <c r="BQ39" s="32"/>
-      <c r="BR39" s="32"/>
-      <c r="BS39" s="32"/>
-      <c r="BT39" s="32"/>
+      <c r="BF39" s="33"/>
+      <c r="BG39" s="33"/>
+      <c r="BH39" s="33"/>
+      <c r="BI39" s="33"/>
+      <c r="BJ39" s="33"/>
+      <c r="BK39" s="33"/>
+      <c r="BL39" s="33"/>
+      <c r="BM39" s="33"/>
+      <c r="BN39" s="33"/>
+      <c r="BO39" s="30"/>
+      <c r="BP39" s="30"/>
+      <c r="BQ39" s="30"/>
+      <c r="BR39" s="30"/>
+      <c r="BS39" s="30"/>
+      <c r="BT39" s="30"/>
       <c r="BU39" s="7"/>
       <c r="BV39" s="7"/>
       <c r="BW39" s="7"/>
@@ -11914,7 +11897,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -11959,7 +11942,7 @@
       <c r="AP41" s="4"/>
       <c r="AQ41" s="5"/>
       <c r="AS41" s="15" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AT41" s="15"/>
       <c r="AU41" s="4"/>
@@ -12076,14 +12059,16 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
-      <c r="L43" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="6"/>
+      <c r="L43" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
       <c r="R43" s="13" t="s">
         <v>138</v>
       </c>
@@ -12109,16 +12094,16 @@
       </c>
       <c r="AE43" s="7"/>
       <c r="AF43" s="7"/>
-      <c r="AG43" s="30" t="s">
+      <c r="AG43" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="AH43" s="30"/>
-      <c r="AI43" s="30"/>
-      <c r="AJ43" s="30" t="s">
+      <c r="AH43" s="31"/>
+      <c r="AI43" s="31"/>
+      <c r="AJ43" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="AK43" s="30"/>
-      <c r="AL43" s="30"/>
+      <c r="AK43" s="31"/>
+      <c r="AL43" s="31"/>
       <c r="AM43" s="6"/>
       <c r="AN43" s="6"/>
       <c r="AO43" s="6"/>
@@ -12135,14 +12120,16 @@
       <c r="BA43" s="6"/>
       <c r="BB43" s="6"/>
       <c r="BC43" s="6"/>
-      <c r="BD43" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="BE43" s="32"/>
-      <c r="BF43" s="32"/>
-      <c r="BG43" s="6"/>
-      <c r="BH43" s="6"/>
-      <c r="BI43" s="6"/>
+      <c r="BD43" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="BE43" s="13"/>
+      <c r="BF43" s="13"/>
+      <c r="BG43" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="BH43" s="30"/>
+      <c r="BI43" s="30"/>
       <c r="BJ43" s="13" t="s">
         <v>138</v>
       </c>
@@ -12177,30 +12164,26 @@
       <c r="CI43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
+      <c r="A44" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" s="33"/>
+      <c r="C44" s="33"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
-      <c r="J44" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="K44" s="32"/>
-      <c r="L44" s="32"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="20"/>
-      <c r="O44" s="20"/>
-      <c r="P44" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q44" s="13"/>
-      <c r="R44" s="13"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
       <c r="S44" s="6" t="s">
         <v>151</v>
       </c>
@@ -12226,11 +12209,9 @@
       </c>
       <c r="AF44" s="13"/>
       <c r="AG44" s="13"/>
-      <c r="AH44" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="AI44" s="32"/>
-      <c r="AJ44" s="32"/>
+      <c r="AH44" s="6"/>
+      <c r="AI44" s="6"/>
+      <c r="AJ44" s="6"/>
       <c r="AK44" s="6"/>
       <c r="AL44" s="6"/>
       <c r="AM44" s="6"/>
@@ -12238,30 +12219,26 @@
       <c r="AO44" s="9"/>
       <c r="AP44" s="9"/>
       <c r="AQ44" s="9"/>
-      <c r="AS44" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="AT44" s="31"/>
-      <c r="AU44" s="31"/>
+      <c r="AS44" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="AT44" s="33"/>
+      <c r="AU44" s="33"/>
       <c r="AV44" s="6"/>
       <c r="AW44" s="6"/>
       <c r="AX44" s="6"/>
       <c r="AY44" s="6"/>
       <c r="AZ44" s="6"/>
       <c r="BA44" s="6"/>
-      <c r="BB44" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="BC44" s="32"/>
-      <c r="BD44" s="32"/>
+      <c r="BB44" s="6"/>
+      <c r="BC44" s="6"/>
+      <c r="BD44" s="6"/>
       <c r="BE44" s="8"/>
       <c r="BF44" s="8"/>
       <c r="BG44" s="8"/>
-      <c r="BH44" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="BI44" s="13"/>
-      <c r="BJ44" s="13"/>
+      <c r="BH44" s="6"/>
+      <c r="BI44" s="6"/>
+      <c r="BJ44" s="6"/>
       <c r="BK44" s="19" t="s">
         <v>158</v>
       </c>
@@ -12282,16 +12259,12 @@
       </c>
       <c r="BU44" s="6"/>
       <c r="BV44" s="6"/>
-      <c r="BW44" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="BX44" s="13"/>
-      <c r="BY44" s="13"/>
-      <c r="BZ44" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="CA44" s="32"/>
-      <c r="CB44" s="32"/>
+      <c r="BW44" s="6"/>
+      <c r="BX44" s="6"/>
+      <c r="BY44" s="6"/>
+      <c r="BZ44" s="6"/>
+      <c r="CA44" s="6"/>
+      <c r="CB44" s="6"/>
       <c r="CC44" s="6"/>
       <c r="CD44" s="6"/>
       <c r="CE44" s="6"/>
@@ -12369,16 +12342,16 @@
       </c>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
-      <c r="AZ45" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="BA45" s="33"/>
-      <c r="BB45" s="33"/>
-      <c r="BC45" s="33" t="s">
-        <v>196</v>
-      </c>
-      <c r="BD45" s="33"/>
-      <c r="BE45" s="33"/>
+      <c r="AZ45" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="BA45" s="34"/>
+      <c r="BB45" s="34"/>
+      <c r="BC45" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="BD45" s="34"/>
+      <c r="BE45" s="34"/>
       <c r="BF45" s="13" t="s">
         <v>157</v>
       </c>
@@ -12394,16 +12367,16 @@
       </c>
       <c r="BM45" s="10"/>
       <c r="BN45" s="10"/>
-      <c r="BO45" s="34" t="s">
+      <c r="BO45" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="BP45" s="34"/>
-      <c r="BQ45" s="34"/>
-      <c r="BR45" s="34" t="s">
+      <c r="BP45" s="35"/>
+      <c r="BQ45" s="35"/>
+      <c r="BR45" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="BS45" s="34"/>
-      <c r="BT45" s="34"/>
+      <c r="BS45" s="35"/>
+      <c r="BT45" s="35"/>
       <c r="BU45" s="6"/>
       <c r="BV45" s="6"/>
       <c r="BW45" s="6"/>
@@ -12434,27 +12407,27 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
-      <c r="N46" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="O46" s="31"/>
-      <c r="P46" s="31"/>
-      <c r="Q46" s="31"/>
-      <c r="R46" s="31"/>
-      <c r="S46" s="31"/>
-      <c r="T46" s="31"/>
-      <c r="U46" s="31"/>
-      <c r="V46" s="31"/>
-      <c r="W46" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="X46" s="32"/>
-      <c r="Y46" s="32"/>
-      <c r="Z46" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA46" s="32"/>
-      <c r="AB46" s="32"/>
+      <c r="N46" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="O46" s="33"/>
+      <c r="P46" s="33"/>
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="33"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
       <c r="AC46" s="7"/>
       <c r="AD46" s="7"/>
       <c r="AE46" s="7"/>
@@ -12483,27 +12456,27 @@
       <c r="BC46" s="7"/>
       <c r="BD46" s="7"/>
       <c r="BE46" s="7"/>
-      <c r="BF46" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="BG46" s="31"/>
-      <c r="BH46" s="31"/>
-      <c r="BI46" s="31"/>
-      <c r="BJ46" s="31"/>
-      <c r="BK46" s="31"/>
-      <c r="BL46" s="31"/>
-      <c r="BM46" s="31"/>
-      <c r="BN46" s="31"/>
-      <c r="BO46" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="BP46" s="32"/>
-      <c r="BQ46" s="32"/>
-      <c r="BR46" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="BS46" s="32"/>
-      <c r="BT46" s="32"/>
+      <c r="BF46" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="BG46" s="33"/>
+      <c r="BH46" s="33"/>
+      <c r="BI46" s="33"/>
+      <c r="BJ46" s="33"/>
+      <c r="BK46" s="33"/>
+      <c r="BL46" s="33"/>
+      <c r="BM46" s="33"/>
+      <c r="BN46" s="33"/>
+      <c r="BO46" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="BP46" s="30"/>
+      <c r="BQ46" s="30"/>
+      <c r="BR46" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="BS46" s="30"/>
+      <c r="BT46" s="30"/>
       <c r="BU46" s="7"/>
       <c r="BV46" s="7"/>
       <c r="BW46" s="7"/>
@@ -12534,21 +12507,21 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="31"/>
-      <c r="U47" s="31"/>
-      <c r="V47" s="31"/>
-      <c r="W47" s="32"/>
-      <c r="X47" s="32"/>
-      <c r="Y47" s="32"/>
-      <c r="Z47" s="32"/>
-      <c r="AA47" s="32"/>
-      <c r="AB47" s="32"/>
+      <c r="N47" s="33"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33"/>
+      <c r="U47" s="33"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="30"/>
+      <c r="X47" s="30"/>
+      <c r="Y47" s="30"/>
+      <c r="Z47" s="30"/>
+      <c r="AA47" s="30"/>
+      <c r="AB47" s="30"/>
       <c r="AC47" s="7"/>
       <c r="AD47" s="7"/>
       <c r="AE47" s="7"/>
@@ -12577,21 +12550,21 @@
       <c r="BC47" s="7"/>
       <c r="BD47" s="7"/>
       <c r="BE47" s="7"/>
-      <c r="BF47" s="31"/>
-      <c r="BG47" s="31"/>
-      <c r="BH47" s="31"/>
-      <c r="BI47" s="31"/>
-      <c r="BJ47" s="31"/>
-      <c r="BK47" s="31"/>
-      <c r="BL47" s="31"/>
-      <c r="BM47" s="31"/>
-      <c r="BN47" s="31"/>
-      <c r="BO47" s="32"/>
-      <c r="BP47" s="32"/>
-      <c r="BQ47" s="32"/>
-      <c r="BR47" s="32"/>
-      <c r="BS47" s="32"/>
-      <c r="BT47" s="32"/>
+      <c r="BF47" s="33"/>
+      <c r="BG47" s="33"/>
+      <c r="BH47" s="33"/>
+      <c r="BI47" s="33"/>
+      <c r="BJ47" s="33"/>
+      <c r="BK47" s="33"/>
+      <c r="BL47" s="33"/>
+      <c r="BM47" s="33"/>
+      <c r="BN47" s="33"/>
+      <c r="BO47" s="30"/>
+      <c r="BP47" s="30"/>
+      <c r="BQ47" s="30"/>
+      <c r="BR47" s="30"/>
+      <c r="BS47" s="30"/>
+      <c r="BT47" s="30"/>
       <c r="BU47" s="7"/>
       <c r="BV47" s="7"/>
       <c r="BW47" s="7"/>
@@ -15000,7 +14973,7 @@
       <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
@@ -15094,7 +15067,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
@@ -15763,7 +15736,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -15969,7 +15942,7 @@
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -16024,7 +15997,7 @@
       <c r="CC19" s="7"/>
       <c r="CD19" s="7"/>
       <c r="CE19" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
@@ -16805,7 +16778,7 @@
       <c r="AK27" s="13"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -16858,7 +16831,7 @@
       <c r="CC27" s="7"/>
       <c r="CD27" s="7"/>
       <c r="CE27" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="CF27" s="6"/>
       <c r="CG27" s="6"/>
@@ -17630,7 +17603,7 @@
       <c r="AK35" s="13"/>
       <c r="AL35" s="13"/>
       <c r="AM35" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -17687,7 +17660,7 @@
       <c r="CC35" s="7"/>
       <c r="CD35" s="7"/>
       <c r="CE35" s="6" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="CF35" s="6"/>
       <c r="CG35" s="6"/>
@@ -19241,7 +19214,7 @@
       <c r="AP1" s="4"/>
       <c r="AQ1" s="5"/>
       <c r="AT1" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -19524,7 +19497,7 @@
         <v>161</v>
       </c>
       <c r="AT4" s="7" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AU4" s="7"/>
       <c r="AV4" s="7"/>
@@ -19532,7 +19505,7 @@
       <c r="AX4" s="8"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="BA4" s="8" t="s">
         <v>56</v>
@@ -19621,8 +19594,8 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
-      <c r="AR5" s="35" t="s">
-        <v>203</v>
+      <c r="AR5" s="36" t="s">
+        <v>207</v>
       </c>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
@@ -19631,7 +19604,7 @@
       <c r="AX5" s="7"/>
       <c r="AY5" s="7"/>
       <c r="AZ5" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="BA5" s="7" t="s">
         <v>172</v>
@@ -19691,10 +19664,10 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
@@ -19737,7 +19710,7 @@
       <c r="AW6" s="7"/>
       <c r="AX6" s="7"/>
       <c r="AY6" s="7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AZ6" s="7"/>
       <c r="BA6" s="7"/>
@@ -19746,7 +19719,7 @@
       <c r="BD6" s="6"/>
       <c r="BE6" s="11"/>
       <c r="BF6" s="6" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="BG6" s="11"/>
       <c r="BH6" s="11"/>
@@ -19811,7 +19784,7 @@
         <v>172</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="BG7" s="6" t="s">
         <v>173</v>
@@ -19865,7 +19838,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -20428,8 +20401,8 @@
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
-      <c r="AR13" s="35" t="s">
-        <v>203</v>
+      <c r="AR13" s="36" t="s">
+        <v>207</v>
       </c>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
@@ -20542,10 +20515,10 @@
       </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -20824,7 +20797,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -21295,8 +21268,8 @@
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
-      <c r="AR21" s="35" t="s">
-        <v>203</v>
+      <c r="AR21" s="36" t="s">
+        <v>207</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
@@ -21405,10 +21378,10 @@
       </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
@@ -22121,8 +22094,8 @@
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
-      <c r="AR29" s="35" t="s">
-        <v>203</v>
+      <c r="AR29" s="36" t="s">
+        <v>207</v>
       </c>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
@@ -22219,10 +22192,10 @@
       </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -22289,7 +22262,7 @@
       </c>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="BR30" s="7"/>
       <c r="BS30" s="7"/>
@@ -22794,7 +22767,7 @@
       <c r="AR36" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="AT36" s="36" t="s">
+      <c r="AT36" s="37" t="s">
         <v>34</v>
       </c>
       <c r="AU36" s="13" t="s">
@@ -22900,8 +22873,8 @@
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
-      <c r="AR37" s="35" t="s">
-        <v>203</v>
+      <c r="AR37" s="36" t="s">
+        <v>207</v>
       </c>
       <c r="AT37" s="7" t="s">
         <v>35</v>
@@ -22984,10 +22957,10 @@
       </c>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -23022,17 +22995,17 @@
       <c r="AW38" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AX38" s="36" t="s">
+      <c r="AX38" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="AY38" s="36" t="s">
+      <c r="AY38" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="AZ38" s="36"/>
-      <c r="BA38" s="36" t="s">
+      <c r="AZ38" s="37"/>
+      <c r="BA38" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="BB38" s="36" t="s">
+      <c r="BB38" s="37" t="s">
         <v>107</v>
       </c>
       <c r="BC38" s="11"/>
@@ -23095,9 +23068,9 @@
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
-      <c r="AZ39" s="36"/>
-      <c r="BA39" s="36"/>
-      <c r="BB39" s="36"/>
+      <c r="AZ39" s="37"/>
+      <c r="BA39" s="37"/>
+      <c r="BB39" s="37"/>
       <c r="BC39" s="11"/>
       <c r="BD39" s="6"/>
       <c r="BE39" s="6"/>
@@ -24342,8 +24315,8 @@
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="35" t="s">
-        <v>203</v>
+      <c r="P5" s="36" t="s">
+        <v>207</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -24474,7 +24447,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -24629,7 +24602,7 @@
       <c r="Z11" s="13"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="13"/>
-      <c r="AC11" s="37"/>
+      <c r="AC11" s="38"/>
       <c r="AD11" s="21"/>
       <c r="AE11" s="6"/>
       <c r="AF11" s="6"/>
@@ -24737,8 +24710,8 @@
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
-      <c r="P13" s="35" t="s">
-        <v>203</v>
+      <c r="P13" s="36" t="s">
+        <v>207</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="13"/>
@@ -24946,8 +24919,8 @@
       <c r="M19" s="13"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
-      <c r="P19" s="38" t="s">
-        <v>209</v>
+      <c r="P19" s="39" t="s">
+        <v>213</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -24966,7 +24939,7 @@
       <c r="AF19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36"/>
+      <c r="A20" s="37"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -25049,11 +25022,11 @@
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="36"/>
+      <c r="V22" s="37"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
-      <c r="Y22" s="39"/>
-      <c r="Z22" s="39"/>
+      <c r="Y22" s="40"/>
+      <c r="Z22" s="40"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="11"/>
@@ -25081,11 +25054,11 @@
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="36"/>
-      <c r="W23" s="36"/>
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
       <c r="X23" s="7"/>
-      <c r="Y23" s="39"/>
-      <c r="Z23" s="39"/>
+      <c r="Y23" s="40"/>
+      <c r="Z23" s="40"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
@@ -25222,7 +25195,7 @@
       <c r="M28" s="13"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="R28" s="36"/>
+      <c r="R28" s="37"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -25276,8 +25249,8 @@
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="11"/>
@@ -25290,9 +25263,9 @@
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
-      <c r="X30" s="36"/>
+      <c r="V30" s="37"/>
+      <c r="W30" s="37"/>
+      <c r="X30" s="37"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="11"/>
@@ -25309,7 +25282,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="36"/>
+      <c r="G31" s="37"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="11"/>
@@ -25324,7 +25297,7 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="36"/>
+      <c r="X31" s="37"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="7"/>
       <c r="AA31" s="11"/>
@@ -25387,7 +25360,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="35"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -25463,7 +25436,7 @@
       <c r="M36" s="13"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="R36" s="36"/>
+      <c r="R36" s="37"/>
       <c r="S36" s="13"/>
       <c r="T36" s="13"/>
       <c r="U36" s="13"/>
@@ -25502,7 +25475,7 @@
       <c r="V37" s="13"/>
       <c r="W37" s="13"/>
       <c r="X37" s="18"/>
-      <c r="Y37" s="40"/>
+      <c r="Y37" s="41"/>
       <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
@@ -25517,8 +25490,8 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="11"/>
@@ -25531,11 +25504,11 @@
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
-      <c r="V38" s="36"/>
-      <c r="W38" s="36"/>
-      <c r="X38" s="36"/>
-      <c r="Y38" s="36"/>
-      <c r="Z38" s="36"/>
+      <c r="V38" s="37"/>
+      <c r="W38" s="37"/>
+      <c r="X38" s="37"/>
+      <c r="Y38" s="37"/>
+      <c r="Z38" s="37"/>
       <c r="AA38" s="11"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="11"/>
@@ -25550,7 +25523,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="36"/>
+      <c r="G39" s="37"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="11"/>
@@ -25565,9 +25538,9 @@
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
-      <c r="X39" s="36"/>
-      <c r="Y39" s="36"/>
-      <c r="Z39" s="36"/>
+      <c r="X39" s="37"/>
+      <c r="Y39" s="37"/>
+      <c r="Z39" s="37"/>
       <c r="AA39" s="11"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
@@ -25688,7 +25661,7 @@
       <c r="AF43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="36"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -25703,7 +25676,7 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
-      <c r="R44" s="36"/>
+      <c r="R44" s="37"/>
       <c r="S44" s="13"/>
       <c r="T44" s="13"/>
       <c r="U44" s="13"/>
@@ -25757,8 +25730,8 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
       <c r="J46" s="11"/>
@@ -25771,11 +25744,11 @@
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
-      <c r="V46" s="36"/>
-      <c r="W46" s="36"/>
-      <c r="X46" s="36"/>
-      <c r="Y46" s="36"/>
-      <c r="Z46" s="36"/>
+      <c r="V46" s="37"/>
+      <c r="W46" s="37"/>
+      <c r="X46" s="37"/>
+      <c r="Y46" s="37"/>
+      <c r="Z46" s="37"/>
       <c r="AA46" s="11"/>
       <c r="AB46" s="6"/>
       <c r="AC46" s="11"/>
@@ -25790,7 +25763,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="36"/>
+      <c r="G47" s="37"/>
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
       <c r="J47" s="11"/>
@@ -25805,9 +25778,9 @@
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
-      <c r="X47" s="36"/>
-      <c r="Y47" s="36"/>
-      <c r="Z47" s="36"/>
+      <c r="X47" s="37"/>
+      <c r="Y47" s="37"/>
+      <c r="Z47" s="37"/>
       <c r="AA47" s="11"/>
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
@@ -25935,7 +25908,7 @@
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
-      <c r="V52" s="41"/>
+      <c r="V52" s="42"/>
       <c r="W52" s="6"/>
       <c r="X52" s="13"/>
       <c r="Y52" s="14"/>
@@ -25984,11 +25957,11 @@
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="36"/>
+      <c r="E54" s="37"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
       <c r="J54" s="11"/>
       <c r="K54" s="6"/>
       <c r="L54" s="11"/>
@@ -26016,11 +25989,11 @@
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
       <c r="J55" s="11"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="213">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -587,18 +587,14 @@
     <t xml:space="preserve">sShift</t>
   </si>
   <si>
-    <t xml:space="preserve">SelCur
-Togle</t>
+    <t xml:space="preserve">Select
+Mode</t>
   </si>
   <si>
     <t xml:space="preserve">F14修飾</t>
   </si>
   <si>
     <t xml:space="preserve">SC+p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select
-Mode</t>
   </si>
   <si>
     <t xml:space="preserve">C+Space</t>
@@ -963,7 +959,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1078,10 +1074,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -9674,11 +9666,11 @@
       </c>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
-      <c r="O19" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
+      <c r="O19" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
       <c r="R19" s="13" t="s">
         <v>138</v>
       </c>
@@ -9704,16 +9696,16 @@
       </c>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
-      <c r="AG19" s="31" t="s">
+      <c r="AG19" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="AH19" s="31"/>
-      <c r="AI19" s="31"/>
-      <c r="AJ19" s="31" t="s">
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="30"/>
+      <c r="AJ19" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="AK19" s="31"/>
-      <c r="AL19" s="31"/>
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="30"/>
       <c r="AM19" s="6"/>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -9807,11 +9799,11 @@
       </c>
       <c r="N20" s="20"/>
       <c r="O20" s="20"/>
-      <c r="P20" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q20" s="31"/>
-      <c r="R20" s="31"/>
+      <c r="P20" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
       <c r="S20" s="6" t="s">
         <v>151</v>
       </c>
@@ -9865,11 +9857,11 @@
       </c>
       <c r="BC20" s="13"/>
       <c r="BD20" s="13"/>
-      <c r="BE20" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="BF20" s="32"/>
-      <c r="BG20" s="32"/>
+      <c r="BE20" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="BF20" s="31"/>
+      <c r="BG20" s="31"/>
       <c r="BH20" s="7"/>
       <c r="BI20" s="7"/>
       <c r="BJ20" s="7"/>
@@ -10493,11 +10485,11 @@
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
-      <c r="O27" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="30"/>
+      <c r="O27" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
       <c r="R27" s="13" t="s">
         <v>138</v>
       </c>
@@ -10523,16 +10515,16 @@
       </c>
       <c r="AE27" s="13"/>
       <c r="AF27" s="13"/>
-      <c r="AG27" s="31" t="s">
+      <c r="AG27" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="AH27" s="31"/>
-      <c r="AI27" s="31"/>
-      <c r="AJ27" s="31" t="s">
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="30"/>
+      <c r="AJ27" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="AK27" s="31"/>
-      <c r="AL27" s="31"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="30"/>
       <c r="AM27" s="6"/>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -10616,11 +10608,11 @@
       </c>
       <c r="N28" s="20"/>
       <c r="O28" s="20"/>
-      <c r="P28" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
+      <c r="P28" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
       <c r="S28" s="6" t="s">
         <v>151</v>
       </c>
@@ -10660,11 +10652,11 @@
       <c r="AO28" s="9"/>
       <c r="AP28" s="9"/>
       <c r="AQ28" s="9"/>
-      <c r="AS28" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="AT28" s="33"/>
-      <c r="AU28" s="33"/>
+      <c r="AS28" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="AT28" s="32"/>
+      <c r="AU28" s="32"/>
       <c r="AV28" s="7"/>
       <c r="AW28" s="7"/>
       <c r="AX28" s="7"/>
@@ -10907,27 +10899,27 @@
       <c r="BC30" s="7"/>
       <c r="BD30" s="7"/>
       <c r="BE30" s="7"/>
-      <c r="BF30" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="BG30" s="33"/>
-      <c r="BH30" s="33"/>
-      <c r="BI30" s="33"/>
-      <c r="BJ30" s="33"/>
-      <c r="BK30" s="33"/>
-      <c r="BL30" s="33"/>
-      <c r="BM30" s="33"/>
-      <c r="BN30" s="33"/>
-      <c r="BO30" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="BP30" s="30"/>
-      <c r="BQ30" s="30"/>
-      <c r="BR30" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="BS30" s="30"/>
-      <c r="BT30" s="30"/>
+      <c r="BF30" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="BG30" s="32"/>
+      <c r="BH30" s="32"/>
+      <c r="BI30" s="32"/>
+      <c r="BJ30" s="32"/>
+      <c r="BK30" s="32"/>
+      <c r="BL30" s="32"/>
+      <c r="BM30" s="32"/>
+      <c r="BN30" s="32"/>
+      <c r="BO30" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="BP30" s="29"/>
+      <c r="BQ30" s="29"/>
+      <c r="BR30" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="BS30" s="29"/>
+      <c r="BT30" s="29"/>
       <c r="BU30" s="7"/>
       <c r="BV30" s="7"/>
       <c r="BW30" s="7"/>
@@ -11003,21 +10995,21 @@
       <c r="BC31" s="7"/>
       <c r="BD31" s="7"/>
       <c r="BE31" s="7"/>
-      <c r="BF31" s="33"/>
-      <c r="BG31" s="33"/>
-      <c r="BH31" s="33"/>
-      <c r="BI31" s="33"/>
-      <c r="BJ31" s="33"/>
-      <c r="BK31" s="33"/>
-      <c r="BL31" s="33"/>
-      <c r="BM31" s="33"/>
-      <c r="BN31" s="33"/>
-      <c r="BO31" s="30"/>
-      <c r="BP31" s="30"/>
-      <c r="BQ31" s="30"/>
-      <c r="BR31" s="30"/>
-      <c r="BS31" s="30"/>
-      <c r="BT31" s="30"/>
+      <c r="BF31" s="32"/>
+      <c r="BG31" s="32"/>
+      <c r="BH31" s="32"/>
+      <c r="BI31" s="32"/>
+      <c r="BJ31" s="32"/>
+      <c r="BK31" s="32"/>
+      <c r="BL31" s="32"/>
+      <c r="BM31" s="32"/>
+      <c r="BN31" s="32"/>
+      <c r="BO31" s="29"/>
+      <c r="BP31" s="29"/>
+      <c r="BQ31" s="29"/>
+      <c r="BR31" s="29"/>
+      <c r="BS31" s="29"/>
+      <c r="BT31" s="29"/>
       <c r="BU31" s="7"/>
       <c r="BV31" s="7"/>
       <c r="BW31" s="7"/>
@@ -11134,7 +11126,7 @@
       <c r="AP33" s="4"/>
       <c r="AQ33" s="5"/>
       <c r="AS33" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AT33" s="5"/>
       <c r="AU33" s="4"/>
@@ -11300,11 +11292,11 @@
       </c>
       <c r="M35" s="13"/>
       <c r="N35" s="13"/>
-      <c r="O35" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="P35" s="30"/>
-      <c r="Q35" s="30"/>
+      <c r="O35" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
       <c r="R35" s="13" t="s">
         <v>138</v>
       </c>
@@ -11330,16 +11322,16 @@
       </c>
       <c r="AE35" s="13"/>
       <c r="AF35" s="13"/>
-      <c r="AG35" s="31" t="s">
+      <c r="AG35" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="AH35" s="31"/>
-      <c r="AI35" s="31"/>
-      <c r="AJ35" s="31" t="s">
+      <c r="AH35" s="30"/>
+      <c r="AI35" s="30"/>
+      <c r="AJ35" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="AK35" s="31"/>
-      <c r="AL35" s="31"/>
+      <c r="AK35" s="30"/>
+      <c r="AL35" s="30"/>
       <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -11427,11 +11419,11 @@
       </c>
       <c r="N36" s="20"/>
       <c r="O36" s="20"/>
-      <c r="P36" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q36" s="31"/>
-      <c r="R36" s="31"/>
+      <c r="P36" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
       <c r="S36" s="6" t="s">
         <v>151</v>
       </c>
@@ -11471,11 +11463,11 @@
       <c r="AO36" s="9"/>
       <c r="AP36" s="9"/>
       <c r="AQ36" s="9"/>
-      <c r="AS36" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="AT36" s="33"/>
-      <c r="AU36" s="33"/>
+      <c r="AS36" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="AT36" s="32"/>
+      <c r="AU36" s="32"/>
       <c r="AV36" s="7"/>
       <c r="AW36" s="7"/>
       <c r="AX36" s="7"/>
@@ -11672,7 +11664,7 @@
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
       <c r="N38" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O38" s="7"/>
       <c r="P38" s="7" t="s">
@@ -11728,27 +11720,27 @@
       <c r="BC38" s="7"/>
       <c r="BD38" s="7"/>
       <c r="BE38" s="7"/>
-      <c r="BF38" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="BG38" s="33"/>
-      <c r="BH38" s="33"/>
-      <c r="BI38" s="33"/>
-      <c r="BJ38" s="33"/>
-      <c r="BK38" s="33"/>
-      <c r="BL38" s="33"/>
-      <c r="BM38" s="33"/>
-      <c r="BN38" s="33"/>
-      <c r="BO38" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="BP38" s="30"/>
-      <c r="BQ38" s="30"/>
-      <c r="BR38" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="BS38" s="30"/>
-      <c r="BT38" s="30"/>
+      <c r="BF38" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="BG38" s="32"/>
+      <c r="BH38" s="32"/>
+      <c r="BI38" s="32"/>
+      <c r="BJ38" s="32"/>
+      <c r="BK38" s="32"/>
+      <c r="BL38" s="32"/>
+      <c r="BM38" s="32"/>
+      <c r="BN38" s="32"/>
+      <c r="BO38" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="BP38" s="29"/>
+      <c r="BQ38" s="29"/>
+      <c r="BR38" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="BS38" s="29"/>
+      <c r="BT38" s="29"/>
       <c r="BU38" s="7"/>
       <c r="BV38" s="7"/>
       <c r="BW38" s="7"/>
@@ -11822,21 +11814,21 @@
       <c r="BC39" s="7"/>
       <c r="BD39" s="7"/>
       <c r="BE39" s="7"/>
-      <c r="BF39" s="33"/>
-      <c r="BG39" s="33"/>
-      <c r="BH39" s="33"/>
-      <c r="BI39" s="33"/>
-      <c r="BJ39" s="33"/>
-      <c r="BK39" s="33"/>
-      <c r="BL39" s="33"/>
-      <c r="BM39" s="33"/>
-      <c r="BN39" s="33"/>
-      <c r="BO39" s="30"/>
-      <c r="BP39" s="30"/>
-      <c r="BQ39" s="30"/>
-      <c r="BR39" s="30"/>
-      <c r="BS39" s="30"/>
-      <c r="BT39" s="30"/>
+      <c r="BF39" s="32"/>
+      <c r="BG39" s="32"/>
+      <c r="BH39" s="32"/>
+      <c r="BI39" s="32"/>
+      <c r="BJ39" s="32"/>
+      <c r="BK39" s="32"/>
+      <c r="BL39" s="32"/>
+      <c r="BM39" s="32"/>
+      <c r="BN39" s="32"/>
+      <c r="BO39" s="29"/>
+      <c r="BP39" s="29"/>
+      <c r="BQ39" s="29"/>
+      <c r="BR39" s="29"/>
+      <c r="BS39" s="29"/>
+      <c r="BT39" s="29"/>
       <c r="BU39" s="7"/>
       <c r="BV39" s="7"/>
       <c r="BW39" s="7"/>
@@ -11897,7 +11889,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -11942,7 +11934,7 @@
       <c r="AP41" s="4"/>
       <c r="AQ41" s="5"/>
       <c r="AS41" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AT41" s="15"/>
       <c r="AU41" s="4"/>
@@ -12064,11 +12056,11 @@
       </c>
       <c r="M43" s="13"/>
       <c r="N43" s="13"/>
-      <c r="O43" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
+      <c r="O43" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
       <c r="R43" s="13" t="s">
         <v>138</v>
       </c>
@@ -12094,16 +12086,16 @@
       </c>
       <c r="AE43" s="7"/>
       <c r="AF43" s="7"/>
-      <c r="AG43" s="31" t="s">
+      <c r="AG43" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="AH43" s="31"/>
-      <c r="AI43" s="31"/>
-      <c r="AJ43" s="31" t="s">
+      <c r="AH43" s="30"/>
+      <c r="AI43" s="30"/>
+      <c r="AJ43" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="AK43" s="31"/>
-      <c r="AL43" s="31"/>
+      <c r="AK43" s="30"/>
+      <c r="AL43" s="30"/>
       <c r="AM43" s="6"/>
       <c r="AN43" s="6"/>
       <c r="AO43" s="6"/>
@@ -12125,11 +12117,11 @@
       </c>
       <c r="BE43" s="13"/>
       <c r="BF43" s="13"/>
-      <c r="BG43" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="BH43" s="30"/>
-      <c r="BI43" s="30"/>
+      <c r="BG43" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="BH43" s="29"/>
+      <c r="BI43" s="29"/>
       <c r="BJ43" s="13" t="s">
         <v>138</v>
       </c>
@@ -12164,11 +12156,11 @@
       <c r="CI43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="B44" s="33"/>
-      <c r="C44" s="33"/>
+      <c r="A44" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -12219,11 +12211,11 @@
       <c r="AO44" s="9"/>
       <c r="AP44" s="9"/>
       <c r="AQ44" s="9"/>
-      <c r="AS44" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="AT44" s="33"/>
-      <c r="AU44" s="33"/>
+      <c r="AS44" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="AT44" s="32"/>
+      <c r="AU44" s="32"/>
       <c r="AV44" s="6"/>
       <c r="AW44" s="6"/>
       <c r="AX44" s="6"/>
@@ -12342,16 +12334,16 @@
       </c>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
-      <c r="AZ45" s="34" t="s">
+      <c r="AZ45" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="BA45" s="33"/>
+      <c r="BB45" s="33"/>
+      <c r="BC45" s="33" t="s">
         <v>199</v>
       </c>
-      <c r="BA45" s="34"/>
-      <c r="BB45" s="34"/>
-      <c r="BC45" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="BD45" s="34"/>
-      <c r="BE45" s="34"/>
+      <c r="BD45" s="33"/>
+      <c r="BE45" s="33"/>
       <c r="BF45" s="13" t="s">
         <v>157</v>
       </c>
@@ -12367,16 +12359,16 @@
       </c>
       <c r="BM45" s="10"/>
       <c r="BN45" s="10"/>
-      <c r="BO45" s="35" t="s">
+      <c r="BO45" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="BP45" s="35"/>
-      <c r="BQ45" s="35"/>
-      <c r="BR45" s="35" t="s">
+      <c r="BP45" s="34"/>
+      <c r="BQ45" s="34"/>
+      <c r="BR45" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="BS45" s="35"/>
-      <c r="BT45" s="35"/>
+      <c r="BS45" s="34"/>
+      <c r="BT45" s="34"/>
       <c r="BU45" s="6"/>
       <c r="BV45" s="6"/>
       <c r="BW45" s="6"/>
@@ -12407,27 +12399,27 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
-      <c r="N46" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="O46" s="33"/>
-      <c r="P46" s="33"/>
-      <c r="Q46" s="33"/>
-      <c r="R46" s="33"/>
-      <c r="S46" s="33"/>
-      <c r="T46" s="33"/>
-      <c r="U46" s="33"/>
-      <c r="V46" s="33"/>
-      <c r="W46" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA46" s="30"/>
-      <c r="AB46" s="30"/>
+      <c r="N46" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
+      <c r="S46" s="32"/>
+      <c r="T46" s="32"/>
+      <c r="U46" s="32"/>
+      <c r="V46" s="32"/>
+      <c r="W46" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="X46" s="29"/>
+      <c r="Y46" s="29"/>
+      <c r="Z46" s="29" t="s">
+        <v>187</v>
+      </c>
+      <c r="AA46" s="29"/>
+      <c r="AB46" s="29"/>
       <c r="AC46" s="7"/>
       <c r="AD46" s="7"/>
       <c r="AE46" s="7"/>
@@ -12456,27 +12448,27 @@
       <c r="BC46" s="7"/>
       <c r="BD46" s="7"/>
       <c r="BE46" s="7"/>
-      <c r="BF46" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="BG46" s="33"/>
-      <c r="BH46" s="33"/>
-      <c r="BI46" s="33"/>
-      <c r="BJ46" s="33"/>
-      <c r="BK46" s="33"/>
-      <c r="BL46" s="33"/>
-      <c r="BM46" s="33"/>
-      <c r="BN46" s="33"/>
-      <c r="BO46" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="BP46" s="30"/>
-      <c r="BQ46" s="30"/>
-      <c r="BR46" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="BS46" s="30"/>
-      <c r="BT46" s="30"/>
+      <c r="BF46" s="32" t="s">
+        <v>192</v>
+      </c>
+      <c r="BG46" s="32"/>
+      <c r="BH46" s="32"/>
+      <c r="BI46" s="32"/>
+      <c r="BJ46" s="32"/>
+      <c r="BK46" s="32"/>
+      <c r="BL46" s="32"/>
+      <c r="BM46" s="32"/>
+      <c r="BN46" s="32"/>
+      <c r="BO46" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="BP46" s="29"/>
+      <c r="BQ46" s="29"/>
+      <c r="BR46" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="BS46" s="29"/>
+      <c r="BT46" s="29"/>
       <c r="BU46" s="7"/>
       <c r="BV46" s="7"/>
       <c r="BW46" s="7"/>
@@ -12507,21 +12499,21 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
-      <c r="N47" s="33"/>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33"/>
-      <c r="S47" s="33"/>
-      <c r="T47" s="33"/>
-      <c r="U47" s="33"/>
-      <c r="V47" s="33"/>
-      <c r="W47" s="30"/>
-      <c r="X47" s="30"/>
-      <c r="Y47" s="30"/>
-      <c r="Z47" s="30"/>
-      <c r="AA47" s="30"/>
-      <c r="AB47" s="30"/>
+      <c r="N47" s="32"/>
+      <c r="O47" s="32"/>
+      <c r="P47" s="32"/>
+      <c r="Q47" s="32"/>
+      <c r="R47" s="32"/>
+      <c r="S47" s="32"/>
+      <c r="T47" s="32"/>
+      <c r="U47" s="32"/>
+      <c r="V47" s="32"/>
+      <c r="W47" s="29"/>
+      <c r="X47" s="29"/>
+      <c r="Y47" s="29"/>
+      <c r="Z47" s="29"/>
+      <c r="AA47" s="29"/>
+      <c r="AB47" s="29"/>
       <c r="AC47" s="7"/>
       <c r="AD47" s="7"/>
       <c r="AE47" s="7"/>
@@ -12550,21 +12542,21 @@
       <c r="BC47" s="7"/>
       <c r="BD47" s="7"/>
       <c r="BE47" s="7"/>
-      <c r="BF47" s="33"/>
-      <c r="BG47" s="33"/>
-      <c r="BH47" s="33"/>
-      <c r="BI47" s="33"/>
-      <c r="BJ47" s="33"/>
-      <c r="BK47" s="33"/>
-      <c r="BL47" s="33"/>
-      <c r="BM47" s="33"/>
-      <c r="BN47" s="33"/>
-      <c r="BO47" s="30"/>
-      <c r="BP47" s="30"/>
-      <c r="BQ47" s="30"/>
-      <c r="BR47" s="30"/>
-      <c r="BS47" s="30"/>
-      <c r="BT47" s="30"/>
+      <c r="BF47" s="32"/>
+      <c r="BG47" s="32"/>
+      <c r="BH47" s="32"/>
+      <c r="BI47" s="32"/>
+      <c r="BJ47" s="32"/>
+      <c r="BK47" s="32"/>
+      <c r="BL47" s="32"/>
+      <c r="BM47" s="32"/>
+      <c r="BN47" s="32"/>
+      <c r="BO47" s="29"/>
+      <c r="BP47" s="29"/>
+      <c r="BQ47" s="29"/>
+      <c r="BR47" s="29"/>
+      <c r="BS47" s="29"/>
+      <c r="BT47" s="29"/>
       <c r="BU47" s="7"/>
       <c r="BV47" s="7"/>
       <c r="BW47" s="7"/>
@@ -14973,7 +14965,7 @@
       <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
@@ -15067,7 +15059,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
@@ -15736,7 +15728,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -15942,7 +15934,7 @@
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -15997,7 +15989,7 @@
       <c r="CC19" s="7"/>
       <c r="CD19" s="7"/>
       <c r="CE19" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
@@ -16778,7 +16770,7 @@
       <c r="AK27" s="13"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -16831,7 +16823,7 @@
       <c r="CC27" s="7"/>
       <c r="CD27" s="7"/>
       <c r="CE27" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="CF27" s="6"/>
       <c r="CG27" s="6"/>
@@ -17603,7 +17595,7 @@
       <c r="AK35" s="13"/>
       <c r="AL35" s="13"/>
       <c r="AM35" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -17660,7 +17652,7 @@
       <c r="CC35" s="7"/>
       <c r="CD35" s="7"/>
       <c r="CE35" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="CF35" s="6"/>
       <c r="CG35" s="6"/>
@@ -19214,7 +19206,7 @@
       <c r="AP1" s="4"/>
       <c r="AQ1" s="5"/>
       <c r="AT1" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -19497,7 +19489,7 @@
         <v>161</v>
       </c>
       <c r="AT4" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AU4" s="7"/>
       <c r="AV4" s="7"/>
@@ -19505,7 +19497,7 @@
       <c r="AX4" s="8"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BA4" s="8" t="s">
         <v>56</v>
@@ -19594,8 +19586,8 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
-      <c r="AR5" s="36" t="s">
-        <v>207</v>
+      <c r="AR5" s="35" t="s">
+        <v>206</v>
       </c>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
@@ -19604,7 +19596,7 @@
       <c r="AX5" s="7"/>
       <c r="AY5" s="7"/>
       <c r="AZ5" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BA5" s="7" t="s">
         <v>172</v>
@@ -19664,10 +19656,10 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
@@ -19710,7 +19702,7 @@
       <c r="AW6" s="7"/>
       <c r="AX6" s="7"/>
       <c r="AY6" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AZ6" s="7"/>
       <c r="BA6" s="7"/>
@@ -19719,7 +19711,7 @@
       <c r="BD6" s="6"/>
       <c r="BE6" s="11"/>
       <c r="BF6" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BG6" s="11"/>
       <c r="BH6" s="11"/>
@@ -19784,7 +19776,7 @@
         <v>172</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BG7" s="6" t="s">
         <v>173</v>
@@ -19838,7 +19830,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -20401,8 +20393,8 @@
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
-      <c r="AR13" s="36" t="s">
-        <v>207</v>
+      <c r="AR13" s="35" t="s">
+        <v>206</v>
       </c>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
@@ -20515,10 +20507,10 @@
       </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -20797,7 +20789,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -21268,8 +21260,8 @@
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
-      <c r="AR21" s="36" t="s">
-        <v>207</v>
+      <c r="AR21" s="35" t="s">
+        <v>206</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
@@ -21378,10 +21370,10 @@
       </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
@@ -22094,8 +22086,8 @@
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
-      <c r="AR29" s="36" t="s">
-        <v>207</v>
+      <c r="AR29" s="35" t="s">
+        <v>206</v>
       </c>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
@@ -22192,10 +22184,10 @@
       </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -22262,7 +22254,7 @@
       </c>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BR30" s="7"/>
       <c r="BS30" s="7"/>
@@ -22767,7 +22759,7 @@
       <c r="AR36" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="AT36" s="37" t="s">
+      <c r="AT36" s="36" t="s">
         <v>34</v>
       </c>
       <c r="AU36" s="13" t="s">
@@ -22873,8 +22865,8 @@
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
-      <c r="AR37" s="36" t="s">
-        <v>207</v>
+      <c r="AR37" s="35" t="s">
+        <v>206</v>
       </c>
       <c r="AT37" s="7" t="s">
         <v>35</v>
@@ -22957,10 +22949,10 @@
       </c>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -22995,17 +22987,17 @@
       <c r="AW38" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AX38" s="37" t="s">
+      <c r="AX38" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="AY38" s="37" t="s">
+      <c r="AY38" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="AZ38" s="37"/>
-      <c r="BA38" s="37" t="s">
+      <c r="AZ38" s="36"/>
+      <c r="BA38" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="BB38" s="37" t="s">
+      <c r="BB38" s="36" t="s">
         <v>107</v>
       </c>
       <c r="BC38" s="11"/>
@@ -23068,9 +23060,9 @@
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
-      <c r="AZ39" s="37"/>
-      <c r="BA39" s="37"/>
-      <c r="BB39" s="37"/>
+      <c r="AZ39" s="36"/>
+      <c r="BA39" s="36"/>
+      <c r="BB39" s="36"/>
       <c r="BC39" s="11"/>
       <c r="BD39" s="6"/>
       <c r="BE39" s="6"/>
@@ -24315,8 +24307,8 @@
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="36" t="s">
-        <v>207</v>
+      <c r="P5" s="35" t="s">
+        <v>206</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -24447,7 +24439,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -24602,7 +24594,7 @@
       <c r="Z11" s="13"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="13"/>
-      <c r="AC11" s="38"/>
+      <c r="AC11" s="37"/>
       <c r="AD11" s="21"/>
       <c r="AE11" s="6"/>
       <c r="AF11" s="6"/>
@@ -24710,8 +24702,8 @@
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
-      <c r="P13" s="36" t="s">
-        <v>207</v>
+      <c r="P13" s="35" t="s">
+        <v>206</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="13"/>
@@ -24919,8 +24911,8 @@
       <c r="M19" s="13"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
-      <c r="P19" s="39" t="s">
-        <v>213</v>
+      <c r="P19" s="38" t="s">
+        <v>212</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -24939,7 +24931,7 @@
       <c r="AF19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37"/>
+      <c r="A20" s="36"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -25022,11 +25014,11 @@
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="37"/>
+      <c r="V22" s="36"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
-      <c r="Y22" s="40"/>
-      <c r="Z22" s="40"/>
+      <c r="Y22" s="39"/>
+      <c r="Z22" s="39"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="11"/>
@@ -25054,11 +25046,11 @@
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="37"/>
-      <c r="W23" s="37"/>
+      <c r="V23" s="36"/>
+      <c r="W23" s="36"/>
       <c r="X23" s="7"/>
-      <c r="Y23" s="40"/>
-      <c r="Z23" s="40"/>
+      <c r="Y23" s="39"/>
+      <c r="Z23" s="39"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
@@ -25195,7 +25187,7 @@
       <c r="M28" s="13"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="R28" s="37"/>
+      <c r="R28" s="36"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -25249,8 +25241,8 @@
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="11"/>
@@ -25263,9 +25255,9 @@
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="37"/>
-      <c r="W30" s="37"/>
-      <c r="X30" s="37"/>
+      <c r="V30" s="36"/>
+      <c r="W30" s="36"/>
+      <c r="X30" s="36"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="11"/>
@@ -25282,7 +25274,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="37"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="11"/>
@@ -25297,7 +25289,7 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="37"/>
+      <c r="X31" s="36"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="7"/>
       <c r="AA31" s="11"/>
@@ -25360,7 +25352,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="35"/>
+      <c r="D34" s="34"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -25436,7 +25428,7 @@
       <c r="M36" s="13"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="R36" s="37"/>
+      <c r="R36" s="36"/>
       <c r="S36" s="13"/>
       <c r="T36" s="13"/>
       <c r="U36" s="13"/>
@@ -25475,7 +25467,7 @@
       <c r="V37" s="13"/>
       <c r="W37" s="13"/>
       <c r="X37" s="18"/>
-      <c r="Y37" s="41"/>
+      <c r="Y37" s="40"/>
       <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
@@ -25490,8 +25482,8 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="11"/>
@@ -25504,11 +25496,11 @@
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
-      <c r="V38" s="37"/>
-      <c r="W38" s="37"/>
-      <c r="X38" s="37"/>
-      <c r="Y38" s="37"/>
-      <c r="Z38" s="37"/>
+      <c r="V38" s="36"/>
+      <c r="W38" s="36"/>
+      <c r="X38" s="36"/>
+      <c r="Y38" s="36"/>
+      <c r="Z38" s="36"/>
       <c r="AA38" s="11"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="11"/>
@@ -25523,7 +25515,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="37"/>
+      <c r="G39" s="36"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="11"/>
@@ -25538,9 +25530,9 @@
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
-      <c r="X39" s="37"/>
-      <c r="Y39" s="37"/>
-      <c r="Z39" s="37"/>
+      <c r="X39" s="36"/>
+      <c r="Y39" s="36"/>
+      <c r="Z39" s="36"/>
       <c r="AA39" s="11"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
@@ -25661,7 +25653,7 @@
       <c r="AF43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="37"/>
+      <c r="A44" s="36"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -25676,7 +25668,7 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
-      <c r="R44" s="37"/>
+      <c r="R44" s="36"/>
       <c r="S44" s="13"/>
       <c r="T44" s="13"/>
       <c r="U44" s="13"/>
@@ -25730,8 +25722,8 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
       <c r="J46" s="11"/>
@@ -25744,11 +25736,11 @@
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
-      <c r="V46" s="37"/>
-      <c r="W46" s="37"/>
-      <c r="X46" s="37"/>
-      <c r="Y46" s="37"/>
-      <c r="Z46" s="37"/>
+      <c r="V46" s="36"/>
+      <c r="W46" s="36"/>
+      <c r="X46" s="36"/>
+      <c r="Y46" s="36"/>
+      <c r="Z46" s="36"/>
       <c r="AA46" s="11"/>
       <c r="AB46" s="6"/>
       <c r="AC46" s="11"/>
@@ -25763,7 +25755,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="37"/>
+      <c r="G47" s="36"/>
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
       <c r="J47" s="11"/>
@@ -25778,9 +25770,9 @@
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
-      <c r="X47" s="37"/>
-      <c r="Y47" s="37"/>
-      <c r="Z47" s="37"/>
+      <c r="X47" s="36"/>
+      <c r="Y47" s="36"/>
+      <c r="Z47" s="36"/>
       <c r="AA47" s="11"/>
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
@@ -25908,7 +25900,7 @@
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
-      <c r="V52" s="42"/>
+      <c r="V52" s="41"/>
       <c r="W52" s="6"/>
       <c r="X52" s="13"/>
       <c r="Y52" s="14"/>
@@ -25957,11 +25949,11 @@
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="37"/>
+      <c r="E54" s="36"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="40"/>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
       <c r="J54" s="11"/>
       <c r="K54" s="6"/>
       <c r="L54" s="11"/>
@@ -25989,11 +25981,11 @@
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
       <c r="J55" s="11"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="211">
   <si>
     <t xml:space="preserve">標準</t>
   </si>
@@ -603,14 +603,7 @@
     <t xml:space="preserve">S+Tab</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard
-Mode</t>
-  </si>
-  <si>
     <t xml:space="preserve">10Key Mode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backspace</t>
   </si>
   <si>
     <t xml:space="preserve">Cursor Mode</t>
@@ -959,7 +952,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1085,10 +1078,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9774,9 +9763,7 @@
       <c r="CI19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="13" t="s">
@@ -10050,7 +10037,9 @@
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
+      <c r="K22" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
       <c r="N22" s="7" t="s">
@@ -10583,9 +10572,7 @@
       <c r="CI27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="13" t="s">
@@ -10652,11 +10639,9 @@
       <c r="AO28" s="9"/>
       <c r="AP28" s="9"/>
       <c r="AQ28" s="9"/>
-      <c r="AS28" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="AT28" s="32"/>
-      <c r="AU28" s="32"/>
+      <c r="AS28" s="7"/>
+      <c r="AT28" s="7"/>
+      <c r="AU28" s="7"/>
       <c r="AV28" s="7"/>
       <c r="AW28" s="7"/>
       <c r="AX28" s="7"/>
@@ -10839,12 +10824,12 @@
       </c>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
+      <c r="K30" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="L30" s="7"/>
       <c r="M30" s="7"/>
-      <c r="N30" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="N30" s="7"/>
       <c r="O30" s="7"/>
       <c r="P30" s="7" t="s">
         <v>52</v>
@@ -10899,17 +10884,15 @@
       <c r="BC30" s="7"/>
       <c r="BD30" s="7"/>
       <c r="BE30" s="7"/>
-      <c r="BF30" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="BG30" s="32"/>
-      <c r="BH30" s="32"/>
-      <c r="BI30" s="32"/>
-      <c r="BJ30" s="32"/>
-      <c r="BK30" s="32"/>
-      <c r="BL30" s="32"/>
-      <c r="BM30" s="32"/>
-      <c r="BN30" s="32"/>
+      <c r="BF30" s="7"/>
+      <c r="BG30" s="7"/>
+      <c r="BH30" s="7"/>
+      <c r="BI30" s="7"/>
+      <c r="BJ30" s="7"/>
+      <c r="BK30" s="7"/>
+      <c r="BL30" s="7"/>
+      <c r="BM30" s="7"/>
+      <c r="BN30" s="7"/>
       <c r="BO30" s="29" t="s">
         <v>187</v>
       </c>
@@ -10995,15 +10978,15 @@
       <c r="BC31" s="7"/>
       <c r="BD31" s="7"/>
       <c r="BE31" s="7"/>
-      <c r="BF31" s="32"/>
-      <c r="BG31" s="32"/>
-      <c r="BH31" s="32"/>
-      <c r="BI31" s="32"/>
-      <c r="BJ31" s="32"/>
-      <c r="BK31" s="32"/>
-      <c r="BL31" s="32"/>
-      <c r="BM31" s="32"/>
-      <c r="BN31" s="32"/>
+      <c r="BF31" s="7"/>
+      <c r="BG31" s="7"/>
+      <c r="BH31" s="7"/>
+      <c r="BI31" s="7"/>
+      <c r="BJ31" s="7"/>
+      <c r="BK31" s="7"/>
+      <c r="BL31" s="7"/>
+      <c r="BM31" s="7"/>
+      <c r="BN31" s="7"/>
       <c r="BO31" s="29"/>
       <c r="BP31" s="29"/>
       <c r="BQ31" s="29"/>
@@ -11080,9 +11063,7 @@
       <c r="AT32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="15"/>
@@ -11126,7 +11107,7 @@
       <c r="AP33" s="4"/>
       <c r="AQ33" s="5"/>
       <c r="AS33" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AT33" s="5"/>
       <c r="AU33" s="4"/>
@@ -11394,9 +11375,7 @@
       <c r="CI35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
       <c r="D36" s="13" t="s">
@@ -11463,11 +11442,9 @@
       <c r="AO36" s="9"/>
       <c r="AP36" s="9"/>
       <c r="AQ36" s="9"/>
-      <c r="AS36" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="AT36" s="32"/>
-      <c r="AU36" s="32"/>
+      <c r="AS36" s="7"/>
+      <c r="AT36" s="7"/>
+      <c r="AU36" s="7"/>
       <c r="AV36" s="7"/>
       <c r="AW36" s="7"/>
       <c r="AX36" s="7"/>
@@ -11660,12 +11637,12 @@
       </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
+      <c r="K38" s="7" t="s">
+        <v>2</v>
+      </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7"/>
-      <c r="N38" s="7" t="s">
-        <v>194</v>
-      </c>
+      <c r="N38" s="7"/>
       <c r="O38" s="7"/>
       <c r="P38" s="7" t="s">
         <v>52</v>
@@ -11720,17 +11697,15 @@
       <c r="BC38" s="7"/>
       <c r="BD38" s="7"/>
       <c r="BE38" s="7"/>
-      <c r="BF38" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="BG38" s="32"/>
-      <c r="BH38" s="32"/>
-      <c r="BI38" s="32"/>
-      <c r="BJ38" s="32"/>
-      <c r="BK38" s="32"/>
-      <c r="BL38" s="32"/>
-      <c r="BM38" s="32"/>
-      <c r="BN38" s="32"/>
+      <c r="BF38" s="7"/>
+      <c r="BG38" s="7"/>
+      <c r="BH38" s="7"/>
+      <c r="BI38" s="7"/>
+      <c r="BJ38" s="7"/>
+      <c r="BK38" s="7"/>
+      <c r="BL38" s="7"/>
+      <c r="BM38" s="7"/>
+      <c r="BN38" s="7"/>
       <c r="BO38" s="29" t="s">
         <v>187</v>
       </c>
@@ -11814,15 +11789,15 @@
       <c r="BC39" s="7"/>
       <c r="BD39" s="7"/>
       <c r="BE39" s="7"/>
-      <c r="BF39" s="32"/>
-      <c r="BG39" s="32"/>
-      <c r="BH39" s="32"/>
-      <c r="BI39" s="32"/>
-      <c r="BJ39" s="32"/>
-      <c r="BK39" s="32"/>
-      <c r="BL39" s="32"/>
-      <c r="BM39" s="32"/>
-      <c r="BN39" s="32"/>
+      <c r="BF39" s="7"/>
+      <c r="BG39" s="7"/>
+      <c r="BH39" s="7"/>
+      <c r="BI39" s="7"/>
+      <c r="BJ39" s="7"/>
+      <c r="BK39" s="7"/>
+      <c r="BL39" s="7"/>
+      <c r="BM39" s="7"/>
+      <c r="BN39" s="7"/>
       <c r="BO39" s="29"/>
       <c r="BP39" s="29"/>
       <c r="BQ39" s="29"/>
@@ -11846,50 +11821,53 @@
       <c r="CI39" s="24"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
-      <c r="AA40" s="27"/>
-      <c r="AB40" s="27"/>
-      <c r="AC40" s="27"/>
-      <c r="AD40" s="27"/>
-      <c r="AE40" s="27"/>
-      <c r="AF40" s="27"/>
-      <c r="AG40" s="27"/>
-      <c r="AH40" s="27"/>
-      <c r="AI40" s="27"/>
-      <c r="AJ40" s="27"/>
-      <c r="AK40" s="27"/>
-      <c r="AL40" s="27"/>
-      <c r="AM40" s="27"/>
-      <c r="AN40" s="27"/>
-      <c r="AO40" s="27"/>
-      <c r="AP40" s="27"/>
-      <c r="AQ40" s="28"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="12"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="12"/>
+      <c r="R40" s="12"/>
+      <c r="S40" s="12"/>
+      <c r="T40" s="12"/>
+      <c r="U40" s="12"/>
+      <c r="V40" s="12"/>
+      <c r="W40" s="12"/>
+      <c r="X40" s="12"/>
+      <c r="Y40" s="12"/>
+      <c r="Z40" s="12"/>
+      <c r="AA40" s="12"/>
+      <c r="AB40" s="12"/>
+      <c r="AC40" s="12"/>
+      <c r="AD40" s="12"/>
+      <c r="AE40" s="12"/>
+      <c r="AF40" s="12"/>
+      <c r="AG40" s="12"/>
+      <c r="AH40" s="12"/>
+      <c r="AI40" s="12"/>
+      <c r="AJ40" s="12"/>
+      <c r="AK40" s="12"/>
+      <c r="AL40" s="12"/>
+      <c r="AM40" s="12"/>
+      <c r="AN40" s="12"/>
+      <c r="AO40" s="12"/>
+      <c r="AP40" s="12"/>
+      <c r="AQ40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -11934,7 +11912,7 @@
       <c r="AP41" s="4"/>
       <c r="AQ41" s="5"/>
       <c r="AS41" s="15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AT41" s="15"/>
       <c r="AU41" s="4"/>
@@ -12118,7 +12096,7 @@
       <c r="BE43" s="13"/>
       <c r="BF43" s="13"/>
       <c r="BG43" s="29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="BH43" s="29"/>
       <c r="BI43" s="29"/>
@@ -12156,11 +12134,9 @@
       <c r="CI43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -12211,11 +12187,9 @@
       <c r="AO44" s="9"/>
       <c r="AP44" s="9"/>
       <c r="AQ44" s="9"/>
-      <c r="AS44" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="AT44" s="32"/>
-      <c r="AU44" s="32"/>
+      <c r="AS44" s="7"/>
+      <c r="AT44" s="7"/>
+      <c r="AU44" s="7"/>
       <c r="AV44" s="6"/>
       <c r="AW44" s="6"/>
       <c r="AX44" s="6"/>
@@ -12334,16 +12308,16 @@
       </c>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
-      <c r="AZ45" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="BA45" s="33"/>
-      <c r="BB45" s="33"/>
-      <c r="BC45" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="BD45" s="33"/>
-      <c r="BE45" s="33"/>
+      <c r="AZ45" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="BA45" s="32"/>
+      <c r="BB45" s="32"/>
+      <c r="BC45" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="BD45" s="32"/>
+      <c r="BE45" s="32"/>
       <c r="BF45" s="13" t="s">
         <v>157</v>
       </c>
@@ -12359,16 +12333,16 @@
       </c>
       <c r="BM45" s="10"/>
       <c r="BN45" s="10"/>
-      <c r="BO45" s="34" t="s">
+      <c r="BO45" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="BP45" s="34"/>
-      <c r="BQ45" s="34"/>
-      <c r="BR45" s="34" t="s">
+      <c r="BP45" s="33"/>
+      <c r="BQ45" s="33"/>
+      <c r="BR45" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="BS45" s="34"/>
-      <c r="BT45" s="34"/>
+      <c r="BS45" s="33"/>
+      <c r="BT45" s="33"/>
       <c r="BU45" s="6"/>
       <c r="BV45" s="6"/>
       <c r="BW45" s="6"/>
@@ -12399,17 +12373,15 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c r="M46" s="7"/>
-      <c r="N46" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="O46" s="32"/>
-      <c r="P46" s="32"/>
-      <c r="Q46" s="32"/>
-      <c r="R46" s="32"/>
-      <c r="S46" s="32"/>
-      <c r="T46" s="32"/>
-      <c r="U46" s="32"/>
-      <c r="V46" s="32"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
+      <c r="V46" s="7"/>
       <c r="W46" s="29" t="s">
         <v>187</v>
       </c>
@@ -12448,24 +12420,22 @@
       <c r="BC46" s="7"/>
       <c r="BD46" s="7"/>
       <c r="BE46" s="7"/>
-      <c r="BF46" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="BG46" s="32"/>
-      <c r="BH46" s="32"/>
-      <c r="BI46" s="32"/>
-      <c r="BJ46" s="32"/>
-      <c r="BK46" s="32"/>
-      <c r="BL46" s="32"/>
-      <c r="BM46" s="32"/>
-      <c r="BN46" s="32"/>
+      <c r="BF46" s="7"/>
+      <c r="BG46" s="7"/>
+      <c r="BH46" s="7"/>
+      <c r="BI46" s="7"/>
+      <c r="BJ46" s="7"/>
+      <c r="BK46" s="7"/>
+      <c r="BL46" s="7"/>
+      <c r="BM46" s="7"/>
+      <c r="BN46" s="7"/>
       <c r="BO46" s="29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="BP46" s="29"/>
       <c r="BQ46" s="29"/>
       <c r="BR46" s="29" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="BS46" s="29"/>
       <c r="BT46" s="29"/>
@@ -12499,15 +12469,15 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c r="M47" s="7"/>
-      <c r="N47" s="32"/>
-      <c r="O47" s="32"/>
-      <c r="P47" s="32"/>
-      <c r="Q47" s="32"/>
-      <c r="R47" s="32"/>
-      <c r="S47" s="32"/>
-      <c r="T47" s="32"/>
-      <c r="U47" s="32"/>
-      <c r="V47" s="32"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
+      <c r="V47" s="7"/>
       <c r="W47" s="29"/>
       <c r="X47" s="29"/>
       <c r="Y47" s="29"/>
@@ -12542,15 +12512,15 @@
       <c r="BC47" s="7"/>
       <c r="BD47" s="7"/>
       <c r="BE47" s="7"/>
-      <c r="BF47" s="32"/>
-      <c r="BG47" s="32"/>
-      <c r="BH47" s="32"/>
-      <c r="BI47" s="32"/>
-      <c r="BJ47" s="32"/>
-      <c r="BK47" s="32"/>
-      <c r="BL47" s="32"/>
-      <c r="BM47" s="32"/>
-      <c r="BN47" s="32"/>
+      <c r="BF47" s="7"/>
+      <c r="BG47" s="7"/>
+      <c r="BH47" s="7"/>
+      <c r="BI47" s="7"/>
+      <c r="BJ47" s="7"/>
+      <c r="BK47" s="7"/>
+      <c r="BL47" s="7"/>
+      <c r="BM47" s="7"/>
+      <c r="BN47" s="7"/>
       <c r="BO47" s="29"/>
       <c r="BP47" s="29"/>
       <c r="BQ47" s="29"/>
@@ -12574,49 +12544,45 @@
       <c r="CI47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="26"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="27"/>
-      <c r="K48" s="27"/>
-      <c r="L48" s="27"/>
-      <c r="M48" s="27"/>
-      <c r="N48" s="27"/>
-      <c r="O48" s="27"/>
-      <c r="P48" s="27"/>
-      <c r="Q48" s="27"/>
-      <c r="R48" s="27"/>
-      <c r="S48" s="27"/>
-      <c r="T48" s="27"/>
-      <c r="U48" s="27"/>
-      <c r="V48" s="27"/>
-      <c r="W48" s="27"/>
-      <c r="X48" s="27"/>
-      <c r="Y48" s="27"/>
-      <c r="Z48" s="27"/>
-      <c r="AA48" s="27"/>
-      <c r="AB48" s="27"/>
-      <c r="AC48" s="27"/>
-      <c r="AD48" s="27"/>
-      <c r="AE48" s="27"/>
-      <c r="AF48" s="27"/>
-      <c r="AG48" s="27"/>
-      <c r="AH48" s="27"/>
-      <c r="AI48" s="27"/>
-      <c r="AJ48" s="27"/>
-      <c r="AK48" s="27"/>
-      <c r="AL48" s="27"/>
-      <c r="AM48" s="27"/>
-      <c r="AN48" s="27"/>
-      <c r="AO48" s="27"/>
-      <c r="AP48" s="27"/>
-      <c r="AQ48" s="28"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="2"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="2"/>
+      <c r="W48" s="2"/>
+      <c r="X48" s="2"/>
+      <c r="Y48" s="2"/>
+      <c r="Z48" s="2"/>
+      <c r="AA48" s="2"/>
+      <c r="AB48" s="2"/>
+      <c r="AC48" s="2"/>
+      <c r="AD48" s="2"/>
+      <c r="AE48" s="2"/>
+      <c r="AF48" s="2"/>
+      <c r="AG48" s="2"/>
+      <c r="AH48" s="2"/>
+      <c r="AI48" s="2"/>
+      <c r="AJ48" s="2"/>
+      <c r="AK48" s="2"/>
+      <c r="AL48" s="2"/>
+      <c r="AM48" s="2"/>
+      <c r="AN48" s="2"/>
+      <c r="AO48" s="2"/>
+      <c r="AP48" s="2"/>
+      <c r="AQ48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
@@ -14965,7 +14931,7 @@
       <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
@@ -15059,7 +15025,7 @@
       <c r="AK11" s="6"/>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AN11" s="6"/>
       <c r="AO11" s="6"/>
@@ -15728,7 +15694,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -15934,7 +15900,7 @@
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AN19" s="6"/>
       <c r="AO19" s="6"/>
@@ -15989,7 +15955,7 @@
       <c r="CC19" s="7"/>
       <c r="CD19" s="7"/>
       <c r="CE19" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
@@ -16770,7 +16736,7 @@
       <c r="AK27" s="13"/>
       <c r="AL27" s="13"/>
       <c r="AM27" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AN27" s="6"/>
       <c r="AO27" s="6"/>
@@ -16823,7 +16789,7 @@
       <c r="CC27" s="7"/>
       <c r="CD27" s="7"/>
       <c r="CE27" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="CF27" s="6"/>
       <c r="CG27" s="6"/>
@@ -17595,7 +17561,7 @@
       <c r="AK35" s="13"/>
       <c r="AL35" s="13"/>
       <c r="AM35" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AN35" s="6"/>
       <c r="AO35" s="6"/>
@@ -17652,7 +17618,7 @@
       <c r="CC35" s="7"/>
       <c r="CD35" s="7"/>
       <c r="CE35" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="CF35" s="6"/>
       <c r="CG35" s="6"/>
@@ -19206,7 +19172,7 @@
       <c r="AP1" s="4"/>
       <c r="AQ1" s="5"/>
       <c r="AT1" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -19489,7 +19455,7 @@
         <v>161</v>
       </c>
       <c r="AT4" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AU4" s="7"/>
       <c r="AV4" s="7"/>
@@ -19497,7 +19463,7 @@
       <c r="AX4" s="8"/>
       <c r="AY4" s="6"/>
       <c r="AZ4" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="BA4" s="8" t="s">
         <v>56</v>
@@ -19586,8 +19552,8 @@
       <c r="AO5" s="6"/>
       <c r="AP5" s="6"/>
       <c r="AQ5" s="6"/>
-      <c r="AR5" s="35" t="s">
-        <v>206</v>
+      <c r="AR5" s="34" t="s">
+        <v>204</v>
       </c>
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
@@ -19596,7 +19562,7 @@
       <c r="AX5" s="7"/>
       <c r="AY5" s="7"/>
       <c r="AZ5" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="BA5" s="7" t="s">
         <v>172</v>
@@ -19656,10 +19622,10 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
@@ -19702,7 +19668,7 @@
       <c r="AW6" s="7"/>
       <c r="AX6" s="7"/>
       <c r="AY6" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AZ6" s="7"/>
       <c r="BA6" s="7"/>
@@ -19711,7 +19677,7 @@
       <c r="BD6" s="6"/>
       <c r="BE6" s="11"/>
       <c r="BF6" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="BG6" s="11"/>
       <c r="BH6" s="11"/>
@@ -19776,7 +19742,7 @@
         <v>172</v>
       </c>
       <c r="BF7" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="BG7" s="6" t="s">
         <v>173</v>
@@ -19830,7 +19796,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -20393,8 +20359,8 @@
       <c r="AO13" s="6"/>
       <c r="AP13" s="6"/>
       <c r="AQ13" s="6"/>
-      <c r="AR13" s="35" t="s">
-        <v>206</v>
+      <c r="AR13" s="34" t="s">
+        <v>204</v>
       </c>
       <c r="AT13" s="7"/>
       <c r="AU13" s="7"/>
@@ -20507,10 +20473,10 @@
       </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z14" s="7"/>
       <c r="AA14" s="7"/>
@@ -20789,7 +20755,7 @@
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>109</v>
@@ -21260,8 +21226,8 @@
       <c r="AO21" s="6"/>
       <c r="AP21" s="6"/>
       <c r="AQ21" s="6"/>
-      <c r="AR21" s="35" t="s">
-        <v>206</v>
+      <c r="AR21" s="34" t="s">
+        <v>204</v>
       </c>
       <c r="AT21" s="7"/>
       <c r="AU21" s="7"/>
@@ -21370,10 +21336,10 @@
       </c>
       <c r="W22" s="7"/>
       <c r="X22" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z22" s="7"/>
       <c r="AA22" s="7"/>
@@ -22086,8 +22052,8 @@
       <c r="AO29" s="6"/>
       <c r="AP29" s="6"/>
       <c r="AQ29" s="6"/>
-      <c r="AR29" s="35" t="s">
-        <v>206</v>
+      <c r="AR29" s="34" t="s">
+        <v>204</v>
       </c>
       <c r="AT29" s="7"/>
       <c r="AU29" s="7"/>
@@ -22184,10 +22150,10 @@
       </c>
       <c r="W30" s="7"/>
       <c r="X30" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y30" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z30" s="7"/>
       <c r="AA30" s="7"/>
@@ -22254,7 +22220,7 @@
       </c>
       <c r="BP30" s="7"/>
       <c r="BQ30" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="BR30" s="7"/>
       <c r="BS30" s="7"/>
@@ -22759,7 +22725,7 @@
       <c r="AR36" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="AT36" s="36" t="s">
+      <c r="AT36" s="35" t="s">
         <v>34</v>
       </c>
       <c r="AU36" s="13" t="s">
@@ -22865,8 +22831,8 @@
       <c r="AO37" s="6"/>
       <c r="AP37" s="6"/>
       <c r="AQ37" s="6"/>
-      <c r="AR37" s="35" t="s">
-        <v>206</v>
+      <c r="AR37" s="34" t="s">
+        <v>204</v>
       </c>
       <c r="AT37" s="7" t="s">
         <v>35</v>
@@ -22949,10 +22915,10 @@
       </c>
       <c r="W38" s="7"/>
       <c r="X38" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Y38" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="Z38" s="7"/>
       <c r="AA38" s="7"/>
@@ -22987,17 +22953,17 @@
       <c r="AW38" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="AX38" s="36" t="s">
+      <c r="AX38" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AY38" s="36" t="s">
+      <c r="AY38" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="AZ38" s="36"/>
-      <c r="BA38" s="36" t="s">
+      <c r="AZ38" s="35"/>
+      <c r="BA38" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="BB38" s="36" t="s">
+      <c r="BB38" s="35" t="s">
         <v>107</v>
       </c>
       <c r="BC38" s="11"/>
@@ -23060,9 +23026,9 @@
       <c r="AW39" s="7"/>
       <c r="AX39" s="7"/>
       <c r="AY39" s="7"/>
-      <c r="AZ39" s="36"/>
-      <c r="BA39" s="36"/>
-      <c r="BB39" s="36"/>
+      <c r="AZ39" s="35"/>
+      <c r="BA39" s="35"/>
+      <c r="BB39" s="35"/>
       <c r="BC39" s="11"/>
       <c r="BD39" s="6"/>
       <c r="BE39" s="6"/>
@@ -24307,8 +24273,8 @@
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
-      <c r="P5" s="35" t="s">
-        <v>206</v>
+      <c r="P5" s="34" t="s">
+        <v>204</v>
       </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -24439,7 +24405,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -24594,7 +24560,7 @@
       <c r="Z11" s="13"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="13"/>
-      <c r="AC11" s="37"/>
+      <c r="AC11" s="36"/>
       <c r="AD11" s="21"/>
       <c r="AE11" s="6"/>
       <c r="AF11" s="6"/>
@@ -24702,8 +24668,8 @@
       </c>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
-      <c r="P13" s="35" t="s">
-        <v>206</v>
+      <c r="P13" s="34" t="s">
+        <v>204</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="13"/>
@@ -24911,8 +24877,8 @@
       <c r="M19" s="13"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
-      <c r="P19" s="38" t="s">
-        <v>212</v>
+      <c r="P19" s="37" t="s">
+        <v>210</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -24931,7 +24897,7 @@
       <c r="AF19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -25014,11 +24980,11 @@
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
       <c r="U22" s="7"/>
-      <c r="V22" s="36"/>
+      <c r="V22" s="35"/>
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
-      <c r="Y22" s="39"/>
-      <c r="Z22" s="39"/>
+      <c r="Y22" s="38"/>
+      <c r="Z22" s="38"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="11"/>
@@ -25046,11 +25012,11 @@
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
-      <c r="V23" s="36"/>
-      <c r="W23" s="36"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
       <c r="X23" s="7"/>
-      <c r="Y23" s="39"/>
-      <c r="Z23" s="39"/>
+      <c r="Y23" s="38"/>
+      <c r="Z23" s="38"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
@@ -25187,7 +25153,7 @@
       <c r="M28" s="13"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
-      <c r="R28" s="36"/>
+      <c r="R28" s="35"/>
       <c r="S28" s="7"/>
       <c r="T28" s="7"/>
       <c r="U28" s="7"/>
@@ -25241,8 +25207,8 @@
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="11"/>
@@ -25255,9 +25221,9 @@
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
-      <c r="X30" s="36"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="35"/>
       <c r="Y30" s="6"/>
       <c r="Z30" s="7"/>
       <c r="AA30" s="11"/>
@@ -25274,7 +25240,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="36"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="11"/>
@@ -25289,7 +25255,7 @@
       <c r="U31" s="7"/>
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
-      <c r="X31" s="36"/>
+      <c r="X31" s="35"/>
       <c r="Y31" s="6"/>
       <c r="Z31" s="7"/>
       <c r="AA31" s="11"/>
@@ -25352,7 +25318,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="33"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -25428,7 +25394,7 @@
       <c r="M36" s="13"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="R36" s="36"/>
+      <c r="R36" s="35"/>
       <c r="S36" s="13"/>
       <c r="T36" s="13"/>
       <c r="U36" s="13"/>
@@ -25467,7 +25433,7 @@
       <c r="V37" s="13"/>
       <c r="W37" s="13"/>
       <c r="X37" s="18"/>
-      <c r="Y37" s="40"/>
+      <c r="Y37" s="39"/>
       <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
       <c r="AB37" s="6"/>
@@ -25482,8 +25448,8 @@
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="11"/>
@@ -25496,11 +25462,11 @@
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
-      <c r="V38" s="36"/>
-      <c r="W38" s="36"/>
-      <c r="X38" s="36"/>
-      <c r="Y38" s="36"/>
-      <c r="Z38" s="36"/>
+      <c r="V38" s="35"/>
+      <c r="W38" s="35"/>
+      <c r="X38" s="35"/>
+      <c r="Y38" s="35"/>
+      <c r="Z38" s="35"/>
       <c r="AA38" s="11"/>
       <c r="AB38" s="6"/>
       <c r="AC38" s="11"/>
@@ -25515,7 +25481,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="36"/>
+      <c r="G39" s="35"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="11"/>
@@ -25530,9 +25496,9 @@
       <c r="U39" s="7"/>
       <c r="V39" s="7"/>
       <c r="W39" s="7"/>
-      <c r="X39" s="36"/>
-      <c r="Y39" s="36"/>
-      <c r="Z39" s="36"/>
+      <c r="X39" s="35"/>
+      <c r="Y39" s="35"/>
+      <c r="Z39" s="35"/>
       <c r="AA39" s="11"/>
       <c r="AB39" s="6"/>
       <c r="AC39" s="6"/>
@@ -25653,7 +25619,7 @@
       <c r="AF43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="36"/>
+      <c r="A44" s="35"/>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
@@ -25668,7 +25634,7 @@
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
-      <c r="R44" s="36"/>
+      <c r="R44" s="35"/>
       <c r="S44" s="13"/>
       <c r="T44" s="13"/>
       <c r="U44" s="13"/>
@@ -25722,8 +25688,8 @@
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
       <c r="J46" s="11"/>
@@ -25736,11 +25702,11 @@
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
-      <c r="V46" s="36"/>
-      <c r="W46" s="36"/>
-      <c r="X46" s="36"/>
-      <c r="Y46" s="36"/>
-      <c r="Z46" s="36"/>
+      <c r="V46" s="35"/>
+      <c r="W46" s="35"/>
+      <c r="X46" s="35"/>
+      <c r="Y46" s="35"/>
+      <c r="Z46" s="35"/>
       <c r="AA46" s="11"/>
       <c r="AB46" s="6"/>
       <c r="AC46" s="11"/>
@@ -25755,7 +25721,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
-      <c r="G47" s="36"/>
+      <c r="G47" s="35"/>
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
       <c r="J47" s="11"/>
@@ -25770,9 +25736,9 @@
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
       <c r="W47" s="7"/>
-      <c r="X47" s="36"/>
-      <c r="Y47" s="36"/>
-      <c r="Z47" s="36"/>
+      <c r="X47" s="35"/>
+      <c r="Y47" s="35"/>
+      <c r="Z47" s="35"/>
       <c r="AA47" s="11"/>
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
@@ -25900,7 +25866,7 @@
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
-      <c r="V52" s="41"/>
+      <c r="V52" s="40"/>
       <c r="W52" s="6"/>
       <c r="X52" s="13"/>
       <c r="Y52" s="14"/>
@@ -25949,11 +25915,11 @@
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
-      <c r="E54" s="36"/>
+      <c r="E54" s="35"/>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
       <c r="J54" s="11"/>
       <c r="K54" s="6"/>
       <c r="L54" s="11"/>
@@ -25981,11 +25947,11 @@
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
       <c r="J55" s="11"/>
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>

--- a/img/keymap.xlsx
+++ b/img/keymap.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="roman_table" sheetId="1" state="visible" r:id="rId3"/>
@@ -4746,11 +4746,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="32898233"/>
-        <c:axId val="25760029"/>
+        <c:axId val="81620111"/>
+        <c:axId val="26171528"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="32898233"/>
+        <c:axId val="81620111"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4817,13 +4817,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25760029"/>
+        <c:crossAx val="26171528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="25760029"/>
+        <c:axId val="26171528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="30"/>
@@ -4900,7 +4900,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32898233"/>
+        <c:crossAx val="81620111"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4938,9 +4938,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>57240</xdr:colOff>
+      <xdr:colOff>56880</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>50760</xdr:rowOff>
+      <xdr:rowOff>50400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -4949,7 +4949,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="1662120" y="478080"/>
-        <a:ext cx="7336080" cy="4124520"/>
+        <a:ext cx="7335720" cy="4124160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -21630,7 +21630,7 @@
       <c r="CW44" s="47"/>
       <c r="CX44" s="47"/>
       <c r="CY44" s="47" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="CZ44" s="47"/>
       <c r="DA44" s="47"/>
@@ -21782,23 +21782,21 @@
       <c r="CL45" s="40"/>
       <c r="CM45" s="40"/>
       <c r="CN45" s="47" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="CO45" s="47"/>
       <c r="CP45" s="47"/>
       <c r="CQ45" s="47" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="CR45" s="47"/>
       <c r="CS45" s="47"/>
       <c r="CT45" s="47" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="CU45" s="47"/>
       <c r="CV45" s="47"/>
-      <c r="CW45" s="77" t="s">
-        <v>463</v>
-      </c>
+      <c r="CW45" s="77"/>
       <c r="CX45" s="77"/>
       <c r="CY45" s="77"/>
       <c r="CZ45" s="47" t="s">
@@ -21951,9 +21949,11 @@
       <c r="CL46" s="42"/>
       <c r="CM46" s="42"/>
       <c r="CN46" s="42"/>
-      <c r="CO46" s="34"/>
-      <c r="CP46" s="34"/>
-      <c r="CQ46" s="34"/>
+      <c r="CO46" s="47" t="s">
+        <v>501</v>
+      </c>
+      <c r="CP46" s="47"/>
+      <c r="CQ46" s="47"/>
       <c r="CR46" s="47" t="s">
         <v>467</v>
       </c>
@@ -48609,15 +48609,15 @@
       <c r="K15" s="62"/>
       <c r="L15" s="62"/>
       <c r="M15" s="62"/>
-      <c r="N15" s="0"/>
-      <c r="O15" s="0"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
-      <c r="R15" s="0"/>
-      <c r="S15" s="0"/>
-      <c r="T15" s="0"/>
-      <c r="U15" s="0"/>
-      <c r="V15" s="0"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
       <c r="W15" s="62"/>
       <c r="X15" s="62"/>
       <c r="Y15" s="62"/>
@@ -48794,15 +48794,15 @@
       <c r="K16" s="62"/>
       <c r="L16" s="62"/>
       <c r="M16" s="62"/>
-      <c r="N16" s="0"/>
-      <c r="O16" s="0"/>
-      <c r="P16" s="0"/>
-      <c r="Q16" s="0"/>
-      <c r="R16" s="0"/>
-      <c r="S16" s="0"/>
-      <c r="T16" s="0"/>
-      <c r="U16" s="0"/>
-      <c r="V16" s="0"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
       <c r="W16" s="62"/>
       <c r="X16" s="62"/>
       <c r="Y16" s="62"/>
